--- a/sup_tables/sup_table_s12_topography_asymmetry.xlsx
+++ b/sup_tables/sup_table_s12_topography_asymmetry.xlsx
@@ -601,22 +601,22 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000922466072349052</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000922466072349051</v>
       </c>
       <c r="D4" t="n">
-        <v>1.31127719745575</v>
+        <v>1.31127719745573</v>
       </c>
       <c r="E4" t="n">
         <v>0.000000000000000000000000000138008965009794</v>
       </c>
       <c r="F4" t="n">
-        <v>0.873721804285366</v>
+        <v>0.873721804285369</v>
       </c>
       <c r="G4" t="n">
         <v>0.000132015844174322</v>
       </c>
       <c r="H4" t="n">
-        <v>1.07994593426838</v>
+        <v>1.07994593426832</v>
       </c>
     </row>
     <row r="5">
@@ -630,19 +630,19 @@
         <v>0.00000000000000166513097073457</v>
       </c>
       <c r="D5" t="n">
-        <v>0.971735768658933</v>
+        <v>0.971735768659077</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00101081966009504</v>
+        <v>0.00101081966009503</v>
       </c>
       <c r="F5" t="n">
-        <v>0.987832754228619</v>
+        <v>0.987832754228664</v>
       </c>
       <c r="G5" t="n">
         <v>0.000329060679789377</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02006884038355</v>
+        <v>1.02006884038344</v>
       </c>
     </row>
     <row r="6">
@@ -656,19 +656,19 @@
         <v>0.00000347052890854179</v>
       </c>
       <c r="D6" t="n">
-        <v>1.45172154725435</v>
+        <v>1.45172154725433</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0916473322938539</v>
+        <v>0.0916473322938538</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1475367462355</v>
+        <v>1.14753674623552</v>
       </c>
       <c r="G6" t="n">
         <v>0.23920752627365</v>
       </c>
       <c r="H6" t="n">
-        <v>0.854086016443205</v>
+        <v>0.854086016443207</v>
       </c>
     </row>
     <row r="7">
@@ -682,19 +682,19 @@
         <v>0.0394913403524524</v>
       </c>
       <c r="D7" t="n">
-        <v>0.721210331711273</v>
+        <v>0.721210331711267</v>
       </c>
       <c r="E7" t="n">
         <v>0.525550365802658</v>
       </c>
       <c r="F7" t="n">
-        <v>1.20841370647869</v>
+        <v>1.20841370647868</v>
       </c>
       <c r="G7" t="n">
         <v>0.733163642721201</v>
       </c>
       <c r="H7" t="n">
-        <v>0.847536370789772</v>
+        <v>0.84753637078977</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0252791360782325</v>
+        <v>0.0252791360782324</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0795153485001</v>
+        <v>1.07951534850008</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0790090436213057</v>
+        <v>0.0790090436213058</v>
       </c>
       <c r="F8" t="n">
-        <v>1.07351762515986</v>
+        <v>1.07351762515983</v>
       </c>
       <c r="G8" t="n">
-        <v>0.360215094454386</v>
+        <v>0.360215094454385</v>
       </c>
       <c r="H8" t="n">
-        <v>0.943150366038236</v>
+        <v>0.943150366038241</v>
       </c>
     </row>
     <row r="9">
@@ -734,19 +734,19 @@
         <v>0.0000000989754530177503</v>
       </c>
       <c r="D9" t="n">
-        <v>1.18431735479591</v>
+        <v>1.18431735479592</v>
       </c>
       <c r="E9" t="n">
-        <v>0.948058870803094</v>
+        <v>0.948058870803095</v>
       </c>
       <c r="F9" t="n">
-        <v>0.99507557514412</v>
+        <v>0.995075575144134</v>
       </c>
       <c r="G9" t="n">
         <v>0.642664620813861</v>
       </c>
       <c r="H9" t="n">
-        <v>0.949340270294985</v>
+        <v>0.949340270294935</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         <v>0.0034838999397818</v>
       </c>
       <c r="D11" t="n">
-        <v>0.815936640974173</v>
+        <v>0.815936640974168</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.681433281872086</v>
+        <v>0.681433281872088</v>
       </c>
       <c r="G11" t="n">
         <v>0.199736158634622</v>
@@ -818,13 +818,13 @@
         <v>0.288078712757212</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9504384737106</v>
+        <v>0.950438473710556</v>
       </c>
       <c r="G12" t="n">
         <v>0.00577769181144538</v>
       </c>
       <c r="H12" t="n">
-        <v>0.808354520163613</v>
+        <v>0.808354520163597</v>
       </c>
     </row>
     <row r="13">
@@ -838,13 +838,13 @@
         <v>0.810763942508219</v>
       </c>
       <c r="D13" t="n">
-        <v>0.933119187290255</v>
+        <v>0.93311918729025</v>
       </c>
       <c r="E13" t="n">
         <v>0.124359395366137</v>
       </c>
       <c r="F13" t="n">
-        <v>0.52348148515006</v>
+        <v>0.523481485150063</v>
       </c>
       <c r="G13" t="n">
         <v>0.624886956094615</v>
@@ -942,19 +942,19 @@
         <v>0.0094765961373514</v>
       </c>
       <c r="D17" t="n">
-        <v>1.62108899459023</v>
+        <v>1.62108899459024</v>
       </c>
       <c r="E17" t="n">
         <v>0.130907670567661</v>
       </c>
       <c r="F17" t="n">
-        <v>0.754498732897385</v>
+        <v>0.754498732897378</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0955755809176804</v>
+        <v>0.0955755809176805</v>
       </c>
       <c r="H17" t="n">
-        <v>0.580231022857204</v>
+        <v>0.580231022857214</v>
       </c>
     </row>
     <row r="18">
@@ -1069,22 +1069,22 @@
         <v>27</v>
       </c>
       <c r="C22" t="n">
-        <v>0.55038481755687</v>
+        <v>0.550384817556869</v>
       </c>
       <c r="D22" t="n">
-        <v>1.01557340672503</v>
+        <v>1.01557340672501</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0232135249301914</v>
+        <v>0.0232135249301915</v>
       </c>
       <c r="F22" t="n">
-        <v>0.890816304196356</v>
+        <v>0.890816304196425</v>
       </c>
       <c r="G22" t="n">
-        <v>0.075656961800209</v>
+        <v>0.0756569618002091</v>
       </c>
       <c r="H22" t="n">
-        <v>1.14812462430034</v>
+        <v>1.14812462430027</v>
       </c>
     </row>
     <row r="23">
@@ -1098,19 +1098,19 @@
         <v>0.0209930588686571</v>
       </c>
       <c r="D23" t="n">
-        <v>1.45774564881274</v>
+        <v>1.45774564881272</v>
       </c>
       <c r="E23" t="n">
         <v>0.0231361420454805</v>
       </c>
       <c r="F23" t="n">
-        <v>0.661267195792122</v>
+        <v>0.661267195792136</v>
       </c>
       <c r="G23" t="n">
-        <v>0.255511738048643</v>
+        <v>0.255511738048644</v>
       </c>
       <c r="H23" t="n">
-        <v>0.694785484579762</v>
+        <v>0.694785484579764</v>
       </c>
     </row>
     <row r="24">
@@ -1124,7 +1124,7 @@
         <v>0.00000305474337826975</v>
       </c>
       <c r="D24" t="n">
-        <v>1.42336839443998</v>
+        <v>1.42336839444</v>
       </c>
       <c r="E24" t="n">
         <v>0.180638270596539</v>
@@ -1136,7 +1136,7 @@
         <v>0.428815396832267</v>
       </c>
       <c r="H24" t="n">
-        <v>0.886647223423073</v>
+        <v>0.886647223423052</v>
       </c>
     </row>
     <row r="25">
@@ -1150,19 +1150,19 @@
         <v>0.487893917043328</v>
       </c>
       <c r="D25" t="n">
-        <v>0.963922279725554</v>
+        <v>0.963922279725594</v>
       </c>
       <c r="E25" t="n">
-        <v>0.716736484840144</v>
+        <v>0.716736484840145</v>
       </c>
       <c r="F25" t="n">
-        <v>0.976654236050315</v>
+        <v>0.976654236050328</v>
       </c>
       <c r="G25" t="n">
         <v>0.0129509301156447</v>
       </c>
       <c r="H25" t="n">
-        <v>0.798063996252816</v>
+        <v>0.798063996252826</v>
       </c>
     </row>
     <row r="26">
@@ -1176,7 +1176,7 @@
         <v>0.3151875729647</v>
       </c>
       <c r="D26" t="n">
-        <v>0.447818321035604</v>
+        <v>0.447818321035605</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1211,10 +1211,10 @@
         <v>0.310744766708336</v>
       </c>
       <c r="G27" t="n">
-        <v>0.635919122505616</v>
+        <v>0.635919122505617</v>
       </c>
       <c r="H27" t="n">
-        <v>0.462873658098542</v>
+        <v>0.462873658098538</v>
       </c>
     </row>
     <row r="28">
@@ -1231,7 +1231,7 @@
         <v>0.767064753622957</v>
       </c>
       <c r="E28" t="n">
-        <v>0.730734120237301</v>
+        <v>0.7307341202373</v>
       </c>
       <c r="F28" t="n">
         <v>1.07043539385569</v>
@@ -1240,7 +1240,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1.02483566334963</v>
+        <v>1.02483566334964</v>
       </c>
     </row>
     <row r="29">
@@ -1280,7 +1280,7 @@
         <v>0.257531111587634</v>
       </c>
       <c r="D30" t="n">
-        <v>0.350505697561629</v>
+        <v>0.350505697561624</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1433,10 +1433,10 @@
         <v>41</v>
       </c>
       <c r="C36" t="n">
-        <v>0.232846516281322</v>
+        <v>0.232846516281321</v>
       </c>
       <c r="D36" t="n">
-        <v>2.25941623235718</v>
+        <v>2.25941623235719</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1459,7 +1459,7 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000824047419460746</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000824047419460744</v>
       </c>
       <c r="D37" t="n">
         <v>1.30459329652964</v>
@@ -1468,13 +1468,13 @@
         <v>0.00000000000000355109469730148</v>
       </c>
       <c r="F37" t="n">
-        <v>0.910695403795111</v>
+        <v>0.910695403795177</v>
       </c>
       <c r="G37" t="n">
-        <v>0.365917701214454</v>
+        <v>0.365917701214455</v>
       </c>
       <c r="H37" t="n">
-        <v>1.01764298783791</v>
+        <v>1.01764298783783</v>
       </c>
     </row>
     <row r="38">
@@ -1488,19 +1488,19 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000464542204884983</v>
       </c>
       <c r="D38" t="n">
-        <v>1.31260040271249</v>
+        <v>1.31260040271252</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00000000000000000000000000000000278754654605781</v>
+        <v>0.0000000000000000000000000000000027875465460578</v>
       </c>
       <c r="F38" t="n">
-        <v>0.883108016720044</v>
+        <v>0.883108016720042</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0000419540183105871</v>
+        <v>0.0000419540183105872</v>
       </c>
       <c r="H38" t="n">
-        <v>1.07280531401702</v>
+        <v>1.07280531401701</v>
       </c>
     </row>
     <row r="39">
@@ -1511,22 +1511,22 @@
         <v>10</v>
       </c>
       <c r="C39" t="n">
-        <v>0.501290447529937</v>
+        <v>0.501290447529939</v>
       </c>
       <c r="D39" t="n">
-        <v>1.0027115942216</v>
+        <v>1.00271159422168</v>
       </c>
       <c r="E39" t="n">
-        <v>0.859609836027089</v>
+        <v>0.859609836027087</v>
       </c>
       <c r="F39" t="n">
-        <v>0.999256023004777</v>
+        <v>0.999256023004878</v>
       </c>
       <c r="G39" t="n">
-        <v>0.000914388199051064</v>
+        <v>0.000914388199051066</v>
       </c>
       <c r="H39" t="n">
-        <v>1.02088426379509</v>
+        <v>1.0208842637952</v>
       </c>
     </row>
     <row r="40">
@@ -1540,19 +1540,19 @@
         <v>0.00000000000000000000000000000000000000000000164266198412956</v>
       </c>
       <c r="D40" t="n">
-        <v>1.25930840229798</v>
+        <v>1.25930840229792</v>
       </c>
       <c r="E40" t="n">
-        <v>0.689575773309217</v>
+        <v>0.689575773309216</v>
       </c>
       <c r="F40" t="n">
-        <v>1.00693563930536</v>
+        <v>1.00693563930543</v>
       </c>
       <c r="G40" t="n">
         <v>0.233442501520793</v>
       </c>
       <c r="H40" t="n">
-        <v>1.03269670684857</v>
+        <v>1.03269670684856</v>
       </c>
     </row>
     <row r="41">
@@ -1566,19 +1566,19 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.997372173862044</v>
+        <v>0.997372173862052</v>
       </c>
       <c r="E41" t="n">
         <v>0.400481358998401</v>
       </c>
       <c r="F41" t="n">
-        <v>1.15619420896224</v>
+        <v>1.15619420896221</v>
       </c>
       <c r="G41" t="n">
         <v>0.309030543613816</v>
       </c>
       <c r="H41" t="n">
-        <v>1.32997876286781</v>
+        <v>1.32997876286782</v>
       </c>
     </row>
     <row r="42">
@@ -1592,7 +1592,7 @@
         <v>0.228817836706709</v>
       </c>
       <c r="D42" t="n">
-        <v>0.966399613701941</v>
+        <v>0.966399613701954</v>
       </c>
       <c r="E42" t="n">
         <v>0.616191654168953</v>
@@ -1604,7 +1604,7 @@
         <v>0.795483720077744</v>
       </c>
       <c r="H42" t="n">
-        <v>0.985984315431693</v>
+        <v>0.985984315431727</v>
       </c>
     </row>
     <row r="43">
@@ -1618,19 +1618,19 @@
         <v>0.00000000525280449271361</v>
       </c>
       <c r="D43" t="n">
-        <v>1.14852630104682</v>
+        <v>1.14852630104686</v>
       </c>
       <c r="E43" t="n">
         <v>0.232278491344155</v>
       </c>
       <c r="F43" t="n">
-        <v>0.940781969776594</v>
+        <v>0.940781969776627</v>
       </c>
       <c r="G43" t="n">
         <v>0.0157073541142414</v>
       </c>
       <c r="H43" t="n">
-        <v>0.820825790187024</v>
+        <v>0.820825790187029</v>
       </c>
     </row>
     <row r="44">
@@ -1670,19 +1670,19 @@
         <v>0.0000000000000000000000286359771381414</v>
       </c>
       <c r="D45" t="n">
-        <v>0.854549227566376</v>
+        <v>0.854549227566388</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0354065455432337</v>
+        <v>0.0354065455432338</v>
       </c>
       <c r="F45" t="n">
-        <v>0.899543812143903</v>
+        <v>0.899543812143905</v>
       </c>
       <c r="G45" t="n">
-        <v>0.574173938211805</v>
+        <v>0.574173938211806</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04446576244367</v>
+        <v>1.0444657624437</v>
       </c>
     </row>
     <row r="46">
@@ -1696,19 +1696,19 @@
         <v>0.000000012544326493074</v>
       </c>
       <c r="D46" t="n">
-        <v>1.1807503073616</v>
+        <v>1.18075030736158</v>
       </c>
       <c r="E46" t="n">
-        <v>0.921400287068706</v>
+        <v>0.921400287068705</v>
       </c>
       <c r="F46" t="n">
-        <v>1.00370581918729</v>
+        <v>1.0037058191873</v>
       </c>
       <c r="G46" t="n">
-        <v>0.750838321416522</v>
+        <v>0.750838321416521</v>
       </c>
       <c r="H46" t="n">
-        <v>1.01732114430603</v>
+        <v>1.01732114430602</v>
       </c>
     </row>
     <row r="47">
@@ -1722,19 +1722,19 @@
         <v>0.0672512466732003</v>
       </c>
       <c r="D47" t="n">
-        <v>0.886603440421742</v>
+        <v>0.886603440421752</v>
       </c>
       <c r="E47" t="n">
         <v>0.442848651436688</v>
       </c>
       <c r="F47" t="n">
-        <v>1.07996244268789</v>
+        <v>1.07996244268792</v>
       </c>
       <c r="G47" t="n">
         <v>0.673441286098744</v>
       </c>
       <c r="H47" t="n">
-        <v>0.934926814104912</v>
+        <v>0.934926814104908</v>
       </c>
     </row>
     <row r="48">
@@ -1832,13 +1832,13 @@
         <v>0.413121811107397</v>
       </c>
       <c r="F51" t="n">
-        <v>0.902530024850501</v>
+        <v>0.902530024850511</v>
       </c>
       <c r="G51" t="n">
-        <v>0.000789653958491942</v>
+        <v>0.000789653958491943</v>
       </c>
       <c r="H51" t="n">
-        <v>0.498963625020566</v>
+        <v>0.498963625020571</v>
       </c>
     </row>
     <row r="52">
@@ -1852,19 +1852,19 @@
         <v>0.00000126551777629386</v>
       </c>
       <c r="D52" t="n">
-        <v>1.52962608858461</v>
+        <v>1.52962608858459</v>
       </c>
       <c r="E52" t="n">
         <v>0.04957818509011</v>
       </c>
       <c r="F52" t="n">
-        <v>1.18602872382441</v>
+        <v>1.18602872382443</v>
       </c>
       <c r="G52" t="n">
         <v>0.234867986151327</v>
       </c>
       <c r="H52" t="n">
-        <v>0.843196069591858</v>
+        <v>0.843196069591849</v>
       </c>
     </row>
     <row r="53">
@@ -1901,22 +1901,22 @@
         <v>25</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00000000417240220483604</v>
+        <v>0.00000000417240220483601</v>
       </c>
       <c r="D54" t="n">
-        <v>0.400397295125703</v>
+        <v>0.400397295125701</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0980693048267291</v>
+        <v>0.0980693048267292</v>
       </c>
       <c r="F54" t="n">
-        <v>0.68332890418959</v>
+        <v>0.683328904189586</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.994624060768414</v>
+        <v>0.994624060768412</v>
       </c>
     </row>
     <row r="55">
@@ -1930,19 +1930,19 @@
         <v>0.0000000000000000118001268644128</v>
       </c>
       <c r="D55" t="n">
-        <v>1.43894773337289</v>
+        <v>1.43894773337291</v>
       </c>
       <c r="E55" t="n">
-        <v>0.459236848959226</v>
+        <v>0.459236848959225</v>
       </c>
       <c r="F55" t="n">
-        <v>1.03358513222201</v>
+        <v>1.03358513222198</v>
       </c>
       <c r="G55" t="n">
         <v>0.000144533664152076</v>
       </c>
       <c r="H55" t="n">
-        <v>0.757987868882087</v>
+        <v>0.757987868882085</v>
       </c>
     </row>
     <row r="56">
@@ -1956,19 +1956,19 @@
         <v>0.301759751380474</v>
       </c>
       <c r="D56" t="n">
-        <v>1.02135566361434</v>
+        <v>1.02135566361432</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0373733526690316</v>
+        <v>0.0373733526690317</v>
       </c>
       <c r="F56" t="n">
-        <v>0.909519623586254</v>
+        <v>0.909519623586308</v>
       </c>
       <c r="G56" t="n">
-        <v>0.776566398656312</v>
+        <v>0.776566398656311</v>
       </c>
       <c r="H56" t="n">
-        <v>1.02188459453</v>
+        <v>1.02188459452994</v>
       </c>
     </row>
     <row r="57">
@@ -2014,13 +2014,13 @@
         <v>0.000135179661941141</v>
       </c>
       <c r="F58" t="n">
-        <v>0.849342034831501</v>
+        <v>0.849342034831479</v>
       </c>
       <c r="G58" t="n">
         <v>0.0292423766225588</v>
       </c>
       <c r="H58" t="n">
-        <v>1.15346982243329</v>
+        <v>1.15346982243332</v>
       </c>
     </row>
     <row r="59">
@@ -2031,22 +2031,22 @@
         <v>30</v>
       </c>
       <c r="C59" t="n">
-        <v>0.00000000000509357306908521</v>
+        <v>0.00000000000509357306908519</v>
       </c>
       <c r="D59" t="n">
-        <v>1.1365497421981</v>
+        <v>1.13654974219811</v>
       </c>
       <c r="E59" t="n">
         <v>0.858460807668461</v>
       </c>
       <c r="F59" t="n">
-        <v>1.0037759257928</v>
+        <v>1.00377592579284</v>
       </c>
       <c r="G59" t="n">
         <v>0.610252416213304</v>
       </c>
       <c r="H59" t="n">
-        <v>0.983037942395891</v>
+        <v>0.983037942395859</v>
       </c>
     </row>
     <row r="60">
@@ -2112,19 +2112,19 @@
         <v>0.00121246817068181</v>
       </c>
       <c r="D62" t="n">
-        <v>0.685698026746237</v>
+        <v>0.685698026746248</v>
       </c>
       <c r="E62" t="n">
-        <v>0.429611233558148</v>
+        <v>0.429611233558147</v>
       </c>
       <c r="F62" t="n">
-        <v>0.893300803065232</v>
+        <v>0.893300803065226</v>
       </c>
       <c r="G62" t="n">
         <v>0.588251412053043</v>
       </c>
       <c r="H62" t="n">
-        <v>0.898462421388017</v>
+        <v>0.89846242138803</v>
       </c>
     </row>
     <row r="63">
@@ -2138,19 +2138,19 @@
         <v>0.176439445091587</v>
       </c>
       <c r="D63" t="n">
-        <v>1.09217193852101</v>
+        <v>1.09217193852098</v>
       </c>
       <c r="E63" t="n">
         <v>0.0624813337571467</v>
       </c>
       <c r="F63" t="n">
-        <v>1.21225819847003</v>
+        <v>1.21225819847004</v>
       </c>
       <c r="G63" t="n">
         <v>0.369730364274729</v>
       </c>
       <c r="H63" t="n">
-        <v>1.15026421229677</v>
+        <v>1.15026421229675</v>
       </c>
     </row>
     <row r="64">
@@ -2164,19 +2164,19 @@
         <v>0.176032717794469</v>
       </c>
       <c r="D64" t="n">
-        <v>1.09709150684211</v>
+        <v>1.09709150684213</v>
       </c>
       <c r="E64" t="n">
-        <v>0.461200644015402</v>
+        <v>0.461200644015401</v>
       </c>
       <c r="F64" t="n">
-        <v>0.94528786088798</v>
+        <v>0.945287860887925</v>
       </c>
       <c r="G64" t="n">
         <v>0.00209918965352188</v>
       </c>
       <c r="H64" t="n">
-        <v>1.42883069814788</v>
+        <v>1.42883069814787</v>
       </c>
     </row>
     <row r="65">
@@ -2219,16 +2219,16 @@
         <v>1.43740109439844</v>
       </c>
       <c r="E66" t="n">
-        <v>0.649175454588751</v>
+        <v>0.64917545458875</v>
       </c>
       <c r="F66" t="n">
-        <v>0.914475412725384</v>
+        <v>0.914475412725387</v>
       </c>
       <c r="G66" t="n">
         <v>0.655568517949128</v>
       </c>
       <c r="H66" t="n">
-        <v>1.14838298399791</v>
+        <v>1.14838298399794</v>
       </c>
     </row>
     <row r="67">
@@ -2346,19 +2346,19 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000378403780328909</v>
       </c>
       <c r="D71" t="n">
-        <v>1.47357418400078</v>
+        <v>1.47357418400083</v>
       </c>
       <c r="E71" t="n">
         <v>0.000000073366084498996</v>
       </c>
       <c r="F71" t="n">
-        <v>0.928319313595486</v>
+        <v>0.928319313595371</v>
       </c>
       <c r="G71" t="n">
-        <v>0.798282733132763</v>
+        <v>0.798282733132764</v>
       </c>
       <c r="H71" t="n">
-        <v>0.993870550449067</v>
+        <v>0.993870550448985</v>
       </c>
     </row>
     <row r="72">
@@ -2369,22 +2369,22 @@
         <v>9</v>
       </c>
       <c r="C72" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000136129677183667</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000136129677183666</v>
       </c>
       <c r="D72" t="n">
-        <v>1.33404572086048</v>
+        <v>1.33404572086038</v>
       </c>
       <c r="E72" t="n">
         <v>0.00000000000000000204032249666615</v>
       </c>
       <c r="F72" t="n">
-        <v>0.862322116287054</v>
+        <v>0.862322116287025</v>
       </c>
       <c r="G72" t="n">
         <v>0.741139192401671</v>
       </c>
       <c r="H72" t="n">
-        <v>0.990851209321309</v>
+        <v>0.990851209321259</v>
       </c>
     </row>
     <row r="73">
@@ -2395,22 +2395,22 @@
         <v>10</v>
       </c>
       <c r="C73" t="n">
-        <v>0.00000000000000000000000000000488745950465429</v>
+        <v>0.00000000000000000000000000000488745950465443</v>
       </c>
       <c r="D73" t="n">
-        <v>1.68869771571957</v>
+        <v>1.68869771571956</v>
       </c>
       <c r="E73" t="n">
-        <v>0.665214481296948</v>
+        <v>0.665214481296949</v>
       </c>
       <c r="F73" t="n">
-        <v>0.980344470243969</v>
+        <v>0.980344470244014</v>
       </c>
       <c r="G73" t="n">
         <v>0.968143977423663</v>
       </c>
       <c r="H73" t="n">
-        <v>0.996727255145731</v>
+        <v>0.996727255145763</v>
       </c>
     </row>
     <row r="74">
@@ -2424,19 +2424,19 @@
         <v>0.669107366373014</v>
       </c>
       <c r="D74" t="n">
-        <v>1.04615918851898</v>
+        <v>1.04615918851899</v>
       </c>
       <c r="E74" t="n">
-        <v>0.802183649444084</v>
+        <v>0.802183649444085</v>
       </c>
       <c r="F74" t="n">
-        <v>0.974035841883724</v>
+        <v>0.974035841883726</v>
       </c>
       <c r="G74" t="n">
         <v>0.023356663647941</v>
       </c>
       <c r="H74" t="n">
-        <v>1.42609871987245</v>
+        <v>1.42609871987243</v>
       </c>
     </row>
     <row r="75">
@@ -2450,19 +2450,19 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0.999311955148016</v>
+        <v>0.999311955148012</v>
       </c>
       <c r="E75" t="n">
-        <v>0.446308036426022</v>
+        <v>0.446308036426021</v>
       </c>
       <c r="F75" t="n">
-        <v>1.10942202535545</v>
+        <v>1.1094220253554</v>
       </c>
       <c r="G75" t="n">
         <v>0.255710609248632</v>
       </c>
       <c r="H75" t="n">
-        <v>0.804146990539388</v>
+        <v>0.804146990539373</v>
       </c>
     </row>
     <row r="76">
@@ -2473,7 +2473,7 @@
         <v>13</v>
       </c>
       <c r="C76" t="n">
-        <v>0.00835635020448825</v>
+        <v>0.00835635020448824</v>
       </c>
       <c r="D76" t="n">
         <v>1.05861112026543</v>
@@ -2488,7 +2488,7 @@
         <v>0.207047644463842</v>
       </c>
       <c r="H76" t="n">
-        <v>1.05106218556027</v>
+        <v>1.0510621855603</v>
       </c>
     </row>
     <row r="77">
@@ -2499,7 +2499,7 @@
         <v>14</v>
       </c>
       <c r="C77" t="n">
-        <v>0.172184068147791</v>
+        <v>0.17218406814779</v>
       </c>
       <c r="D77" t="n">
         <v>1.04434713675143</v>
@@ -2508,13 +2508,13 @@
         <v>0.56049992753136</v>
       </c>
       <c r="F77" t="n">
-        <v>0.955568189065347</v>
+        <v>0.955568189065287</v>
       </c>
       <c r="G77" t="n">
         <v>0.675198398677524</v>
       </c>
       <c r="H77" t="n">
-        <v>1.05810741096657</v>
+        <v>1.05810741096661</v>
       </c>
     </row>
     <row r="78">
@@ -2551,22 +2551,22 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>0.000791909559857664</v>
+        <v>0.000791909559857665</v>
       </c>
       <c r="D79" t="n">
-        <v>0.918088639177899</v>
+        <v>0.91808863917788</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.981000183753409</v>
+        <v>0.981000183753362</v>
       </c>
       <c r="G79" t="n">
         <v>0.113324739422094</v>
       </c>
       <c r="H79" t="n">
-        <v>0.550464576076964</v>
+        <v>0.550464576076989</v>
       </c>
     </row>
     <row r="80">
@@ -2580,19 +2580,19 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000577091439002143</v>
       </c>
       <c r="D80" t="n">
-        <v>1.35631332100369</v>
+        <v>1.35631332100366</v>
       </c>
       <c r="E80" t="n">
-        <v>0.316981161953871</v>
+        <v>0.31698116195387</v>
       </c>
       <c r="F80" t="n">
-        <v>0.983883517475966</v>
+        <v>0.983883517475952</v>
       </c>
       <c r="G80" t="n">
         <v>0.00908369349106299</v>
       </c>
       <c r="H80" t="n">
-        <v>0.932430507135408</v>
+        <v>0.932430507135383</v>
       </c>
     </row>
     <row r="81">
@@ -2606,13 +2606,13 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1.01235445907991</v>
+        <v>1.01235445907989</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>1.19375432807502</v>
+        <v>1.19375432807505</v>
       </c>
       <c r="G81" t="n">
         <v>0.106318803702309</v>
@@ -2664,13 +2664,13 @@
         <v>0.0716813113563829</v>
       </c>
       <c r="F83" t="n">
-        <v>0.156106669537388</v>
+        <v>0.156106669537374</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>0.692315694326417</v>
+        <v>0.692315694326426</v>
       </c>
     </row>
     <row r="84">
@@ -2684,19 +2684,19 @@
         <v>0.0000000000000000032133295723814</v>
       </c>
       <c r="D84" t="n">
-        <v>1.44308837481753</v>
+        <v>1.44308837481751</v>
       </c>
       <c r="E84" t="n">
-        <v>0.319669652763478</v>
+        <v>0.319669652763479</v>
       </c>
       <c r="F84" t="n">
-        <v>1.06042112383531</v>
+        <v>1.06042112383537</v>
       </c>
       <c r="G84" t="n">
         <v>0.191234724696961</v>
       </c>
       <c r="H84" t="n">
-        <v>1.1376772955166</v>
+        <v>1.13767729551661</v>
       </c>
     </row>
     <row r="85">
@@ -2739,7 +2739,7 @@
         <v>1.27613374600746</v>
       </c>
       <c r="E86" t="n">
-        <v>0.573199654986432</v>
+        <v>0.573199654986433</v>
       </c>
       <c r="F86" t="n">
         <v>0.890271628143827</v>
@@ -2788,13 +2788,13 @@
         <v>0.24548464536638</v>
       </c>
       <c r="D88" t="n">
-        <v>1.26093974668851</v>
+        <v>1.2609397466885</v>
       </c>
       <c r="E88" t="n">
         <v>0.14461209391771</v>
       </c>
       <c r="F88" t="n">
-        <v>0.565712577897351</v>
+        <v>0.565712577897361</v>
       </c>
       <c r="G88" t="n">
         <v>0.770465911869278</v>
@@ -2840,19 +2840,19 @@
         <v>0.86017283177494</v>
       </c>
       <c r="D90" t="n">
-        <v>1.00288830118973</v>
+        <v>1.0028883011898</v>
       </c>
       <c r="E90" t="n">
         <v>0.00123287913075575</v>
       </c>
       <c r="F90" t="n">
-        <v>0.892562596803115</v>
+        <v>0.892562596803068</v>
       </c>
       <c r="G90" t="n">
-        <v>0.832347932069672</v>
+        <v>0.832347932069673</v>
       </c>
       <c r="H90" t="n">
-        <v>1.01180901592406</v>
+        <v>1.01180901592402</v>
       </c>
     </row>
     <row r="91">
@@ -2869,16 +2869,16 @@
         <v>1.53809085392126</v>
       </c>
       <c r="E91" t="n">
-        <v>0.919397900725098</v>
+        <v>0.919397900725097</v>
       </c>
       <c r="F91" t="n">
-        <v>0.960633362417687</v>
+        <v>0.960633362417689</v>
       </c>
       <c r="G91" t="n">
         <v>0.860346091449238</v>
       </c>
       <c r="H91" t="n">
-        <v>0.930178850799729</v>
+        <v>0.93017885079974</v>
       </c>
     </row>
     <row r="92">
@@ -2892,19 +2892,19 @@
         <v>0.0795006064638203</v>
       </c>
       <c r="D92" t="n">
-        <v>1.09506613179996</v>
+        <v>1.0950661318</v>
       </c>
       <c r="E92" t="n">
         <v>0.384713153882404</v>
       </c>
       <c r="F92" t="n">
-        <v>0.945339869635038</v>
+        <v>0.945339869635103</v>
       </c>
       <c r="G92" t="n">
         <v>0.618132404230593</v>
       </c>
       <c r="H92" t="n">
-        <v>0.950278370297652</v>
+        <v>0.950278370297668</v>
       </c>
     </row>
     <row r="93">
@@ -2918,13 +2918,13 @@
         <v>0.000297784069695275</v>
       </c>
       <c r="D93" t="n">
-        <v>1.08336546303255</v>
+        <v>1.08336546303254</v>
       </c>
       <c r="E93" t="n">
         <v>0.212440958238381</v>
       </c>
       <c r="F93" t="n">
-        <v>0.967215501592033</v>
+        <v>0.967215501592077</v>
       </c>
       <c r="G93" t="n">
         <v>0.838047719373992</v>
@@ -2944,7 +2944,7 @@
         <v>0.0665865620001364</v>
       </c>
       <c r="D94" t="n">
-        <v>1.68705612766812</v>
+        <v>1.68705612766814</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -2996,19 +2996,19 @@
         <v>0.000455568028317969</v>
       </c>
       <c r="D96" t="n">
-        <v>0.756666427080482</v>
+        <v>0.756666427080477</v>
       </c>
       <c r="E96" t="n">
         <v>0.746021852919672</v>
       </c>
       <c r="F96" t="n">
-        <v>0.966328908567025</v>
+        <v>0.966328908567016</v>
       </c>
       <c r="G96" t="n">
         <v>0.210000045739726</v>
       </c>
       <c r="H96" t="n">
-        <v>0.848564601273739</v>
+        <v>0.848564601273752</v>
       </c>
     </row>
     <row r="97">
@@ -3022,7 +3022,7 @@
         <v>0.00152633070461232</v>
       </c>
       <c r="D97" t="n">
-        <v>0.804231887477671</v>
+        <v>0.804231887477673</v>
       </c>
       <c r="E97" t="n">
         <v>0.363137701272981</v>
@@ -3031,10 +3031,10 @@
         <v>1.10439189808168</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0163374867125685</v>
+        <v>0.0163374867125684</v>
       </c>
       <c r="H97" t="n">
-        <v>0.692375343500744</v>
+        <v>0.692375343500741</v>
       </c>
     </row>
     <row r="98">
@@ -3048,19 +3048,19 @@
         <v>0.0141215329447274</v>
       </c>
       <c r="D98" t="n">
-        <v>1.99702929386111</v>
+        <v>1.9970292938611</v>
       </c>
       <c r="E98" t="n">
-        <v>0.796960546871475</v>
+        <v>0.796960546871476</v>
       </c>
       <c r="F98" t="n">
-        <v>1.0948261965136</v>
+        <v>1.09482619651359</v>
       </c>
       <c r="G98" t="n">
         <v>0.00158564252460271</v>
       </c>
       <c r="H98" t="n">
-        <v>7.48441260270748</v>
+        <v>7.48441260270732</v>
       </c>
     </row>
     <row r="99">
@@ -3080,7 +3080,7 @@
         <v>0.268479296671999</v>
       </c>
       <c r="F99" t="n">
-        <v>0.565491902939504</v>
+        <v>0.565491902939497</v>
       </c>
       <c r="G99" t="n">
         <v>0.72269123174938</v>
@@ -3097,22 +3097,22 @@
         <v>37</v>
       </c>
       <c r="C100" t="n">
-        <v>0.680246444555456</v>
+        <v>0.680246444555457</v>
       </c>
       <c r="D100" t="n">
-        <v>1.11517926491244</v>
+        <v>1.11517926491243</v>
       </c>
       <c r="E100" t="n">
         <v>0.459210618638949</v>
       </c>
       <c r="F100" t="n">
-        <v>0.796841843614708</v>
+        <v>0.796841843614711</v>
       </c>
       <c r="G100" t="n">
-        <v>0.359310822658913</v>
+        <v>0.359310822658912</v>
       </c>
       <c r="H100" t="n">
-        <v>0.640506689032201</v>
+        <v>0.640506689032208</v>
       </c>
     </row>
     <row r="101">
@@ -3126,19 +3126,19 @@
         <v>0.494738130858129</v>
       </c>
       <c r="D101" t="n">
-        <v>0.761358321593861</v>
+        <v>0.761358321593859</v>
       </c>
       <c r="E101" t="n">
         <v>0.037319653350889</v>
       </c>
       <c r="F101" t="n">
-        <v>0.130005124136879</v>
+        <v>0.130005124136881</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>0.657133517837928</v>
+        <v>0.657133517837925</v>
       </c>
     </row>
     <row r="102">
@@ -3164,7 +3164,7 @@
         <v>0.785602695112364</v>
       </c>
       <c r="H102" t="n">
-        <v>0.834189433525276</v>
+        <v>0.834189433525282</v>
       </c>
     </row>
     <row r="103">
@@ -3227,22 +3227,22 @@
         <v>42</v>
       </c>
       <c r="C105" t="n">
-        <v>0.00000000000000000000000000000000000000000910692659091426</v>
+        <v>0.00000000000000000000000000000000000000000910692659091419</v>
       </c>
       <c r="D105" t="n">
-        <v>1.63723671725823</v>
+        <v>1.63723671725816</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0357052858207297</v>
+        <v>0.0357052858207298</v>
       </c>
       <c r="F105" t="n">
-        <v>0.925386069157976</v>
+        <v>0.92538606915799</v>
       </c>
       <c r="G105" t="n">
-        <v>0.441004302438848</v>
+        <v>0.441004302438847</v>
       </c>
       <c r="H105" t="n">
-        <v>0.951506720364202</v>
+        <v>0.951506720364197</v>
       </c>
     </row>
     <row r="106">
@@ -3256,19 +3256,19 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000021465525934084</v>
       </c>
       <c r="D106" t="n">
-        <v>1.1494439736297</v>
+        <v>1.14944397362975</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000256429396121179</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000256429396121178</v>
       </c>
       <c r="F106" t="n">
-        <v>0.883861797446123</v>
+        <v>0.883861797446103</v>
       </c>
       <c r="G106" t="n">
-        <v>0.00589146869924155</v>
+        <v>0.00589146869924156</v>
       </c>
       <c r="H106" t="n">
-        <v>1.0265884164986</v>
+        <v>1.02658841649867</v>
       </c>
     </row>
     <row r="107">
@@ -3282,19 +3282,19 @@
         <v>0.000000000000000000000619585044900663</v>
       </c>
       <c r="D107" t="n">
-        <v>0.977113322656183</v>
+        <v>0.977113322656344</v>
       </c>
       <c r="E107" t="n">
         <v>0.00129748450702086</v>
       </c>
       <c r="F107" t="n">
-        <v>0.992113795763812</v>
+        <v>0.992113795763839</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0000000000000312078033355741</v>
+        <v>0.0000000000000312078033355742</v>
       </c>
       <c r="H107" t="n">
-        <v>1.02822813018537</v>
+        <v>1.02822813018544</v>
       </c>
     </row>
     <row r="108">
@@ -3305,22 +3305,22 @@
         <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000859397230111647</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000859397230111654</v>
       </c>
       <c r="D108" t="n">
-        <v>1.7089827663075</v>
+        <v>1.70898276630753</v>
       </c>
       <c r="E108" t="n">
         <v>0.534879179549556</v>
       </c>
       <c r="F108" t="n">
-        <v>0.961250449248118</v>
+        <v>0.961250449248102</v>
       </c>
       <c r="G108" t="n">
         <v>0.00502861273508725</v>
       </c>
       <c r="H108" t="n">
-        <v>0.750137229420358</v>
+        <v>0.750137229420365</v>
       </c>
     </row>
     <row r="109">
@@ -3331,22 +3331,22 @@
         <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0000351768261964564</v>
+        <v>0.0000351768261964563</v>
       </c>
       <c r="D109" t="n">
-        <v>0.941386929129038</v>
+        <v>0.941386929129078</v>
       </c>
       <c r="E109" t="n">
-        <v>0.095267674272816</v>
+        <v>0.0952676742728157</v>
       </c>
       <c r="F109" t="n">
-        <v>0.955519799512755</v>
+        <v>0.955519799512716</v>
       </c>
       <c r="G109" t="n">
         <v>0.045106010943945</v>
       </c>
       <c r="H109" t="n">
-        <v>1.08469291789097</v>
+        <v>1.08469291789093</v>
       </c>
     </row>
     <row r="110">
@@ -3360,13 +3360,13 @@
         <v>0.177681803739871</v>
       </c>
       <c r="D110" t="n">
-        <v>0.985568533018366</v>
+        <v>0.985568533018282</v>
       </c>
       <c r="E110" t="n">
-        <v>0.777465202909387</v>
+        <v>0.777465202909385</v>
       </c>
       <c r="F110" t="n">
-        <v>0.996217218410005</v>
+        <v>0.996217218409968</v>
       </c>
       <c r="G110" t="n">
         <v>0.319782275245108</v>
@@ -3383,22 +3383,22 @@
         <v>14</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000872417892102716</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000872417892102715</v>
       </c>
       <c r="D111" t="n">
-        <v>1.12035837959457</v>
+        <v>1.12035837959442</v>
       </c>
       <c r="E111" t="n">
-        <v>0.79443521417741</v>
+        <v>0.794435214177411</v>
       </c>
       <c r="F111" t="n">
-        <v>0.996963246657164</v>
+        <v>0.996963246657103</v>
       </c>
       <c r="G111" t="n">
         <v>0.0140666479127968</v>
       </c>
       <c r="H111" t="n">
-        <v>0.956100960581258</v>
+        <v>0.956100960581306</v>
       </c>
     </row>
     <row r="112">
@@ -3412,19 +3412,19 @@
         <v>0.00000000000313494295332726</v>
       </c>
       <c r="D112" t="n">
-        <v>0.791965935806441</v>
+        <v>0.791965935806429</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0395093133052996</v>
+        <v>0.0395093133052995</v>
       </c>
       <c r="F112" t="n">
-        <v>0.931314005361653</v>
+        <v>0.931314005361696</v>
       </c>
       <c r="G112" t="n">
         <v>0.540838403785173</v>
       </c>
       <c r="H112" t="n">
-        <v>0.971491129428947</v>
+        <v>0.971491129428958</v>
       </c>
     </row>
     <row r="113">
@@ -3438,19 +3438,19 @@
         <v>0.0000000000000333386695810442</v>
       </c>
       <c r="D113" t="n">
-        <v>0.910548767763109</v>
+        <v>0.910548767763141</v>
       </c>
       <c r="E113" t="n">
-        <v>0.97149351985102</v>
+        <v>0.971493519851019</v>
       </c>
       <c r="F113" t="n">
-        <v>0.995630494999638</v>
+        <v>0.995630494999767</v>
       </c>
       <c r="G113" t="n">
         <v>0.958256055268196</v>
       </c>
       <c r="H113" t="n">
-        <v>0.991242837416859</v>
+        <v>0.991242837416917</v>
       </c>
     </row>
     <row r="114">
@@ -3464,19 +3464,19 @@
         <v>0.0000000000000000000000000000000000233034284018083</v>
       </c>
       <c r="D114" t="n">
-        <v>1.20375221760523</v>
+        <v>1.20375221760522</v>
       </c>
       <c r="E114" t="n">
-        <v>0.781351089896818</v>
+        <v>0.78135108989682</v>
       </c>
       <c r="F114" t="n">
-        <v>0.995561608849378</v>
+        <v>0.995561608849352</v>
       </c>
       <c r="G114" t="n">
-        <v>0.182669024821927</v>
+        <v>0.182669024821928</v>
       </c>
       <c r="H114" t="n">
-        <v>1.03417366891325</v>
+        <v>1.03417366891334</v>
       </c>
     </row>
     <row r="115">
@@ -3490,13 +3490,13 @@
         <v>0.0780790389728091</v>
       </c>
       <c r="D115" t="n">
-        <v>0.887291897523769</v>
+        <v>0.887291897523802</v>
       </c>
       <c r="E115" t="n">
         <v>0.78694767792444</v>
       </c>
       <c r="F115" t="n">
-        <v>1.03191256946252</v>
+        <v>1.0319125694625</v>
       </c>
       <c r="G115" t="n">
         <v>0.126667234767455</v>
@@ -3516,13 +3516,13 @@
         <v>0.32299048232434</v>
       </c>
       <c r="D116" t="n">
-        <v>0.665813255721312</v>
+        <v>0.665813255721316</v>
       </c>
       <c r="E116" t="n">
         <v>0.693704452089021</v>
       </c>
       <c r="F116" t="n">
-        <v>0.842242041769124</v>
+        <v>0.84224204176912</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
@@ -3542,7 +3542,7 @@
         <v>0.81662298796223</v>
       </c>
       <c r="D117" t="n">
-        <v>0.885541485610684</v>
+        <v>0.885541485610687</v>
       </c>
       <c r="E117" t="n">
         <v>0.469512195121951</v>
@@ -3568,19 +3568,19 @@
         <v>0.107481080666184</v>
       </c>
       <c r="D118" t="n">
-        <v>1.70905844918917</v>
+        <v>1.70905844918916</v>
       </c>
       <c r="E118" t="n">
-        <v>0.169874622277138</v>
+        <v>0.169874622277139</v>
       </c>
       <c r="F118" t="n">
-        <v>0.645761082677009</v>
+        <v>0.645761082677007</v>
       </c>
       <c r="G118" t="n">
         <v>0.784205659339812</v>
       </c>
       <c r="H118" t="n">
-        <v>0.744334411212481</v>
+        <v>0.744334411212483</v>
       </c>
     </row>
     <row r="119">
@@ -3591,22 +3591,22 @@
         <v>22</v>
       </c>
       <c r="C119" t="n">
-        <v>0.220366651272321</v>
+        <v>0.22036665127232</v>
       </c>
       <c r="D119" t="n">
-        <v>1.13263813465888</v>
+        <v>1.13263813465889</v>
       </c>
       <c r="E119" t="n">
         <v>0.190273770248706</v>
       </c>
       <c r="F119" t="n">
-        <v>0.873520882436254</v>
+        <v>0.873520882436237</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0000000558731068334452</v>
+        <v>0.0000000558731068334451</v>
       </c>
       <c r="H119" t="n">
-        <v>0.41399246674742</v>
+        <v>0.413992466747411</v>
       </c>
     </row>
     <row r="120">
@@ -3620,13 +3620,13 @@
         <v>0.939279694755997</v>
       </c>
       <c r="D120" t="n">
-        <v>0.989228261612235</v>
+        <v>0.989228261612234</v>
       </c>
       <c r="E120" t="n">
         <v>0.204875413943901</v>
       </c>
       <c r="F120" t="n">
-        <v>0.812544519192378</v>
+        <v>0.812544519192374</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -3669,22 +3669,22 @@
         <v>25</v>
       </c>
       <c r="C122" t="n">
-        <v>0.00000498050956241873</v>
+        <v>0.00000498050956241871</v>
       </c>
       <c r="D122" t="n">
-        <v>0.65621749290161</v>
+        <v>0.656217492901603</v>
       </c>
       <c r="E122" t="n">
         <v>0.882197334622362</v>
       </c>
       <c r="F122" t="n">
-        <v>1.03114127683169</v>
+        <v>1.03114127683168</v>
       </c>
       <c r="G122" t="n">
         <v>0.598987466877328</v>
       </c>
       <c r="H122" t="n">
-        <v>1.13007563610038</v>
+        <v>1.13007563610037</v>
       </c>
     </row>
     <row r="123">
@@ -3721,22 +3721,22 @@
         <v>27</v>
       </c>
       <c r="C124" t="n">
-        <v>0.00005755102851678</v>
+        <v>0.0000575510285167801</v>
       </c>
       <c r="D124" t="n">
-        <v>0.966338004868087</v>
+        <v>0.966338004868081</v>
       </c>
       <c r="E124" t="n">
-        <v>0.0000517897471280042</v>
+        <v>0.0000517897471280041</v>
       </c>
       <c r="F124" t="n">
-        <v>0.935008455091725</v>
+        <v>0.935008455092071</v>
       </c>
       <c r="G124" t="n">
-        <v>0.720736502803343</v>
+        <v>0.720736502803344</v>
       </c>
       <c r="H124" t="n">
-        <v>0.990976362430945</v>
+        <v>0.99097636243105</v>
       </c>
     </row>
     <row r="125">
@@ -3750,19 +3750,19 @@
         <v>0.211027359355727</v>
       </c>
       <c r="D125" t="n">
-        <v>0.859974331237589</v>
+        <v>0.859974331237586</v>
       </c>
       <c r="E125" t="n">
         <v>0.615533110640765</v>
       </c>
       <c r="F125" t="n">
-        <v>1.08556265018802</v>
+        <v>1.08556265018801</v>
       </c>
       <c r="G125" t="n">
         <v>0.195190323283075</v>
       </c>
       <c r="H125" t="n">
-        <v>0.747395767255516</v>
+        <v>0.747395767255525</v>
       </c>
     </row>
     <row r="126">
@@ -3776,19 +3776,19 @@
         <v>0.235019303297684</v>
       </c>
       <c r="D126" t="n">
-        <v>0.976554293656101</v>
+        <v>0.97655429365605</v>
       </c>
       <c r="E126" t="n">
-        <v>0.000000128192713353099</v>
+        <v>0.0000001281927133531</v>
       </c>
       <c r="F126" t="n">
-        <v>0.890398368003928</v>
+        <v>0.890398368003892</v>
       </c>
       <c r="G126" t="n">
         <v>0.0000199639088759709</v>
       </c>
       <c r="H126" t="n">
-        <v>1.14877623682703</v>
+        <v>1.14877623682701</v>
       </c>
     </row>
     <row r="127">
@@ -3802,19 +3802,19 @@
         <v>0.0147887600311541</v>
       </c>
       <c r="D127" t="n">
-        <v>0.976246058835349</v>
+        <v>0.976246058835361</v>
       </c>
       <c r="E127" t="n">
         <v>0.00315584258968539</v>
       </c>
       <c r="F127" t="n">
-        <v>0.965619574261824</v>
+        <v>0.965619574261813</v>
       </c>
       <c r="G127" t="n">
         <v>0.287866996427468</v>
       </c>
       <c r="H127" t="n">
-        <v>0.981295804079085</v>
+        <v>0.981295804079042</v>
       </c>
     </row>
     <row r="128">
@@ -3840,7 +3840,7 @@
         <v>0.0179810023966773</v>
       </c>
       <c r="H128" t="n">
-        <v>0.590263559091312</v>
+        <v>0.590263559091313</v>
       </c>
     </row>
     <row r="129">
@@ -3854,7 +3854,7 @@
         <v>0.0790378847959877</v>
       </c>
       <c r="D129" t="n">
-        <v>1.56464559225047</v>
+        <v>1.56464559225046</v>
       </c>
       <c r="E129" t="n">
         <v>0.61782337054993</v>
@@ -3880,13 +3880,13 @@
         <v>0.0000000000000000000000000000462722119896023</v>
       </c>
       <c r="D130" t="n">
-        <v>0.69027576408562</v>
+        <v>0.690275764085632</v>
       </c>
       <c r="E130" t="n">
         <v>0.0340590970515598</v>
       </c>
       <c r="F130" t="n">
-        <v>0.921929723966564</v>
+        <v>0.921929723966613</v>
       </c>
       <c r="G130" t="n">
         <v>0.538583217889115</v>
@@ -3903,22 +3903,22 @@
         <v>34</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0891245654647443</v>
+        <v>0.0891245654647444</v>
       </c>
       <c r="D131" t="n">
-        <v>0.922722366095112</v>
+        <v>0.922722366095141</v>
       </c>
       <c r="E131" t="n">
         <v>0.0597598757655194</v>
       </c>
       <c r="F131" t="n">
-        <v>1.15315215987768</v>
+        <v>1.15315215987769</v>
       </c>
       <c r="G131" t="n">
         <v>0.000355659831822288</v>
       </c>
       <c r="H131" t="n">
-        <v>0.673534265478414</v>
+        <v>0.673534265478412</v>
       </c>
     </row>
     <row r="132">
@@ -3958,7 +3958,7 @@
         <v>0.455445563896001</v>
       </c>
       <c r="D133" t="n">
-        <v>0.908372079993091</v>
+        <v>0.908372079993092</v>
       </c>
       <c r="E133" t="n">
         <v>0.314284458107718</v>
@@ -3970,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0.877713278513253</v>
+        <v>0.877713278513251</v>
       </c>
     </row>
     <row r="134">
@@ -3984,19 +3984,19 @@
         <v>0.556123851355734</v>
       </c>
       <c r="D134" t="n">
-        <v>0.92589317131586</v>
+        <v>0.92589317131588</v>
       </c>
       <c r="E134" t="n">
         <v>0.424320217596866</v>
       </c>
       <c r="F134" t="n">
-        <v>0.896040141183011</v>
+        <v>0.896040141183005</v>
       </c>
       <c r="G134" t="n">
         <v>0.627286542508126</v>
       </c>
       <c r="H134" t="n">
-        <v>0.90648986127317</v>
+        <v>0.906489861273157</v>
       </c>
     </row>
     <row r="135">
@@ -4007,22 +4007,22 @@
         <v>38</v>
       </c>
       <c r="C135" t="n">
-        <v>0.000184085427078365</v>
+        <v>0.000184085427078364</v>
       </c>
       <c r="D135" t="n">
-        <v>1.20394730944693</v>
+        <v>1.20394730944702</v>
       </c>
       <c r="E135" t="n">
         <v>0.028669252482064</v>
       </c>
       <c r="F135" t="n">
-        <v>1.26801240938681</v>
+        <v>1.26801240938661</v>
       </c>
       <c r="G135" t="n">
         <v>0.933666811222756</v>
       </c>
       <c r="H135" t="n">
-        <v>0.981521140937835</v>
+        <v>0.981521140938226</v>
       </c>
     </row>
     <row r="136">
@@ -4120,13 +4120,13 @@
         <v>0.000000000272623425000902</v>
       </c>
       <c r="F139" t="n">
-        <v>0.936515553868015</v>
+        <v>0.936515553867985</v>
       </c>
       <c r="G139" t="n">
         <v>0.475950565651131</v>
       </c>
       <c r="H139" t="n">
-        <v>0.988366329530528</v>
+        <v>0.988366329530475</v>
       </c>
     </row>
     <row r="140">
@@ -4140,19 +4140,19 @@
         <v>0.00000000000000000000000000000131269556954436</v>
       </c>
       <c r="D140" t="n">
-        <v>1.0497055404495</v>
+        <v>1.04970554044949</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0000000000000000000000000000000000584733517166426</v>
+        <v>0.0000000000000000000000000000000000584733517166427</v>
       </c>
       <c r="F140" t="n">
-        <v>1.0549239714565</v>
+        <v>1.05492397145664</v>
       </c>
       <c r="G140" t="n">
-        <v>0.00000505339696798599</v>
+        <v>0.000005053396967986</v>
       </c>
       <c r="H140" t="n">
-        <v>1.03065910046522</v>
+        <v>1.03065910046528</v>
       </c>
     </row>
     <row r="141">
@@ -4166,19 +4166,19 @@
         <v>0.00000000000000000000887972459041118</v>
       </c>
       <c r="D141" t="n">
-        <v>1.1893140842003</v>
+        <v>1.18931408420032</v>
       </c>
       <c r="E141" t="n">
         <v>0.415780655313911</v>
       </c>
       <c r="F141" t="n">
-        <v>0.984545594024053</v>
+        <v>0.984545594024136</v>
       </c>
       <c r="G141" t="n">
         <v>0.0319015598579538</v>
       </c>
       <c r="H141" t="n">
-        <v>1.06590397247755</v>
+        <v>1.06590397247756</v>
       </c>
     </row>
     <row r="142">
@@ -4192,19 +4192,19 @@
         <v>0.0320510312524493</v>
       </c>
       <c r="D142" t="n">
-        <v>1.63083733813721</v>
+        <v>1.6308373381372</v>
       </c>
       <c r="E142" t="n">
         <v>0.826198245720097</v>
       </c>
       <c r="F142" t="n">
-        <v>1.05686157504997</v>
+        <v>1.05686157504996</v>
       </c>
       <c r="G142" t="n">
         <v>0.450207183196641</v>
       </c>
       <c r="H142" t="n">
-        <v>0.727100401049516</v>
+        <v>0.727100401049518</v>
       </c>
     </row>
     <row r="143">
@@ -4218,7 +4218,7 @@
         <v>0.00000495050758005093</v>
       </c>
       <c r="D143" t="n">
-        <v>0.929268139696148</v>
+        <v>0.929268139696204</v>
       </c>
       <c r="E143" t="n">
         <v>0.267610040169271</v>
@@ -4227,10 +4227,10 @@
         <v>1.03391334240572</v>
       </c>
       <c r="G143" t="n">
-        <v>0.699017097519284</v>
+        <v>0.699017097519285</v>
       </c>
       <c r="H143" t="n">
-        <v>0.983016071984007</v>
+        <v>0.983016071983981</v>
       </c>
     </row>
     <row r="144">
@@ -4244,13 +4244,13 @@
         <v>0.00773020636774056</v>
       </c>
       <c r="D144" t="n">
-        <v>1.10713424922806</v>
+        <v>1.10713424922799</v>
       </c>
       <c r="E144" t="n">
-        <v>0.67735081086776</v>
+        <v>0.677350810867761</v>
       </c>
       <c r="F144" t="n">
-        <v>0.98084618971192</v>
+        <v>0.980846189711966</v>
       </c>
       <c r="G144" t="n">
         <v>0.525092949935555</v>
@@ -4270,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>0.679382516228923</v>
+        <v>0.679382516228922</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
@@ -4319,22 +4319,22 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0892965053227237</v>
+        <v>0.0892965053227238</v>
       </c>
       <c r="D147" t="n">
-        <v>0.92846343092869</v>
+        <v>0.928463430928684</v>
       </c>
       <c r="E147" t="n">
-        <v>0.00985454910115614</v>
+        <v>0.00985454910115613</v>
       </c>
       <c r="F147" t="n">
-        <v>2.81131419842086</v>
+        <v>2.81131419842087</v>
       </c>
       <c r="G147" t="n">
         <v>0.797292007675495</v>
       </c>
       <c r="H147" t="n">
-        <v>1.22825146453548</v>
+        <v>1.22825146453543</v>
       </c>
     </row>
     <row r="148">
@@ -4345,22 +4345,22 @@
         <v>17</v>
       </c>
       <c r="C148" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000376699224920396</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000376699224920395</v>
       </c>
       <c r="D148" t="n">
-        <v>1.55599960717023</v>
+        <v>1.5559996071703</v>
       </c>
       <c r="E148" t="n">
-        <v>0.333795063238494</v>
+        <v>0.333795063238493</v>
       </c>
       <c r="F148" t="n">
-        <v>0.97992982126047</v>
+        <v>0.979929821260514</v>
       </c>
       <c r="G148" t="n">
-        <v>0.4113373625353</v>
+        <v>0.411337362535299</v>
       </c>
       <c r="H148" t="n">
-        <v>0.970654088157491</v>
+        <v>0.970654088157493</v>
       </c>
     </row>
     <row r="149">
@@ -4374,19 +4374,19 @@
         <v>0.0370656590719731</v>
       </c>
       <c r="D149" t="n">
-        <v>0.655696268360805</v>
+        <v>0.655696268360802</v>
       </c>
       <c r="E149" t="n">
         <v>0.815431563661823</v>
       </c>
       <c r="F149" t="n">
-        <v>0.889082184040745</v>
+        <v>0.889082184040746</v>
       </c>
       <c r="G149" t="n">
         <v>0.723593551460927</v>
       </c>
       <c r="H149" t="n">
-        <v>0.636110939944488</v>
+        <v>0.636110939944486</v>
       </c>
     </row>
     <row r="150">
@@ -4452,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>0.689937406122245</v>
+        <v>0.689937406122242</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4504,13 +4504,13 @@
         <v>0.887145456727421</v>
       </c>
       <c r="D154" t="n">
-        <v>1.08138883252457</v>
+        <v>1.08138883252456</v>
       </c>
       <c r="E154" t="n">
         <v>0.456449721750357</v>
       </c>
       <c r="F154" t="n">
-        <v>1.28914013197243</v>
+        <v>1.28914013197241</v>
       </c>
       <c r="G154" t="n">
         <v>0.179562223080677</v>
@@ -4530,7 +4530,7 @@
         <v>0.332591768631813</v>
       </c>
       <c r="D155" t="n">
-        <v>4.76982835899567</v>
+        <v>4.76982835899566</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4608,19 +4608,19 @@
         <v>0.0000369847165476683</v>
       </c>
       <c r="D158" t="n">
-        <v>1.10016200502065</v>
+        <v>1.10016200502061</v>
       </c>
       <c r="E158" t="n">
         <v>0.826587890170033</v>
       </c>
       <c r="F158" t="n">
-        <v>0.989260718186555</v>
+        <v>0.989260718186603</v>
       </c>
       <c r="G158" t="n">
-        <v>0.470046751468503</v>
+        <v>0.470046751468502</v>
       </c>
       <c r="H158" t="n">
-        <v>1.05769372945033</v>
+        <v>1.05769372945035</v>
       </c>
     </row>
     <row r="159">
@@ -4634,19 +4634,19 @@
         <v>0.754260524046151</v>
       </c>
       <c r="D159" t="n">
-        <v>0.95168791285682</v>
+        <v>0.951687912856825</v>
       </c>
       <c r="E159" t="n">
-        <v>0.859877934725722</v>
+        <v>0.859877934725723</v>
       </c>
       <c r="F159" t="n">
-        <v>0.954288868821928</v>
+        <v>0.954288868821939</v>
       </c>
       <c r="G159" t="n">
-        <v>0.710943311162311</v>
+        <v>0.71094331116231</v>
       </c>
       <c r="H159" t="n">
-        <v>1.10300785996678</v>
+        <v>1.10300785996679</v>
       </c>
     </row>
     <row r="160">
@@ -4660,19 +4660,19 @@
         <v>0.000501551731822395</v>
       </c>
       <c r="D160" t="n">
-        <v>1.29475660005463</v>
+        <v>1.29475660005461</v>
       </c>
       <c r="E160" t="n">
-        <v>0.933139039473654</v>
+        <v>0.933139039473653</v>
       </c>
       <c r="F160" t="n">
-        <v>1.00915406909754</v>
+        <v>1.00915406909753</v>
       </c>
       <c r="G160" t="n">
         <v>0.372575190853965</v>
       </c>
       <c r="H160" t="n">
-        <v>1.13993596047156</v>
+        <v>1.13993596047155</v>
       </c>
     </row>
     <row r="161">
@@ -4686,19 +4686,19 @@
         <v>0.000000237629678147529</v>
       </c>
       <c r="D161" t="n">
-        <v>1.12401381778378</v>
+        <v>1.12401381778376</v>
       </c>
       <c r="E161" t="n">
         <v>0.419025707978741</v>
       </c>
       <c r="F161" t="n">
-        <v>0.97835211264293</v>
+        <v>0.978352112642983</v>
       </c>
       <c r="G161" t="n">
-        <v>0.86753009428431</v>
+        <v>0.867530094284311</v>
       </c>
       <c r="H161" t="n">
-        <v>0.992970763395895</v>
+        <v>0.992970763395891</v>
       </c>
     </row>
     <row r="162">
@@ -4712,7 +4712,7 @@
         <v>0.154587502790587</v>
       </c>
       <c r="D162" t="n">
-        <v>1.58866110069454</v>
+        <v>1.58866110069451</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
@@ -4724,7 +4724,7 @@
         <v>0.735536547606244</v>
       </c>
       <c r="H162" t="n">
-        <v>1.58923151090559</v>
+        <v>1.5892315109056</v>
       </c>
     </row>
     <row r="163">
@@ -4738,19 +4738,19 @@
         <v>0.271415757607819</v>
       </c>
       <c r="D163" t="n">
-        <v>1.14882757976393</v>
+        <v>1.14882757976391</v>
       </c>
       <c r="E163" t="n">
         <v>0.860859556951613</v>
       </c>
       <c r="F163" t="n">
-        <v>1.03338975896421</v>
+        <v>1.03338975896423</v>
       </c>
       <c r="G163" t="n">
         <v>0.692033339305176</v>
       </c>
       <c r="H163" t="n">
-        <v>0.886733520537349</v>
+        <v>0.886733520537345</v>
       </c>
     </row>
     <row r="164">
@@ -4790,7 +4790,7 @@
         <v>0.303795130231093</v>
       </c>
       <c r="D165" t="n">
-        <v>0.680543340225244</v>
+        <v>0.68054334022525</v>
       </c>
       <c r="E165" t="n">
         <v>1</v>
@@ -4865,22 +4865,22 @@
         <v>37</v>
       </c>
       <c r="C168" t="n">
-        <v>0.00492663389850859</v>
+        <v>0.00492663389850858</v>
       </c>
       <c r="D168" t="n">
-        <v>1.47860745650301</v>
+        <v>1.47860745650302</v>
       </c>
       <c r="E168" t="n">
-        <v>0.725072604457095</v>
+        <v>0.725072604457096</v>
       </c>
       <c r="F168" t="n">
-        <v>1.05295980013402</v>
+        <v>1.05295980013405</v>
       </c>
       <c r="G168" t="n">
         <v>0.133258959184192</v>
       </c>
       <c r="H168" t="n">
-        <v>0.693719213312873</v>
+        <v>0.693719213312887</v>
       </c>
     </row>
     <row r="169">
@@ -4894,19 +4894,19 @@
         <v>0.186470017164653</v>
       </c>
       <c r="D169" t="n">
-        <v>1.06050024268976</v>
+        <v>1.06050024268983</v>
       </c>
       <c r="E169" t="n">
-        <v>0.575012303985569</v>
+        <v>0.575012303985568</v>
       </c>
       <c r="F169" t="n">
-        <v>0.966781279655005</v>
+        <v>0.966781279654963</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0432515755818085</v>
+        <v>0.0432515755818084</v>
       </c>
       <c r="H169" t="n">
-        <v>0.839322458608635</v>
+        <v>0.839322458608638</v>
       </c>
     </row>
     <row r="170">
@@ -4946,7 +4946,7 @@
         <v>0.806318052403854</v>
       </c>
       <c r="D171" t="n">
-        <v>0.809340503443835</v>
+        <v>0.809340503443828</v>
       </c>
       <c r="E171" t="n">
         <v>1</v>
@@ -4972,7 +4972,7 @@
         <v>0.409083786405877</v>
       </c>
       <c r="D172" t="n">
-        <v>2.95569617894774</v>
+        <v>2.95569617894773</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
@@ -4998,19 +4998,19 @@
         <v>0.00369673864035157</v>
       </c>
       <c r="D173" t="n">
-        <v>1.03444339781133</v>
+        <v>1.03444339781139</v>
       </c>
       <c r="E173" t="n">
         <v>0.000000219179871365367</v>
       </c>
       <c r="F173" t="n">
-        <v>0.941365324656655</v>
+        <v>0.941365324656681</v>
       </c>
       <c r="G173" t="n">
-        <v>0.000571701338221959</v>
+        <v>0.00057170133822196</v>
       </c>
       <c r="H173" t="n">
-        <v>1.06301134337292</v>
+        <v>1.06301134337281</v>
       </c>
     </row>
     <row r="174">
@@ -5024,19 +5024,19 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>1.36416112403983</v>
+        <v>1.36416112403986</v>
       </c>
       <c r="E174" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000294506948568485</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000294506948568486</v>
       </c>
       <c r="F174" t="n">
         <v>0.918858128270922</v>
       </c>
       <c r="G174" t="n">
-        <v>0.115708678148143</v>
+        <v>0.115708678148144</v>
       </c>
       <c r="H174" t="n">
-        <v>1.00939888095713</v>
+        <v>1.00939888095715</v>
       </c>
     </row>
     <row r="175">
@@ -5050,19 +5050,19 @@
         <v>0.00000000000000000000162550934042677</v>
       </c>
       <c r="D175" t="n">
-        <v>0.991258819926745</v>
+        <v>0.991258819926465</v>
       </c>
       <c r="E175" t="n">
-        <v>0.00000000000449595770081571</v>
+        <v>0.00000000000449595770081565</v>
       </c>
       <c r="F175" t="n">
-        <v>0.993451800208921</v>
+        <v>0.993451800209277</v>
       </c>
       <c r="G175" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000057597079879109</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000575970798791086</v>
       </c>
       <c r="H175" t="n">
-        <v>1.0236331421201</v>
+        <v>1.02363314212008</v>
       </c>
     </row>
     <row r="176">
@@ -5073,22 +5073,22 @@
         <v>11</v>
       </c>
       <c r="C176" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000350340052353186</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000350340052353202</v>
       </c>
       <c r="D176" t="n">
-        <v>1.77569506251668</v>
+        <v>1.77569506251665</v>
       </c>
       <c r="E176" t="n">
         <v>0.0157261487654545</v>
       </c>
       <c r="F176" t="n">
-        <v>1.29371849952089</v>
+        <v>1.29371849952102</v>
       </c>
       <c r="G176" t="n">
         <v>0.734554084154444</v>
       </c>
       <c r="H176" t="n">
-        <v>0.933571045914049</v>
+        <v>0.933571045914072</v>
       </c>
     </row>
     <row r="177">
@@ -5102,19 +5102,19 @@
         <v>0.0721316187190199</v>
       </c>
       <c r="D177" t="n">
-        <v>1.13465914731463</v>
+        <v>1.13465914731465</v>
       </c>
       <c r="E177" t="n">
         <v>0.453061428831015</v>
       </c>
       <c r="F177" t="n">
-        <v>0.913965227342383</v>
+        <v>0.91396522734239</v>
       </c>
       <c r="G177" t="n">
         <v>0.44797149609429</v>
       </c>
       <c r="H177" t="n">
-        <v>0.879108952112504</v>
+        <v>0.879108952112499</v>
       </c>
     </row>
     <row r="178">
@@ -5128,19 +5128,19 @@
         <v>0.000000000165435237500985</v>
       </c>
       <c r="D178" t="n">
-        <v>1.20046864096633</v>
+        <v>1.20046864096638</v>
       </c>
       <c r="E178" t="n">
-        <v>0.82232246887507</v>
+        <v>0.822322468875071</v>
       </c>
       <c r="F178" t="n">
-        <v>1.00837763110327</v>
+        <v>1.00837763110321</v>
       </c>
       <c r="G178" t="n">
-        <v>0.602608001290493</v>
+        <v>0.602608001290492</v>
       </c>
       <c r="H178" t="n">
-        <v>0.97061819470275</v>
+        <v>0.970618194702701</v>
       </c>
     </row>
     <row r="179">
@@ -5154,19 +5154,19 @@
         <v>0.0000125695695858002</v>
       </c>
       <c r="D179" t="n">
-        <v>1.12685186669426</v>
+        <v>1.12685186669423</v>
       </c>
       <c r="E179" t="n">
         <v>0.393177467908408</v>
       </c>
       <c r="F179" t="n">
-        <v>0.943597023172677</v>
+        <v>0.943597023172647</v>
       </c>
       <c r="G179" t="n">
         <v>0.601055750645115</v>
       </c>
       <c r="H179" t="n">
-        <v>1.0573121571827</v>
+        <v>1.05731215718263</v>
       </c>
     </row>
     <row r="180">
@@ -5180,19 +5180,19 @@
         <v>0.0882478226754806</v>
       </c>
       <c r="D180" t="n">
-        <v>0.933262173305663</v>
+        <v>0.933262173305606</v>
       </c>
       <c r="E180" t="n">
         <v>0.448238651283559</v>
       </c>
       <c r="F180" t="n">
-        <v>0.96757559094884</v>
+        <v>0.96757559094883</v>
       </c>
       <c r="G180" t="n">
         <v>0.0655502758222661</v>
       </c>
       <c r="H180" t="n">
-        <v>0.891728582403834</v>
+        <v>0.891728582403887</v>
       </c>
     </row>
     <row r="181">
@@ -5206,19 +5206,19 @@
         <v>0.0273803612750635</v>
       </c>
       <c r="D181" t="n">
-        <v>0.923761626643543</v>
+        <v>0.923761626643519</v>
       </c>
       <c r="E181" t="n">
         <v>0.133099255191926</v>
       </c>
       <c r="F181" t="n">
-        <v>0.762158278015368</v>
+        <v>0.762158278015372</v>
       </c>
       <c r="G181" t="n">
-        <v>0.496397744067058</v>
+        <v>0.496397744067057</v>
       </c>
       <c r="H181" t="n">
-        <v>0.822839972507068</v>
+        <v>0.822839972507052</v>
       </c>
     </row>
     <row r="182">
@@ -5232,13 +5232,13 @@
         <v>0.000000000000000000379416430866315</v>
       </c>
       <c r="D182" t="n">
-        <v>1.43826612996596</v>
+        <v>1.43826612996592</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0652311961346289</v>
+        <v>0.0652311961346288</v>
       </c>
       <c r="F182" t="n">
-        <v>0.924549715571894</v>
+        <v>0.924549715571901</v>
       </c>
       <c r="G182" t="n">
         <v>0.0261954076052356</v>
@@ -5258,13 +5258,13 @@
         <v>0.587150120089219</v>
       </c>
       <c r="D183" t="n">
-        <v>1.03173635023746</v>
+        <v>1.03173635023744</v>
       </c>
       <c r="E183" t="n">
         <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>0.994907458502701</v>
+        <v>0.994907458502715</v>
       </c>
       <c r="G183" t="n">
         <v>0.0846918548501398</v>
@@ -5362,19 +5362,19 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>1.41794810121863</v>
+        <v>1.41794810121862</v>
       </c>
       <c r="E187" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000583804365192473</v>
       </c>
       <c r="F187" t="n">
-        <v>0.8891930106302</v>
+        <v>0.889193010630206</v>
       </c>
       <c r="G187" t="n">
         <v>3.69800119008229e-295</v>
       </c>
       <c r="H187" t="n">
-        <v>0.637730614421656</v>
+        <v>0.637730614421692</v>
       </c>
     </row>
     <row r="188">
@@ -5463,22 +5463,22 @@
         <v>26</v>
       </c>
       <c r="C191" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000906790402974641</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000906790402974642</v>
       </c>
       <c r="D191" t="n">
-        <v>1.51800130508237</v>
+        <v>1.51800130508239</v>
       </c>
       <c r="E191" t="n">
-        <v>0.0729678428347063</v>
+        <v>0.0729678428347064</v>
       </c>
       <c r="F191" t="n">
-        <v>1.02834158675656</v>
+        <v>1.02834158675648</v>
       </c>
       <c r="G191" t="n">
         <v>0.00000000484198317581545</v>
       </c>
       <c r="H191" t="n">
-        <v>0.857110266644307</v>
+        <v>0.857110266644333</v>
       </c>
     </row>
     <row r="192">
@@ -5492,19 +5492,19 @@
         <v>0.00000000304021818220821</v>
       </c>
       <c r="D192" t="n">
-        <v>1.08662498285356</v>
+        <v>1.08662498285355</v>
       </c>
       <c r="E192" t="n">
         <v>0.0231449767177875</v>
       </c>
       <c r="F192" t="n">
-        <v>0.915173056773091</v>
+        <v>0.915173056772622</v>
       </c>
       <c r="G192" t="n">
         <v>0.849898625460202</v>
       </c>
       <c r="H192" t="n">
-        <v>0.988038782071398</v>
+        <v>0.988038782071537</v>
       </c>
     </row>
     <row r="193">
@@ -5524,7 +5524,7 @@
         <v>0.29802973530333</v>
       </c>
       <c r="F193" t="n">
-        <v>1.10055485922514</v>
+        <v>1.10055485922515</v>
       </c>
       <c r="G193" t="n">
         <v>0.503156675897436</v>
@@ -5541,22 +5541,22 @@
         <v>29</v>
       </c>
       <c r="C194" t="n">
-        <v>2.55761146216147e-270</v>
+        <v>2.5576114621617e-270</v>
       </c>
       <c r="D194" t="n">
-        <v>1.67752467878156</v>
+        <v>1.67752467878158</v>
       </c>
       <c r="E194" t="n">
         <v>0.0202571185264488</v>
       </c>
       <c r="F194" t="n">
-        <v>0.963893359191711</v>
+        <v>0.963893359191733</v>
       </c>
       <c r="G194" t="n">
         <v>0.0195208663553134</v>
       </c>
       <c r="H194" t="n">
-        <v>0.938090346582911</v>
+        <v>0.938090346582817</v>
       </c>
     </row>
     <row r="195">
@@ -5567,22 +5567,22 @@
         <v>30</v>
       </c>
       <c r="C195" t="n">
-        <v>0.000000000000000000249001167746827</v>
+        <v>0.000000000000000000249001167746826</v>
       </c>
       <c r="D195" t="n">
-        <v>1.19376810112446</v>
+        <v>1.19376810112445</v>
       </c>
       <c r="E195" t="n">
-        <v>0.0462989442563977</v>
+        <v>0.0462989442563976</v>
       </c>
       <c r="F195" t="n">
-        <v>0.95260638589613</v>
+        <v>0.952606385896103</v>
       </c>
       <c r="G195" t="n">
         <v>0.145679008991714</v>
       </c>
       <c r="H195" t="n">
-        <v>0.944657638546759</v>
+        <v>0.944657638546766</v>
       </c>
     </row>
     <row r="196">
@@ -5593,22 +5593,22 @@
         <v>31</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0722271067752892</v>
+        <v>0.0722271067752893</v>
       </c>
       <c r="D196" t="n">
-        <v>1.14247444351597</v>
+        <v>1.14247444351596</v>
       </c>
       <c r="E196" t="n">
         <v>0.117913865321542</v>
       </c>
       <c r="F196" t="n">
-        <v>1.12500375946255</v>
+        <v>1.12500375946256</v>
       </c>
       <c r="G196" t="n">
         <v>0.000000252281113629374</v>
       </c>
       <c r="H196" t="n">
-        <v>1.83183758143606</v>
+        <v>1.83183758143604</v>
       </c>
     </row>
     <row r="197">
@@ -5622,19 +5622,19 @@
         <v>0.157320528580776</v>
       </c>
       <c r="D197" t="n">
-        <v>0.976419792698575</v>
+        <v>0.97641979269861</v>
       </c>
       <c r="E197" t="n">
         <v>0.0375870471577235</v>
       </c>
       <c r="F197" t="n">
-        <v>0.955402758241929</v>
+        <v>0.955402758241958</v>
       </c>
       <c r="G197" t="n">
         <v>0.106029124965133</v>
       </c>
       <c r="H197" t="n">
-        <v>0.950367864825056</v>
+        <v>0.950367864825064</v>
       </c>
     </row>
     <row r="198">
@@ -5648,19 +5648,19 @@
         <v>0.55906529538849</v>
       </c>
       <c r="D198" t="n">
-        <v>0.962414940993494</v>
+        <v>0.962414940993499</v>
       </c>
       <c r="E198" t="n">
         <v>0.102910123780776</v>
       </c>
       <c r="F198" t="n">
-        <v>0.886691516366908</v>
+        <v>0.886691516366866</v>
       </c>
       <c r="G198" t="n">
-        <v>0.527048620107746</v>
+        <v>0.527048620107747</v>
       </c>
       <c r="H198" t="n">
-        <v>0.934943266009883</v>
+        <v>0.934943266009876</v>
       </c>
     </row>
     <row r="199">
@@ -5674,7 +5674,7 @@
         <v>0.0259263832750257</v>
       </c>
       <c r="D199" t="n">
-        <v>0.837591419372456</v>
+        <v>0.837591419372452</v>
       </c>
       <c r="E199" t="n">
         <v>0.228488502529235</v>
@@ -5686,7 +5686,7 @@
         <v>0.208548629764119</v>
       </c>
       <c r="H199" t="n">
-        <v>0.785060744286155</v>
+        <v>0.785060744286154</v>
       </c>
     </row>
     <row r="200">
@@ -5700,19 +5700,19 @@
         <v>0.000282237289131638</v>
       </c>
       <c r="D200" t="n">
-        <v>1.4023415673134</v>
+        <v>1.40234156731344</v>
       </c>
       <c r="E200" t="n">
         <v>0.514594834148359</v>
       </c>
       <c r="F200" t="n">
-        <v>0.939858599001759</v>
+        <v>0.939858599001752</v>
       </c>
       <c r="G200" t="n">
-        <v>0.00000000978646906207756</v>
+        <v>0.00000000978646906207754</v>
       </c>
       <c r="H200" t="n">
-        <v>2.54998995064099</v>
+        <v>2.549989950641</v>
       </c>
     </row>
     <row r="201">
@@ -5749,16 +5749,16 @@
         <v>37</v>
       </c>
       <c r="C202" t="n">
-        <v>0.00169925092053037</v>
+        <v>0.00169925092053038</v>
       </c>
       <c r="D202" t="n">
-        <v>1.60483531041846</v>
+        <v>1.60483531041847</v>
       </c>
       <c r="E202" t="n">
         <v>0.21276525426537</v>
       </c>
       <c r="F202" t="n">
-        <v>0.819113531390858</v>
+        <v>0.819113531390855</v>
       </c>
       <c r="G202" t="n">
         <v>0.615187271060601</v>
@@ -5775,22 +5775,22 @@
         <v>38</v>
       </c>
       <c r="C203" t="n">
-        <v>0.0000892540464651498</v>
+        <v>0.0000892540464651495</v>
       </c>
       <c r="D203" t="n">
-        <v>2.89320497913662</v>
+        <v>2.89325429402224</v>
       </c>
       <c r="E203" t="n">
         <v>0.275521173250635</v>
       </c>
       <c r="F203" t="n">
-        <v>0.497687893279146</v>
+        <v>0.497687893279132</v>
       </c>
       <c r="G203" t="n">
         <v>1</v>
       </c>
       <c r="H203" t="n">
-        <v>0.716362263245207</v>
+        <v>0.71636226324519</v>
       </c>
     </row>
     <row r="204">
@@ -5801,22 +5801,22 @@
         <v>39</v>
       </c>
       <c r="C204" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000154878446748348</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000154878446748358</v>
       </c>
       <c r="D204" t="n">
-        <v>1.65396269549254</v>
+        <v>1.65396269549261</v>
       </c>
       <c r="E204" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000232582373769573</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000232582373769572</v>
       </c>
       <c r="F204" t="n">
-        <v>1.38413513964155</v>
+        <v>1.38413513964151</v>
       </c>
       <c r="G204" t="n">
         <v>0.00000058206427722365</v>
       </c>
       <c r="H204" t="n">
-        <v>0.842583098188952</v>
+        <v>0.842583098188975</v>
       </c>
     </row>
     <row r="205">
@@ -5856,19 +5856,19 @@
         <v>0.842888099821557</v>
       </c>
       <c r="D206" t="n">
-        <v>0.961156276125347</v>
+        <v>0.961156276125338</v>
       </c>
       <c r="E206" t="n">
         <v>0.722733408279804</v>
       </c>
       <c r="F206" t="n">
-        <v>0.865975284873879</v>
+        <v>0.865975284873892</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
       </c>
       <c r="H206" t="n">
-        <v>0.995959221090356</v>
+        <v>0.995959221090371</v>
       </c>
     </row>
     <row r="207">
@@ -5882,19 +5882,19 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>1.45233397862278</v>
+        <v>1.45233397862283</v>
       </c>
       <c r="E207" t="n">
-        <v>0.000000000000000000000000000000000000000000000539313134183851</v>
+        <v>0.000000000000000000000000000000000000000000000539313134183853</v>
       </c>
       <c r="F207" t="n">
-        <v>0.957946206361049</v>
+        <v>0.957946206360936</v>
       </c>
       <c r="G207" t="n">
-        <v>0.973849850467475</v>
+        <v>0.973849850467477</v>
       </c>
       <c r="H207" t="n">
-        <v>0.999856671320253</v>
+        <v>0.999856671320238</v>
       </c>
     </row>
     <row r="208">
@@ -5905,22 +5905,22 @@
         <v>9</v>
       </c>
       <c r="C208" t="n">
-        <v>4.15809719868208e-289</v>
+        <v>4.15809719868207e-289</v>
       </c>
       <c r="D208" t="n">
-        <v>1.29392251778479</v>
+        <v>1.29392251778476</v>
       </c>
       <c r="E208" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000735725021467975</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000735725021467973</v>
       </c>
       <c r="F208" t="n">
-        <v>0.866809442849598</v>
+        <v>0.86680944284956</v>
       </c>
       <c r="G208" t="n">
-        <v>0.571732697802717</v>
+        <v>0.571732697802715</v>
       </c>
       <c r="H208" t="n">
-        <v>1.00736794451704</v>
+        <v>1.00736794451703</v>
       </c>
     </row>
     <row r="209">
@@ -5934,19 +5934,19 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>1.31872863779617</v>
+        <v>1.31872863779618</v>
       </c>
       <c r="E209" t="n">
         <v>0.0389006074517984</v>
       </c>
       <c r="F209" t="n">
-        <v>1.01166255181869</v>
+        <v>1.01166255181868</v>
       </c>
       <c r="G209" t="n">
         <v>0.179459057056903</v>
       </c>
       <c r="H209" t="n">
-        <v>0.987829952990771</v>
+        <v>0.987829952990714</v>
       </c>
     </row>
     <row r="210">
@@ -5957,22 +5957,22 @@
         <v>11</v>
       </c>
       <c r="C210" t="n">
-        <v>0.000000000000000000000000000521773329721668</v>
+        <v>0.000000000000000000000000000521773329721654</v>
       </c>
       <c r="D210" t="n">
-        <v>1.63466447540243</v>
+        <v>1.63466447540245</v>
       </c>
       <c r="E210" t="n">
         <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>0.968393004613231</v>
+        <v>0.968393004612357</v>
       </c>
       <c r="G210" t="n">
         <v>0.784432692332899</v>
       </c>
       <c r="H210" t="n">
-        <v>0.796243793558921</v>
+        <v>0.796243793558899</v>
       </c>
     </row>
     <row r="211">
@@ -5986,7 +5986,7 @@
         <v>0.954918869331123</v>
       </c>
       <c r="D211" t="n">
-        <v>0.993907647321972</v>
+        <v>0.993907647321959</v>
       </c>
       <c r="E211" t="n">
         <v>0.29004294397135</v>
@@ -5998,7 +5998,7 @@
         <v>0.627332524625595</v>
       </c>
       <c r="H211" t="n">
-        <v>1.21048111608088</v>
+        <v>1.21048111608087</v>
       </c>
     </row>
     <row r="212">
@@ -6012,19 +6012,19 @@
         <v>0.0000000000000000000000000780614062647286</v>
       </c>
       <c r="D212" t="n">
-        <v>1.19696058236834</v>
+        <v>1.19696058236839</v>
       </c>
       <c r="E212" t="n">
         <v>0.118755014864589</v>
       </c>
       <c r="F212" t="n">
-        <v>0.968346648312483</v>
+        <v>0.968346648312504</v>
       </c>
       <c r="G212" t="n">
         <v>0.907901193082736</v>
       </c>
       <c r="H212" t="n">
-        <v>1.00386945074097</v>
+        <v>1.00386945074096</v>
       </c>
     </row>
     <row r="213">
@@ -6038,13 +6038,13 @@
         <v>0.00000000000000274067712632688</v>
       </c>
       <c r="D213" t="n">
-        <v>1.24544603869933</v>
+        <v>1.24544603869935</v>
       </c>
       <c r="E213" t="n">
         <v>0.971446666922853</v>
       </c>
       <c r="F213" t="n">
-        <v>1.00399635224839</v>
+        <v>1.00399635224846</v>
       </c>
       <c r="G213" t="n">
         <v>0.312327050173655</v>
@@ -6087,22 +6087,22 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>0.298001866621824</v>
+        <v>0.298001866621823</v>
       </c>
       <c r="D215" t="n">
-        <v>0.894967347249488</v>
+        <v>0.894967347249481</v>
       </c>
       <c r="E215" t="n">
         <v>0.129644792994261</v>
       </c>
       <c r="F215" t="n">
-        <v>0.190976118256293</v>
+        <v>0.19097611825628</v>
       </c>
       <c r="G215" t="n">
         <v>0.306153479766245</v>
       </c>
       <c r="H215" t="n">
-        <v>0.225244178352104</v>
+        <v>0.225244178352102</v>
       </c>
     </row>
     <row r="216">
@@ -6119,16 +6119,16 @@
         <v>1.30245340408315</v>
       </c>
       <c r="E216" t="n">
-        <v>0.738217347263677</v>
+        <v>0.738217347263676</v>
       </c>
       <c r="F216" t="n">
-        <v>1.01113215323281</v>
+        <v>1.01113215323279</v>
       </c>
       <c r="G216" t="n">
         <v>0.677965071198134</v>
       </c>
       <c r="H216" t="n">
-        <v>1.02220536763239</v>
+        <v>1.02220536763238</v>
       </c>
     </row>
     <row r="217">
@@ -6139,7 +6139,7 @@
         <v>18</v>
       </c>
       <c r="C217" t="n">
-        <v>0.253176563079364</v>
+        <v>0.253176563079363</v>
       </c>
       <c r="D217" t="n">
         <v>1.20392820166735</v>
@@ -6148,13 +6148,13 @@
         <v>0.474472149234392</v>
       </c>
       <c r="F217" t="n">
-        <v>0.724953478606783</v>
+        <v>0.724953478606778</v>
       </c>
       <c r="G217" t="n">
         <v>0.22423744073853</v>
       </c>
       <c r="H217" t="n">
-        <v>2.4225874829038</v>
+        <v>2.42258748290381</v>
       </c>
     </row>
     <row r="218">
@@ -6226,13 +6226,13 @@
         <v>0.0494479711543606</v>
       </c>
       <c r="F220" t="n">
-        <v>0.865157967231625</v>
+        <v>0.86515796723164</v>
       </c>
       <c r="G220" t="n">
         <v>0.392943201681875</v>
       </c>
       <c r="H220" t="n">
-        <v>0.89795916089146</v>
+        <v>0.897959160891462</v>
       </c>
     </row>
     <row r="221">
@@ -6243,22 +6243,22 @@
         <v>22</v>
       </c>
       <c r="C221" t="n">
-        <v>0.000000000000000000000000000000000000000347588732154531</v>
+        <v>0.00000000000000000000000000000000000000034758873215453</v>
       </c>
       <c r="D221" t="n">
-        <v>1.44122676453632</v>
+        <v>1.44122676453629</v>
       </c>
       <c r="E221" t="n">
-        <v>0.0000721768512939455</v>
+        <v>0.0000721768512939456</v>
       </c>
       <c r="F221" t="n">
-        <v>0.895053040642535</v>
+        <v>0.895053040642512</v>
       </c>
       <c r="G221" t="n">
-        <v>0.00000000000000000000000000023742797254253</v>
+        <v>0.000000000000000000000000000237427972542537</v>
       </c>
       <c r="H221" t="n">
-        <v>0.597751151729554</v>
+        <v>0.597751151729566</v>
       </c>
     </row>
     <row r="222">
@@ -6376,19 +6376,19 @@
         <v>0.00143565192992511</v>
       </c>
       <c r="D226" t="n">
-        <v>1.07440512917375</v>
+        <v>1.07440512917368</v>
       </c>
       <c r="E226" t="n">
-        <v>0.118559112823178</v>
+        <v>0.118559112823179</v>
       </c>
       <c r="F226" t="n">
-        <v>0.919458777872471</v>
+        <v>0.919458777872575</v>
       </c>
       <c r="G226" t="n">
         <v>0.0108345132884298</v>
       </c>
       <c r="H226" t="n">
-        <v>1.23197808553739</v>
+        <v>1.23197808553747</v>
       </c>
     </row>
     <row r="227">
@@ -6425,22 +6425,22 @@
         <v>29</v>
       </c>
       <c r="C228" t="n">
-        <v>0.00000000000910599780559687</v>
+        <v>0.00000000000910599780559685</v>
       </c>
       <c r="D228" t="n">
-        <v>1.58158064743095</v>
+        <v>1.58158064743094</v>
       </c>
       <c r="E228" t="n">
         <v>0.000798241208339965</v>
       </c>
       <c r="F228" t="n">
-        <v>0.788581401594372</v>
+        <v>0.788581401594353</v>
       </c>
       <c r="G228" t="n">
-        <v>0.675377037036197</v>
+        <v>0.675377037036196</v>
       </c>
       <c r="H228" t="n">
-        <v>0.950126906390128</v>
+        <v>0.95012690639015</v>
       </c>
     </row>
     <row r="229">
@@ -6454,19 +6454,19 @@
         <v>0.00000377767018123381</v>
       </c>
       <c r="D229" t="n">
-        <v>1.1896170462173</v>
+        <v>1.18961704621729</v>
       </c>
       <c r="E229" t="n">
-        <v>0.237875558925154</v>
+        <v>0.237875558925155</v>
       </c>
       <c r="F229" t="n">
-        <v>0.946660512676373</v>
+        <v>0.946660512676362</v>
       </c>
       <c r="G229" t="n">
         <v>0.970697220557706</v>
       </c>
       <c r="H229" t="n">
-        <v>0.996922353755672</v>
+        <v>0.996922353755696</v>
       </c>
     </row>
     <row r="230">
@@ -6477,22 +6477,22 @@
         <v>31</v>
       </c>
       <c r="C230" t="n">
-        <v>0.000093715886669758</v>
+        <v>0.0000937158866697577</v>
       </c>
       <c r="D230" t="n">
-        <v>1.85483488712555</v>
+        <v>1.85483488712556</v>
       </c>
       <c r="E230" t="n">
         <v>0.939069936086012</v>
       </c>
       <c r="F230" t="n">
-        <v>1.02311404831989</v>
+        <v>1.02311404831988</v>
       </c>
       <c r="G230" t="n">
         <v>0.0201170204825466</v>
       </c>
       <c r="H230" t="n">
-        <v>0.513243426498325</v>
+        <v>0.513243426498323</v>
       </c>
     </row>
     <row r="231">
@@ -6506,13 +6506,13 @@
         <v>0.558143805044115</v>
       </c>
       <c r="D231" t="n">
-        <v>0.852718975841383</v>
+        <v>0.852718975841379</v>
       </c>
       <c r="E231" t="n">
         <v>0.40463631361805</v>
       </c>
       <c r="F231" t="n">
-        <v>1.30450884829048</v>
+        <v>1.30450884829047</v>
       </c>
       <c r="G231" t="n">
         <v>0.694463215596503</v>
@@ -6529,16 +6529,16 @@
         <v>33</v>
       </c>
       <c r="C232" t="n">
-        <v>0.683700330264419</v>
+        <v>0.68370033026442</v>
       </c>
       <c r="D232" t="n">
-        <v>0.932158660830058</v>
+        <v>0.932158660830072</v>
       </c>
       <c r="E232" t="n">
         <v>0.377198294566573</v>
       </c>
       <c r="F232" t="n">
-        <v>0.850194839140964</v>
+        <v>0.850194839140966</v>
       </c>
       <c r="G232" t="n">
         <v>0.899892119333254</v>
@@ -6636,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>0.953639237091159</v>
+        <v>0.953639237091164</v>
       </c>
       <c r="E236" t="n">
         <v>0.278818199830593</v>
@@ -6648,7 +6648,7 @@
         <v>0.789074178892274</v>
       </c>
       <c r="H236" t="n">
-        <v>1.22776304073644</v>
+        <v>1.22776304073643</v>
       </c>
     </row>
     <row r="237">
@@ -6746,13 +6746,13 @@
         <v>0.503773403146866</v>
       </c>
       <c r="F240" t="n">
-        <v>0.531941202549484</v>
+        <v>0.531941202549483</v>
       </c>
       <c r="G240" t="n">
         <v>0.38552321007081</v>
       </c>
       <c r="H240" t="n">
-        <v>3.19804578621709</v>
+        <v>3.19804578621705</v>
       </c>
     </row>
     <row r="241">
@@ -6766,19 +6766,19 @@
         <v>0</v>
       </c>
       <c r="D241" t="n">
-        <v>1.53702173059429</v>
+        <v>1.5370217305943</v>
       </c>
       <c r="E241" t="n">
         <v>0.0000000000000000000000000000215937608057625</v>
       </c>
       <c r="F241" t="n">
-        <v>0.945101419568891</v>
+        <v>0.945101419568716</v>
       </c>
       <c r="G241" t="n">
-        <v>0.000173912569877611</v>
+        <v>0.00017391256987761</v>
       </c>
       <c r="H241" t="n">
-        <v>0.968310613144487</v>
+        <v>0.968310613144352</v>
       </c>
     </row>
     <row r="242">
@@ -6792,19 +6792,19 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000134392539086941</v>
       </c>
       <c r="D242" t="n">
-        <v>1.39402548122525</v>
+        <v>1.3940254812253</v>
       </c>
       <c r="E242" t="n">
         <v>0.00000000000000878596766539496</v>
       </c>
       <c r="F242" t="n">
-        <v>0.8944354215578</v>
+        <v>0.894435421557751</v>
       </c>
       <c r="G242" t="n">
         <v>0.163888336501843</v>
       </c>
       <c r="H242" t="n">
-        <v>1.03381334914122</v>
+        <v>1.03381334914131</v>
       </c>
     </row>
     <row r="243">
@@ -6815,22 +6815,22 @@
         <v>10</v>
       </c>
       <c r="C243" t="n">
-        <v>0.171729860495396</v>
+        <v>0.171729860495397</v>
       </c>
       <c r="D243" t="n">
-        <v>0.983007382819436</v>
+        <v>0.983007382819472</v>
       </c>
       <c r="E243" t="n">
         <v>0.577183262953643</v>
       </c>
       <c r="F243" t="n">
-        <v>0.992745089463299</v>
+        <v>0.992745089463324</v>
       </c>
       <c r="G243" t="n">
-        <v>0.2620618706944</v>
+        <v>0.262061870694401</v>
       </c>
       <c r="H243" t="n">
-        <v>1.02207219493389</v>
+        <v>1.02207219493391</v>
       </c>
     </row>
     <row r="244">
@@ -6841,22 +6841,22 @@
         <v>11</v>
       </c>
       <c r="C244" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000325385556331877</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000325385556331879</v>
       </c>
       <c r="D244" t="n">
-        <v>1.69679035939768</v>
+        <v>1.69679035939762</v>
       </c>
       <c r="E244" t="n">
-        <v>0.255893570145856</v>
+        <v>0.255893570145855</v>
       </c>
       <c r="F244" t="n">
-        <v>1.04494118362138</v>
+        <v>1.04494118362125</v>
       </c>
       <c r="G244" t="n">
         <v>0.40820424401555</v>
       </c>
       <c r="H244" t="n">
-        <v>0.947520460676921</v>
+        <v>0.947520460676884</v>
       </c>
     </row>
     <row r="245">
@@ -6867,22 +6867,22 @@
         <v>12</v>
       </c>
       <c r="C245" t="n">
-        <v>0.000000000000000000000000000101976096503364</v>
+        <v>0.000000000000000000000000000101976096503365</v>
       </c>
       <c r="D245" t="n">
-        <v>0.593865461232389</v>
+        <v>0.593865461232372</v>
       </c>
       <c r="E245" t="n">
         <v>0.844164922630947</v>
       </c>
       <c r="F245" t="n">
-        <v>0.981824012314021</v>
+        <v>0.981824012314054</v>
       </c>
       <c r="G245" t="n">
         <v>0.312645389424526</v>
       </c>
       <c r="H245" t="n">
-        <v>1.11749519059793</v>
+        <v>1.11749519059792</v>
       </c>
     </row>
     <row r="246">
@@ -6896,19 +6896,19 @@
         <v>0.326353854778176</v>
       </c>
       <c r="D246" t="n">
-        <v>0.982132113333039</v>
+        <v>0.98213211333312</v>
       </c>
       <c r="E246" t="n">
         <v>0.67981335280701</v>
       </c>
       <c r="F246" t="n">
-        <v>0.990846300266559</v>
+        <v>0.990846300266555</v>
       </c>
       <c r="G246" t="n">
-        <v>0.0000000000159370660550775</v>
+        <v>0.0000000000159370660550776</v>
       </c>
       <c r="H246" t="n">
-        <v>1.24664349884731</v>
+        <v>1.24664349884732</v>
       </c>
     </row>
     <row r="247">
@@ -6922,19 +6922,19 @@
         <v>0.306320793429936</v>
       </c>
       <c r="D247" t="n">
-        <v>1.04262675947001</v>
+        <v>1.04262675947002</v>
       </c>
       <c r="E247" t="n">
-        <v>0.779101713000531</v>
+        <v>0.779101713000532</v>
       </c>
       <c r="F247" t="n">
-        <v>1.03528263707314</v>
+        <v>1.03528263707317</v>
       </c>
       <c r="G247" t="n">
         <v>0.809031892692215</v>
       </c>
       <c r="H247" t="n">
-        <v>1.04084292125075</v>
+        <v>1.04084292125074</v>
       </c>
     </row>
     <row r="248">
@@ -6974,19 +6974,19 @@
         <v>0.0010208575115146</v>
       </c>
       <c r="D249" t="n">
-        <v>0.884370431893826</v>
+        <v>0.884370431893806</v>
       </c>
       <c r="E249" t="n">
         <v>1</v>
       </c>
       <c r="F249" t="n">
-        <v>1.06679344248546</v>
+        <v>1.06679344248549</v>
       </c>
       <c r="G249" t="n">
         <v>0.161036461973716</v>
       </c>
       <c r="H249" t="n">
-        <v>0.391676812104126</v>
+        <v>0.391676812104152</v>
       </c>
     </row>
     <row r="250">
@@ -7000,19 +7000,19 @@
         <v>0.0000260421820217368</v>
       </c>
       <c r="D250" t="n">
-        <v>1.30335388590869</v>
+        <v>1.30335388590867</v>
       </c>
       <c r="E250" t="n">
         <v>0.389572950471147</v>
       </c>
       <c r="F250" t="n">
-        <v>0.94175304217963</v>
+        <v>0.941753042179602</v>
       </c>
       <c r="G250" t="n">
-        <v>0.267095534416677</v>
+        <v>0.267095534416678</v>
       </c>
       <c r="H250" t="n">
-        <v>0.882412968869043</v>
+        <v>0.882412968869046</v>
       </c>
     </row>
     <row r="251">
@@ -7026,7 +7026,7 @@
         <v>0.359613708314656</v>
       </c>
       <c r="D251" t="n">
-        <v>1.4913124954827</v>
+        <v>1.49131249548269</v>
       </c>
       <c r="E251" t="n">
         <v>1</v>
@@ -7130,19 +7130,19 @@
         <v>0.0168685286158502</v>
       </c>
       <c r="D255" t="n">
-        <v>1.54613974859951</v>
+        <v>1.54613974859952</v>
       </c>
       <c r="E255" t="n">
         <v>0.332021413075423</v>
       </c>
       <c r="F255" t="n">
-        <v>0.83671765595407</v>
+        <v>0.836717655954068</v>
       </c>
       <c r="G255" t="n">
         <v>0.472894163989923</v>
       </c>
       <c r="H255" t="n">
-        <v>0.794695753808265</v>
+        <v>0.794695753808266</v>
       </c>
     </row>
     <row r="256">
@@ -7231,7 +7231,7 @@
         <v>26</v>
       </c>
       <c r="C259" t="n">
-        <v>0.0000000000000000086016259559246</v>
+        <v>0.00000000000000000860162595592454</v>
       </c>
       <c r="D259" t="n">
         <v>1.63820379587806</v>
@@ -7240,13 +7240,13 @@
         <v>0.300907461717942</v>
       </c>
       <c r="F259" t="n">
-        <v>0.939170627248536</v>
+        <v>0.939170627248539</v>
       </c>
       <c r="G259" t="n">
         <v>0.640758698754571</v>
       </c>
       <c r="H259" t="n">
-        <v>0.949718165587296</v>
+        <v>0.949718165587299</v>
       </c>
     </row>
     <row r="260">
@@ -7260,19 +7260,19 @@
         <v>0.389932994884443</v>
       </c>
       <c r="D260" t="n">
-        <v>1.0296403194585</v>
+        <v>1.02964031945855</v>
       </c>
       <c r="E260" t="n">
         <v>0.436319293635815</v>
       </c>
       <c r="F260" t="n">
-        <v>0.944673161241171</v>
+        <v>0.944673161241125</v>
       </c>
       <c r="G260" t="n">
         <v>0.0436014373801298</v>
       </c>
       <c r="H260" t="n">
-        <v>1.24505610100979</v>
+        <v>1.24505610100977</v>
       </c>
     </row>
     <row r="261">
@@ -7286,19 +7286,19 @@
         <v>0.116429815305326</v>
       </c>
       <c r="D261" t="n">
-        <v>0.796382045856907</v>
+        <v>0.796382045856891</v>
       </c>
       <c r="E261" t="n">
         <v>0.823846706106535</v>
       </c>
       <c r="F261" t="n">
-        <v>0.957951902612589</v>
+        <v>0.957951902612593</v>
       </c>
       <c r="G261" t="n">
         <v>0.0378482365693007</v>
       </c>
       <c r="H261" t="n">
-        <v>0.639472446123212</v>
+        <v>0.639472446123204</v>
       </c>
     </row>
     <row r="262">
@@ -7309,22 +7309,22 @@
         <v>29</v>
       </c>
       <c r="C262" t="n">
-        <v>0.451549276965702</v>
+        <v>0.451549276965701</v>
       </c>
       <c r="D262" t="n">
-        <v>1.05597246221378</v>
+        <v>1.05597246221375</v>
       </c>
       <c r="E262" t="n">
-        <v>0.749240529755274</v>
+        <v>0.749240529755275</v>
       </c>
       <c r="F262" t="n">
-        <v>0.974242191112885</v>
+        <v>0.974242191112884</v>
       </c>
       <c r="G262" t="n">
         <v>0.717321893753861</v>
       </c>
       <c r="H262" t="n">
-        <v>0.951126962540739</v>
+        <v>0.95112696254071</v>
       </c>
     </row>
     <row r="263">
@@ -7341,16 +7341,16 @@
         <v>1.04438683871636</v>
       </c>
       <c r="E263" t="n">
-        <v>0.948275287277864</v>
+        <v>0.948275287277863</v>
       </c>
       <c r="F263" t="n">
-        <v>1.00234585303832</v>
+        <v>1.00234585303828</v>
       </c>
       <c r="G263" t="n">
         <v>0.0522916575402123</v>
       </c>
       <c r="H263" t="n">
-        <v>1.10145807905516</v>
+        <v>1.1014580790552</v>
       </c>
     </row>
     <row r="264">
@@ -7387,22 +7387,22 @@
         <v>32</v>
       </c>
       <c r="C265" t="n">
-        <v>0.541238287991607</v>
+        <v>0.541238287991608</v>
       </c>
       <c r="D265" t="n">
-        <v>1.03615923230144</v>
+        <v>1.03615923230146</v>
       </c>
       <c r="E265" t="n">
         <v>0.121155332093949</v>
       </c>
       <c r="F265" t="n">
-        <v>0.911180077089201</v>
+        <v>0.911180077089175</v>
       </c>
       <c r="G265" t="n">
         <v>0.321980287838153</v>
       </c>
       <c r="H265" t="n">
-        <v>1.09250393957983</v>
+        <v>1.09250393957985</v>
       </c>
     </row>
     <row r="266">
@@ -7416,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>1.02802555494465</v>
+        <v>1.02802555494464</v>
       </c>
       <c r="E266" t="n">
         <v>1</v>
@@ -7442,19 +7442,19 @@
         <v>0.0000281348803672055</v>
       </c>
       <c r="D267" t="n">
-        <v>0.798095537711647</v>
+        <v>0.798095537711642</v>
       </c>
       <c r="E267" t="n">
         <v>0.21721501559796</v>
       </c>
       <c r="F267" t="n">
-        <v>1.10079665019968</v>
+        <v>1.1007966501997</v>
       </c>
       <c r="G267" t="n">
         <v>0.055364529845004</v>
       </c>
       <c r="H267" t="n">
-        <v>0.810098363311384</v>
+        <v>0.810098363311375</v>
       </c>
     </row>
     <row r="268">
@@ -7468,16 +7468,16 @@
         <v>0.79541320789574</v>
       </c>
       <c r="D268" t="n">
-        <v>0.982078638051893</v>
+        <v>0.982078638051896</v>
       </c>
       <c r="E268" t="n">
         <v>0.0127287857968509</v>
       </c>
       <c r="F268" t="n">
-        <v>0.84532226387238</v>
+        <v>0.845322263872388</v>
       </c>
       <c r="G268" t="n">
-        <v>0.00000000000000513086017577784</v>
+        <v>0.0000000000000051308601757778</v>
       </c>
       <c r="H268" t="n">
         <v>2.25276150070237</v>
@@ -7647,22 +7647,22 @@
         <v>42</v>
       </c>
       <c r="C275" t="n">
-        <v>0.0000000000000000000000000281355418109522</v>
+        <v>0.0000000000000000000000000281355418109521</v>
       </c>
       <c r="D275" t="n">
         <v>1.20648861700376</v>
       </c>
       <c r="E275" t="n">
-        <v>0.0000000254044247948325</v>
+        <v>0.0000000254044247948326</v>
       </c>
       <c r="F275" t="n">
-        <v>0.905980970442071</v>
+        <v>0.905980970442084</v>
       </c>
       <c r="G275" t="n">
         <v>0.0835814337134734</v>
       </c>
       <c r="H275" t="n">
-        <v>1.05032346590261</v>
+        <v>1.05032346590263</v>
       </c>
     </row>
     <row r="276">
@@ -7676,19 +7676,19 @@
         <v>0.0000000000000000000000000000000131155315683718</v>
       </c>
       <c r="D276" t="n">
-        <v>1.25761504959774</v>
+        <v>1.2576150495977</v>
       </c>
       <c r="E276" t="n">
         <v>0.0000000000000136693007399048</v>
       </c>
       <c r="F276" t="n">
-        <v>0.856022572391931</v>
+        <v>0.856022572391945</v>
       </c>
       <c r="G276" t="n">
         <v>0.00334074126807671</v>
       </c>
       <c r="H276" t="n">
-        <v>1.10047593375415</v>
+        <v>1.10047593375418</v>
       </c>
     </row>
     <row r="277">
@@ -7699,22 +7699,22 @@
         <v>10</v>
       </c>
       <c r="C277" t="n">
-        <v>0.317225320031252</v>
+        <v>0.317225320031251</v>
       </c>
       <c r="D277" t="n">
-        <v>1.00837979743829</v>
+        <v>1.00837979743834</v>
       </c>
       <c r="E277" t="n">
         <v>0.000104114098183935</v>
       </c>
       <c r="F277" t="n">
-        <v>0.967109911639356</v>
+        <v>0.967109911639305</v>
       </c>
       <c r="G277" t="n">
         <v>0.133902212772287</v>
       </c>
       <c r="H277" t="n">
-        <v>1.01966116018321</v>
+        <v>1.01966116018318</v>
       </c>
     </row>
     <row r="278">
@@ -7728,7 +7728,7 @@
         <v>0.573658042895542</v>
       </c>
       <c r="D278" t="n">
-        <v>1.19738407430648</v>
+        <v>1.19738407430647</v>
       </c>
       <c r="E278" t="n">
         <v>1</v>
@@ -7754,19 +7754,19 @@
         <v>0.0000337619744399785</v>
       </c>
       <c r="D279" t="n">
-        <v>0.791988091599988</v>
+        <v>0.791988091600004</v>
       </c>
       <c r="E279" t="n">
-        <v>0.316628102904243</v>
+        <v>0.316628102904242</v>
       </c>
       <c r="F279" t="n">
-        <v>0.732768703482139</v>
+        <v>0.732768703482119</v>
       </c>
       <c r="G279" t="n">
         <v>0.168866567443007</v>
       </c>
       <c r="H279" t="n">
-        <v>0.572214976059882</v>
+        <v>0.572214976059896</v>
       </c>
     </row>
     <row r="280">
@@ -7780,19 +7780,19 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000960323596285003</v>
       </c>
       <c r="D280" t="n">
-        <v>0.896203605822878</v>
+        <v>0.89620360582284</v>
       </c>
       <c r="E280" t="n">
         <v>0.421995735068773</v>
       </c>
       <c r="F280" t="n">
-        <v>1.00472564859744</v>
+        <v>1.00472564859743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.13377068620204</v>
+        <v>0.133770686202039</v>
       </c>
       <c r="H280" t="n">
-        <v>0.987215258707794</v>
+        <v>0.987215258707818</v>
       </c>
     </row>
     <row r="281">
@@ -7803,7 +7803,7 @@
         <v>14</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0087336634872028</v>
+        <v>0.00873366348720279</v>
       </c>
       <c r="D281" t="n">
         <v>1.26909712580734</v>
@@ -7818,7 +7818,7 @@
         <v>0.0477992110009974</v>
       </c>
       <c r="H281" t="n">
-        <v>3.66666330045234</v>
+        <v>3.66666330045242</v>
       </c>
     </row>
     <row r="282">
@@ -7829,22 +7829,22 @@
         <v>15</v>
       </c>
       <c r="C282" t="n">
-        <v>0.749910333109747</v>
+        <v>0.749910333109748</v>
       </c>
       <c r="D282" t="n">
-        <v>1.02516226897781</v>
+        <v>1.02516226897779</v>
       </c>
       <c r="E282" t="n">
         <v>1</v>
       </c>
       <c r="F282" t="n">
-        <v>1.0025560596534</v>
+        <v>1.00255605965338</v>
       </c>
       <c r="G282" t="n">
         <v>0.459555527235452</v>
       </c>
       <c r="H282" t="n">
-        <v>0.923490199309135</v>
+        <v>0.923490199309144</v>
       </c>
     </row>
     <row r="283">
@@ -7858,7 +7858,7 @@
         <v>0.102071666920202</v>
       </c>
       <c r="D283" t="n">
-        <v>0.828120592612111</v>
+        <v>0.828120592612125</v>
       </c>
       <c r="E283" t="n">
         <v>0.500086251509401</v>
@@ -7884,19 +7884,19 @@
         <v>0.0000000803629990428076</v>
       </c>
       <c r="D284" t="n">
-        <v>1.54675753496284</v>
+        <v>1.54675753496286</v>
       </c>
       <c r="E284" t="n">
         <v>0.773804920509488</v>
       </c>
       <c r="F284" t="n">
-        <v>0.962758696949949</v>
+        <v>0.96275869694997</v>
       </c>
       <c r="G284" t="n">
         <v>0.629573762540817</v>
       </c>
       <c r="H284" t="n">
-        <v>0.904325341325219</v>
+        <v>0.904325341325206</v>
       </c>
     </row>
     <row r="285">
@@ -7988,7 +7988,7 @@
         <v>1</v>
       </c>
       <c r="D288" t="n">
-        <v>1.07277018937874</v>
+        <v>1.07277018937875</v>
       </c>
       <c r="E288" t="n">
         <v>1</v>
@@ -8092,7 +8092,7 @@
         <v>0.617181940143263</v>
       </c>
       <c r="D292" t="n">
-        <v>0.755741804918703</v>
+        <v>0.755741804918702</v>
       </c>
       <c r="E292" t="n">
         <v>1</v>
@@ -8144,19 +8144,19 @@
         <v>0.493818878329515</v>
       </c>
       <c r="D294" t="n">
-        <v>1.02237237402863</v>
+        <v>1.02237237402864</v>
       </c>
       <c r="E294" t="n">
         <v>0.236057050876257</v>
       </c>
       <c r="F294" t="n">
-        <v>0.902806889447534</v>
+        <v>0.902806889447588</v>
       </c>
       <c r="G294" t="n">
         <v>0.557113602714613</v>
       </c>
       <c r="H294" t="n">
-        <v>1.08927490466639</v>
+        <v>1.08927490466643</v>
       </c>
     </row>
     <row r="295">
@@ -8170,19 +8170,19 @@
         <v>0.0000000000048061921721538</v>
       </c>
       <c r="D295" t="n">
-        <v>1.41567538611107</v>
+        <v>1.41567538611108</v>
       </c>
       <c r="E295" t="n">
         <v>0.353297241126476</v>
       </c>
       <c r="F295" t="n">
-        <v>1.05244949150708</v>
+        <v>1.05244949150709</v>
       </c>
       <c r="G295" t="n">
-        <v>0.00430017622572883</v>
+        <v>0.00430017622572884</v>
       </c>
       <c r="H295" t="n">
-        <v>0.77230070660207</v>
+        <v>0.772300706602079</v>
       </c>
     </row>
     <row r="296">
@@ -8202,7 +8202,7 @@
         <v>0.863872819187571</v>
       </c>
       <c r="F296" t="n">
-        <v>0.901611937325632</v>
+        <v>0.901611937325648</v>
       </c>
       <c r="G296" t="n">
         <v>0.783194493973614</v>
@@ -8222,19 +8222,19 @@
         <v>0.0459884059183643</v>
       </c>
       <c r="D297" t="n">
-        <v>0.855112820345101</v>
+        <v>0.855112820345086</v>
       </c>
       <c r="E297" t="n">
-        <v>0.441957351580526</v>
+        <v>0.441957351580527</v>
       </c>
       <c r="F297" t="n">
-        <v>1.20199068287656</v>
+        <v>1.2019906828766</v>
       </c>
       <c r="G297" t="n">
         <v>0.490511946139288</v>
       </c>
       <c r="H297" t="n">
-        <v>1.33211961156568</v>
+        <v>1.33211961156556</v>
       </c>
     </row>
     <row r="298">
@@ -8248,7 +8248,7 @@
         <v>0.654991674141241</v>
       </c>
       <c r="D298" t="n">
-        <v>1.30531503903083</v>
+        <v>1.30531503903082</v>
       </c>
       <c r="E298" t="n">
         <v>1</v>
@@ -8297,22 +8297,22 @@
         <v>33</v>
       </c>
       <c r="C300" t="n">
-        <v>0.000982461211796802</v>
+        <v>0.0009824612117968</v>
       </c>
       <c r="D300" t="n">
-        <v>0.778445353329401</v>
+        <v>0.77844535332942</v>
       </c>
       <c r="E300" t="n">
         <v>0.0399914909024082</v>
       </c>
       <c r="F300" t="n">
-        <v>0.836856017897913</v>
+        <v>0.836856017897917</v>
       </c>
       <c r="G300" t="n">
         <v>0.319621138008038</v>
       </c>
       <c r="H300" t="n">
-        <v>0.885736839890923</v>
+        <v>0.885736839890903</v>
       </c>
     </row>
     <row r="301">
@@ -8326,19 +8326,19 @@
         <v>0.846440441502443</v>
       </c>
       <c r="D301" t="n">
-        <v>0.98112673245506</v>
+        <v>0.981126732455036</v>
       </c>
       <c r="E301" t="n">
         <v>0.0827659053233949</v>
       </c>
       <c r="F301" t="n">
-        <v>1.29126652206433</v>
+        <v>1.29126652206436</v>
       </c>
       <c r="G301" t="n">
         <v>0.138098902383187</v>
       </c>
       <c r="H301" t="n">
-        <v>0.717150842284628</v>
+        <v>0.717150842284626</v>
       </c>
     </row>
     <row r="302">
@@ -8352,7 +8352,7 @@
         <v>0.85069596711411</v>
       </c>
       <c r="D302" t="n">
-        <v>1.08136638608985</v>
+        <v>1.08136638608986</v>
       </c>
       <c r="E302" t="n">
         <v>1</v>
@@ -8534,19 +8534,19 @@
         <v>0.00000000125607225609493</v>
       </c>
       <c r="D309" t="n">
-        <v>1.172681001387</v>
+        <v>1.17268100138696</v>
       </c>
       <c r="E309" t="n">
-        <v>0.000921366127063592</v>
+        <v>0.000921366127063594</v>
       </c>
       <c r="F309" t="n">
-        <v>0.917252933642482</v>
+        <v>0.917252933642525</v>
       </c>
       <c r="G309" t="n">
         <v>0.171259845620753</v>
       </c>
       <c r="H309" t="n">
-        <v>1.0584053049606</v>
+        <v>1.05840530496062</v>
       </c>
     </row>
     <row r="310">
@@ -8557,22 +8557,22 @@
         <v>9</v>
       </c>
       <c r="C310" t="n">
-        <v>7.06726693379372e-256</v>
+        <v>7.06726693379373e-256</v>
       </c>
       <c r="D310" t="n">
-        <v>1.3202889040181</v>
+        <v>1.320288904018</v>
       </c>
       <c r="E310" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000161898217583247</v>
       </c>
       <c r="F310" t="n">
-        <v>0.85672590079835</v>
+        <v>0.856725900798483</v>
       </c>
       <c r="G310" t="n">
-        <v>0.00909266189179171</v>
+        <v>0.00909266189179172</v>
       </c>
       <c r="H310" t="n">
-        <v>1.03717417247458</v>
+        <v>1.03717417247453</v>
       </c>
     </row>
     <row r="311">
@@ -8583,22 +8583,22 @@
         <v>10</v>
       </c>
       <c r="C311" t="n">
-        <v>0.0596002753801625</v>
+        <v>0.0596002753801624</v>
       </c>
       <c r="D311" t="n">
-        <v>0.976234309274223</v>
+        <v>0.976234309274303</v>
       </c>
       <c r="E311" t="n">
-        <v>0.307065360836037</v>
+        <v>0.307065360836038</v>
       </c>
       <c r="F311" t="n">
-        <v>0.986746158639603</v>
+        <v>0.986746158639559</v>
       </c>
       <c r="G311" t="n">
         <v>0.00124188523619531</v>
       </c>
       <c r="H311" t="n">
-        <v>1.06514515240897</v>
+        <v>1.06514515240891</v>
       </c>
     </row>
     <row r="312">
@@ -8615,16 +8615,16 @@
         <v>1.29734268254593</v>
       </c>
       <c r="E312" t="n">
-        <v>0.690115507615005</v>
+        <v>0.690115507615003</v>
       </c>
       <c r="F312" t="n">
-        <v>0.994979252339986</v>
+        <v>0.994979252339997</v>
       </c>
       <c r="G312" t="n">
         <v>0.00102889798860952</v>
       </c>
       <c r="H312" t="n">
-        <v>0.937401067276942</v>
+        <v>0.937401067276957</v>
       </c>
     </row>
     <row r="313">
@@ -8661,22 +8661,22 @@
         <v>13</v>
       </c>
       <c r="C314" t="n">
-        <v>0.000000000000000000943972502814583</v>
+        <v>0.000000000000000000943972502814581</v>
       </c>
       <c r="D314" t="n">
-        <v>0.933213316211194</v>
+        <v>0.93321331621118</v>
       </c>
       <c r="E314" t="n">
         <v>0.167874174685225</v>
       </c>
       <c r="F314" t="n">
-        <v>1.0134141423918</v>
+        <v>1.01341414239189</v>
       </c>
       <c r="G314" t="n">
         <v>0.00218861503946825</v>
       </c>
       <c r="H314" t="n">
-        <v>1.04557466464386</v>
+        <v>1.04557466464388</v>
       </c>
     </row>
     <row r="315">
@@ -8690,19 +8690,19 @@
         <v>0.000525169227363778</v>
       </c>
       <c r="D315" t="n">
-        <v>1.13130857888491</v>
+        <v>1.1313085788849</v>
       </c>
       <c r="E315" t="n">
-        <v>0.712763485922793</v>
+        <v>0.712763485922792</v>
       </c>
       <c r="F315" t="n">
-        <v>1.05382856035138</v>
+        <v>1.05382856035141</v>
       </c>
       <c r="G315" t="n">
         <v>0.0853218831142667</v>
       </c>
       <c r="H315" t="n">
-        <v>0.712174923072751</v>
+        <v>0.712174923072744</v>
       </c>
     </row>
     <row r="316">
@@ -8716,19 +8716,19 @@
         <v>0.843425777585995</v>
       </c>
       <c r="D316" t="n">
-        <v>1.01739143492994</v>
+        <v>1.01739143492997</v>
       </c>
       <c r="E316" t="n">
         <v>1</v>
       </c>
       <c r="F316" t="n">
-        <v>0.999709503180625</v>
+        <v>0.999709503180628</v>
       </c>
       <c r="G316" t="n">
         <v>0.353506081901131</v>
       </c>
       <c r="H316" t="n">
-        <v>1.11762600656814</v>
+        <v>1.11762600656817</v>
       </c>
     </row>
     <row r="317">
@@ -8742,19 +8742,19 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000805176082866219</v>
       </c>
       <c r="D317" t="n">
-        <v>0.651944935420076</v>
+        <v>0.651944935420086</v>
       </c>
       <c r="E317" t="n">
         <v>0.333264737385609</v>
       </c>
       <c r="F317" t="n">
-        <v>0.816581097206339</v>
+        <v>0.816581097206224</v>
       </c>
       <c r="G317" t="n">
         <v>0.783088464488255</v>
       </c>
       <c r="H317" t="n">
-        <v>0.916874689075302</v>
+        <v>0.916874689075391</v>
       </c>
     </row>
     <row r="318">
@@ -8765,22 +8765,22 @@
         <v>17</v>
       </c>
       <c r="C318" t="n">
-        <v>0.00000000895003606732089</v>
+        <v>0.0000000089500360673209</v>
       </c>
       <c r="D318" t="n">
-        <v>1.29808099537436</v>
+        <v>1.29808099537434</v>
       </c>
       <c r="E318" t="n">
         <v>0.133655581815413</v>
       </c>
       <c r="F318" t="n">
-        <v>1.07540254501381</v>
+        <v>1.07540254501382</v>
       </c>
       <c r="G318" t="n">
         <v>0.0699565150866549</v>
       </c>
       <c r="H318" t="n">
-        <v>0.866538764720781</v>
+        <v>0.866538764720786</v>
       </c>
     </row>
     <row r="319">
@@ -8924,19 +8924,19 @@
         <v>0.00116023107792924</v>
       </c>
       <c r="D324" t="n">
-        <v>1.60808801987466</v>
+        <v>1.60808801987465</v>
       </c>
       <c r="E324" t="n">
         <v>0.484195001590464</v>
       </c>
       <c r="F324" t="n">
-        <v>1.10643464305908</v>
+        <v>1.10643464305907</v>
       </c>
       <c r="G324" t="n">
         <v>0.906346019409805</v>
       </c>
       <c r="H324" t="n">
-        <v>1.05044768266443</v>
+        <v>1.05044768266442</v>
       </c>
     </row>
     <row r="325">
@@ -9028,19 +9028,19 @@
         <v>0.130335039040392</v>
       </c>
       <c r="D328" t="n">
-        <v>1.07286100590523</v>
+        <v>1.07286100590521</v>
       </c>
       <c r="E328" t="n">
         <v>0.0570817556651875</v>
       </c>
       <c r="F328" t="n">
-        <v>0.754109473941711</v>
+        <v>0.754109473941729</v>
       </c>
       <c r="G328" t="n">
         <v>0.383514158719175</v>
       </c>
       <c r="H328" t="n">
-        <v>0.792223450236678</v>
+        <v>0.792223450236672</v>
       </c>
     </row>
     <row r="329">
@@ -9054,19 +9054,19 @@
         <v>0.00192210751826613</v>
       </c>
       <c r="D329" t="n">
-        <v>1.19991673503976</v>
+        <v>1.19991673503975</v>
       </c>
       <c r="E329" t="n">
         <v>0.557910513157528</v>
       </c>
       <c r="F329" t="n">
-        <v>1.04084497571409</v>
+        <v>1.04084497571407</v>
       </c>
       <c r="G329" t="n">
-        <v>0.040557964983038</v>
+        <v>0.0405579649830379</v>
       </c>
       <c r="H329" t="n">
-        <v>0.807818228670313</v>
+        <v>0.807818228670297</v>
       </c>
     </row>
     <row r="330">
@@ -9086,13 +9086,13 @@
         <v>0.933990986714612</v>
       </c>
       <c r="F330" t="n">
-        <v>1.02442142697264</v>
+        <v>1.02442142697263</v>
       </c>
       <c r="G330" t="n">
         <v>0.698690882536434</v>
       </c>
       <c r="H330" t="n">
-        <v>0.884063616398993</v>
+        <v>0.884063616399003</v>
       </c>
     </row>
     <row r="331">
@@ -9103,22 +9103,22 @@
         <v>30</v>
       </c>
       <c r="C331" t="n">
-        <v>0.448465740460735</v>
+        <v>0.448465740460734</v>
       </c>
       <c r="D331" t="n">
-        <v>0.987626115505756</v>
+        <v>0.987626115505769</v>
       </c>
       <c r="E331" t="n">
         <v>0.0162080432636543</v>
       </c>
       <c r="F331" t="n">
-        <v>1.05055108388735</v>
+        <v>1.05055108388731</v>
       </c>
       <c r="G331" t="n">
-        <v>0.139622271945968</v>
+        <v>0.139622271945969</v>
       </c>
       <c r="H331" t="n">
-        <v>0.95410573035652</v>
+        <v>0.954105730356541</v>
       </c>
     </row>
     <row r="332">
@@ -9184,19 +9184,19 @@
         <v>0.013546491518947</v>
       </c>
       <c r="D334" t="n">
-        <v>0.754973399405236</v>
+        <v>0.754973399405231</v>
       </c>
       <c r="E334" t="n">
-        <v>0.894616848401941</v>
+        <v>0.89461684840194</v>
       </c>
       <c r="F334" t="n">
-        <v>1.02576620258867</v>
+        <v>1.02576620258866</v>
       </c>
       <c r="G334" t="n">
         <v>0.122439802945368</v>
       </c>
       <c r="H334" t="n">
-        <v>0.751911625110159</v>
+        <v>0.751911625110153</v>
       </c>
     </row>
     <row r="335">
@@ -9210,13 +9210,13 @@
         <v>0.0878144213262931</v>
       </c>
       <c r="D335" t="n">
-        <v>0.667260564889156</v>
+        <v>0.667260564889154</v>
       </c>
       <c r="E335" t="n">
         <v>0.308109054073072</v>
       </c>
       <c r="F335" t="n">
-        <v>1.96812832199368</v>
+        <v>1.96812832199367</v>
       </c>
       <c r="G335" t="n">
         <v>0.280005448545813</v>
@@ -9236,19 +9236,19 @@
         <v>0.00317429827749223</v>
       </c>
       <c r="D336" t="n">
-        <v>1.43046966493108</v>
+        <v>1.43046966493106</v>
       </c>
       <c r="E336" t="n">
         <v>0.23985360955124</v>
       </c>
       <c r="F336" t="n">
-        <v>0.866771634551915</v>
+        <v>0.866771634551908</v>
       </c>
       <c r="G336" t="n">
         <v>0.212472676732053</v>
       </c>
       <c r="H336" t="n">
-        <v>1.277690117703</v>
+        <v>1.27769011770299</v>
       </c>
     </row>
     <row r="337">
@@ -9418,19 +9418,19 @@
         <v>0.0000533072250664203</v>
       </c>
       <c r="D343" t="n">
-        <v>1.09209221916405</v>
+        <v>1.09209221916401</v>
       </c>
       <c r="E343" t="n">
         <v>0.000816512499930141</v>
       </c>
       <c r="F343" t="n">
-        <v>0.929910238071079</v>
+        <v>0.929910238071065</v>
       </c>
       <c r="G343" t="n">
         <v>0.00192499612195019</v>
       </c>
       <c r="H343" t="n">
-        <v>1.1096581960135</v>
+        <v>1.10965819601351</v>
       </c>
     </row>
     <row r="344">
@@ -9444,19 +9444,19 @@
         <v>0</v>
       </c>
       <c r="D344" t="n">
-        <v>1.35808046262954</v>
+        <v>1.35808046262955</v>
       </c>
       <c r="E344" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000238892880114623</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000238892880114622</v>
       </c>
       <c r="F344" t="n">
-        <v>0.866876775868861</v>
+        <v>0.86687677586886</v>
       </c>
       <c r="G344" t="n">
-        <v>0.00072013864927522</v>
+        <v>0.000720138649275221</v>
       </c>
       <c r="H344" t="n">
-        <v>1.03703114956794</v>
+        <v>1.03703114956789</v>
       </c>
     </row>
     <row r="345">
@@ -9470,19 +9470,19 @@
         <v>0.00000000195097858005009</v>
       </c>
       <c r="D345" t="n">
-        <v>1.02678923677415</v>
+        <v>1.02678923677419</v>
       </c>
       <c r="E345" t="n">
-        <v>0.205734494291135</v>
+        <v>0.205734494291134</v>
       </c>
       <c r="F345" t="n">
-        <v>0.994296612184518</v>
+        <v>0.994296612184484</v>
       </c>
       <c r="G345" t="n">
-        <v>0.0145503794848779</v>
+        <v>0.0145503794848778</v>
       </c>
       <c r="H345" t="n">
-        <v>1.01682446382731</v>
+        <v>1.01682446382729</v>
       </c>
     </row>
     <row r="346">
@@ -9496,19 +9496,19 @@
         <v>0</v>
       </c>
       <c r="D346" t="n">
-        <v>1.70817075781956</v>
+        <v>1.70817075781951</v>
       </c>
       <c r="E346" t="n">
-        <v>0.00887202568961816</v>
+        <v>0.00887202568961815</v>
       </c>
       <c r="F346" t="n">
-        <v>1.00751876100637</v>
+        <v>1.0075187610064</v>
       </c>
       <c r="G346" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000132596177840102</v>
       </c>
       <c r="H346" t="n">
-        <v>0.890478135443066</v>
+        <v>0.89047813544312</v>
       </c>
     </row>
     <row r="347">
@@ -9522,7 +9522,7 @@
         <v>0.00000000739456866228772</v>
       </c>
       <c r="D347" t="n">
-        <v>0.855553311641642</v>
+        <v>0.855553311641636</v>
       </c>
       <c r="E347" t="n">
         <v>0.727430769452905</v>
@@ -9534,7 +9534,7 @@
         <v>0.399259198788655</v>
       </c>
       <c r="H347" t="n">
-        <v>0.945988624556229</v>
+        <v>0.94598862455622</v>
       </c>
     </row>
     <row r="348">
@@ -9548,19 +9548,19 @@
         <v>0.000000157745338657572</v>
       </c>
       <c r="D348" t="n">
-        <v>1.08629611716627</v>
+        <v>1.0862961171662</v>
       </c>
       <c r="E348" t="n">
-        <v>0.0587356346865672</v>
+        <v>0.0587356346865673</v>
       </c>
       <c r="F348" t="n">
-        <v>0.961413458966588</v>
+        <v>0.961413458966569</v>
       </c>
       <c r="G348" t="n">
-        <v>0.0220023419128867</v>
+        <v>0.0220023419128868</v>
       </c>
       <c r="H348" t="n">
-        <v>1.07818260159306</v>
+        <v>1.07818260159312</v>
       </c>
     </row>
     <row r="349">
@@ -9574,10 +9574,10 @@
         <v>0.00000000000000000000003799443298929</v>
       </c>
       <c r="D349" t="n">
-        <v>1.18138210955583</v>
+        <v>1.18138210955578</v>
       </c>
       <c r="E349" t="n">
-        <v>0.242028868546842</v>
+        <v>0.242028868546841</v>
       </c>
       <c r="F349" t="n">
         <v>1.07173696071755</v>
@@ -9586,7 +9586,7 @@
         <v>0.479982164240481</v>
       </c>
       <c r="H349" t="n">
-        <v>0.934373603216631</v>
+        <v>0.93437360321664</v>
       </c>
     </row>
     <row r="350">
@@ -9600,19 +9600,19 @@
         <v>0.00237964654461392</v>
       </c>
       <c r="D350" t="n">
-        <v>1.15749246161784</v>
+        <v>1.15749246161785</v>
       </c>
       <c r="E350" t="n">
         <v>0.0520772932484878</v>
       </c>
       <c r="F350" t="n">
-        <v>0.91087030306425</v>
+        <v>0.910870303064252</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>0.997965928185063</v>
+        <v>0.997965928185072</v>
       </c>
     </row>
     <row r="351">
@@ -9626,7 +9626,7 @@
         <v>0.00000000000200965241067933</v>
       </c>
       <c r="D351" t="n">
-        <v>0.850594319032734</v>
+        <v>0.850594319032757</v>
       </c>
       <c r="E351" t="n">
         <v>0.167510888604687</v>
@@ -9638,7 +9638,7 @@
         <v>0.79374094286667</v>
       </c>
       <c r="H351" t="n">
-        <v>1.08188080723493</v>
+        <v>1.08188080723499</v>
       </c>
     </row>
     <row r="352">
@@ -9652,19 +9652,19 @@
         <v>0.00000000000000000000000000000000000000000000000000000012858230340037</v>
       </c>
       <c r="D352" t="n">
-        <v>1.30165426002496</v>
+        <v>1.30165426002499</v>
       </c>
       <c r="E352" t="n">
-        <v>0.87624735323376</v>
+        <v>0.876247353233758</v>
       </c>
       <c r="F352" t="n">
-        <v>1.00322347542088</v>
+        <v>1.00322347542085</v>
       </c>
       <c r="G352" t="n">
         <v>0.0107309700900521</v>
       </c>
       <c r="H352" t="n">
-        <v>0.920812397415381</v>
+        <v>0.92081239741537</v>
       </c>
     </row>
     <row r="353">
@@ -9678,19 +9678,19 @@
         <v>0.558166893755108</v>
       </c>
       <c r="D353" t="n">
-        <v>1.09491397088544</v>
+        <v>1.09491397088542</v>
       </c>
       <c r="E353" t="n">
         <v>0.451526406697387</v>
       </c>
       <c r="F353" t="n">
-        <v>0.702407006440575</v>
+        <v>0.702407006440578</v>
       </c>
       <c r="G353" t="n">
         <v>1</v>
       </c>
       <c r="H353" t="n">
-        <v>0.939543228526059</v>
+        <v>0.93954322852608</v>
       </c>
     </row>
     <row r="354">
@@ -9730,13 +9730,13 @@
         <v>0.22161402927911</v>
       </c>
       <c r="D355" t="n">
-        <v>4.24139570496305</v>
+        <v>4.24139570496304</v>
       </c>
       <c r="E355" t="n">
         <v>1</v>
       </c>
       <c r="F355" t="n">
-        <v>0.87227949827013</v>
+        <v>0.872279498270126</v>
       </c>
       <c r="G355" t="n">
         <v>1</v>
@@ -9779,22 +9779,22 @@
         <v>22</v>
       </c>
       <c r="C357" t="n">
-        <v>0.000000000814805833965158</v>
+        <v>0.00000000081480583396515</v>
       </c>
       <c r="D357" t="n">
-        <v>1.81380248632775</v>
+        <v>1.81380248632776</v>
       </c>
       <c r="E357" t="n">
-        <v>0.0764507928657411</v>
+        <v>0.0764507928657412</v>
       </c>
       <c r="F357" t="n">
-        <v>0.842427027351717</v>
+        <v>0.842427027351737</v>
       </c>
       <c r="G357" t="n">
-        <v>0.00472352324347412</v>
+        <v>0.00472352324347413</v>
       </c>
       <c r="H357" t="n">
-        <v>0.605560345873553</v>
+        <v>0.60556034587355</v>
       </c>
     </row>
     <row r="358">
@@ -9860,19 +9860,19 @@
         <v>0.648730126249955</v>
       </c>
       <c r="D360" t="n">
-        <v>1.04836957839036</v>
+        <v>1.04836957839035</v>
       </c>
       <c r="E360" t="n">
-        <v>0.722460537136872</v>
+        <v>0.722460537136873</v>
       </c>
       <c r="F360" t="n">
-        <v>0.927848355948467</v>
+        <v>0.927848355948479</v>
       </c>
       <c r="G360" t="n">
         <v>0.351473030914783</v>
       </c>
       <c r="H360" t="n">
-        <v>1.32438196439141</v>
+        <v>1.3243819643914</v>
       </c>
     </row>
     <row r="361">
@@ -9909,22 +9909,22 @@
         <v>27</v>
       </c>
       <c r="C362" t="n">
-        <v>0.00000203356726260154</v>
+        <v>0.00000203356726260155</v>
       </c>
       <c r="D362" t="n">
-        <v>1.07110073482337</v>
+        <v>1.07110073482335</v>
       </c>
       <c r="E362" t="n">
         <v>0.00257855831035319</v>
       </c>
       <c r="F362" t="n">
-        <v>0.894227511494853</v>
+        <v>0.894227511494957</v>
       </c>
       <c r="G362" t="n">
         <v>0.18258549137724</v>
       </c>
       <c r="H362" t="n">
-        <v>0.925073968152191</v>
+        <v>0.925073968152364</v>
       </c>
     </row>
     <row r="363">
@@ -9938,19 +9938,19 @@
         <v>0.0984497179926531</v>
       </c>
       <c r="D363" t="n">
-        <v>0.681693486472194</v>
+        <v>0.681693486472197</v>
       </c>
       <c r="E363" t="n">
         <v>0.103588378498975</v>
       </c>
       <c r="F363" t="n">
-        <v>0.678929815197521</v>
+        <v>0.678929815197517</v>
       </c>
       <c r="G363" t="n">
         <v>0.0591565048189389</v>
       </c>
       <c r="H363" t="n">
-        <v>1.86564151150233</v>
+        <v>1.86564151150232</v>
       </c>
     </row>
     <row r="364">
@@ -9964,19 +9964,19 @@
         <v>0.144932132077307</v>
       </c>
       <c r="D364" t="n">
-        <v>1.10857251961053</v>
+        <v>1.10857251961049</v>
       </c>
       <c r="E364" t="n">
         <v>0.0667984957159152</v>
       </c>
       <c r="F364" t="n">
-        <v>1.22301363146792</v>
+        <v>1.22301363146793</v>
       </c>
       <c r="G364" t="n">
         <v>0.869828864677171</v>
       </c>
       <c r="H364" t="n">
-        <v>1.03062121554246</v>
+        <v>1.03062121554247</v>
       </c>
     </row>
     <row r="365">
@@ -9990,19 +9990,19 @@
         <v>0.678578105265114</v>
       </c>
       <c r="D365" t="n">
-        <v>1.00691136068976</v>
+        <v>1.00691136068984</v>
       </c>
       <c r="E365" t="n">
-        <v>0.00237354474381378</v>
+        <v>0.00237354474381379</v>
       </c>
       <c r="F365" t="n">
-        <v>0.932888703998234</v>
+        <v>0.932888703998237</v>
       </c>
       <c r="G365" t="n">
         <v>0.0386984157415463</v>
       </c>
       <c r="H365" t="n">
-        <v>1.07604286876477</v>
+        <v>1.07604286876475</v>
       </c>
     </row>
     <row r="366">
@@ -10039,22 +10039,22 @@
         <v>32</v>
       </c>
       <c r="C367" t="n">
-        <v>0.0906541213832261</v>
+        <v>0.0906541213832262</v>
       </c>
       <c r="D367" t="n">
-        <v>1.21851853741296</v>
+        <v>1.21851853741295</v>
       </c>
       <c r="E367" t="n">
         <v>0.0708790301351725</v>
       </c>
       <c r="F367" t="n">
-        <v>1.2624045280936</v>
+        <v>1.26240452809362</v>
       </c>
       <c r="G367" t="n">
         <v>0.299685379822696</v>
       </c>
       <c r="H367" t="n">
-        <v>0.818324068466714</v>
+        <v>0.818324068466709</v>
       </c>
     </row>
     <row r="368">
@@ -10068,19 +10068,19 @@
         <v>0.000078841985055033</v>
       </c>
       <c r="D368" t="n">
-        <v>0.834827732742547</v>
+        <v>0.834827732742584</v>
       </c>
       <c r="E368" t="n">
         <v>0.289532158862791</v>
       </c>
       <c r="F368" t="n">
-        <v>0.944856519227677</v>
+        <v>0.944856519227667</v>
       </c>
       <c r="G368" t="n">
         <v>0.688300548405949</v>
       </c>
       <c r="H368" t="n">
-        <v>1.03104914411207</v>
+        <v>1.03104914411208</v>
       </c>
     </row>
     <row r="369">
@@ -10094,7 +10094,7 @@
         <v>0.0770584535412093</v>
       </c>
       <c r="D369" t="n">
-        <v>0.918453241227185</v>
+        <v>0.918453241227187</v>
       </c>
       <c r="E369" t="n">
         <v>0.0319791442845163</v>
@@ -10106,7 +10106,7 @@
         <v>0.00156874874797794</v>
       </c>
       <c r="H369" t="n">
-        <v>0.681964372936638</v>
+        <v>0.681964372936642</v>
       </c>
     </row>
     <row r="370">
@@ -10120,10 +10120,10 @@
         <v>0.000232809328576567</v>
       </c>
       <c r="D370" t="n">
-        <v>1.19961509430479</v>
+        <v>1.19961509430482</v>
       </c>
       <c r="E370" t="n">
-        <v>0.575210971392425</v>
+        <v>0.575210971392424</v>
       </c>
       <c r="F370" t="n">
         <v>0.97020455673346</v>
@@ -10132,7 +10132,7 @@
         <v>0.0000169635747340395</v>
       </c>
       <c r="H370" t="n">
-        <v>1.44294287137583</v>
+        <v>1.44294287137584</v>
       </c>
     </row>
     <row r="371">
@@ -10172,19 +10172,19 @@
         <v>0.814324585867092</v>
       </c>
       <c r="D372" t="n">
-        <v>1.14721684072621</v>
+        <v>1.1472168407262</v>
       </c>
       <c r="E372" t="n">
         <v>1</v>
       </c>
       <c r="F372" t="n">
-        <v>0.89147209997684</v>
+        <v>0.891472099976845</v>
       </c>
       <c r="G372" t="n">
         <v>1</v>
       </c>
       <c r="H372" t="n">
-        <v>0.978474053713582</v>
+        <v>0.978474053713585</v>
       </c>
     </row>
     <row r="373">
@@ -10204,13 +10204,13 @@
         <v>1</v>
       </c>
       <c r="F373" t="n">
-        <v>1.13801896043108</v>
+        <v>1.13801896043104</v>
       </c>
       <c r="G373" t="n">
         <v>0.40828266902063</v>
       </c>
       <c r="H373" t="n">
-        <v>0.466142590591957</v>
+        <v>0.466142590591944</v>
       </c>
     </row>
     <row r="374">
@@ -10250,19 +10250,19 @@
         <v>0.246496502519224</v>
       </c>
       <c r="D375" t="n">
-        <v>0.708930767373956</v>
+        <v>0.708930767373949</v>
       </c>
       <c r="E375" t="n">
         <v>0.555493269513561</v>
       </c>
       <c r="F375" t="n">
-        <v>0.821234143476221</v>
+        <v>0.82123414347622</v>
       </c>
       <c r="G375" t="n">
         <v>0.241187886295241</v>
       </c>
       <c r="H375" t="n">
-        <v>0.608456881413815</v>
+        <v>0.608456881413813</v>
       </c>
     </row>
     <row r="376">
@@ -10276,7 +10276,7 @@
         <v>0.463263422261338</v>
       </c>
       <c r="D376" t="n">
-        <v>0.481238196664896</v>
+        <v>0.481238196664897</v>
       </c>
       <c r="E376" t="n">
         <v>0.505107252298264</v>
@@ -10302,19 +10302,19 @@
         <v>9.3072554780677e-206</v>
       </c>
       <c r="D377" t="n">
-        <v>1.30625832971766</v>
+        <v>1.30625832971755</v>
       </c>
       <c r="E377" t="n">
         <v>0.000000000000000296612166511416</v>
       </c>
       <c r="F377" t="n">
-        <v>0.931499380992958</v>
+        <v>0.931499380992996</v>
       </c>
       <c r="G377" t="n">
-        <v>0.0848787576447024</v>
+        <v>0.0848787576447022</v>
       </c>
       <c r="H377" t="n">
-        <v>1.02461842743179</v>
+        <v>1.02461842743173</v>
       </c>
     </row>
     <row r="378">
@@ -10334,7 +10334,7 @@
         <v>0.00000000000000000000000000000332827878494898</v>
       </c>
       <c r="F378" t="n">
-        <v>0.849889177915328</v>
+        <v>0.849889177915296</v>
       </c>
       <c r="G378" t="n">
         <v>0.732444630582304</v>
@@ -10354,19 +10354,19 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000807753475962727</v>
       </c>
       <c r="D379" t="n">
-        <v>1.299377533694</v>
+        <v>1.29937753369394</v>
       </c>
       <c r="E379" t="n">
-        <v>0.00000887726447973414</v>
+        <v>0.00000887726447973413</v>
       </c>
       <c r="F379" t="n">
-        <v>1.07033363418282</v>
+        <v>1.07033363418279</v>
       </c>
       <c r="G379" t="n">
         <v>0.430232880068204</v>
       </c>
       <c r="H379" t="n">
-        <v>0.980751689800082</v>
+        <v>0.980751689800109</v>
       </c>
     </row>
     <row r="380">
@@ -10380,7 +10380,7 @@
         <v>0.438265116539626</v>
       </c>
       <c r="D380" t="n">
-        <v>0.626415790856432</v>
+        <v>0.626415790856428</v>
       </c>
       <c r="E380" t="n">
         <v>1</v>
@@ -10412,13 +10412,13 @@
         <v>0.241530421445548</v>
       </c>
       <c r="F381" t="n">
-        <v>0.786142306333655</v>
+        <v>0.786142306333665</v>
       </c>
       <c r="G381" t="n">
         <v>0.880776720762511</v>
       </c>
       <c r="H381" t="n">
-        <v>1.07153749835065</v>
+        <v>1.07153749835063</v>
       </c>
     </row>
     <row r="382">
@@ -10429,7 +10429,7 @@
         <v>13</v>
       </c>
       <c r="C382" t="n">
-        <v>0.000000000661711217167799</v>
+        <v>0.0000000006617112171678</v>
       </c>
       <c r="D382" t="n">
         <v>1.23323267949231</v>
@@ -10438,13 +10438,13 @@
         <v>0.024824248277967</v>
       </c>
       <c r="F382" t="n">
-        <v>0.89653856206413</v>
+        <v>0.896538562064155</v>
       </c>
       <c r="G382" t="n">
         <v>0.783423892915452</v>
       </c>
       <c r="H382" t="n">
-        <v>0.977815759484882</v>
+        <v>0.97781575948491</v>
       </c>
     </row>
     <row r="383">
@@ -10458,19 +10458,19 @@
         <v>0.000000436296482621577</v>
       </c>
       <c r="D383" t="n">
-        <v>1.28859887105495</v>
+        <v>1.28859887105492</v>
       </c>
       <c r="E383" t="n">
-        <v>0.539385704910576</v>
+        <v>0.539385704910575</v>
       </c>
       <c r="F383" t="n">
-        <v>0.866560339608658</v>
+        <v>0.866560339608675</v>
       </c>
       <c r="G383" t="n">
-        <v>0.726035685287666</v>
+        <v>0.726035685287667</v>
       </c>
       <c r="H383" t="n">
-        <v>0.861679660643633</v>
+        <v>0.861679660643661</v>
       </c>
     </row>
     <row r="384">
@@ -10507,10 +10507,10 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>0.043294395565053</v>
+        <v>0.0432943955650529</v>
       </c>
       <c r="D385" t="n">
-        <v>0.582169471990497</v>
+        <v>0.582169471990498</v>
       </c>
       <c r="E385" t="n">
         <v>1</v>
@@ -10536,19 +10536,19 @@
         <v>0.00000000000000000000000105925524405868</v>
       </c>
       <c r="D386" t="n">
-        <v>1.33315453633928</v>
+        <v>1.33315453633925</v>
       </c>
       <c r="E386" t="n">
-        <v>0.901692649706517</v>
+        <v>0.901692649706519</v>
       </c>
       <c r="F386" t="n">
-        <v>0.99513990560664</v>
+        <v>0.995139905606652</v>
       </c>
       <c r="G386" t="n">
         <v>0.0894728267318022</v>
       </c>
       <c r="H386" t="n">
-        <v>0.904439152411747</v>
+        <v>0.904439152411765</v>
       </c>
     </row>
     <row r="387">
@@ -10562,7 +10562,7 @@
         <v>0.810398176804105</v>
       </c>
       <c r="D387" t="n">
-        <v>0.823318241035583</v>
+        <v>0.823318241035586</v>
       </c>
       <c r="E387" t="n">
         <v>1</v>
@@ -10637,22 +10637,22 @@
         <v>21</v>
       </c>
       <c r="C390" t="n">
-        <v>0.00000000198998706734726</v>
+        <v>0.00000000198998706734727</v>
       </c>
       <c r="D390" t="n">
         <v>1.71782755670066</v>
       </c>
       <c r="E390" t="n">
-        <v>0.115944610543624</v>
+        <v>0.115944610543623</v>
       </c>
       <c r="F390" t="n">
-        <v>0.855178058123995</v>
+        <v>0.855178058123991</v>
       </c>
       <c r="G390" t="n">
-        <v>0.382812784100712</v>
+        <v>0.382812784100713</v>
       </c>
       <c r="H390" t="n">
-        <v>1.17545500908198</v>
+        <v>1.17545500908199</v>
       </c>
     </row>
     <row r="391">
@@ -10770,19 +10770,19 @@
         <v>0.417758278653303</v>
       </c>
       <c r="D395" t="n">
-        <v>0.687427547020113</v>
+        <v>0.687427547020112</v>
       </c>
       <c r="E395" t="n">
         <v>0.608401326456237</v>
       </c>
       <c r="F395" t="n">
-        <v>0.681449031412846</v>
+        <v>0.681449031412838</v>
       </c>
       <c r="G395" t="n">
         <v>0.700040544112726</v>
       </c>
       <c r="H395" t="n">
-        <v>0.598014386915142</v>
+        <v>0.598014386915143</v>
       </c>
     </row>
     <row r="396">
@@ -10796,19 +10796,19 @@
         <v>0.0117086176927966</v>
       </c>
       <c r="D396" t="n">
-        <v>1.13180579770222</v>
+        <v>1.13180579770223</v>
       </c>
       <c r="E396" t="n">
-        <v>0.0865560349770776</v>
+        <v>0.0865560349770775</v>
       </c>
       <c r="F396" t="n">
-        <v>0.84789039104337</v>
+        <v>0.847890391043396</v>
       </c>
       <c r="G396" t="n">
-        <v>0.887194709720502</v>
+        <v>0.887194709720503</v>
       </c>
       <c r="H396" t="n">
-        <v>1.02946530184199</v>
+        <v>1.02946530184201</v>
       </c>
     </row>
     <row r="397">
@@ -10828,13 +10828,13 @@
         <v>0.63814363000128</v>
       </c>
       <c r="F397" t="n">
-        <v>0.933459504960395</v>
+        <v>0.93345950496037</v>
       </c>
       <c r="G397" t="n">
         <v>0.588263383005049</v>
       </c>
       <c r="H397" t="n">
-        <v>0.871934812142921</v>
+        <v>0.871934812142911</v>
       </c>
     </row>
     <row r="398">
@@ -10845,22 +10845,22 @@
         <v>29</v>
       </c>
       <c r="C398" t="n">
-        <v>0.00162731770069261</v>
+        <v>0.00162731770069262</v>
       </c>
       <c r="D398" t="n">
-        <v>1.5923712758541</v>
+        <v>1.59237127585409</v>
       </c>
       <c r="E398" t="n">
         <v>0.749709668825683</v>
       </c>
       <c r="F398" t="n">
-        <v>0.917602964566282</v>
+        <v>0.917602964566281</v>
       </c>
       <c r="G398" t="n">
         <v>1</v>
       </c>
       <c r="H398" t="n">
-        <v>1.04035597198681</v>
+        <v>1.04035597198682</v>
       </c>
     </row>
     <row r="399">
@@ -10874,19 +10874,19 @@
         <v>0.00105075438411023</v>
       </c>
       <c r="D399" t="n">
-        <v>1.28075099381781</v>
+        <v>1.2807509938178</v>
       </c>
       <c r="E399" t="n">
         <v>0.880178544032319</v>
       </c>
       <c r="F399" t="n">
-        <v>0.982915610675044</v>
+        <v>0.982915610675029</v>
       </c>
       <c r="G399" t="n">
         <v>0.568889484543604</v>
       </c>
       <c r="H399" t="n">
-        <v>0.908419647694885</v>
+        <v>0.908419647694889</v>
       </c>
     </row>
     <row r="400">
@@ -10926,7 +10926,7 @@
         <v>0.445367426800114</v>
       </c>
       <c r="D401" t="n">
-        <v>0.661788929903521</v>
+        <v>0.66178892990352</v>
       </c>
       <c r="E401" t="n">
         <v>0.437661702220807</v>
@@ -10938,7 +10938,7 @@
         <v>0.49922687834811</v>
       </c>
       <c r="H401" t="n">
-        <v>0.603960217000164</v>
+        <v>0.603960217000166</v>
       </c>
     </row>
     <row r="402">
@@ -10978,7 +10978,7 @@
         <v>0.305698649925127</v>
       </c>
       <c r="D403" t="n">
-        <v>1.20296337825152</v>
+        <v>1.20296337825153</v>
       </c>
       <c r="E403" t="n">
         <v>1</v>
@@ -11186,19 +11186,19 @@
         <v>0</v>
       </c>
       <c r="D411" t="n">
-        <v>1.55559273658947</v>
+        <v>1.55559273658959</v>
       </c>
       <c r="E411" t="n">
         <v>0.00000136079214061959</v>
       </c>
       <c r="F411" t="n">
-        <v>0.963192220162622</v>
+        <v>0.963192220162554</v>
       </c>
       <c r="G411" t="n">
         <v>0.598594693010736</v>
       </c>
       <c r="H411" t="n">
-        <v>0.992950644170675</v>
+        <v>0.992950644170598</v>
       </c>
     </row>
     <row r="412">
@@ -11209,22 +11209,22 @@
         <v>9</v>
       </c>
       <c r="C412" t="n">
-        <v>0.00000114262253015517</v>
+        <v>0.00000114262253015518</v>
       </c>
       <c r="D412" t="n">
-        <v>1.30530694377448</v>
+        <v>1.30530694377447</v>
       </c>
       <c r="E412" t="n">
         <v>0.0807269071901967</v>
       </c>
       <c r="F412" t="n">
-        <v>0.893793117176754</v>
+        <v>0.893793117176684</v>
       </c>
       <c r="G412" t="n">
         <v>0.305178784259319</v>
       </c>
       <c r="H412" t="n">
-        <v>1.11724749351</v>
+        <v>1.11724749351001</v>
       </c>
     </row>
     <row r="413">
@@ -11238,19 +11238,19 @@
         <v>0.0393259344669299</v>
       </c>
       <c r="D413" t="n">
-        <v>1.88964678275923</v>
+        <v>1.88964678275925</v>
       </c>
       <c r="E413" t="n">
         <v>0.801600959434612</v>
       </c>
       <c r="F413" t="n">
-        <v>0.805169230103232</v>
+        <v>0.805169230103222</v>
       </c>
       <c r="G413" t="n">
         <v>0.392898903525313</v>
       </c>
       <c r="H413" t="n">
-        <v>3.09588483675546</v>
+        <v>3.09588483675543</v>
       </c>
     </row>
     <row r="414">
@@ -11264,19 +11264,19 @@
         <v>0.0913599272357547</v>
       </c>
       <c r="D414" t="n">
-        <v>1.42232641320542</v>
+        <v>1.42232641320543</v>
       </c>
       <c r="E414" t="n">
         <v>0.38591931811081</v>
       </c>
       <c r="F414" t="n">
-        <v>1.39215891564084</v>
+        <v>1.39215891564082</v>
       </c>
       <c r="G414" t="n">
         <v>0.0120218745597768</v>
       </c>
       <c r="H414" t="n">
-        <v>4.55094802635426</v>
+        <v>4.55094802635434</v>
       </c>
     </row>
     <row r="415">
@@ -11290,7 +11290,7 @@
         <v>0.38680403414671</v>
       </c>
       <c r="D415" t="n">
-        <v>3.10248896777234</v>
+        <v>3.10248896777235</v>
       </c>
       <c r="E415" t="n">
         <v>1</v>
@@ -11316,19 +11316,19 @@
         <v>0.348197849071332</v>
       </c>
       <c r="D416" t="n">
-        <v>1.11488672520124</v>
+        <v>1.11488672520122</v>
       </c>
       <c r="E416" t="n">
         <v>0.714099461584533</v>
       </c>
       <c r="F416" t="n">
-        <v>0.82451830137658</v>
+        <v>0.824518301376556</v>
       </c>
       <c r="G416" t="n">
         <v>0.706095784750671</v>
       </c>
       <c r="H416" t="n">
-        <v>0.590875166211705</v>
+        <v>0.590875166211675</v>
       </c>
     </row>
     <row r="417">
@@ -11394,7 +11394,7 @@
         <v>0.830347955284394</v>
       </c>
       <c r="D419" t="n">
-        <v>0.888838806175013</v>
+        <v>0.888838806175012</v>
       </c>
       <c r="E419" t="n">
         <v>1</v>
@@ -11420,19 +11420,19 @@
         <v>0.0079564459807781</v>
       </c>
       <c r="D420" t="n">
-        <v>1.22415871258138</v>
+        <v>1.22415871258142</v>
       </c>
       <c r="E420" t="n">
-        <v>0.663780108205795</v>
+        <v>0.663780108205796</v>
       </c>
       <c r="F420" t="n">
-        <v>0.932217563707436</v>
+        <v>0.932217563707427</v>
       </c>
       <c r="G420" t="n">
         <v>0.484452467751083</v>
       </c>
       <c r="H420" t="n">
-        <v>1.18705421810583</v>
+        <v>1.18705421810589</v>
       </c>
     </row>
     <row r="421">
@@ -11443,10 +11443,10 @@
         <v>18</v>
       </c>
       <c r="C421" t="n">
-        <v>0.516214467764504</v>
+        <v>0.516214467764503</v>
       </c>
       <c r="D421" t="n">
-        <v>1.27716551415788</v>
+        <v>1.27716551415787</v>
       </c>
       <c r="E421" t="n">
         <v>1</v>
@@ -11472,7 +11472,7 @@
         <v>0.213696853094517</v>
       </c>
       <c r="D422" t="n">
-        <v>0.522862490911031</v>
+        <v>0.522862490911032</v>
       </c>
       <c r="E422" t="n">
         <v>1</v>
@@ -11625,10 +11625,10 @@
         <v>25</v>
       </c>
       <c r="C428" t="n">
-        <v>0.76258671378874</v>
+        <v>0.762586713788741</v>
       </c>
       <c r="D428" t="n">
-        <v>0.796756959555741</v>
+        <v>0.796756959555749</v>
       </c>
       <c r="E428" t="n">
         <v>1</v>
@@ -11680,19 +11680,19 @@
         <v>0.631295342371216</v>
       </c>
       <c r="D430" t="n">
-        <v>0.934165810749453</v>
+        <v>0.934165810749454</v>
       </c>
       <c r="E430" t="n">
         <v>1</v>
       </c>
       <c r="F430" t="n">
-        <v>1.11103041071885</v>
+        <v>1.11103041071887</v>
       </c>
       <c r="G430" t="n">
         <v>0.455151099529419</v>
       </c>
       <c r="H430" t="n">
-        <v>2.26587743774028</v>
+        <v>2.26587743774031</v>
       </c>
     </row>
     <row r="431">
@@ -11706,7 +11706,7 @@
         <v>0.213952911152548</v>
       </c>
       <c r="D431" t="n">
-        <v>1.43885860927223</v>
+        <v>1.43885860927222</v>
       </c>
       <c r="E431" t="n">
         <v>1</v>
@@ -11732,19 +11732,19 @@
         <v>0.86993936044728</v>
       </c>
       <c r="D432" t="n">
-        <v>0.970413988572596</v>
+        <v>0.970413988572584</v>
       </c>
       <c r="E432" t="n">
         <v>0.227257193835028</v>
       </c>
       <c r="F432" t="n">
-        <v>1.92038422090248</v>
+        <v>1.92038422090239</v>
       </c>
       <c r="G432" t="n">
         <v>0.450529061399415</v>
       </c>
       <c r="H432" t="n">
-        <v>2.01700623626743</v>
+        <v>2.01700623626739</v>
       </c>
     </row>
     <row r="433">
@@ -11758,7 +11758,7 @@
         <v>0.658726062660444</v>
       </c>
       <c r="D433" t="n">
-        <v>0.935155684324244</v>
+        <v>0.935155684324266</v>
       </c>
       <c r="E433" t="n">
         <v>1</v>
@@ -11784,19 +11784,19 @@
         <v>0.876171863557835</v>
       </c>
       <c r="D434" t="n">
-        <v>1.05806311304281</v>
+        <v>1.0580631130428</v>
       </c>
       <c r="E434" t="n">
         <v>0.624940248183875</v>
       </c>
       <c r="F434" t="n">
-        <v>2.72890014321586</v>
+        <v>2.72890014321583</v>
       </c>
       <c r="G434" t="n">
         <v>1</v>
       </c>
       <c r="H434" t="n">
-        <v>1.05163596961347</v>
+        <v>1.05163596961349</v>
       </c>
     </row>
     <row r="435">
@@ -11885,10 +11885,10 @@
         <v>35</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0514148556834213</v>
+        <v>0.0514148556834214</v>
       </c>
       <c r="D438" t="n">
-        <v>0.514391582021089</v>
+        <v>0.51439158202109</v>
       </c>
       <c r="E438" t="n">
         <v>1</v>
@@ -11992,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="D442" t="n">
-        <v>0.679382516228923</v>
+        <v>0.679382516228922</v>
       </c>
       <c r="E442" t="n">
         <v>1</v>
@@ -12044,7 +12044,7 @@
         <v>0.69932414655548</v>
       </c>
       <c r="D444" t="n">
-        <v>0.635380026825383</v>
+        <v>0.635380026825385</v>
       </c>
       <c r="E444" t="n">
         <v>1</v>
@@ -12067,22 +12067,22 @@
         <v>42</v>
       </c>
       <c r="C445" t="n">
-        <v>0.0000000000438450242728169</v>
+        <v>0.0000000000438450242728167</v>
       </c>
       <c r="D445" t="n">
-        <v>2.12468230896216</v>
+        <v>2.12468230896222</v>
       </c>
       <c r="E445" t="n">
         <v>0.643079827619142</v>
       </c>
       <c r="F445" t="n">
-        <v>0.939709097693396</v>
+        <v>0.939709097693421</v>
       </c>
       <c r="G445" t="n">
         <v>0.243794888949951</v>
       </c>
       <c r="H445" t="n">
-        <v>0.731474892285764</v>
+        <v>0.731474892285788</v>
       </c>
     </row>
     <row r="446">
@@ -12096,19 +12096,19 @@
         <v>1.68641224231559e-231</v>
       </c>
       <c r="D446" t="n">
-        <v>1.31163346711507</v>
+        <v>1.31163346711519</v>
       </c>
       <c r="E446" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000715316397050984</v>
+        <v>0.000000000000000000000000000000000000000000000000000000715316397050983</v>
       </c>
       <c r="F446" t="n">
-        <v>0.867506819297167</v>
+        <v>0.8675068192972</v>
       </c>
       <c r="G446" t="n">
         <v>0.00373884431735046</v>
       </c>
       <c r="H446" t="n">
-        <v>1.04435964967219</v>
+        <v>1.04435964967224</v>
       </c>
     </row>
     <row r="447">
@@ -12122,19 +12122,19 @@
         <v>0.00140470226250983</v>
       </c>
       <c r="D447" t="n">
-        <v>1.01579648389678</v>
+        <v>1.01579648389657</v>
       </c>
       <c r="E447" t="n">
-        <v>0.000163368754569612</v>
+        <v>0.000163368754569613</v>
       </c>
       <c r="F447" t="n">
-        <v>0.981196618378818</v>
+        <v>0.981196618378801</v>
       </c>
       <c r="G447" t="n">
         <v>0.000247859234300006</v>
       </c>
       <c r="H447" t="n">
-        <v>1.02817550642209</v>
+        <v>1.02817550642202</v>
       </c>
     </row>
     <row r="448">
@@ -12148,19 +12148,19 @@
         <v>0</v>
       </c>
       <c r="D448" t="n">
-        <v>1.71034285690123</v>
+        <v>1.71034285690115</v>
       </c>
       <c r="E448" t="n">
         <v>0.498793756017371</v>
       </c>
       <c r="F448" t="n">
-        <v>1.00603541292703</v>
+        <v>1.00603541292701</v>
       </c>
       <c r="G448" t="n">
         <v>0.0000000000000177935728287076</v>
       </c>
       <c r="H448" t="n">
-        <v>0.888981580942823</v>
+        <v>0.888981580942873</v>
       </c>
     </row>
     <row r="449">
@@ -12171,22 +12171,22 @@
         <v>12</v>
       </c>
       <c r="C449" t="n">
-        <v>0.40571341747844</v>
+        <v>0.405713417478439</v>
       </c>
       <c r="D449" t="n">
-        <v>1.04384780203267</v>
+        <v>1.04384780203268</v>
       </c>
       <c r="E449" t="n">
         <v>0.093709040612803</v>
       </c>
       <c r="F449" t="n">
-        <v>0.853378484221674</v>
+        <v>0.853378484221677</v>
       </c>
       <c r="G449" t="n">
         <v>0.183002624135626</v>
       </c>
       <c r="H449" t="n">
-        <v>0.832956272816781</v>
+        <v>0.832956272816792</v>
       </c>
     </row>
     <row r="450">
@@ -12206,13 +12206,13 @@
         <v>0.339561659699301</v>
       </c>
       <c r="F450" t="n">
-        <v>1.02436827402392</v>
+        <v>1.02436827402394</v>
       </c>
       <c r="G450" t="n">
         <v>0.567153859433931</v>
       </c>
       <c r="H450" t="n">
-        <v>1.02224069545431</v>
+        <v>1.02224069545433</v>
       </c>
     </row>
     <row r="451">
@@ -12226,19 +12226,19 @@
         <v>0.00000118167159552955</v>
       </c>
       <c r="D451" t="n">
-        <v>1.12960696005788</v>
+        <v>1.1296069600579</v>
       </c>
       <c r="E451" t="n">
         <v>0.978790402084705</v>
       </c>
       <c r="F451" t="n">
-        <v>0.997459759130101</v>
+        <v>0.997459759130098</v>
       </c>
       <c r="G451" t="n">
         <v>0.467591797714467</v>
       </c>
       <c r="H451" t="n">
-        <v>0.938948366055035</v>
+        <v>0.938948366055033</v>
       </c>
     </row>
     <row r="452">
@@ -12252,19 +12252,19 @@
         <v>0.46646316243788</v>
       </c>
       <c r="D452" t="n">
-        <v>0.91698776143274</v>
+        <v>0.916987761432748</v>
       </c>
       <c r="E452" t="n">
         <v>0.115444405058614</v>
       </c>
       <c r="F452" t="n">
-        <v>0.833538919119712</v>
+        <v>0.833538919119713</v>
       </c>
       <c r="G452" t="n">
         <v>0.344826645825939</v>
       </c>
       <c r="H452" t="n">
-        <v>1.17246073243356</v>
+        <v>1.17246073243355</v>
       </c>
     </row>
     <row r="453">
@@ -12275,22 +12275,22 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>0.0490519054269875</v>
+        <v>0.0490519054269874</v>
       </c>
       <c r="D453" t="n">
-        <v>0.944174946107493</v>
+        <v>0.94417494610752</v>
       </c>
       <c r="E453" t="n">
         <v>0.745936655634385</v>
       </c>
       <c r="F453" t="n">
-        <v>0.91419070663752</v>
+        <v>0.914190706637492</v>
       </c>
       <c r="G453" t="n">
         <v>0.545656102306162</v>
       </c>
       <c r="H453" t="n">
-        <v>0.83129814513425</v>
+        <v>0.831298145134263</v>
       </c>
     </row>
     <row r="454">
@@ -12307,16 +12307,16 @@
         <v>1.45964774238773</v>
       </c>
       <c r="E454" t="n">
-        <v>0.0781872634710389</v>
+        <v>0.0781872634710388</v>
       </c>
       <c r="F454" t="n">
-        <v>0.946651257289488</v>
+        <v>0.946651257289442</v>
       </c>
       <c r="G454" t="n">
-        <v>0.738303485031814</v>
+        <v>0.738303485031815</v>
       </c>
       <c r="H454" t="n">
-        <v>0.982826805278206</v>
+        <v>0.982826805278193</v>
       </c>
     </row>
     <row r="455">
@@ -12330,7 +12330,7 @@
         <v>0.961664779411628</v>
       </c>
       <c r="D455" t="n">
-        <v>1.00811136997715</v>
+        <v>1.00811136997714</v>
       </c>
       <c r="E455" t="n">
         <v>0.11844462838438</v>
@@ -12353,22 +12353,22 @@
         <v>19</v>
       </c>
       <c r="C456" t="n">
-        <v>0.394882640339572</v>
+        <v>0.394882640339573</v>
       </c>
       <c r="D456" t="n">
-        <v>1.25983701734893</v>
+        <v>1.25983701734891</v>
       </c>
       <c r="E456" t="n">
         <v>0.0920099048837903</v>
       </c>
       <c r="F456" t="n">
-        <v>1.63095866074697</v>
+        <v>1.63095866074694</v>
       </c>
       <c r="G456" t="n">
         <v>0.0982951325991184</v>
       </c>
       <c r="H456" t="n">
-        <v>2.39403172580882</v>
+        <v>2.39403172580884</v>
       </c>
     </row>
     <row r="457">
@@ -12382,19 +12382,19 @@
         <v>0.607491893416684</v>
       </c>
       <c r="D457" t="n">
-        <v>1.21753989754873</v>
+        <v>1.21753989754872</v>
       </c>
       <c r="E457" t="n">
         <v>0.261687473243514</v>
       </c>
       <c r="F457" t="n">
-        <v>2.01755425956119</v>
+        <v>2.01755425956117</v>
       </c>
       <c r="G457" t="n">
         <v>0.698511403627597</v>
       </c>
       <c r="H457" t="n">
-        <v>0.724423428697886</v>
+        <v>0.724423428697887</v>
       </c>
     </row>
     <row r="458">
@@ -12408,19 +12408,19 @@
         <v>0.430207576415505</v>
       </c>
       <c r="D458" t="n">
-        <v>1.08685091059517</v>
+        <v>1.08685091059519</v>
       </c>
       <c r="E458" t="n">
         <v>0.140982353220097</v>
       </c>
       <c r="F458" t="n">
-        <v>1.1571181142343</v>
+        <v>1.15711811423432</v>
       </c>
       <c r="G458" t="n">
-        <v>0.940381678316903</v>
+        <v>0.940381678316904</v>
       </c>
       <c r="H458" t="n">
-        <v>1.01838893452469</v>
+        <v>1.01838893452467</v>
       </c>
     </row>
     <row r="459">
@@ -12434,19 +12434,19 @@
         <v>0.0000000000000468568959220635</v>
       </c>
       <c r="D459" t="n">
-        <v>1.32312412965921</v>
+        <v>1.32312412965922</v>
       </c>
       <c r="E459" t="n">
         <v>0.000330132556237201</v>
       </c>
       <c r="F459" t="n">
-        <v>0.869393616614502</v>
+        <v>0.869393616614484</v>
       </c>
       <c r="G459" t="n">
         <v>0.00000000000000000274921040763749</v>
       </c>
       <c r="H459" t="n">
-        <v>0.573193981841793</v>
+        <v>0.573193981841775</v>
       </c>
     </row>
     <row r="460">
@@ -12460,19 +12460,19 @@
         <v>0.533450789057759</v>
       </c>
       <c r="D460" t="n">
-        <v>1.1914379442346</v>
+        <v>1.19143794423459</v>
       </c>
       <c r="E460" t="n">
         <v>0.521705838538145</v>
       </c>
       <c r="F460" t="n">
-        <v>1.19937241351419</v>
+        <v>1.19937241351417</v>
       </c>
       <c r="G460" t="n">
         <v>1</v>
       </c>
       <c r="H460" t="n">
-        <v>0.971752716808662</v>
+        <v>0.971752716808663</v>
       </c>
     </row>
     <row r="461">
@@ -12509,22 +12509,22 @@
         <v>25</v>
       </c>
       <c r="C462" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000261856935737468</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000261856935737486</v>
       </c>
       <c r="D462" t="n">
-        <v>0.596200780180067</v>
+        <v>0.596200780180082</v>
       </c>
       <c r="E462" t="n">
         <v>0.576796880608542</v>
       </c>
       <c r="F462" t="n">
-        <v>1.03198378059212</v>
+        <v>1.03198378059215</v>
       </c>
       <c r="G462" t="n">
         <v>0.421091156075671</v>
       </c>
       <c r="H462" t="n">
-        <v>1.06260117906021</v>
+        <v>1.0626011790602</v>
       </c>
     </row>
     <row r="463">
@@ -12544,7 +12544,7 @@
         <v>0.388261536697438</v>
       </c>
       <c r="F463" t="n">
-        <v>1.12956619886167</v>
+        <v>1.12956619886165</v>
       </c>
       <c r="G463" t="n">
         <v>1</v>
@@ -12561,22 +12561,22 @@
         <v>27</v>
       </c>
       <c r="C464" t="n">
-        <v>0.691278993263094</v>
+        <v>0.691278993263093</v>
       </c>
       <c r="D464" t="n">
-        <v>1.00560694350007</v>
+        <v>1.00560694350008</v>
       </c>
       <c r="E464" t="n">
         <v>0.0000254506979499607</v>
       </c>
       <c r="F464" t="n">
-        <v>0.883170201107005</v>
+        <v>0.883170201107012</v>
       </c>
       <c r="G464" t="n">
         <v>0.0493112870749549</v>
       </c>
       <c r="H464" t="n">
-        <v>1.09208865532516</v>
+        <v>1.09208865532511</v>
       </c>
     </row>
     <row r="465">
@@ -12590,19 +12590,19 @@
         <v>0.126873910772646</v>
       </c>
       <c r="D465" t="n">
-        <v>1.29011721353559</v>
+        <v>1.2901172135356</v>
       </c>
       <c r="E465" t="n">
         <v>0.800676264033029</v>
       </c>
       <c r="F465" t="n">
-        <v>1.0497065475769</v>
+        <v>1.04970654757691</v>
       </c>
       <c r="G465" t="n">
         <v>0.267690578179825</v>
       </c>
       <c r="H465" t="n">
-        <v>1.39501623478598</v>
+        <v>1.39501623478596</v>
       </c>
     </row>
     <row r="466">
@@ -12616,19 +12616,19 @@
         <v>0.0000000000000000276833143404176</v>
       </c>
       <c r="D466" t="n">
-        <v>1.32049953966977</v>
+        <v>1.32049953966972</v>
       </c>
       <c r="E466" t="n">
-        <v>0.81582920485184</v>
+        <v>0.815829204851839</v>
       </c>
       <c r="F466" t="n">
-        <v>1.00871584032048</v>
+        <v>1.00871584032046</v>
       </c>
       <c r="G466" t="n">
-        <v>0.642626006802681</v>
+        <v>0.64262600680268</v>
       </c>
       <c r="H466" t="n">
-        <v>1.02783482939599</v>
+        <v>1.02783482939602</v>
       </c>
     </row>
     <row r="467">
@@ -12642,19 +12642,19 @@
         <v>0.1914547265903</v>
       </c>
       <c r="D467" t="n">
-        <v>1.02530825031943</v>
+        <v>1.02530825031942</v>
       </c>
       <c r="E467" t="n">
-        <v>0.345816986972853</v>
+        <v>0.345816986972854</v>
       </c>
       <c r="F467" t="n">
-        <v>0.978551627909218</v>
+        <v>0.9785516279092</v>
       </c>
       <c r="G467" t="n">
         <v>0.109749557593874</v>
       </c>
       <c r="H467" t="n">
-        <v>0.946165307843723</v>
+        <v>0.94616530784373</v>
       </c>
     </row>
     <row r="468">
@@ -12668,19 +12668,19 @@
         <v>0.896065634432033</v>
       </c>
       <c r="D468" t="n">
-        <v>1.02290350160145</v>
+        <v>1.02290350160146</v>
       </c>
       <c r="E468" t="n">
         <v>0.835775736933473</v>
       </c>
       <c r="F468" t="n">
-        <v>1.03260379912367</v>
+        <v>1.03260379912365</v>
       </c>
       <c r="G468" t="n">
         <v>0.399610919696509</v>
       </c>
       <c r="H468" t="n">
-        <v>1.20560342738779</v>
+        <v>1.2056034273878</v>
       </c>
     </row>
     <row r="469">
@@ -12691,22 +12691,22 @@
         <v>32</v>
       </c>
       <c r="C469" t="n">
-        <v>0.0450096536922968</v>
+        <v>0.0450096536922969</v>
       </c>
       <c r="D469" t="n">
-        <v>0.573913351941723</v>
+        <v>0.573913351941721</v>
       </c>
       <c r="E469" t="n">
         <v>0.566017844661603</v>
       </c>
       <c r="F469" t="n">
-        <v>1.21660355536239</v>
+        <v>1.21660355536238</v>
       </c>
       <c r="G469" t="n">
         <v>0.860378720680421</v>
       </c>
       <c r="H469" t="n">
-        <v>1.0945823992601</v>
+        <v>1.09458239926011</v>
       </c>
     </row>
     <row r="470">
@@ -12720,19 +12720,19 @@
         <v>0.551882637820158</v>
       </c>
       <c r="D470" t="n">
-        <v>0.955552209541286</v>
+        <v>0.955552209541257</v>
       </c>
       <c r="E470" t="n">
         <v>0.0135774500392615</v>
       </c>
       <c r="F470" t="n">
-        <v>0.812916076103868</v>
+        <v>0.812916076103866</v>
       </c>
       <c r="G470" t="n">
         <v>0.634682987930659</v>
       </c>
       <c r="H470" t="n">
-        <v>0.942645321387202</v>
+        <v>0.942645321387224</v>
       </c>
     </row>
     <row r="471">
@@ -12746,7 +12746,7 @@
         <v>0.00000125825167306967</v>
       </c>
       <c r="D471" t="n">
-        <v>0.904471605923362</v>
+        <v>0.904471605923347</v>
       </c>
       <c r="E471" t="n">
         <v>0.100868221515719</v>
@@ -12758,7 +12758,7 @@
         <v>0.000000193456970067204</v>
       </c>
       <c r="H471" t="n">
-        <v>0.785813595618946</v>
+        <v>0.785813595618952</v>
       </c>
     </row>
     <row r="472">
@@ -12772,19 +12772,19 @@
         <v>0.0116175115837564</v>
       </c>
       <c r="D472" t="n">
-        <v>1.17109186673958</v>
+        <v>1.17109186673961</v>
       </c>
       <c r="E472" t="n">
         <v>0.399330024467772</v>
       </c>
       <c r="F472" t="n">
-        <v>0.94291558853306</v>
+        <v>0.942915588533092</v>
       </c>
       <c r="G472" t="n">
-        <v>0.000000559979214858294</v>
+        <v>0.000000559979214858292</v>
       </c>
       <c r="H472" t="n">
-        <v>1.70870339889675</v>
+        <v>1.70870339889676</v>
       </c>
     </row>
     <row r="473">
@@ -12830,13 +12830,13 @@
         <v>0.343595502316472</v>
       </c>
       <c r="F474" t="n">
-        <v>1.33277068214492</v>
+        <v>1.3327706821449</v>
       </c>
       <c r="G474" t="n">
         <v>0.831921259969967</v>
       </c>
       <c r="H474" t="n">
-        <v>0.83439996730782</v>
+        <v>0.834399967307825</v>
       </c>
     </row>
     <row r="475">
@@ -12850,19 +12850,19 @@
         <v>0.0179191676945101</v>
       </c>
       <c r="D475" t="n">
-        <v>1.13925273370083</v>
+        <v>1.13925273370089</v>
       </c>
       <c r="E475" t="n">
-        <v>0.0000593605261505237</v>
+        <v>0.0000593605261505241</v>
       </c>
       <c r="F475" t="n">
-        <v>1.55407231349365</v>
+        <v>1.55407231349375</v>
       </c>
       <c r="G475" t="n">
         <v>0.043754750774779</v>
       </c>
       <c r="H475" t="n">
-        <v>0.699281130879802</v>
+        <v>0.699281130879764</v>
       </c>
     </row>
     <row r="476">
@@ -12876,19 +12876,19 @@
         <v>0.00189152397626781</v>
       </c>
       <c r="D476" t="n">
-        <v>2.41882492888489</v>
+        <v>2.41882492888491</v>
       </c>
       <c r="E476" t="n">
         <v>0.526762842399213</v>
       </c>
       <c r="F476" t="n">
-        <v>1.18530605026999</v>
+        <v>1.18530605027</v>
       </c>
       <c r="G476" t="n">
         <v>0.313337271324098</v>
       </c>
       <c r="H476" t="n">
-        <v>0.566169434562696</v>
+        <v>0.566169434562704</v>
       </c>
     </row>
     <row r="477">
@@ -12960,13 +12960,13 @@
         <v>0.00000219716500191775</v>
       </c>
       <c r="F479" t="n">
-        <v>0.950076235340275</v>
+        <v>0.950076235340248</v>
       </c>
       <c r="G479" t="n">
-        <v>0.781020416935104</v>
+        <v>0.781020416935103</v>
       </c>
       <c r="H479" t="n">
-        <v>0.995036264072338</v>
+        <v>0.995036264072392</v>
       </c>
     </row>
     <row r="480">
@@ -12980,19 +12980,19 @@
         <v>0.000000000000000000000000000000000000000000000000000000975956219159654</v>
       </c>
       <c r="D480" t="n">
-        <v>1.18522330068242</v>
+        <v>1.18522330068243</v>
       </c>
       <c r="E480" t="n">
         <v>0.00000000000000000000307245493645308</v>
       </c>
       <c r="F480" t="n">
-        <v>0.896344489892155</v>
+        <v>0.896344489892105</v>
       </c>
       <c r="G480" t="n">
         <v>0.0233100088529969</v>
       </c>
       <c r="H480" t="n">
-        <v>1.04228822531494</v>
+        <v>1.04228822531498</v>
       </c>
     </row>
     <row r="481">
@@ -13003,22 +13003,22 @@
         <v>10</v>
       </c>
       <c r="C481" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000138721372062933</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000138721372062947</v>
       </c>
       <c r="D481" t="n">
         <v>1.84337660637885</v>
       </c>
       <c r="E481" t="n">
-        <v>0.00548039654838059</v>
+        <v>0.0054803965483806</v>
       </c>
       <c r="F481" t="n">
-        <v>1.10232501898088</v>
+        <v>1.10232501898089</v>
       </c>
       <c r="G481" t="n">
         <v>0.0319114637424706</v>
       </c>
       <c r="H481" t="n">
-        <v>0.873215072123887</v>
+        <v>0.873215072123866</v>
       </c>
     </row>
     <row r="482">
@@ -13044,7 +13044,7 @@
         <v>0.00310445457310941</v>
       </c>
       <c r="H482" t="n">
-        <v>0.411668535861496</v>
+        <v>0.411668535861487</v>
       </c>
     </row>
     <row r="483">
@@ -13058,19 +13058,19 @@
         <v>0.30889653169591</v>
       </c>
       <c r="D483" t="n">
-        <v>1.0456362900984</v>
+        <v>1.04563629009842</v>
       </c>
       <c r="E483" t="n">
         <v>0.678297691570337</v>
       </c>
       <c r="F483" t="n">
-        <v>1.04297104225727</v>
+        <v>1.04297104225724</v>
       </c>
       <c r="G483" t="n">
         <v>0.482196427640512</v>
       </c>
       <c r="H483" t="n">
-        <v>1.11127561848902</v>
+        <v>1.11127561848903</v>
       </c>
     </row>
     <row r="484">
@@ -13084,19 +13084,19 @@
         <v>0.00000362576684072601</v>
       </c>
       <c r="D484" t="n">
-        <v>1.17070909828071</v>
+        <v>1.17070909828069</v>
       </c>
       <c r="E484" t="n">
-        <v>0.719014598660346</v>
+        <v>0.719014598660344</v>
       </c>
       <c r="F484" t="n">
-        <v>0.98349011914044</v>
+        <v>0.983490119140428</v>
       </c>
       <c r="G484" t="n">
-        <v>0.274132747000058</v>
+        <v>0.274132747000057</v>
       </c>
       <c r="H484" t="n">
-        <v>1.08204276535253</v>
+        <v>1.08204276535254</v>
       </c>
     </row>
     <row r="485">
@@ -13110,19 +13110,19 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000131462507764679</v>
       </c>
       <c r="D485" t="n">
-        <v>1.2041856079564</v>
+        <v>1.20418560795639</v>
       </c>
       <c r="E485" t="n">
         <v>0.0133059951384902</v>
       </c>
       <c r="F485" t="n">
-        <v>0.963061342564306</v>
+        <v>0.963061342564304</v>
       </c>
       <c r="G485" t="n">
         <v>0.371980504133055</v>
       </c>
       <c r="H485" t="n">
-        <v>0.978145287333027</v>
+        <v>0.978145287333001</v>
       </c>
     </row>
     <row r="486">
@@ -13162,19 +13162,19 @@
         <v>0.772936585829805</v>
       </c>
       <c r="D487" t="n">
-        <v>0.992258692008363</v>
+        <v>0.992258692008332</v>
       </c>
       <c r="E487" t="n">
         <v>0.270462246821308</v>
       </c>
       <c r="F487" t="n">
-        <v>0.821021640455689</v>
+        <v>0.821021640455662</v>
       </c>
       <c r="G487" t="n">
         <v>0.538674573899639</v>
       </c>
       <c r="H487" t="n">
-        <v>0.839758357110863</v>
+        <v>0.839758357110872</v>
       </c>
     </row>
     <row r="488">
@@ -13188,19 +13188,19 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000333540593219003</v>
       </c>
       <c r="D488" t="n">
-        <v>1.39057011100736</v>
+        <v>1.39057011100729</v>
       </c>
       <c r="E488" t="n">
-        <v>0.816498860814162</v>
+        <v>0.81649886081416</v>
       </c>
       <c r="F488" t="n">
-        <v>1.00381426997011</v>
+        <v>1.00381426997008</v>
       </c>
       <c r="G488" t="n">
-        <v>0.333831867521439</v>
+        <v>0.33383186752144</v>
       </c>
       <c r="H488" t="n">
-        <v>0.974575953837661</v>
+        <v>0.974575953837675</v>
       </c>
     </row>
     <row r="489">
@@ -13350,13 +13350,13 @@
         <v>0.00403809380092953</v>
       </c>
       <c r="F494" t="n">
-        <v>3.34984849485292</v>
+        <v>3.34984849485297</v>
       </c>
       <c r="G494" t="n">
         <v>1</v>
       </c>
       <c r="H494" t="n">
-        <v>0.873921307382617</v>
+        <v>0.873921307382619</v>
       </c>
     </row>
     <row r="495">
@@ -13396,19 +13396,19 @@
         <v>0.492141070796688</v>
       </c>
       <c r="D496" t="n">
-        <v>0.767259305769177</v>
+        <v>0.767259305769184</v>
       </c>
       <c r="E496" t="n">
         <v>0.620184951050308</v>
       </c>
       <c r="F496" t="n">
-        <v>1.40015202151655</v>
+        <v>1.40015202151656</v>
       </c>
       <c r="G496" t="n">
         <v>0.321990116154249</v>
       </c>
       <c r="H496" t="n">
-        <v>2.40683936872868</v>
+        <v>2.40683936872869</v>
       </c>
     </row>
     <row r="497">
@@ -13445,22 +13445,22 @@
         <v>27</v>
       </c>
       <c r="C498" t="n">
-        <v>0.049000075049848</v>
+        <v>0.0490000750498479</v>
       </c>
       <c r="D498" t="n">
-        <v>1.03853044375351</v>
+        <v>1.03853044375349</v>
       </c>
       <c r="E498" t="n">
         <v>0.0835048959101331</v>
       </c>
       <c r="F498" t="n">
-        <v>0.932192342218547</v>
+        <v>0.93219234221851</v>
       </c>
       <c r="G498" t="n">
-        <v>0.781070835629013</v>
+        <v>0.781070835629012</v>
       </c>
       <c r="H498" t="n">
-        <v>0.981319406755844</v>
+        <v>0.981319406755953</v>
       </c>
     </row>
     <row r="499">
@@ -13500,19 +13500,19 @@
         <v>0.00724485768387049</v>
       </c>
       <c r="D500" t="n">
-        <v>1.22477550456361</v>
+        <v>1.22477550456359</v>
       </c>
       <c r="E500" t="n">
         <v>0.150233895028613</v>
       </c>
       <c r="F500" t="n">
-        <v>1.13568653744174</v>
+        <v>1.13568653744173</v>
       </c>
       <c r="G500" t="n">
         <v>0.126455851304293</v>
       </c>
       <c r="H500" t="n">
-        <v>1.23983478599361</v>
+        <v>1.2398347859936</v>
       </c>
     </row>
     <row r="501">
@@ -13526,19 +13526,19 @@
         <v>0.000000142992907168512</v>
       </c>
       <c r="D501" t="n">
-        <v>1.15988832801367</v>
+        <v>1.15988832801368</v>
       </c>
       <c r="E501" t="n">
-        <v>0.728303492702015</v>
+        <v>0.728303492702014</v>
       </c>
       <c r="F501" t="n">
-        <v>0.988532387475251</v>
+        <v>0.988532387475283</v>
       </c>
       <c r="G501" t="n">
         <v>0.0207176462202998</v>
       </c>
       <c r="H501" t="n">
-        <v>0.8874932828955</v>
+        <v>0.887493282895484</v>
       </c>
     </row>
     <row r="502">
@@ -13604,19 +13604,19 @@
         <v>0.0546588253650668</v>
       </c>
       <c r="D504" t="n">
-        <v>0.807930511652712</v>
+        <v>0.807930511652708</v>
       </c>
       <c r="E504" t="n">
         <v>0.757784623915541</v>
       </c>
       <c r="F504" t="n">
-        <v>1.04313136694623</v>
+        <v>1.04313136694621</v>
       </c>
       <c r="G504" t="n">
         <v>0.451087374950539</v>
       </c>
       <c r="H504" t="n">
-        <v>0.872140528261797</v>
+        <v>0.872140528261783</v>
       </c>
     </row>
     <row r="505">
@@ -13636,13 +13636,13 @@
         <v>1</v>
       </c>
       <c r="F505" t="n">
-        <v>1.0645065810713</v>
+        <v>1.06450658107131</v>
       </c>
       <c r="G505" t="n">
         <v>0.479679911543235</v>
       </c>
       <c r="H505" t="n">
-        <v>0.457140951972628</v>
+        <v>0.45714095197263</v>
       </c>
     </row>
     <row r="506">
@@ -13653,22 +13653,22 @@
         <v>35</v>
       </c>
       <c r="C506" t="n">
-        <v>0.270490403992506</v>
+        <v>0.270490403992507</v>
       </c>
       <c r="D506" t="n">
-        <v>1.24159452783752</v>
+        <v>1.2415945278375</v>
       </c>
       <c r="E506" t="n">
         <v>0.301461475420851</v>
       </c>
       <c r="F506" t="n">
-        <v>0.816109551571954</v>
+        <v>0.816109551571951</v>
       </c>
       <c r="G506" t="n">
         <v>0.448959203842472</v>
       </c>
       <c r="H506" t="n">
-        <v>1.30399519197873</v>
+        <v>1.30399519197871</v>
       </c>
     </row>
     <row r="507">
@@ -13838,19 +13838,19 @@
         <v>0.000000000000000000000000000000000000000000270673701266499</v>
       </c>
       <c r="D513" t="n">
-        <v>1.4064563276337</v>
+        <v>1.40645632763365</v>
       </c>
       <c r="E513" t="n">
-        <v>0.667838384339841</v>
+        <v>0.66783838433984</v>
       </c>
       <c r="F513" t="n">
-        <v>0.989478196761692</v>
+        <v>0.989478196761637</v>
       </c>
       <c r="G513" t="n">
         <v>0.302730994578264</v>
       </c>
       <c r="H513" t="n">
-        <v>0.959227864475351</v>
+        <v>0.959227864475387</v>
       </c>
     </row>
     <row r="514">
@@ -13864,19 +13864,19 @@
         <v>0</v>
       </c>
       <c r="D514" t="n">
-        <v>1.29193190598308</v>
+        <v>1.29193190598314</v>
       </c>
       <c r="E514" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000197142468527753</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000197142468527752</v>
       </c>
       <c r="F514" t="n">
-        <v>0.889242411086771</v>
+        <v>0.889242411086798</v>
       </c>
       <c r="G514" t="n">
         <v>0.98698498333628</v>
       </c>
       <c r="H514" t="n">
-        <v>1.00020648733545</v>
+        <v>1.00020648733542</v>
       </c>
     </row>
     <row r="515">
@@ -13890,13 +13890,13 @@
         <v>0.468314205143763</v>
       </c>
       <c r="D515" t="n">
-        <v>0.996936164525817</v>
+        <v>0.996936164525796</v>
       </c>
       <c r="E515" t="n">
-        <v>0.0467226345079184</v>
+        <v>0.0467226345079185</v>
       </c>
       <c r="F515" t="n">
-        <v>1.00871133648618</v>
+        <v>1.00871133648633</v>
       </c>
       <c r="G515" t="n">
         <v>0.00779703248733193</v>
@@ -13913,16 +13913,16 @@
         <v>11</v>
       </c>
       <c r="C516" t="n">
-        <v>0.550697182014817</v>
+        <v>0.550697182014818</v>
       </c>
       <c r="D516" t="n">
-        <v>0.909653229689674</v>
+        <v>0.909653229689676</v>
       </c>
       <c r="E516" t="n">
         <v>0.237921705127382</v>
       </c>
       <c r="F516" t="n">
-        <v>0.739978126126362</v>
+        <v>0.739978126126359</v>
       </c>
       <c r="G516" t="n">
         <v>0.423788999230854</v>
@@ -13942,19 +13942,19 @@
         <v>0.314574988904446</v>
       </c>
       <c r="D517" t="n">
-        <v>0.934461087208448</v>
+        <v>0.934461087208418</v>
       </c>
       <c r="E517" t="n">
-        <v>0.0947450533270169</v>
+        <v>0.0947450533270168</v>
       </c>
       <c r="F517" t="n">
-        <v>1.31151382941056</v>
+        <v>1.31151382941055</v>
       </c>
       <c r="G517" t="n">
         <v>0.422503122828032</v>
       </c>
       <c r="H517" t="n">
-        <v>1.21805333938799</v>
+        <v>1.21805333938794</v>
       </c>
     </row>
     <row r="518">
@@ -13968,19 +13968,19 @@
         <v>0.487232188017587</v>
       </c>
       <c r="D518" t="n">
-        <v>1.01966800181922</v>
+        <v>1.01966800181929</v>
       </c>
       <c r="E518" t="n">
-        <v>0.631267390607194</v>
+        <v>0.631267390607195</v>
       </c>
       <c r="F518" t="n">
-        <v>1.01798157240189</v>
+        <v>1.01798157240195</v>
       </c>
       <c r="G518" t="n">
         <v>1</v>
       </c>
       <c r="H518" t="n">
-        <v>1.00044141411058</v>
+        <v>1.00044141411059</v>
       </c>
     </row>
     <row r="519">
@@ -13994,19 +13994,19 @@
         <v>0.00000000000000000000000000681526476741947</v>
       </c>
       <c r="D519" t="n">
-        <v>1.13917204729399</v>
+        <v>1.13917204729402</v>
       </c>
       <c r="E519" t="n">
-        <v>0.653137295701988</v>
+        <v>0.653137295701989</v>
       </c>
       <c r="F519" t="n">
-        <v>0.989184589077061</v>
+        <v>0.989184589077109</v>
       </c>
       <c r="G519" t="n">
         <v>0.807815439124343</v>
       </c>
       <c r="H519" t="n">
-        <v>1.00971498048744</v>
+        <v>1.00971498048752</v>
       </c>
     </row>
     <row r="520">
@@ -14046,19 +14046,19 @@
         <v>0.0772139890281119</v>
       </c>
       <c r="D521" t="n">
-        <v>0.894910451966126</v>
+        <v>0.894910451966115</v>
       </c>
       <c r="E521" t="n">
         <v>0.127837209910985</v>
       </c>
       <c r="F521" t="n">
-        <v>0.184938426905431</v>
+        <v>0.184938426905426</v>
       </c>
       <c r="G521" t="n">
         <v>0.0900470120175854</v>
       </c>
       <c r="H521" t="n">
-        <v>0.151090833343601</v>
+        <v>0.151090833343611</v>
       </c>
     </row>
     <row r="522">
@@ -14072,19 +14072,19 @@
         <v>0.00000000000000000000865284006387172</v>
       </c>
       <c r="D522" t="n">
-        <v>1.2752851051341</v>
+        <v>1.27528510513408</v>
       </c>
       <c r="E522" t="n">
         <v>0.2518031455833</v>
       </c>
       <c r="F522" t="n">
-        <v>1.03501104548897</v>
+        <v>1.03501104548894</v>
       </c>
       <c r="G522" t="n">
-        <v>0.734034492552325</v>
+        <v>0.734034492552324</v>
       </c>
       <c r="H522" t="n">
-        <v>1.01738450659371</v>
+        <v>1.01738450659375</v>
       </c>
     </row>
     <row r="523">
@@ -14095,22 +14095,22 @@
         <v>18</v>
       </c>
       <c r="C523" t="n">
-        <v>0.290556307613612</v>
+        <v>0.290556307613611</v>
       </c>
       <c r="D523" t="n">
-        <v>0.809098265914324</v>
+        <v>0.80909826591432</v>
       </c>
       <c r="E523" t="n">
         <v>0.0703384086875147</v>
       </c>
       <c r="F523" t="n">
-        <v>6.55953514511486</v>
+        <v>6.55953514511514</v>
       </c>
       <c r="G523" t="n">
         <v>0.256596767796502</v>
       </c>
       <c r="H523" t="n">
-        <v>0.340691649260114</v>
+        <v>0.340691649260121</v>
       </c>
     </row>
     <row r="524">
@@ -14124,19 +14124,19 @@
         <v>0.262305102085096</v>
       </c>
       <c r="D524" t="n">
-        <v>0.967747022523223</v>
+        <v>0.967747022523191</v>
       </c>
       <c r="E524" t="n">
         <v>0.578396922756476</v>
       </c>
       <c r="F524" t="n">
-        <v>0.983625363497842</v>
+        <v>0.983625363497901</v>
       </c>
       <c r="G524" t="n">
         <v>0.77944846071027</v>
       </c>
       <c r="H524" t="n">
-        <v>0.987364678260041</v>
+        <v>0.987364678260044</v>
       </c>
     </row>
     <row r="525">
@@ -14150,19 +14150,19 @@
         <v>0.222384881277746</v>
       </c>
       <c r="D525" t="n">
-        <v>1.38671221909569</v>
+        <v>1.38671221909571</v>
       </c>
       <c r="E525" t="n">
         <v>0.819645481585379</v>
       </c>
       <c r="F525" t="n">
-        <v>1.13426168707288</v>
+        <v>1.13426168707287</v>
       </c>
       <c r="G525" t="n">
         <v>0.651871812884979</v>
       </c>
       <c r="H525" t="n">
-        <v>2.56755754997013</v>
+        <v>2.5675575499701</v>
       </c>
     </row>
     <row r="526">
@@ -14202,19 +14202,19 @@
         <v>0.276276365662978</v>
       </c>
       <c r="D527" t="n">
-        <v>1.28794460345049</v>
+        <v>1.2879446034505</v>
       </c>
       <c r="E527" t="n">
         <v>0.744496084786157</v>
       </c>
       <c r="F527" t="n">
-        <v>0.922804668614202</v>
+        <v>0.922804668614196</v>
       </c>
       <c r="G527" t="n">
         <v>0.0381990204244226</v>
       </c>
       <c r="H527" t="n">
-        <v>0.470111080592791</v>
+        <v>0.470111080592796</v>
       </c>
     </row>
     <row r="528">
@@ -14254,7 +14254,7 @@
         <v>0.672371344502492</v>
       </c>
       <c r="D529" t="n">
-        <v>0.473016140328578</v>
+        <v>0.473016140328577</v>
       </c>
       <c r="E529" t="n">
         <v>1</v>
@@ -14306,19 +14306,19 @@
         <v>0.532416085133227</v>
       </c>
       <c r="D531" t="n">
-        <v>1.41163856366984</v>
+        <v>1.41163856366983</v>
       </c>
       <c r="E531" t="n">
         <v>0.425847578071802</v>
       </c>
       <c r="F531" t="n">
-        <v>1.70880273063673</v>
+        <v>1.70880273063672</v>
       </c>
       <c r="G531" t="n">
         <v>1</v>
       </c>
       <c r="H531" t="n">
-        <v>0.940424641294715</v>
+        <v>0.940424641294724</v>
       </c>
     </row>
     <row r="532">
@@ -14332,7 +14332,7 @@
         <v>0.296487341331589</v>
       </c>
       <c r="D532" t="n">
-        <v>1.03253149186484</v>
+        <v>1.03253149186486</v>
       </c>
       <c r="E532" t="n">
         <v>0.16670959263239</v>
@@ -14344,7 +14344,7 @@
         <v>0.960448782542096</v>
       </c>
       <c r="H532" t="n">
-        <v>0.990369043734351</v>
+        <v>0.990369043734371</v>
       </c>
     </row>
     <row r="533">
@@ -14384,13 +14384,13 @@
         <v>0.0139392702801531</v>
       </c>
       <c r="D534" t="n">
-        <v>1.30161273770802</v>
+        <v>1.30161273770804</v>
       </c>
       <c r="E534" t="n">
         <v>0.00175172462530347</v>
       </c>
       <c r="F534" t="n">
-        <v>1.67474912409859</v>
+        <v>1.67474912409858</v>
       </c>
       <c r="G534" t="n">
         <v>0.0104372917055884</v>
@@ -14410,19 +14410,19 @@
         <v>0.0599196988733517</v>
       </c>
       <c r="D535" t="n">
-        <v>0.946410263972887</v>
+        <v>0.946410263972825</v>
       </c>
       <c r="E535" t="n">
-        <v>0.0968175971681736</v>
+        <v>0.0968175971681735</v>
       </c>
       <c r="F535" t="n">
-        <v>1.0657618572144</v>
+        <v>1.06576185721435</v>
       </c>
       <c r="G535" t="n">
-        <v>0.661299556729261</v>
+        <v>0.661299556729262</v>
       </c>
       <c r="H535" t="n">
-        <v>1.02658377687279</v>
+        <v>1.0265837768728</v>
       </c>
     </row>
     <row r="536">
@@ -14436,7 +14436,7 @@
         <v>0.295588006696063</v>
       </c>
       <c r="D536" t="n">
-        <v>0.613617926043063</v>
+        <v>0.613617926043065</v>
       </c>
       <c r="E536" t="n">
         <v>1</v>
@@ -14514,7 +14514,7 @@
         <v>1</v>
       </c>
       <c r="D539" t="n">
-        <v>1.04841226243002</v>
+        <v>1.04841226243001</v>
       </c>
       <c r="E539" t="n">
         <v>0.0818045112781955</v>
@@ -14670,13 +14670,13 @@
         <v>0.426927985610727</v>
       </c>
       <c r="D545" t="n">
-        <v>0.956172587620082</v>
+        <v>0.956172587620057</v>
       </c>
       <c r="E545" t="n">
         <v>0.00311071934469938</v>
       </c>
       <c r="F545" t="n">
-        <v>0.844633936427559</v>
+        <v>0.844633936427574</v>
       </c>
       <c r="G545" t="n">
         <v>0.903190577085322</v>
@@ -14725,16 +14725,16 @@
         <v>1.47662089560566</v>
       </c>
       <c r="E547" t="n">
-        <v>0.00113250961264734</v>
+        <v>0.00113250961264735</v>
       </c>
       <c r="F547" t="n">
-        <v>0.970093316079188</v>
+        <v>0.970093316079171</v>
       </c>
       <c r="G547" t="n">
-        <v>0.987510756229052</v>
+        <v>0.987510756229053</v>
       </c>
       <c r="H547" t="n">
-        <v>0.999738456179314</v>
+        <v>0.999738456179308</v>
       </c>
     </row>
     <row r="548">
@@ -14748,19 +14748,19 @@
         <v>0</v>
       </c>
       <c r="D548" t="n">
-        <v>1.26013022027379</v>
+        <v>1.2601302202738</v>
       </c>
       <c r="E548" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000014542405137948</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000145424051379481</v>
       </c>
       <c r="F548" t="n">
-        <v>0.901063450392541</v>
+        <v>0.901063450392538</v>
       </c>
       <c r="G548" t="n">
         <v>0.398444846884837</v>
       </c>
       <c r="H548" t="n">
-        <v>1.00647716006942</v>
+        <v>1.00647716006948</v>
       </c>
     </row>
     <row r="549">
@@ -14771,22 +14771,22 @@
         <v>10</v>
       </c>
       <c r="C549" t="n">
-        <v>0.0000000000000000000000901178724369997</v>
+        <v>0.0000000000000000000000901178724369998</v>
       </c>
       <c r="D549" t="n">
-        <v>0.982587512575229</v>
+        <v>0.982587512575127</v>
       </c>
       <c r="E549" t="n">
-        <v>0.00000000000000174983296543548</v>
+        <v>0.00000000000000174983296543546</v>
       </c>
       <c r="F549" t="n">
-        <v>0.985410650966469</v>
+        <v>0.985410650966616</v>
       </c>
       <c r="G549" t="n">
-        <v>0.0000000000000000000000468557182068718</v>
+        <v>0.0000000000000000000000468557182068717</v>
       </c>
       <c r="H549" t="n">
-        <v>1.02756473329935</v>
+        <v>1.02756473329949</v>
       </c>
     </row>
     <row r="550">
@@ -14797,22 +14797,22 @@
         <v>11</v>
       </c>
       <c r="C550" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000565026930090693</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000565026930090692</v>
       </c>
       <c r="D550" t="n">
-        <v>1.58414983583554</v>
+        <v>1.58414983583553</v>
       </c>
       <c r="E550" t="n">
         <v>1</v>
       </c>
       <c r="F550" t="n">
-        <v>1.00117900966069</v>
+        <v>1.00117900966062</v>
       </c>
       <c r="G550" t="n">
         <v>0.0226557947757278</v>
       </c>
       <c r="H550" t="n">
-        <v>1.23459494916773</v>
+        <v>1.23459494916771</v>
       </c>
     </row>
     <row r="551">
@@ -14823,22 +14823,22 @@
         <v>12</v>
       </c>
       <c r="C551" t="n">
-        <v>0.0357873095555311</v>
+        <v>0.035787309555531</v>
       </c>
       <c r="D551" t="n">
-        <v>0.893743682366093</v>
+        <v>0.893743682366101</v>
       </c>
       <c r="E551" t="n">
-        <v>0.0617785746617942</v>
+        <v>0.0617785746617943</v>
       </c>
       <c r="F551" t="n">
-        <v>0.849176042192908</v>
+        <v>0.849176042192911</v>
       </c>
       <c r="G551" t="n">
         <v>0.390117245572529</v>
       </c>
       <c r="H551" t="n">
-        <v>1.12004430306009</v>
+        <v>1.12004430306011</v>
       </c>
     </row>
     <row r="552">
@@ -14852,19 +14852,19 @@
         <v>0.01181164295633</v>
       </c>
       <c r="D552" t="n">
-        <v>1.02425604521605</v>
+        <v>1.02425604521598</v>
       </c>
       <c r="E552" t="n">
-        <v>0.940736738314136</v>
+        <v>0.940736738314138</v>
       </c>
       <c r="F552" t="n">
-        <v>1.0008870202234</v>
+        <v>1.00088702022338</v>
       </c>
       <c r="G552" t="n">
-        <v>0.773210020214194</v>
+        <v>0.773210020214193</v>
       </c>
       <c r="H552" t="n">
-        <v>1.00508577035691</v>
+        <v>1.00508577035681</v>
       </c>
     </row>
     <row r="553">
@@ -14875,22 +14875,22 @@
         <v>14</v>
       </c>
       <c r="C553" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000530277637307493</v>
+        <v>0.000000000000000000000000000000000000000000000000000000530277637307499</v>
       </c>
       <c r="D553" t="n">
-        <v>1.1327811269443</v>
+        <v>1.13278112694424</v>
       </c>
       <c r="E553" t="n">
-        <v>0.423222005750652</v>
+        <v>0.423222005750651</v>
       </c>
       <c r="F553" t="n">
-        <v>1.01289331924702</v>
+        <v>1.01289331924696</v>
       </c>
       <c r="G553" t="n">
         <v>0.000293083159274119</v>
       </c>
       <c r="H553" t="n">
-        <v>0.912979602261699</v>
+        <v>0.912979602261696</v>
       </c>
     </row>
     <row r="554">
@@ -14904,19 +14904,19 @@
         <v>0.0000000405896934903348</v>
       </c>
       <c r="D554" t="n">
-        <v>0.912964737367532</v>
+        <v>0.912964737367525</v>
       </c>
       <c r="E554" t="n">
-        <v>0.97913311416856</v>
+        <v>0.979133114168559</v>
       </c>
       <c r="F554" t="n">
-        <v>1.00056903669891</v>
+        <v>1.0005690366989</v>
       </c>
       <c r="G554" t="n">
         <v>0.247376755810775</v>
       </c>
       <c r="H554" t="n">
-        <v>0.971650078829006</v>
+        <v>0.971650078829014</v>
       </c>
     </row>
     <row r="555">
@@ -14930,19 +14930,19 @@
         <v>0.0000133016728043304</v>
       </c>
       <c r="D555" t="n">
-        <v>0.895883052492861</v>
+        <v>0.895883052492849</v>
       </c>
       <c r="E555" t="n">
         <v>0.477936195029252</v>
       </c>
       <c r="F555" t="n">
-        <v>0.831470877519872</v>
+        <v>0.831470877519878</v>
       </c>
       <c r="G555" t="n">
         <v>0.252797801502818</v>
       </c>
       <c r="H555" t="n">
-        <v>0.7077490598903</v>
+        <v>0.707749059890277</v>
       </c>
     </row>
     <row r="556">
@@ -14959,16 +14959,16 @@
         <v>1.33277343749819</v>
       </c>
       <c r="E556" t="n">
-        <v>0.352186314233338</v>
+        <v>0.352186314233337</v>
       </c>
       <c r="F556" t="n">
-        <v>0.981520442110648</v>
+        <v>0.981520442110668</v>
       </c>
       <c r="G556" t="n">
         <v>0.104635822189358</v>
       </c>
       <c r="H556" t="n">
-        <v>1.05465068796775</v>
+        <v>1.05465068796777</v>
       </c>
     </row>
     <row r="557">
@@ -14982,7 +14982,7 @@
         <v>0.116449014343972</v>
       </c>
       <c r="D557" t="n">
-        <v>1.22576553872055</v>
+        <v>1.22576553872052</v>
       </c>
       <c r="E557" t="n">
         <v>0.201478249721491</v>
@@ -14994,7 +14994,7 @@
         <v>1</v>
       </c>
       <c r="H557" t="n">
-        <v>0.916044718645075</v>
+        <v>0.916044718645073</v>
       </c>
     </row>
     <row r="558">
@@ -15034,19 +15034,19 @@
         <v>0.000678414823384969</v>
       </c>
       <c r="D559" t="n">
-        <v>1.19651916202407</v>
+        <v>1.19651916202403</v>
       </c>
       <c r="E559" t="n">
         <v>0.0522795308829216</v>
       </c>
       <c r="F559" t="n">
-        <v>1.18410205171063</v>
+        <v>1.1841020517106</v>
       </c>
       <c r="G559" t="n">
         <v>0.839603266376229</v>
       </c>
       <c r="H559" t="n">
-        <v>1.0371560076586</v>
+        <v>1.03715600765861</v>
       </c>
     </row>
     <row r="560">
@@ -15060,7 +15060,7 @@
         <v>0.65797055208377</v>
       </c>
       <c r="D560" t="n">
-        <v>0.760548995430866</v>
+        <v>0.760548995430869</v>
       </c>
       <c r="E560" t="n">
         <v>1</v>
@@ -15092,13 +15092,13 @@
         <v>0.665171796495822</v>
       </c>
       <c r="F561" t="n">
-        <v>0.930048642018182</v>
+        <v>0.930048642018187</v>
       </c>
       <c r="G561" t="n">
         <v>0.0179482464820725</v>
       </c>
       <c r="H561" t="n">
-        <v>0.539841740691543</v>
+        <v>0.539841740691542</v>
       </c>
     </row>
     <row r="562">
@@ -15112,13 +15112,13 @@
         <v>0.0175145794724192</v>
       </c>
       <c r="D562" t="n">
-        <v>1.68938737924645</v>
+        <v>1.68938737924644</v>
       </c>
       <c r="E562" t="n">
         <v>0.419947701376824</v>
       </c>
       <c r="F562" t="n">
-        <v>0.827065792406683</v>
+        <v>0.827065792406685</v>
       </c>
       <c r="G562" t="n">
         <v>0.141750139261151</v>
@@ -15164,7 +15164,7 @@
         <v>0.366419533096439</v>
       </c>
       <c r="D564" t="n">
-        <v>0.691542340148791</v>
+        <v>0.691542340148794</v>
       </c>
       <c r="E564" t="n">
         <v>1</v>
@@ -15190,13 +15190,13 @@
         <v>0.763311236654901</v>
       </c>
       <c r="D565" t="n">
-        <v>1.11767410450624</v>
+        <v>1.11767410450625</v>
       </c>
       <c r="E565" t="n">
         <v>0.588470134920712</v>
       </c>
       <c r="F565" t="n">
-        <v>0.646993804795305</v>
+        <v>0.646993804795304</v>
       </c>
       <c r="G565" t="n">
         <v>1</v>
@@ -15213,22 +15213,22 @@
         <v>27</v>
       </c>
       <c r="C566" t="n">
-        <v>0.00000585847859410786</v>
+        <v>0.00000585847859410785</v>
       </c>
       <c r="D566" t="n">
-        <v>1.06311843397525</v>
+        <v>1.06311843397519</v>
       </c>
       <c r="E566" t="n">
         <v>0.000562162190433421</v>
       </c>
       <c r="F566" t="n">
-        <v>0.904673131731135</v>
+        <v>0.904673131731054</v>
       </c>
       <c r="G566" t="n">
         <v>0.200582895761237</v>
       </c>
       <c r="H566" t="n">
-        <v>0.943699739428979</v>
+        <v>0.943699739429003</v>
       </c>
     </row>
     <row r="567">
@@ -15239,22 +15239,22 @@
         <v>28</v>
       </c>
       <c r="C567" t="n">
-        <v>0.477167113825563</v>
+        <v>0.477167113825564</v>
       </c>
       <c r="D567" t="n">
-        <v>1.09246281145754</v>
+        <v>1.09246281145753</v>
       </c>
       <c r="E567" t="n">
         <v>0.279332018716921</v>
       </c>
       <c r="F567" t="n">
-        <v>0.870460147204187</v>
+        <v>0.870460147204182</v>
       </c>
       <c r="G567" t="n">
         <v>0.424810619382248</v>
       </c>
       <c r="H567" t="n">
-        <v>0.839048462059942</v>
+        <v>0.839048462059959</v>
       </c>
     </row>
     <row r="568">
@@ -15268,19 +15268,19 @@
         <v>0.582004514497404</v>
       </c>
       <c r="D568" t="n">
-        <v>1.07716797587559</v>
+        <v>1.07716797587562</v>
       </c>
       <c r="E568" t="n">
         <v>0.632848084157489</v>
       </c>
       <c r="F568" t="n">
-        <v>0.917726917778521</v>
+        <v>0.917726917778493</v>
       </c>
       <c r="G568" t="n">
         <v>0.551764311084268</v>
       </c>
       <c r="H568" t="n">
-        <v>0.854697361788367</v>
+        <v>0.854697361788374</v>
       </c>
     </row>
     <row r="569">
@@ -15294,19 +15294,19 @@
         <v>0.107845065245259</v>
       </c>
       <c r="D569" t="n">
-        <v>1.0244718150488</v>
+        <v>1.02447181504887</v>
       </c>
       <c r="E569" t="n">
-        <v>0.848039022722268</v>
+        <v>0.848039022722267</v>
       </c>
       <c r="F569" t="n">
-        <v>1.00359269215193</v>
+        <v>1.00359269215199</v>
       </c>
       <c r="G569" t="n">
         <v>0.0970422682251122</v>
       </c>
       <c r="H569" t="n">
-        <v>0.954439174599565</v>
+        <v>0.954439174599573</v>
       </c>
     </row>
     <row r="570">
@@ -15320,19 +15320,19 @@
         <v>1</v>
       </c>
       <c r="D570" t="n">
-        <v>0.978874376535362</v>
+        <v>0.978874376535348</v>
       </c>
       <c r="E570" t="n">
         <v>1</v>
       </c>
       <c r="F570" t="n">
-        <v>1.01708234052699</v>
+        <v>1.01708234052698</v>
       </c>
       <c r="G570" t="n">
         <v>0.355762513785293</v>
       </c>
       <c r="H570" t="n">
-        <v>1.60317878615511</v>
+        <v>1.60317878615509</v>
       </c>
     </row>
     <row r="571">
@@ -15346,19 +15346,19 @@
         <v>0.0106759775673831</v>
       </c>
       <c r="D571" t="n">
-        <v>1.10582062340873</v>
+        <v>1.10582062340869</v>
       </c>
       <c r="E571" t="n">
-        <v>0.0507840758364257</v>
+        <v>0.0507840758364256</v>
       </c>
       <c r="F571" t="n">
-        <v>1.12304676620179</v>
+        <v>1.12304676620181</v>
       </c>
       <c r="G571" t="n">
         <v>0.0244127557262492</v>
       </c>
       <c r="H571" t="n">
-        <v>0.818070890939139</v>
+        <v>0.818070890939117</v>
       </c>
     </row>
     <row r="572">
@@ -15369,22 +15369,22 @@
         <v>33</v>
       </c>
       <c r="C572" t="n">
-        <v>0.0000000000103977868343922</v>
+        <v>0.0000000000103977868343921</v>
       </c>
       <c r="D572" t="n">
-        <v>0.71570716254149</v>
+        <v>0.715707162541487</v>
       </c>
       <c r="E572" t="n">
         <v>0.295793671620832</v>
       </c>
       <c r="F572" t="n">
-        <v>0.943446876703646</v>
+        <v>0.943446876703656</v>
       </c>
       <c r="G572" t="n">
         <v>0.330436298976125</v>
       </c>
       <c r="H572" t="n">
-        <v>0.928959715298957</v>
+        <v>0.928959715298985</v>
       </c>
     </row>
     <row r="573">
@@ -15398,10 +15398,10 @@
         <v>0.0883725601834859</v>
       </c>
       <c r="D573" t="n">
-        <v>0.906795297470752</v>
+        <v>0.906795297470773</v>
       </c>
       <c r="E573" t="n">
-        <v>0.791238534894554</v>
+        <v>0.791238534894555</v>
       </c>
       <c r="F573" t="n">
         <v>1.02699893912439</v>
@@ -15410,7 +15410,7 @@
         <v>0.176216354863248</v>
       </c>
       <c r="H573" t="n">
-        <v>0.838252832560234</v>
+        <v>0.838252832560252</v>
       </c>
     </row>
     <row r="574">
@@ -15450,13 +15450,13 @@
         <v>0.608067501586568</v>
       </c>
       <c r="D575" t="n">
-        <v>1.12417894179551</v>
+        <v>1.12417894179553</v>
       </c>
       <c r="E575" t="n">
         <v>1</v>
       </c>
       <c r="F575" t="n">
-        <v>1.16269445227068</v>
+        <v>1.16269445227067</v>
       </c>
       <c r="G575" t="n">
         <v>1</v>
@@ -15502,7 +15502,7 @@
         <v>0.135820033492071</v>
       </c>
       <c r="D577" t="n">
-        <v>1.63287648769174</v>
+        <v>1.63287648769173</v>
       </c>
       <c r="E577" t="n">
         <v>1</v>
@@ -15528,19 +15528,19 @@
         <v>0.103814119045205</v>
       </c>
       <c r="D578" t="n">
-        <v>0.79301100043365</v>
+        <v>0.79301100043364</v>
       </c>
       <c r="E578" t="n">
         <v>0.472629438728859</v>
       </c>
       <c r="F578" t="n">
-        <v>1.11918519081712</v>
+        <v>1.11918519081713</v>
       </c>
       <c r="G578" t="n">
         <v>0.612681850819489</v>
       </c>
       <c r="H578" t="n">
-        <v>1.11715125027671</v>
+        <v>1.11715125027673</v>
       </c>
     </row>
     <row r="579">
@@ -15563,7 +15563,7 @@
         <v>1.6088485330933</v>
       </c>
       <c r="G579" t="n">
-        <v>0.500990099009902</v>
+        <v>0.500990099009901</v>
       </c>
       <c r="H579" t="s">
         <v>63</v>
@@ -15580,19 +15580,19 @@
         <v>0.513191773181467</v>
       </c>
       <c r="D580" t="n">
-        <v>1.08284667376261</v>
+        <v>1.08284667376262</v>
       </c>
       <c r="E580" t="n">
         <v>0.0118044077624771</v>
       </c>
       <c r="F580" t="n">
-        <v>1.48782470105429</v>
+        <v>1.4878247010543</v>
       </c>
       <c r="G580" t="n">
-        <v>0.0199100631913108</v>
+        <v>0.0199100631913107</v>
       </c>
       <c r="H580" t="n">
-        <v>0.558879910378678</v>
+        <v>0.558879910378669</v>
       </c>
     </row>
     <row r="581">
@@ -15606,19 +15606,19 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000114486948471904</v>
       </c>
       <c r="D581" t="n">
-        <v>1.12647794736734</v>
+        <v>1.12647794736732</v>
       </c>
       <c r="E581" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000724405737466697</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000724405737466698</v>
       </c>
       <c r="F581" t="n">
-        <v>0.916283184591474</v>
+        <v>0.916283184591501</v>
       </c>
       <c r="G581" t="n">
         <v>0.0000000000380188125632054</v>
       </c>
       <c r="H581" t="n">
-        <v>1.05790575920584</v>
+        <v>1.05790575920575</v>
       </c>
     </row>
     <row r="582">
@@ -15632,19 +15632,19 @@
         <v>0.0000000000000000000000000000000000000000000000000000200857004344256</v>
       </c>
       <c r="D582" t="n">
-        <v>1.20296426557243</v>
+        <v>1.20296426557246</v>
       </c>
       <c r="E582" t="n">
         <v>0.0000000000137270660704125</v>
       </c>
       <c r="F582" t="n">
-        <v>0.916636401113635</v>
+        <v>0.916636401113646</v>
       </c>
       <c r="G582" t="n">
         <v>0.0301833092752634</v>
       </c>
       <c r="H582" t="n">
-        <v>1.04535779974021</v>
+        <v>1.04535779974014</v>
       </c>
     </row>
     <row r="583">
@@ -15655,22 +15655,22 @@
         <v>10</v>
       </c>
       <c r="C583" t="n">
-        <v>0.00022028161412747</v>
+        <v>0.000220281614127469</v>
       </c>
       <c r="D583" t="n">
-        <v>1.03150345419104</v>
+        <v>1.03150345419103</v>
       </c>
       <c r="E583" t="n">
-        <v>0.0740630020272999</v>
+        <v>0.0740630020272998</v>
       </c>
       <c r="F583" t="n">
-        <v>0.984792717558788</v>
+        <v>0.984792717558826</v>
       </c>
       <c r="G583" t="n">
         <v>0.190241489376232</v>
       </c>
       <c r="H583" t="n">
-        <v>1.01719568869565</v>
+        <v>1.01719568869577</v>
       </c>
     </row>
     <row r="584">
@@ -15681,22 +15681,22 @@
         <v>11</v>
       </c>
       <c r="C584" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000112916612589645</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000112916612589647</v>
       </c>
       <c r="D584" t="n">
-        <v>1.71531751352835</v>
+        <v>1.71531751352842</v>
       </c>
       <c r="E584" t="n">
         <v>0.297794982478684</v>
       </c>
       <c r="F584" t="n">
-        <v>1.13404482609923</v>
+        <v>1.13404482609918</v>
       </c>
       <c r="G584" t="n">
         <v>0.134114611026097</v>
       </c>
       <c r="H584" t="n">
-        <v>0.729950924140929</v>
+        <v>0.729950924140931</v>
       </c>
     </row>
     <row r="585">
@@ -15710,19 +15710,19 @@
         <v>0.00000000000000000000000000000303490278333374</v>
       </c>
       <c r="D585" t="n">
-        <v>0.737230235106317</v>
+        <v>0.737230235106311</v>
       </c>
       <c r="E585" t="n">
         <v>0.185539092156289</v>
       </c>
       <c r="F585" t="n">
-        <v>0.944198429658717</v>
+        <v>0.94419842965871</v>
       </c>
       <c r="G585" t="n">
         <v>0.100254664667145</v>
       </c>
       <c r="H585" t="n">
-        <v>1.10520364748481</v>
+        <v>1.10520364748482</v>
       </c>
     </row>
     <row r="586">
@@ -15742,13 +15742,13 @@
         <v>0.457903442247923</v>
       </c>
       <c r="F586" t="n">
-        <v>0.973395483743301</v>
+        <v>0.973395483743337</v>
       </c>
       <c r="G586" t="n">
         <v>0.909459336764517</v>
       </c>
       <c r="H586" t="n">
-        <v>0.99212220778183</v>
+        <v>0.992122207781887</v>
       </c>
     </row>
     <row r="587">
@@ -15762,7 +15762,7 @@
         <v>0.0000783880601574023</v>
       </c>
       <c r="D587" t="n">
-        <v>1.34240947995506</v>
+        <v>1.34240947995507</v>
       </c>
       <c r="E587" t="n">
         <v>1</v>
@@ -15785,22 +15785,22 @@
         <v>15</v>
       </c>
       <c r="C588" t="n">
-        <v>0.0332746580660307</v>
+        <v>0.0332746580660306</v>
       </c>
       <c r="D588" t="n">
-        <v>0.892947457407687</v>
+        <v>0.892947457407697</v>
       </c>
       <c r="E588" t="n">
         <v>0.245608788573093</v>
       </c>
       <c r="F588" t="n">
-        <v>1.06641120250725</v>
+        <v>1.06641120250724</v>
       </c>
       <c r="G588" t="n">
         <v>0.640305032278429</v>
       </c>
       <c r="H588" t="n">
-        <v>1.03927118118863</v>
+        <v>1.03927118118862</v>
       </c>
     </row>
     <row r="589">
@@ -15814,19 +15814,19 @@
         <v>0.197305916947396</v>
       </c>
       <c r="D589" t="n">
-        <v>0.976666123250901</v>
+        <v>0.976666123250916</v>
       </c>
       <c r="E589" t="n">
         <v>0.689722396346315</v>
       </c>
       <c r="F589" t="n">
-        <v>0.910225401440645</v>
+        <v>0.910225401440779</v>
       </c>
       <c r="G589" t="n">
         <v>0.302410377411535</v>
       </c>
       <c r="H589" t="n">
-        <v>1.38378473898783</v>
+        <v>1.38378473898769</v>
       </c>
     </row>
     <row r="590">
@@ -15837,22 +15837,22 @@
         <v>17</v>
       </c>
       <c r="C590" t="n">
-        <v>0.0000000000000000000000000680166354417683</v>
+        <v>0.0000000000000000000000000680166354417684</v>
       </c>
       <c r="D590" t="n">
-        <v>1.35808786562185</v>
+        <v>1.35808786562186</v>
       </c>
       <c r="E590" t="n">
         <v>0.206219786356027</v>
       </c>
       <c r="F590" t="n">
-        <v>1.04064708800556</v>
+        <v>1.04064708800552</v>
       </c>
       <c r="G590" t="n">
         <v>0.460298005088185</v>
       </c>
       <c r="H590" t="n">
-        <v>1.03876746859239</v>
+        <v>1.03876746859236</v>
       </c>
     </row>
     <row r="591">
@@ -15872,13 +15872,13 @@
         <v>0.109485700804602</v>
       </c>
       <c r="F591" t="n">
-        <v>1.70176177017617</v>
+        <v>1.70176177017613</v>
       </c>
       <c r="G591" t="n">
         <v>0.812680194224799</v>
       </c>
       <c r="H591" t="n">
-        <v>0.873130431999708</v>
+        <v>0.873130431999707</v>
       </c>
     </row>
     <row r="592">
@@ -15944,19 +15944,19 @@
         <v>0</v>
       </c>
       <c r="D594" t="n">
-        <v>1.31733823119515</v>
+        <v>1.31733823119513</v>
       </c>
       <c r="E594" t="n">
         <v>0.0000378010488935427</v>
       </c>
       <c r="F594" t="n">
-        <v>0.976613079650841</v>
+        <v>0.976613079650848</v>
       </c>
       <c r="G594" t="n">
-        <v>0.00000000000000000000000000000310714318491429</v>
+        <v>0.00000000000000000000000000000310714318491428</v>
       </c>
       <c r="H594" t="n">
-        <v>1.11412332411305</v>
+        <v>1.11412332411319</v>
       </c>
     </row>
     <row r="595">
@@ -15970,19 +15970,19 @@
         <v>0.238268053073943</v>
       </c>
       <c r="D595" t="n">
-        <v>1.22994822427617</v>
+        <v>1.22994822427618</v>
       </c>
       <c r="E595" t="n">
         <v>0.866907113399774</v>
       </c>
       <c r="F595" t="n">
-        <v>0.961046809750555</v>
+        <v>0.961046809750562</v>
       </c>
       <c r="G595" t="n">
         <v>0.0626717839928048</v>
       </c>
       <c r="H595" t="n">
-        <v>0.5867403828403</v>
+        <v>0.586740382840292</v>
       </c>
     </row>
     <row r="596">
@@ -16097,22 +16097,22 @@
         <v>27</v>
       </c>
       <c r="C600" t="n">
-        <v>0.000000000000000000565205486304363</v>
+        <v>0.000000000000000000565205486304364</v>
       </c>
       <c r="D600" t="n">
-        <v>1.12221082397626</v>
+        <v>1.12221082397627</v>
       </c>
       <c r="E600" t="n">
         <v>0.000000000000000000502633891203517</v>
       </c>
       <c r="F600" t="n">
-        <v>0.79261459946486</v>
+        <v>0.792614599464861</v>
       </c>
       <c r="G600" t="n">
         <v>0.00000000239729795739537</v>
       </c>
       <c r="H600" t="n">
-        <v>1.28378930103745</v>
+        <v>1.28378930103738</v>
       </c>
     </row>
     <row r="601">
@@ -16123,16 +16123,16 @@
         <v>28</v>
       </c>
       <c r="C601" t="n">
-        <v>0.246445426790626</v>
+        <v>0.246445426790625</v>
       </c>
       <c r="D601" t="n">
-        <v>1.24169428770345</v>
+        <v>1.24169428770348</v>
       </c>
       <c r="E601" t="n">
         <v>0.657163950936331</v>
       </c>
       <c r="F601" t="n">
-        <v>0.896126458690365</v>
+        <v>0.896126458690358</v>
       </c>
       <c r="G601" t="n">
         <v>0.723628353503296</v>
@@ -16152,19 +16152,19 @@
         <v>0.000403416677594299</v>
       </c>
       <c r="D602" t="n">
-        <v>1.21930147154025</v>
+        <v>1.21930147154026</v>
       </c>
       <c r="E602" t="n">
         <v>0.245272911674504</v>
       </c>
       <c r="F602" t="n">
-        <v>0.930319023438413</v>
+        <v>0.930319023438389</v>
       </c>
       <c r="G602" t="n">
         <v>0.00287311290647862</v>
       </c>
       <c r="H602" t="n">
-        <v>1.3402991056905</v>
+        <v>1.34029910569049</v>
       </c>
     </row>
     <row r="603">
@@ -16178,19 +16178,19 @@
         <v>0.027501459105805</v>
       </c>
       <c r="D603" t="n">
-        <v>1.06535475159668</v>
+        <v>1.06535475159664</v>
       </c>
       <c r="E603" t="n">
-        <v>0.0792218536211643</v>
+        <v>0.0792218536211644</v>
       </c>
       <c r="F603" t="n">
-        <v>0.939658375216795</v>
+        <v>0.939658375216784</v>
       </c>
       <c r="G603" t="n">
         <v>0.062139510328732</v>
       </c>
       <c r="H603" t="n">
-        <v>1.10801379469032</v>
+        <v>1.10801379469034</v>
       </c>
     </row>
     <row r="604">
@@ -16201,22 +16201,22 @@
         <v>31</v>
       </c>
       <c r="C604" t="n">
-        <v>0.525164480278591</v>
+        <v>0.525164480278592</v>
       </c>
       <c r="D604" t="n">
-        <v>1.08007255651599</v>
+        <v>1.08007255651598</v>
       </c>
       <c r="E604" t="n">
         <v>0.260612066542524</v>
       </c>
       <c r="F604" t="n">
-        <v>0.874035157423808</v>
+        <v>0.874035157423814</v>
       </c>
       <c r="G604" t="n">
         <v>0.150304203978566</v>
       </c>
       <c r="H604" t="n">
-        <v>1.30981308552282</v>
+        <v>1.30981308552283</v>
       </c>
     </row>
     <row r="605">
@@ -16230,19 +16230,19 @@
         <v>0.000362566446932001</v>
       </c>
       <c r="D605" t="n">
-        <v>1.26780398221398</v>
+        <v>1.26780398221392</v>
       </c>
       <c r="E605" t="n">
         <v>0.236625984476885</v>
       </c>
       <c r="F605" t="n">
-        <v>1.09246644842182</v>
+        <v>1.09246644842183</v>
       </c>
       <c r="G605" t="n">
         <v>0.555333126059376</v>
       </c>
       <c r="H605" t="n">
-        <v>0.933467909119711</v>
+        <v>0.933467909119703</v>
       </c>
     </row>
     <row r="606">
@@ -16253,22 +16253,22 @@
         <v>33</v>
       </c>
       <c r="C606" t="n">
-        <v>0.000723663044730819</v>
+        <v>0.00072366304473082</v>
       </c>
       <c r="D606" t="n">
-        <v>0.838782210102731</v>
+        <v>0.838782210102727</v>
       </c>
       <c r="E606" t="n">
         <v>0.976302869522768</v>
       </c>
       <c r="F606" t="n">
-        <v>0.997020992539955</v>
+        <v>0.997020992540001</v>
       </c>
       <c r="G606" t="n">
         <v>0.409293803034942</v>
       </c>
       <c r="H606" t="n">
-        <v>0.932296174501442</v>
+        <v>0.932296174501439</v>
       </c>
     </row>
     <row r="607">
@@ -16282,7 +16282,7 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000262891470685043</v>
       </c>
       <c r="D607" t="n">
-        <v>0.658782253261498</v>
+        <v>0.658782253261492</v>
       </c>
       <c r="E607" t="n">
         <v>0.00000290356953755593</v>
@@ -16291,10 +16291,10 @@
         <v>1.16821891787551</v>
       </c>
       <c r="G607" t="n">
-        <v>0.0000000000000000000000000178156291393392</v>
+        <v>0.0000000000000000000000000178156291393394</v>
       </c>
       <c r="H607" t="n">
-        <v>0.616886017767347</v>
+        <v>0.61688601776734</v>
       </c>
     </row>
     <row r="608">
@@ -16308,7 +16308,7 @@
         <v>0.000516437493650053</v>
       </c>
       <c r="D608" t="n">
-        <v>1.2802460338843</v>
+        <v>1.28024603388429</v>
       </c>
       <c r="E608" t="n">
         <v>1</v>
@@ -16320,7 +16320,7 @@
         <v>0.0000340160779636234</v>
       </c>
       <c r="H608" t="n">
-        <v>1.68963738119493</v>
+        <v>1.68963738119492</v>
       </c>
     </row>
     <row r="609">
@@ -16334,13 +16334,13 @@
         <v>0.052570750225723</v>
       </c>
       <c r="D609" t="n">
-        <v>0.930952569922767</v>
+        <v>0.930952569922748</v>
       </c>
       <c r="E609" t="n">
         <v>0.46559118847277</v>
       </c>
       <c r="F609" t="n">
-        <v>0.82976260113</v>
+        <v>0.829762601130022</v>
       </c>
       <c r="G609" t="n">
         <v>0.250807185169289</v>
@@ -16360,19 +16360,19 @@
         <v>0.00000141367836876089</v>
       </c>
       <c r="D610" t="n">
-        <v>1.45373258158161</v>
+        <v>1.45373258158164</v>
       </c>
       <c r="E610" t="n">
         <v>0.235449830491758</v>
       </c>
       <c r="F610" t="n">
-        <v>1.09978140309418</v>
+        <v>1.09978140309417</v>
       </c>
       <c r="G610" t="n">
         <v>0.404131876235905</v>
       </c>
       <c r="H610" t="n">
-        <v>1.1189853077171</v>
+        <v>1.11898530771712</v>
       </c>
     </row>
     <row r="611">
@@ -16386,19 +16386,19 @@
         <v>0.136984897201509</v>
       </c>
       <c r="D611" t="n">
-        <v>1.08677469901706</v>
+        <v>1.08677469901704</v>
       </c>
       <c r="E611" t="n">
         <v>0.00465156259957712</v>
       </c>
       <c r="F611" t="n">
-        <v>1.35627026863182</v>
+        <v>1.35627026863178</v>
       </c>
       <c r="G611" t="n">
         <v>0.535025703304809</v>
       </c>
       <c r="H611" t="n">
-        <v>0.890132534246287</v>
+        <v>0.890132534246319</v>
       </c>
     </row>
     <row r="612">
@@ -16438,7 +16438,7 @@
         <v>0.000226886648236892</v>
       </c>
       <c r="D613" t="n">
-        <v>0.434950510339339</v>
+        <v>0.43495051033933</v>
       </c>
       <c r="E613" t="n">
         <v>0.654587150409877</v>
@@ -16447,10 +16447,10 @@
         <v>1.1138330954873</v>
       </c>
       <c r="G613" t="n">
-        <v>0.889022360240232</v>
+        <v>0.889022360240231</v>
       </c>
       <c r="H613" t="n">
-        <v>1.07242739858942</v>
+        <v>1.07242739858941</v>
       </c>
     </row>
     <row r="614">
@@ -16464,7 +16464,7 @@
         <v>0.0537997781250105</v>
       </c>
       <c r="D614" t="n">
-        <v>0.253456907048442</v>
+        <v>0.253456907048444</v>
       </c>
       <c r="E614" t="n">
         <v>0.506211180124224</v>
@@ -16490,19 +16490,19 @@
         <v>0.0000000000000000000000000000000000000000000000000117604354614253</v>
       </c>
       <c r="D615" t="n">
-        <v>1.25345546535025</v>
+        <v>1.25345546535023</v>
       </c>
       <c r="E615" t="n">
         <v>0.000000000766058214074198</v>
       </c>
       <c r="F615" t="n">
-        <v>0.911587715705529</v>
+        <v>0.911587715705606</v>
       </c>
       <c r="G615" t="n">
         <v>0.0299360393505606</v>
       </c>
       <c r="H615" t="n">
-        <v>1.05365953828764</v>
+        <v>1.05365953828765</v>
       </c>
     </row>
     <row r="616">
@@ -16516,19 +16516,19 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000187283444021136</v>
       </c>
       <c r="D616" t="n">
-        <v>1.29934698551896</v>
+        <v>1.29934698551889</v>
       </c>
       <c r="E616" t="n">
-        <v>0.00000000000000798659683463916</v>
+        <v>0.00000000000000798659683463918</v>
       </c>
       <c r="F616" t="n">
-        <v>0.894746150381507</v>
+        <v>0.894746150381456</v>
       </c>
       <c r="G616" t="n">
         <v>0.990644574179999</v>
       </c>
       <c r="H616" t="n">
-        <v>1.00044982397969</v>
+        <v>1.00044982397968</v>
       </c>
     </row>
     <row r="617">
@@ -16539,22 +16539,22 @@
         <v>10</v>
       </c>
       <c r="C617" t="n">
-        <v>0.000000000000000000116474261663494</v>
+        <v>0.000000000000000000116474261663493</v>
       </c>
       <c r="D617" t="n">
-        <v>0.978156191868789</v>
+        <v>0.978156191868827</v>
       </c>
       <c r="E617" t="n">
-        <v>0.0449143287503612</v>
+        <v>0.0449143287503613</v>
       </c>
       <c r="F617" t="n">
-        <v>1.00499335786359</v>
+        <v>1.00499335786354</v>
       </c>
       <c r="G617" t="n">
-        <v>0.000622631487167527</v>
+        <v>0.000622631487167529</v>
       </c>
       <c r="H617" t="n">
-        <v>1.01274901724209</v>
+        <v>1.01274901724214</v>
       </c>
     </row>
     <row r="618">
@@ -16594,7 +16594,7 @@
         <v>0.550739726347398</v>
       </c>
       <c r="D619" t="n">
-        <v>1.0495007447344</v>
+        <v>1.04950074473438</v>
       </c>
       <c r="E619" t="n">
         <v>0.791067208661289</v>
@@ -16603,7 +16603,7 @@
         <v>1.04285402649149</v>
       </c>
       <c r="G619" t="n">
-        <v>0.840896344473761</v>
+        <v>0.84089634447376</v>
       </c>
       <c r="H619" t="n">
         <v>1.05713096539496</v>
@@ -16617,22 +16617,22 @@
         <v>13</v>
       </c>
       <c r="C620" t="n">
-        <v>0.0000000232552211633656</v>
+        <v>0.0000000232552211633657</v>
       </c>
       <c r="D620" t="n">
         <v>1.16876067351878</v>
       </c>
       <c r="E620" t="n">
-        <v>0.443939805654396</v>
+        <v>0.443939805654395</v>
       </c>
       <c r="F620" t="n">
-        <v>1.02733198817297</v>
+        <v>1.02733198817295</v>
       </c>
       <c r="G620" t="n">
-        <v>0.676881967565688</v>
+        <v>0.676881967565687</v>
       </c>
       <c r="H620" t="n">
-        <v>0.976322211192232</v>
+        <v>0.976322211192233</v>
       </c>
     </row>
     <row r="621">
@@ -16643,22 +16643,22 @@
         <v>14</v>
       </c>
       <c r="C621" t="n">
-        <v>0.0000565064563636961</v>
+        <v>0.000056506456363696</v>
       </c>
       <c r="D621" t="n">
-        <v>1.10066623146567</v>
+        <v>1.10066623146569</v>
       </c>
       <c r="E621" t="n">
         <v>0.713157679992947</v>
       </c>
       <c r="F621" t="n">
-        <v>0.981548888749698</v>
+        <v>0.981548888749729</v>
       </c>
       <c r="G621" t="n">
-        <v>0.0075296542049003</v>
+        <v>0.00752965420490029</v>
       </c>
       <c r="H621" t="n">
-        <v>0.815107322873765</v>
+        <v>0.815107322873766</v>
       </c>
     </row>
     <row r="622">
@@ -16669,22 +16669,22 @@
         <v>15</v>
       </c>
       <c r="C622" t="n">
-        <v>0.0000000443978478781202</v>
+        <v>0.0000000443978478781203</v>
       </c>
       <c r="D622" t="n">
-        <v>0.883737311891886</v>
+        <v>0.883737311891888</v>
       </c>
       <c r="E622" t="n">
-        <v>0.805088301993657</v>
+        <v>0.805088301993656</v>
       </c>
       <c r="F622" t="n">
-        <v>0.994207247710006</v>
+        <v>0.994207247709976</v>
       </c>
       <c r="G622" t="n">
         <v>0.0486568274262946</v>
       </c>
       <c r="H622" t="n">
-        <v>0.936959499778339</v>
+        <v>0.936959499778372</v>
       </c>
     </row>
     <row r="623">
@@ -16724,19 +16724,19 @@
         <v>0.0324134792413608</v>
       </c>
       <c r="D624" t="n">
-        <v>1.13126139429004</v>
+        <v>1.13126139429003</v>
       </c>
       <c r="E624" t="n">
         <v>0.3726129217927</v>
       </c>
       <c r="F624" t="n">
-        <v>1.06351545374967</v>
+        <v>1.0635154537497</v>
       </c>
       <c r="G624" t="n">
         <v>0.739382742580521</v>
       </c>
       <c r="H624" t="n">
-        <v>1.0409004718622</v>
+        <v>1.04090047186219</v>
       </c>
     </row>
     <row r="625">
@@ -16750,7 +16750,7 @@
         <v>0.186511800290635</v>
       </c>
       <c r="D625" t="n">
-        <v>1.52559637584659</v>
+        <v>1.5255963758466</v>
       </c>
       <c r="E625" t="n">
         <v>1</v>
@@ -16776,7 +16776,7 @@
         <v>0.0613545059787978</v>
       </c>
       <c r="D626" t="n">
-        <v>0.141875663815531</v>
+        <v>0.14187566381553</v>
       </c>
       <c r="E626" t="n">
         <v>1</v>
@@ -16854,19 +16854,19 @@
         <v>0.000000000780111531073748</v>
       </c>
       <c r="D629" t="n">
-        <v>1.23221982740504</v>
+        <v>1.23221982740503</v>
       </c>
       <c r="E629" t="n">
         <v>0.157339381544812</v>
       </c>
       <c r="F629" t="n">
-        <v>0.950375891944806</v>
+        <v>0.950375891944823</v>
       </c>
       <c r="G629" t="n">
-        <v>0.0000000000000000000280395970516483</v>
+        <v>0.000000000000000000028039597051647</v>
       </c>
       <c r="H629" t="n">
-        <v>0.586488461713181</v>
+        <v>0.586488461713184</v>
       </c>
     </row>
     <row r="630">
@@ -16984,19 +16984,19 @@
         <v>0.485710594137957</v>
       </c>
       <c r="D634" t="n">
-        <v>0.965602493809159</v>
+        <v>0.965602493809157</v>
       </c>
       <c r="E634" t="n">
         <v>0.954574240269905</v>
       </c>
       <c r="F634" t="n">
-        <v>1.0128277981268</v>
+        <v>1.01282779812677</v>
       </c>
       <c r="G634" t="n">
         <v>0.231548943651217</v>
       </c>
       <c r="H634" t="n">
-        <v>0.813847783264067</v>
+        <v>0.813847783264065</v>
       </c>
     </row>
     <row r="635">
@@ -17036,16 +17036,16 @@
         <v>0.847294328502584</v>
       </c>
       <c r="D636" t="n">
-        <v>0.882741057712376</v>
+        <v>0.882741057712373</v>
       </c>
       <c r="E636" t="n">
         <v>0.0784596566133361</v>
       </c>
       <c r="F636" t="n">
-        <v>2.08935752661585</v>
+        <v>2.08935752661584</v>
       </c>
       <c r="G636" t="n">
-        <v>0.786818182856486</v>
+        <v>0.786818182856487</v>
       </c>
       <c r="H636" t="n">
         <v>0.80461713023101</v>
@@ -17062,7 +17062,7 @@
         <v>0.00179369584059632</v>
       </c>
       <c r="D637" t="n">
-        <v>1.24865192538862</v>
+        <v>1.24865192538861</v>
       </c>
       <c r="E637" t="n">
         <v>0.165945841621359</v>
@@ -17114,19 +17114,19 @@
         <v>0</v>
       </c>
       <c r="D639" t="n">
-        <v>0.761881055999235</v>
+        <v>0.761881055999286</v>
       </c>
       <c r="E639" t="n">
-        <v>0.000000000324493718510989</v>
+        <v>0.000000000324493718510988</v>
       </c>
       <c r="F639" t="n">
-        <v>0.973109155276097</v>
+        <v>0.973109155276009</v>
       </c>
       <c r="G639" t="n">
-        <v>0.0000000488756601842671</v>
+        <v>0.0000000488756601842672</v>
       </c>
       <c r="H639" t="n">
-        <v>1.03363279741342</v>
+        <v>1.03363279741335</v>
       </c>
     </row>
     <row r="640">
@@ -17163,7 +17163,7 @@
         <v>34</v>
       </c>
       <c r="C641" t="n">
-        <v>0.090855226255454</v>
+        <v>0.0908552262554538</v>
       </c>
       <c r="D641" t="n">
         <v>1.92003676479659</v>
@@ -17172,13 +17172,13 @@
         <v>0.0314995815817196</v>
       </c>
       <c r="F641" t="n">
-        <v>0.128252991867676</v>
+        <v>0.128252991867678</v>
       </c>
       <c r="G641" t="n">
         <v>1</v>
       </c>
       <c r="H641" t="n">
-        <v>0.908249169223652</v>
+        <v>0.908249169223649</v>
       </c>
     </row>
     <row r="642">
@@ -17192,19 +17192,19 @@
         <v>0.642649831174912</v>
       </c>
       <c r="D642" t="n">
-        <v>1.05126104865504</v>
+        <v>1.05126104865505</v>
       </c>
       <c r="E642" t="n">
         <v>0.236109176458635</v>
       </c>
       <c r="F642" t="n">
-        <v>0.851867006150873</v>
+        <v>0.851867006150867</v>
       </c>
       <c r="G642" t="n">
         <v>0.00128835566076163</v>
       </c>
       <c r="H642" t="n">
-        <v>1.99208905244977</v>
+        <v>1.99208905244979</v>
       </c>
     </row>
     <row r="643">
@@ -17322,7 +17322,7 @@
         <v>0.000195513729381624</v>
       </c>
       <c r="D647" t="n">
-        <v>0.874717926468135</v>
+        <v>0.874717926468191</v>
       </c>
       <c r="E647" t="n">
         <v>0.073123455088461</v>
@@ -17334,7 +17334,7 @@
         <v>0.00463816342144581</v>
       </c>
       <c r="H647" t="n">
-        <v>0.839630061161557</v>
+        <v>0.83963006116154</v>
       </c>
     </row>
     <row r="648">
@@ -17374,19 +17374,19 @@
         <v>1.08928615188143e-257</v>
       </c>
       <c r="D649" t="n">
-        <v>1.34173769321107</v>
+        <v>1.34173769321113</v>
       </c>
       <c r="E649" t="n">
         <v>0.0000000000000000000116912756163838</v>
       </c>
       <c r="F649" t="n">
-        <v>0.921725630121333</v>
+        <v>0.921725630121216</v>
       </c>
       <c r="G649" t="n">
-        <v>0.0376754054277159</v>
+        <v>0.0376754054277158</v>
       </c>
       <c r="H649" t="n">
-        <v>1.03036086657439</v>
+        <v>1.03036086657434</v>
       </c>
     </row>
     <row r="650">
@@ -17397,22 +17397,22 @@
         <v>9</v>
       </c>
       <c r="C650" t="n">
-        <v>0.000904507487429824</v>
+        <v>0.000904507487429823</v>
       </c>
       <c r="D650" t="n">
-        <v>1.14050060608454</v>
+        <v>1.14050060608455</v>
       </c>
       <c r="E650" t="n">
         <v>0.008440271416077</v>
       </c>
       <c r="F650" t="n">
-        <v>0.886715743270421</v>
+        <v>0.886715743270454</v>
       </c>
       <c r="G650" t="n">
-        <v>0.13113598237882</v>
+        <v>0.131135982378819</v>
       </c>
       <c r="H650" t="n">
-        <v>1.11818808271227</v>
+        <v>1.11818808271222</v>
       </c>
     </row>
     <row r="651">
@@ -17426,7 +17426,7 @@
         <v>0.0000270132113053105</v>
       </c>
       <c r="D651" t="n">
-        <v>1.58505232305043</v>
+        <v>1.58505232305039</v>
       </c>
       <c r="E651" t="n">
         <v>0.161735329128833</v>
@@ -17438,7 +17438,7 @@
         <v>0.282761883740804</v>
       </c>
       <c r="H651" t="n">
-        <v>0.792581117193117</v>
+        <v>0.792581117193123</v>
       </c>
     </row>
     <row r="652">
@@ -17452,19 +17452,19 @@
         <v>0.0224525020745314</v>
       </c>
       <c r="D652" t="n">
-        <v>1.32639744480792</v>
+        <v>1.3263974448079</v>
       </c>
       <c r="E652" t="n">
         <v>0.345130745394954</v>
       </c>
       <c r="F652" t="n">
-        <v>0.846875528298833</v>
+        <v>0.846875528298853</v>
       </c>
       <c r="G652" t="n">
         <v>0.35828206615863</v>
       </c>
       <c r="H652" t="n">
-        <v>0.779015523313533</v>
+        <v>0.779015523313498</v>
       </c>
     </row>
     <row r="653">
@@ -17478,19 +17478,19 @@
         <v>1</v>
       </c>
       <c r="D653" t="n">
-        <v>0.998680037569601</v>
+        <v>0.998680037569586</v>
       </c>
       <c r="E653" t="n">
         <v>0.0825418025031519</v>
       </c>
       <c r="F653" t="n">
-        <v>2.23453157480064</v>
+        <v>2.2345315748006</v>
       </c>
       <c r="G653" t="n">
         <v>0.140489966196215</v>
       </c>
       <c r="H653" t="n">
-        <v>0.374893617896945</v>
+        <v>0.374893617896944</v>
       </c>
     </row>
     <row r="654">
@@ -17504,19 +17504,19 @@
         <v>0.889110277569071</v>
       </c>
       <c r="D654" t="n">
-        <v>0.988735915754884</v>
+        <v>0.988735915754899</v>
       </c>
       <c r="E654" t="n">
         <v>1</v>
       </c>
       <c r="F654" t="n">
-        <v>1.01106968618506</v>
+        <v>1.01106968618516</v>
       </c>
       <c r="G654" t="n">
         <v>0.269023038497323</v>
       </c>
       <c r="H654" t="n">
-        <v>1.44732630876824</v>
+        <v>1.44732630876818</v>
       </c>
     </row>
     <row r="655">
@@ -17530,7 +17530,7 @@
         <v>1</v>
       </c>
       <c r="D655" t="n">
-        <v>1.07176568437401</v>
+        <v>1.071765684374</v>
       </c>
       <c r="E655" t="n">
         <v>1</v>
@@ -17582,19 +17582,19 @@
         <v>0.286275338199817</v>
       </c>
       <c r="D657" t="n">
-        <v>0.85480831197375</v>
+        <v>0.854808311973745</v>
       </c>
       <c r="E657" t="n">
         <v>0.276406159049098</v>
       </c>
       <c r="F657" t="n">
-        <v>1.68682671549102</v>
+        <v>1.68682671549104</v>
       </c>
       <c r="G657" t="n">
         <v>0.27934018787812</v>
       </c>
       <c r="H657" t="n">
-        <v>0.385853903424555</v>
+        <v>0.385853903424546</v>
       </c>
     </row>
     <row r="658">
@@ -17634,7 +17634,7 @@
         <v>0.816032278301833</v>
       </c>
       <c r="D659" t="n">
-        <v>0.885554092982598</v>
+        <v>0.885554092982603</v>
       </c>
       <c r="E659" t="n">
         <v>1</v>
@@ -17686,7 +17686,7 @@
         <v>0.4488689349639</v>
       </c>
       <c r="D661" t="n">
-        <v>1.19515606553228</v>
+        <v>1.19515606553227</v>
       </c>
       <c r="E661" t="n">
         <v>1</v>
@@ -17738,19 +17738,19 @@
         <v>0.0000362014580240889</v>
       </c>
       <c r="D663" t="n">
-        <v>1.43787404344863</v>
+        <v>1.43787404344862</v>
       </c>
       <c r="E663" t="n">
         <v>0.0174688440917484</v>
       </c>
       <c r="F663" t="n">
-        <v>0.79896853934363</v>
+        <v>0.798968539343655</v>
       </c>
       <c r="G663" t="n">
         <v>0.104990278139993</v>
       </c>
       <c r="H663" t="n">
-        <v>0.773512647729752</v>
+        <v>0.773512647729767</v>
       </c>
     </row>
     <row r="664">
@@ -17764,7 +17764,7 @@
         <v>0.523208033688722</v>
       </c>
       <c r="D664" t="n">
-        <v>0.760840046714955</v>
+        <v>0.760840046714958</v>
       </c>
       <c r="E664" t="n">
         <v>1</v>
@@ -17868,16 +17868,16 @@
         <v>0.0746821710141107</v>
       </c>
       <c r="D668" t="n">
-        <v>1.12014607257619</v>
+        <v>1.12014607257617</v>
       </c>
       <c r="E668" t="n">
         <v>0.460151581293896</v>
       </c>
       <c r="F668" t="n">
-        <v>0.915572556904227</v>
+        <v>0.91557255690422</v>
       </c>
       <c r="G668" t="n">
-        <v>0.0677782248967006</v>
+        <v>0.0677782248967007</v>
       </c>
       <c r="H668" t="n">
         <v>1.36579513974921</v>
@@ -17894,7 +17894,7 @@
         <v>1</v>
       </c>
       <c r="D669" t="n">
-        <v>0.947730885907055</v>
+        <v>0.947730885907057</v>
       </c>
       <c r="E669" t="n">
         <v>1</v>
@@ -17920,7 +17920,7 @@
         <v>0.580770457484514</v>
       </c>
       <c r="D670" t="n">
-        <v>0.886818198797736</v>
+        <v>0.886818198797737</v>
       </c>
       <c r="E670" t="n">
         <v>1</v>
@@ -17946,7 +17946,7 @@
         <v>0.682903374442729</v>
       </c>
       <c r="D671" t="n">
-        <v>0.972255732712673</v>
+        <v>0.972255732712633</v>
       </c>
       <c r="E671" t="n">
         <v>0.169925431398435</v>
@@ -17955,10 +17955,10 @@
         <v>1.21134096488934</v>
       </c>
       <c r="G671" t="n">
-        <v>0.556708083899851</v>
+        <v>0.556708083899852</v>
       </c>
       <c r="H671" t="n">
-        <v>1.13368945530951</v>
+        <v>1.13368945530954</v>
       </c>
     </row>
     <row r="672">
@@ -17972,7 +17972,7 @@
         <v>1</v>
       </c>
       <c r="D672" t="n">
-        <v>1.0603971160782</v>
+        <v>1.06039711607821</v>
       </c>
       <c r="E672" t="n">
         <v>1</v>
@@ -18024,7 +18024,7 @@
         <v>0.809712676385802</v>
       </c>
       <c r="D674" t="n">
-        <v>0.844734676344329</v>
+        <v>0.844734676344332</v>
       </c>
       <c r="E674" t="n">
         <v>1</v>
@@ -18076,7 +18076,7 @@
         <v>0.057604203962312</v>
       </c>
       <c r="D676" t="n">
-        <v>0.359555070493094</v>
+        <v>0.3595550704931</v>
       </c>
       <c r="E676" t="n">
         <v>1</v>
@@ -18128,7 +18128,7 @@
         <v>0.637705493421365</v>
       </c>
       <c r="D678" t="n">
-        <v>2.14409108840398</v>
+        <v>2.14409108840399</v>
       </c>
       <c r="E678" t="n">
         <v>1</v>
@@ -18151,16 +18151,16 @@
         <v>38</v>
       </c>
       <c r="C679" t="n">
-        <v>0.905024821575117</v>
+        <v>0.905024821575116</v>
       </c>
       <c r="D679" t="n">
-        <v>1.05472457774752</v>
+        <v>1.05472457774751</v>
       </c>
       <c r="E679" t="n">
         <v>0.220025307179764</v>
       </c>
       <c r="F679" t="n">
-        <v>0.218304424476442</v>
+        <v>0.218304424476441</v>
       </c>
       <c r="G679" t="n">
         <v>0.509624401138902</v>
@@ -18255,22 +18255,22 @@
         <v>42</v>
       </c>
       <c r="C683" t="n">
-        <v>0.00000000000000000000000000000000419774556726734</v>
+        <v>0.0000000000000000000000000000000041977455672673</v>
       </c>
       <c r="D683" t="n">
-        <v>1.63923422421666</v>
+        <v>1.63923422421667</v>
       </c>
       <c r="E683" t="n">
         <v>0.741341804523935</v>
       </c>
       <c r="F683" t="n">
-        <v>1.01408010656403</v>
+        <v>1.01408010656404</v>
       </c>
       <c r="G683" t="n">
         <v>0.693353053473235</v>
       </c>
       <c r="H683" t="n">
-        <v>0.971892060982757</v>
+        <v>0.971892060982755</v>
       </c>
     </row>
     <row r="684">
@@ -18284,19 +18284,19 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000321506963008846</v>
       </c>
       <c r="D684" t="n">
-        <v>1.2957535419756</v>
+        <v>1.29575354197553</v>
       </c>
       <c r="E684" t="n">
-        <v>0.00000696459834528906</v>
+        <v>0.00000696459834528908</v>
       </c>
       <c r="F684" t="n">
-        <v>0.932401567005902</v>
+        <v>0.9324015670059</v>
       </c>
       <c r="G684" t="n">
         <v>0.191119134733279</v>
       </c>
       <c r="H684" t="n">
-        <v>1.03410707717239</v>
+        <v>1.03410707717229</v>
       </c>
     </row>
     <row r="685">
@@ -18307,22 +18307,22 @@
         <v>10</v>
       </c>
       <c r="C685" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000690093107738537</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000690093107738535</v>
       </c>
       <c r="D685" t="n">
-        <v>0.954122870129183</v>
+        <v>0.95412287012916</v>
       </c>
       <c r="E685" t="n">
-        <v>0.000000000000000000000000351316506871853</v>
+        <v>0.000000000000000000000000351316506871852</v>
       </c>
       <c r="F685" t="n">
-        <v>0.973203535357852</v>
+        <v>0.973203535357877</v>
       </c>
       <c r="G685" t="n">
         <v>0.000000000176465246184103</v>
       </c>
       <c r="H685" t="n">
-        <v>1.02504671223838</v>
+        <v>1.0250467122384</v>
       </c>
     </row>
     <row r="686">
@@ -18359,16 +18359,16 @@
         <v>12</v>
       </c>
       <c r="C687" t="n">
-        <v>0.237675622152907</v>
+        <v>0.237675622152908</v>
       </c>
       <c r="D687" t="n">
-        <v>0.939227433518999</v>
+        <v>0.93922743351897</v>
       </c>
       <c r="E687" t="n">
         <v>0.630679431567102</v>
       </c>
       <c r="F687" t="n">
-        <v>1.0483647448635</v>
+        <v>1.04836474486351</v>
       </c>
       <c r="G687" t="n">
         <v>0.525779522974607</v>
@@ -18388,19 +18388,19 @@
         <v>0.912154633207903</v>
       </c>
       <c r="D688" t="n">
-        <v>0.995595971138573</v>
+        <v>0.995595971138533</v>
       </c>
       <c r="E688" t="n">
-        <v>0.394850747962836</v>
+        <v>0.394850747962837</v>
       </c>
       <c r="F688" t="n">
-        <v>1.03813877556818</v>
+        <v>1.03813877556815</v>
       </c>
       <c r="G688" t="n">
         <v>0.713227121975787</v>
       </c>
       <c r="H688" t="n">
-        <v>0.973695682212293</v>
+        <v>0.973695682212339</v>
       </c>
     </row>
     <row r="689">
@@ -18414,19 +18414,19 @@
         <v>0.00000000139605197896176</v>
       </c>
       <c r="D689" t="n">
-        <v>1.16804196908395</v>
+        <v>1.16804196908397</v>
       </c>
       <c r="E689" t="n">
         <v>0.756590412307206</v>
       </c>
       <c r="F689" t="n">
-        <v>1.01716300786157</v>
+        <v>1.01716300786155</v>
       </c>
       <c r="G689" t="n">
         <v>0.463861087624518</v>
       </c>
       <c r="H689" t="n">
-        <v>0.937784663975326</v>
+        <v>0.937784663975283</v>
       </c>
     </row>
     <row r="690">
@@ -18440,13 +18440,13 @@
         <v>0.57418627229534</v>
       </c>
       <c r="D690" t="n">
-        <v>0.980677507339192</v>
+        <v>0.980677507339207</v>
       </c>
       <c r="E690" t="n">
         <v>0.725450153839105</v>
       </c>
       <c r="F690" t="n">
-        <v>0.986515260799024</v>
+        <v>0.986515260799063</v>
       </c>
       <c r="G690" t="n">
         <v>0.978831044323394</v>
@@ -18466,19 +18466,19 @@
         <v>0.000524354218565523</v>
       </c>
       <c r="D691" t="n">
-        <v>0.829671673473241</v>
+        <v>0.829671673473249</v>
       </c>
       <c r="E691" t="n">
         <v>0.549835978326289</v>
       </c>
       <c r="F691" t="n">
-        <v>0.609130363292742</v>
+        <v>0.609130363292696</v>
       </c>
       <c r="G691" t="n">
         <v>0.160275992744359</v>
       </c>
       <c r="H691" t="n">
-        <v>3.33204029989962</v>
+        <v>3.33204029989968</v>
       </c>
     </row>
     <row r="692">
@@ -18498,13 +18498,13 @@
         <v>0.790464552315093</v>
       </c>
       <c r="F692" t="n">
-        <v>0.99164271907761</v>
+        <v>0.991642719077672</v>
       </c>
       <c r="G692" t="n">
         <v>0.633032936001642</v>
       </c>
       <c r="H692" t="n">
-        <v>1.02438747013091</v>
+        <v>1.0243874701309</v>
       </c>
     </row>
     <row r="693">
@@ -18518,19 +18518,19 @@
         <v>0.611047931659783</v>
       </c>
       <c r="D693" t="n">
-        <v>0.940132560211247</v>
+        <v>0.940132560211257</v>
       </c>
       <c r="E693" t="n">
         <v>0.626936390200427</v>
       </c>
       <c r="F693" t="n">
-        <v>0.893018282008931</v>
+        <v>0.893018282008936</v>
       </c>
       <c r="G693" t="n">
         <v>0.0184007852829475</v>
       </c>
       <c r="H693" t="n">
-        <v>2.07252690391775</v>
+        <v>2.07252690391774</v>
       </c>
     </row>
     <row r="694">
@@ -18700,19 +18700,19 @@
         <v>0.0000252583501657785</v>
       </c>
       <c r="D700" t="n">
-        <v>0.206164180017291</v>
+        <v>0.206164180017289</v>
       </c>
       <c r="E700" t="n">
         <v>0.636188893891782</v>
       </c>
       <c r="F700" t="n">
-        <v>0.724342621339331</v>
+        <v>0.724342621339328</v>
       </c>
       <c r="G700" t="n">
         <v>0.775308758835474</v>
       </c>
       <c r="H700" t="n">
-        <v>1.26561988344118</v>
+        <v>1.26561988344117</v>
       </c>
     </row>
     <row r="701">
@@ -18752,19 +18752,19 @@
         <v>0.62795364717319</v>
       </c>
       <c r="D702" t="n">
-        <v>0.984431506800375</v>
+        <v>0.984431506800337</v>
       </c>
       <c r="E702" t="n">
         <v>0.325094520608292</v>
       </c>
       <c r="F702" t="n">
-        <v>0.93028180367726</v>
+        <v>0.930281803677307</v>
       </c>
       <c r="G702" t="n">
         <v>0.440969773106467</v>
       </c>
       <c r="H702" t="n">
-        <v>1.09553870565893</v>
+        <v>1.09553870565897</v>
       </c>
     </row>
     <row r="703">
@@ -18804,13 +18804,13 @@
         <v>0.44767530288168</v>
       </c>
       <c r="D704" t="n">
-        <v>1.05572183734844</v>
+        <v>1.05572183734846</v>
       </c>
       <c r="E704" t="n">
-        <v>0.733841634739533</v>
+        <v>0.733841634739534</v>
       </c>
       <c r="F704" t="n">
-        <v>0.973212071119652</v>
+        <v>0.973212071119626</v>
       </c>
       <c r="G704" t="n">
         <v>0.0014350610871833</v>
@@ -18827,19 +18827,19 @@
         <v>30</v>
       </c>
       <c r="C705" t="n">
-        <v>0.00396794714684321</v>
+        <v>0.00396794714684322</v>
       </c>
       <c r="D705" t="n">
-        <v>1.08476862831737</v>
+        <v>1.08476862831739</v>
       </c>
       <c r="E705" t="n">
         <v>0.0279150586518981</v>
       </c>
       <c r="F705" t="n">
-        <v>0.926157887313893</v>
+        <v>0.926157887313889</v>
       </c>
       <c r="G705" t="n">
-        <v>0.978652760287206</v>
+        <v>0.978652760287208</v>
       </c>
       <c r="H705" t="n">
         <v>1.00246284162385</v>
@@ -18882,19 +18882,19 @@
         <v>0.9610086604974</v>
       </c>
       <c r="D707" t="n">
-        <v>0.998715187127819</v>
+        <v>0.998715187127779</v>
       </c>
       <c r="E707" t="n">
-        <v>0.00000063387853159761</v>
+        <v>0.000000633878531597611</v>
       </c>
       <c r="F707" t="n">
-        <v>0.857942490541037</v>
+        <v>0.857942490541002</v>
       </c>
       <c r="G707" t="n">
         <v>0.158917537318867</v>
       </c>
       <c r="H707" t="n">
-        <v>0.938404934842745</v>
+        <v>0.938404934842734</v>
       </c>
     </row>
     <row r="708">
@@ -18908,19 +18908,19 @@
         <v>0.000000151134549670337</v>
       </c>
       <c r="D708" t="n">
-        <v>0.682920253442715</v>
+        <v>0.682920253442716</v>
       </c>
       <c r="E708" t="n">
         <v>0.309108784536105</v>
       </c>
       <c r="F708" t="n">
-        <v>0.91608453892095</v>
+        <v>0.916084538920959</v>
       </c>
       <c r="G708" t="n">
         <v>0.607772206775206</v>
       </c>
       <c r="H708" t="n">
-        <v>0.938354871161655</v>
+        <v>0.938354871161661</v>
       </c>
     </row>
     <row r="709">
@@ -18940,13 +18940,13 @@
         <v>1</v>
       </c>
       <c r="F709" t="n">
-        <v>1.12925950270471</v>
+        <v>1.12925950270472</v>
       </c>
       <c r="G709" t="n">
         <v>0.109199103022498</v>
       </c>
       <c r="H709" t="n">
-        <v>6.53905032504288</v>
+        <v>6.53905032504283</v>
       </c>
     </row>
     <row r="710">
@@ -18960,19 +18960,19 @@
         <v>0.184228909341624</v>
       </c>
       <c r="D710" t="n">
-        <v>1.12194622303807</v>
+        <v>1.12194622303805</v>
       </c>
       <c r="E710" t="n">
         <v>0.382297087134463</v>
       </c>
       <c r="F710" t="n">
-        <v>0.921397908651841</v>
+        <v>0.921397908651831</v>
       </c>
       <c r="G710" t="n">
         <v>0.00384969932822236</v>
       </c>
       <c r="H710" t="n">
-        <v>1.52042373254865</v>
+        <v>1.52042373254862</v>
       </c>
     </row>
     <row r="711">
@@ -19064,19 +19064,19 @@
         <v>0.000303912199535346</v>
       </c>
       <c r="D714" t="n">
-        <v>0.962432510343838</v>
+        <v>0.962432510343764</v>
       </c>
       <c r="E714" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000029468672599617</v>
       </c>
       <c r="F714" t="n">
-        <v>1.27450409666359</v>
+        <v>1.27450409666367</v>
       </c>
       <c r="G714" t="n">
         <v>0.000000000000132318971830697</v>
       </c>
       <c r="H714" t="n">
-        <v>0.889305056258088</v>
+        <v>0.889305056258071</v>
       </c>
     </row>
     <row r="715">
@@ -19090,19 +19090,19 @@
         <v>0.168991570204463</v>
       </c>
       <c r="D715" t="n">
-        <v>0.639055044017673</v>
+        <v>0.639055044017671</v>
       </c>
       <c r="E715" t="n">
         <v>0.874817571859601</v>
       </c>
       <c r="F715" t="n">
-        <v>0.926246412978964</v>
+        <v>0.926246412978971</v>
       </c>
       <c r="G715" t="n">
         <v>0.0132026431480684</v>
       </c>
       <c r="H715" t="n">
-        <v>3.12577904176418</v>
+        <v>3.12577904176417</v>
       </c>
     </row>
     <row r="716">
@@ -19139,22 +19139,22 @@
         <v>42</v>
       </c>
       <c r="C717" t="n">
-        <v>0.0287062040681734</v>
+        <v>0.0287062040681733</v>
       </c>
       <c r="D717" t="n">
-        <v>1.00860041356262</v>
+        <v>1.00860041356255</v>
       </c>
       <c r="E717" t="n">
         <v>0.00000000000000000369786769735766</v>
       </c>
       <c r="F717" t="n">
-        <v>1.03473231726384</v>
+        <v>1.03473231726391</v>
       </c>
       <c r="G717" t="n">
         <v>0.0057485962542786</v>
       </c>
       <c r="H717" t="n">
-        <v>1.01651060452255</v>
+        <v>1.01651060452251</v>
       </c>
     </row>
   </sheetData>

--- a/sup_tables/sup_table_s12_topography_asymmetry.xlsx
+++ b/sup_tables/sup_table_s12_topography_asymmetry.xlsx
@@ -601,10 +601,10 @@
         <v>1.33165446852313</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000000000000000000000000000138008965009794</v>
+        <v>0.000000000000000000000000032073676287302</v>
       </c>
       <c r="F4" t="n">
-        <v>0.873721804285369</v>
+        <v>0.861075341526755</v>
       </c>
       <c r="G4" t="n">
         <v>0.00100060308031344</v>
@@ -627,10 +627,10 @@
         <v>0.974949145060145</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00101081966009503</v>
+        <v>0.00370937148667626</v>
       </c>
       <c r="F5" t="n">
-        <v>0.987832754228664</v>
+        <v>0.980179352194129</v>
       </c>
       <c r="G5" t="n">
         <v>0.000291997878785293</v>
@@ -653,10 +653,10 @@
         <v>1.38554121207847</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0916473322938538</v>
+        <v>0.0377374045682727</v>
       </c>
       <c r="F6" t="n">
-        <v>1.14753674623552</v>
+        <v>1.1659545969594</v>
       </c>
       <c r="G6" t="n">
         <v>0.953351935009013</v>
@@ -679,10 +679,10 @@
         <v>0.877709068412511</v>
       </c>
       <c r="E7" t="n">
-        <v>0.525550365802658</v>
+        <v>0.927931543167435</v>
       </c>
       <c r="F7" t="n">
-        <v>1.20841370647868</v>
+        <v>1.0216463709227</v>
       </c>
       <c r="G7" t="n">
         <v>0.529257490084894</v>
@@ -705,10 +705,10 @@
         <v>1.04912238715371</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0790090436213058</v>
+        <v>0.361962316800042</v>
       </c>
       <c r="F8" t="n">
-        <v>1.07351762515983</v>
+        <v>1.03332719146854</v>
       </c>
       <c r="G8" t="n">
         <v>0.0589877932490627</v>
@@ -731,10 +731,10 @@
         <v>1.18557259602331</v>
       </c>
       <c r="E9" t="n">
-        <v>0.948058870803095</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.995075575144134</v>
+        <v>1.00068638535341</v>
       </c>
       <c r="G9" t="n">
         <v>0.716109471759585</v>
@@ -757,10 +757,10 @@
         <v>0.978319604910165</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.0000000443873299035677</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.962759818288946</v>
       </c>
       <c r="G10" t="n">
         <v>0.838058018416371</v>
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.681433281872088</v>
+        <v>0.784278679764511</v>
       </c>
       <c r="G11" t="n">
         <v>0.212887754312679</v>
@@ -809,10 +809,10 @@
         <v>1.30237129619612</v>
       </c>
       <c r="E12" t="n">
-        <v>0.288078712757212</v>
+        <v>0.316580705883507</v>
       </c>
       <c r="F12" t="n">
-        <v>0.950438473710556</v>
+        <v>0.952883667976212</v>
       </c>
       <c r="G12" t="n">
         <v>0.0118720594247491</v>
@@ -835,10 +835,10 @@
         <v>0.726695505449286</v>
       </c>
       <c r="E13" t="n">
-        <v>0.124359395366137</v>
+        <v>0.383502353509475</v>
       </c>
       <c r="F13" t="n">
-        <v>0.523481485150063</v>
+        <v>0.710810018008092</v>
       </c>
       <c r="G13" t="n">
         <v>0.496165542830036</v>
@@ -864,7 +864,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.00605580387924</v>
       </c>
       <c r="G14" t="n">
         <v>0.216475522723254</v>
@@ -939,10 +939,10 @@
         <v>1.36742941906795</v>
       </c>
       <c r="E17" t="n">
-        <v>0.130907670567661</v>
+        <v>0.0307345782356316</v>
       </c>
       <c r="F17" t="n">
-        <v>0.754498732897378</v>
+        <v>0.698830565813217</v>
       </c>
       <c r="G17" t="n">
         <v>0.0169002197203834</v>
@@ -965,7 +965,7 @@
         <v>0.308351531186033</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.464285714285714</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1017,10 +1017,10 @@
         <v>1.04007582666071</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0232135249301915</v>
+        <v>0.0003199808561556</v>
       </c>
       <c r="F20" t="n">
-        <v>0.890816304196425</v>
+        <v>0.85914545931299</v>
       </c>
       <c r="G20" t="n">
         <v>0.00711470236013027</v>
@@ -1043,10 +1043,10 @@
         <v>1.76480289251127</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0231361420454805</v>
+        <v>0.384467060231598</v>
       </c>
       <c r="F21" t="n">
-        <v>0.661267195792136</v>
+        <v>0.854631677917199</v>
       </c>
       <c r="G21" t="n">
         <v>0.168296138768724</v>
@@ -1069,10 +1069,10 @@
         <v>1.34738880669942</v>
       </c>
       <c r="E22" t="n">
-        <v>0.180638270596539</v>
+        <v>0.336832387452705</v>
       </c>
       <c r="F22" t="n">
-        <v>1.12055038963868</v>
+        <v>1.07696188855672</v>
       </c>
       <c r="G22" t="n">
         <v>0.115729556958293</v>
@@ -1095,10 +1095,10 @@
         <v>1.01862131354891</v>
       </c>
       <c r="E23" t="n">
-        <v>0.716736484840145</v>
+        <v>0.732658505238025</v>
       </c>
       <c r="F23" t="n">
-        <v>0.976654236050328</v>
+        <v>1.02676309027889</v>
       </c>
       <c r="G23" t="n">
         <v>0.263072336839789</v>
@@ -1147,10 +1147,10 @@
         <v>0.988354364486659</v>
       </c>
       <c r="E25" t="n">
-        <v>0.152959944934201</v>
+        <v>0.159761675617786</v>
       </c>
       <c r="F25" t="n">
-        <v>0.310744766708336</v>
+        <v>0.959081437784491</v>
       </c>
       <c r="G25" t="n">
         <v>0.594986816128981</v>
@@ -1173,10 +1173,10 @@
         <v>0.757693153256771</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7307341202373</v>
+        <v>0.549099380816973</v>
       </c>
       <c r="F26" t="n">
-        <v>1.07043539385569</v>
+        <v>1.105974702533</v>
       </c>
       <c r="G26" t="n">
         <v>0.400535634433936</v>
@@ -1225,10 +1225,10 @@
         <v>0.915141702709363</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0.407429338826465</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.768465484460642</v>
       </c>
       <c r="G28" t="n">
         <v>0.277500279001391</v>
@@ -1329,10 +1329,10 @@
         <v>0.804481373055023</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.317423889151341</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1.72353370822392</v>
       </c>
       <c r="G32" t="n">
         <v>0.461806051426304</v>
@@ -1381,10 +1381,10 @@
         <v>1.2623249262827</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="s">
-        <v>61</v>
+        <v>0.359391972723775</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.736310803887407</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -1407,10 +1407,10 @@
         <v>1.61505334043404</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00000000000000355109469730148</v>
+        <v>0.000110607113454328</v>
       </c>
       <c r="F35" t="n">
-        <v>0.910695403795177</v>
+        <v>0.946037010868562</v>
       </c>
       <c r="G35" t="n">
         <v>0.107721649692151</v>
@@ -1433,10 +1433,10 @@
         <v>1.33190933056027</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0000000000000000000000000000000027875465460578</v>
+        <v>0.00000000000000000000000000412846132953674</v>
       </c>
       <c r="F36" t="n">
-        <v>0.883108016720042</v>
+        <v>0.867429601361717</v>
       </c>
       <c r="G36" t="n">
         <v>0.000171878656769209</v>
@@ -1459,10 +1459,10 @@
         <v>1.00940266723775</v>
       </c>
       <c r="E37" t="n">
-        <v>0.859609836027087</v>
+        <v>0.142811275877873</v>
       </c>
       <c r="F37" t="n">
-        <v>0.999256023004878</v>
+        <v>1.00985167753881</v>
       </c>
       <c r="G37" t="n">
         <v>0.0000027692225143546</v>
@@ -1485,10 +1485,10 @@
         <v>1.25603175195305</v>
       </c>
       <c r="E38" t="n">
-        <v>0.689575773309216</v>
+        <v>0.48348177177087</v>
       </c>
       <c r="F38" t="n">
-        <v>1.00693563930543</v>
+        <v>1.01113140242128</v>
       </c>
       <c r="G38" t="n">
         <v>0.186953659338382</v>
@@ -1511,10 +1511,10 @@
         <v>0.916331283212428</v>
       </c>
       <c r="E39" t="n">
-        <v>0.400481358998401</v>
+        <v>0.810575267020151</v>
       </c>
       <c r="F39" t="n">
-        <v>1.15619420896221</v>
+        <v>0.967188054053067</v>
       </c>
       <c r="G39" t="n">
         <v>0.0813651838399436</v>
@@ -1537,10 +1537,10 @@
         <v>1.04754506133121</v>
       </c>
       <c r="E40" t="n">
-        <v>0.616191654168953</v>
+        <v>0.38038091445509</v>
       </c>
       <c r="F40" t="n">
-        <v>1.01798211076411</v>
+        <v>0.974829981090259</v>
       </c>
       <c r="G40" t="n">
         <v>0.560852529575032</v>
@@ -1563,10 +1563,10 @@
         <v>1.12943356603067</v>
       </c>
       <c r="E41" t="n">
-        <v>0.232278491344155</v>
+        <v>0.361198985142992</v>
       </c>
       <c r="F41" t="n">
-        <v>0.940781969776627</v>
+        <v>0.954221359190738</v>
       </c>
       <c r="G41" t="n">
         <v>0.0327329121682454</v>
@@ -1589,10 +1589,10 @@
         <v>0.962101947229286</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.0082394982682202</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.985446719400103</v>
       </c>
       <c r="G42" t="n">
         <v>0.0768291221673363</v>
@@ -1615,10 +1615,10 @@
         <v>0.826021866061841</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0354065455432338</v>
+        <v>0.84780691473689</v>
       </c>
       <c r="F43" t="n">
-        <v>0.899543812143905</v>
+        <v>0.991136578654099</v>
       </c>
       <c r="G43" t="n">
         <v>0.579696165068033</v>
@@ -1641,10 +1641,10 @@
         <v>1.17412442152089</v>
       </c>
       <c r="E44" t="n">
-        <v>0.921400287068705</v>
+        <v>0.11410823789943</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0037058191873</v>
+        <v>0.952004083752213</v>
       </c>
       <c r="G44" t="n">
         <v>0.374746441290472</v>
@@ -1667,10 +1667,10 @@
         <v>0.832013394037852</v>
       </c>
       <c r="E45" t="n">
-        <v>0.442848651436688</v>
+        <v>0.871011375481709</v>
       </c>
       <c r="F45" t="n">
-        <v>1.07996244268792</v>
+        <v>1.01333729852203</v>
       </c>
       <c r="G45" t="n">
         <v>0.764485664111494</v>
@@ -1719,10 +1719,10 @@
         <v>1.21786996297634</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0.816403254246812</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.800273948643554</v>
       </c>
       <c r="G47" t="n">
         <v>0.690042919398041</v>
@@ -1771,10 +1771,10 @@
         <v>1.54692624712002</v>
       </c>
       <c r="E49" t="n">
-        <v>0.413121811107397</v>
+        <v>0.296794270880035</v>
       </c>
       <c r="F49" t="n">
-        <v>0.902530024850511</v>
+        <v>0.889244399417798</v>
       </c>
       <c r="G49" t="n">
         <v>0.00000760285480853008</v>
@@ -1797,10 +1797,10 @@
         <v>0.468777136708098</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0980693048267292</v>
+        <v>0.139673341321894</v>
       </c>
       <c r="F50" t="n">
-        <v>0.683328904189586</v>
+        <v>0.721726075444965</v>
       </c>
       <c r="G50" t="n">
         <v>0.782538779074735</v>
@@ -1823,10 +1823,10 @@
         <v>1.4299289248614</v>
       </c>
       <c r="E51" t="n">
-        <v>0.459236848959225</v>
+        <v>0.325377397272097</v>
       </c>
       <c r="F51" t="n">
-        <v>1.03358513222198</v>
+        <v>1.04588087823063</v>
       </c>
       <c r="G51" t="n">
         <v>0.000843505439033454</v>
@@ -1849,10 +1849,10 @@
         <v>1.0163815371831</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0373733526690317</v>
+        <v>0.093996334324176</v>
       </c>
       <c r="F52" t="n">
-        <v>0.909519623586308</v>
+        <v>0.94059087080882</v>
       </c>
       <c r="G52" t="n">
         <v>0.507044776896055</v>
@@ -1901,10 +1901,10 @@
         <v>1.05259258430382</v>
       </c>
       <c r="E54" t="n">
-        <v>0.000135179661941141</v>
+        <v>0.000000446068803941354</v>
       </c>
       <c r="F54" t="n">
-        <v>0.849342034831479</v>
+        <v>0.789629695379976</v>
       </c>
       <c r="G54" t="n">
         <v>0.0629295364966505</v>
@@ -1927,10 +1927,10 @@
         <v>1.06963447781361</v>
       </c>
       <c r="E55" t="n">
-        <v>0.858460807668461</v>
+        <v>0.489099802502169</v>
       </c>
       <c r="F55" t="n">
-        <v>1.00377592579284</v>
+        <v>1.01730293571351</v>
       </c>
       <c r="G55" t="n">
         <v>0.561107648290514</v>
@@ -1979,10 +1979,10 @@
         <v>1.02672745102059</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.000707830184146408</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1.11285334827077</v>
       </c>
       <c r="G57" t="n">
         <v>0.0642871043340556</v>
@@ -2005,10 +2005,10 @@
         <v>0.703887660933407</v>
       </c>
       <c r="E58" t="n">
-        <v>0.429611233558147</v>
+        <v>0.371353439260344</v>
       </c>
       <c r="F58" t="n">
-        <v>0.893300803065226</v>
+        <v>0.888760579346521</v>
       </c>
       <c r="G58" t="n">
         <v>0.653583056471918</v>
@@ -2031,10 +2031,10 @@
         <v>1.09448043865265</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0624813337571467</v>
+        <v>0.0468166300101501</v>
       </c>
       <c r="F59" t="n">
-        <v>1.21225819847004</v>
+        <v>1.23684226452736</v>
       </c>
       <c r="G59" t="n">
         <v>0.696336204748269</v>
@@ -2057,10 +2057,10 @@
         <v>1.16938702654674</v>
       </c>
       <c r="E60" t="n">
-        <v>0.461200644015401</v>
+        <v>0.299772863459309</v>
       </c>
       <c r="F60" t="n">
-        <v>0.945287860887925</v>
+        <v>0.918381842434754</v>
       </c>
       <c r="G60" t="n">
         <v>0.00100926452008182</v>
@@ -2109,10 +2109,10 @@
         <v>1.28829830529606</v>
       </c>
       <c r="E62" t="n">
-        <v>0.64917545458875</v>
+        <v>0.555061734686834</v>
       </c>
       <c r="F62" t="n">
-        <v>0.914475412725387</v>
+        <v>0.898746953145349</v>
       </c>
       <c r="G62" t="n">
         <v>0.586418706201509</v>
@@ -2135,10 +2135,10 @@
         <v>1.22177216697284</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0.646431467529172</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>0.753612388144899</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -2161,10 +2161,10 @@
         <v>1.85842990780119</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>0.512025101565542</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1.30336762813515</v>
       </c>
       <c r="G64" t="n">
         <v>0.381951103590538</v>
@@ -2213,10 +2213,10 @@
         <v>0.975477155513254</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0.0608692729655371</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>0.497256691951913</v>
       </c>
       <c r="G66" t="n">
         <v>0.607865803995008</v>
@@ -2239,10 +2239,10 @@
         <v>1.53722766777992</v>
       </c>
       <c r="E67" t="n">
-        <v>0.000000073366084498996</v>
+        <v>0.000000180887200244505</v>
       </c>
       <c r="F67" t="n">
-        <v>0.928319313595371</v>
+        <v>0.946531272171828</v>
       </c>
       <c r="G67" t="n">
         <v>0.214127962073402</v>
@@ -2265,10 +2265,10 @@
         <v>1.33329353534734</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00000000000000000204032249666615</v>
+        <v>0.000000000000000239898641470142</v>
       </c>
       <c r="F68" t="n">
-        <v>0.862322116287025</v>
+        <v>0.863834831549905</v>
       </c>
       <c r="G68" t="n">
         <v>0.779404428664873</v>
@@ -2291,10 +2291,10 @@
         <v>1.70273892025904</v>
       </c>
       <c r="E69" t="n">
-        <v>0.665214481296949</v>
+        <v>0.924406168534423</v>
       </c>
       <c r="F69" t="n">
-        <v>0.980344470244014</v>
+        <v>1.03395005077119</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -2317,10 +2317,10 @@
         <v>0.990624371272959</v>
       </c>
       <c r="E70" t="n">
-        <v>0.802183649444085</v>
+        <v>0.812838309005695</v>
       </c>
       <c r="F70" t="n">
-        <v>0.974035841883726</v>
+        <v>0.973981830226146</v>
       </c>
       <c r="G70" t="n">
         <v>0.124396383375945</v>
@@ -2343,10 +2343,10 @@
         <v>1.01506794044861</v>
       </c>
       <c r="E71" t="n">
-        <v>0.446308036426021</v>
+        <v>0.233720544947516</v>
       </c>
       <c r="F71" t="n">
-        <v>1.1094220253554</v>
+        <v>1.16186791866162</v>
       </c>
       <c r="G71" t="n">
         <v>0.387262276571795</v>
@@ -2369,10 +2369,10 @@
         <v>0.990994889058501</v>
       </c>
       <c r="E72" t="n">
-        <v>0.49951575987295</v>
+        <v>0.504672352945867</v>
       </c>
       <c r="F72" t="n">
-        <v>1.0176715903654</v>
+        <v>1.02638514569704</v>
       </c>
       <c r="G72" t="n">
         <v>0.907903630965601</v>
@@ -2395,10 +2395,10 @@
         <v>1.02952353692833</v>
       </c>
       <c r="E73" t="n">
-        <v>0.56049992753136</v>
+        <v>0.534989642889118</v>
       </c>
       <c r="F73" t="n">
-        <v>0.955568189065287</v>
+        <v>0.952648137741757</v>
       </c>
       <c r="G73" t="n">
         <v>0.714074185111485</v>
@@ -2447,10 +2447,10 @@
         <v>0.926797940028062</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0.499606088347327</v>
       </c>
       <c r="F75" t="n">
-        <v>0.981000183753362</v>
+        <v>1.49391904653236</v>
       </c>
       <c r="G75" t="n">
         <v>0.296440647445806</v>
@@ -2473,10 +2473,10 @@
         <v>1.35145235250155</v>
       </c>
       <c r="E76" t="n">
-        <v>0.31698116195387</v>
+        <v>0.187592298493792</v>
       </c>
       <c r="F76" t="n">
-        <v>0.983883517475952</v>
+        <v>0.979400771775042</v>
       </c>
       <c r="G76" t="n">
         <v>0.0333666205427923</v>
@@ -2502,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>1.19375432807505</v>
+        <v>0.875750900981375</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -2551,10 +2551,10 @@
         <v>1.13843232598869</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0716813113563829</v>
+        <v>0.0688548917409771</v>
       </c>
       <c r="F79" t="n">
-        <v>0.156106669537374</v>
+        <v>0.146413681040837</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -2577,10 +2577,10 @@
         <v>1.47163831977662</v>
       </c>
       <c r="E80" t="n">
-        <v>0.319669652763479</v>
+        <v>0.434633361594465</v>
       </c>
       <c r="F80" t="n">
-        <v>1.06042112383537</v>
+        <v>1.04719208239522</v>
       </c>
       <c r="G80" t="n">
         <v>0.134249910402451</v>
@@ -2629,10 +2629,10 @@
         <v>1.02035495591485</v>
       </c>
       <c r="E82" t="n">
-        <v>0.14461209391771</v>
+        <v>0.0517487076681811</v>
       </c>
       <c r="F82" t="n">
-        <v>0.565712577897361</v>
+        <v>0.543244877540626</v>
       </c>
       <c r="G82" t="n">
         <v>0.490532428643517</v>
@@ -2681,10 +2681,10 @@
         <v>1.01311069732121</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00123287913075575</v>
+        <v>0.0130184511961765</v>
       </c>
       <c r="F84" t="n">
-        <v>0.892562596803068</v>
+        <v>0.921396641483747</v>
       </c>
       <c r="G84" t="n">
         <v>0.919139398706596</v>
@@ -2707,10 +2707,10 @@
         <v>0.95239499563612</v>
       </c>
       <c r="E85" t="n">
-        <v>0.919397900725097</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0.960633362417689</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -2733,10 +2733,10 @@
         <v>1.07463121883036</v>
       </c>
       <c r="E86" t="n">
-        <v>0.384713153882404</v>
+        <v>0.849496710312536</v>
       </c>
       <c r="F86" t="n">
-        <v>0.945339869635103</v>
+        <v>0.984570585300559</v>
       </c>
       <c r="G86" t="n">
         <v>0.140070927110592</v>
@@ -2759,10 +2759,10 @@
         <v>0.987008053368046</v>
       </c>
       <c r="E87" t="n">
-        <v>0.212440958238381</v>
+        <v>0.981992190945351</v>
       </c>
       <c r="F87" t="n">
-        <v>0.967215501592077</v>
+        <v>1.00073667698711</v>
       </c>
       <c r="G87" t="n">
         <v>0.123252300021476</v>
@@ -2811,10 +2811,10 @@
         <v>1.18477086689915</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.833351580189857</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1.14113748952438</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -2837,10 +2837,10 @@
         <v>0.756179708683463</v>
       </c>
       <c r="E90" t="n">
-        <v>0.746021852919672</v>
+        <v>0.711383558600758</v>
       </c>
       <c r="F90" t="n">
-        <v>0.966328908567016</v>
+        <v>0.965733826598517</v>
       </c>
       <c r="G90" t="n">
         <v>0.0939834535410991</v>
@@ -2863,10 +2863,10 @@
         <v>0.805983300093842</v>
       </c>
       <c r="E91" t="n">
-        <v>0.363137701272981</v>
+        <v>0.392529865474079</v>
       </c>
       <c r="F91" t="n">
-        <v>1.10439189808168</v>
+        <v>1.09945879731619</v>
       </c>
       <c r="G91" t="n">
         <v>0.0152249577022765</v>
@@ -2889,10 +2889,10 @@
         <v>1.84368873463495</v>
       </c>
       <c r="E92" t="n">
-        <v>0.796960546871476</v>
+        <v>0.79949099145588</v>
       </c>
       <c r="F92" t="n">
-        <v>1.09482619651359</v>
+        <v>1.07204505897509</v>
       </c>
       <c r="G92" t="n">
         <v>0.00522524279497826</v>
@@ -2915,10 +2915,10 @@
         <v>0.877990412327761</v>
       </c>
       <c r="E93" t="n">
-        <v>0.268479296671999</v>
+        <v>0.0594955092133579</v>
       </c>
       <c r="F93" t="n">
-        <v>0.565491902939497</v>
+        <v>0.359389143105668</v>
       </c>
       <c r="G93" t="n">
         <v>0.445458195534799</v>
@@ -2941,10 +2941,10 @@
         <v>1.05450562281997</v>
       </c>
       <c r="E94" t="n">
-        <v>0.459210618638949</v>
+        <v>0.914475960772013</v>
       </c>
       <c r="F94" t="n">
-        <v>0.796841843614711</v>
+        <v>0.959797124779668</v>
       </c>
       <c r="G94" t="n">
         <v>0.146176067097699</v>
@@ -3071,10 +3071,10 @@
         <v>1.58103840222098</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0357052858207298</v>
+        <v>0.0000855432004197609</v>
       </c>
       <c r="F99" t="n">
-        <v>0.92538606915799</v>
+        <v>0.907856256890399</v>
       </c>
       <c r="G99" t="n">
         <v>0.187015907669292</v>
@@ -3097,10 +3097,10 @@
         <v>1.15111330503203</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000256429396121178</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000421202856534271</v>
       </c>
       <c r="F100" t="n">
-        <v>0.883861797446103</v>
+        <v>0.882544255980788</v>
       </c>
       <c r="G100" t="n">
         <v>0.0173011431119252</v>
@@ -3123,10 +3123,10 @@
         <v>0.964000889347176</v>
       </c>
       <c r="E101" t="n">
-        <v>0.00129748450702086</v>
+        <v>0.0644731615824182</v>
       </c>
       <c r="F101" t="n">
-        <v>0.992113795763839</v>
+        <v>0.994448856400424</v>
       </c>
       <c r="G101" t="n">
         <v>0.000000000000000000000000000000000251601466696381</v>
@@ -3149,10 +3149,10 @@
         <v>1.61686470898021</v>
       </c>
       <c r="E102" t="n">
-        <v>0.534879179549556</v>
+        <v>0.189911743591456</v>
       </c>
       <c r="F102" t="n">
-        <v>0.961250449248102</v>
+        <v>0.937093199489613</v>
       </c>
       <c r="G102" t="n">
         <v>0.0211647243666072</v>
@@ -3175,10 +3175,10 @@
         <v>0.953013099072038</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0952676742728157</v>
+        <v>0.0649665095232867</v>
       </c>
       <c r="F103" t="n">
-        <v>0.955519799512716</v>
+        <v>0.951245262258121</v>
       </c>
       <c r="G103" t="n">
         <v>0.0273051805323203</v>
@@ -3201,10 +3201,10 @@
         <v>0.9672317790217</v>
       </c>
       <c r="E104" t="n">
-        <v>0.777465202909385</v>
+        <v>0.398615436137045</v>
       </c>
       <c r="F104" t="n">
-        <v>0.996217218409968</v>
+        <v>0.985895613373518</v>
       </c>
       <c r="G104" t="n">
         <v>0.375813093379209</v>
@@ -3227,10 +3227,10 @@
         <v>1.12096629362657</v>
       </c>
       <c r="E105" t="n">
-        <v>0.794435214177411</v>
+        <v>0.921774943183787</v>
       </c>
       <c r="F105" t="n">
-        <v>0.996963246657103</v>
+        <v>0.998802884241631</v>
       </c>
       <c r="G105" t="n">
         <v>0.0468455972810657</v>
@@ -3253,10 +3253,10 @@
         <v>0.9673572163109</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0395093133052995</v>
+        <v>0.00403178275005432</v>
       </c>
       <c r="F106" t="n">
-        <v>0.931314005361696</v>
+        <v>0.987345851943441</v>
       </c>
       <c r="G106" t="n">
         <v>0.00140141285079385</v>
@@ -3279,10 +3279,10 @@
         <v>0.973380081942132</v>
       </c>
       <c r="E107" t="n">
-        <v>0.971493519851019</v>
+        <v>0.819729201817087</v>
       </c>
       <c r="F107" t="n">
-        <v>0.995630494999767</v>
+        <v>0.984377333769243</v>
       </c>
       <c r="G107" t="n">
         <v>0.803497322956639</v>
@@ -3305,10 +3305,10 @@
         <v>1.18331106030231</v>
       </c>
       <c r="E108" t="n">
-        <v>0.78135108989682</v>
+        <v>0.962493270635762</v>
       </c>
       <c r="F108" t="n">
-        <v>0.995561608849352</v>
+        <v>1.00077333669786</v>
       </c>
       <c r="G108" t="n">
         <v>0.339151594315334</v>
@@ -3331,10 +3331,10 @@
         <v>0.906387643396795</v>
       </c>
       <c r="E109" t="n">
-        <v>0.78694767792444</v>
+        <v>0.822750922587272</v>
       </c>
       <c r="F109" t="n">
-        <v>1.0319125694625</v>
+        <v>1.01825479241358</v>
       </c>
       <c r="G109" t="n">
         <v>0.820681917267075</v>
@@ -3357,10 +3357,10 @@
         <v>0.966047945705225</v>
       </c>
       <c r="E110" t="n">
-        <v>0.693704452089021</v>
+        <v>0.91366339305754</v>
       </c>
       <c r="F110" t="n">
-        <v>0.84224204176912</v>
+        <v>0.982774698033586</v>
       </c>
       <c r="G110" t="n">
         <v>0.570819261088772</v>
@@ -3383,10 +3383,10 @@
         <v>0.904995438552139</v>
       </c>
       <c r="E111" t="n">
-        <v>0.469512195121951</v>
-      </c>
-      <c r="F111" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.07784834417093</v>
       </c>
       <c r="G111" t="n">
         <v>0.758831412949048</v>
@@ -3435,10 +3435,10 @@
         <v>1.2527837826987</v>
       </c>
       <c r="E113" t="n">
-        <v>0.190273770248706</v>
+        <v>0.0668014038618902</v>
       </c>
       <c r="F113" t="n">
-        <v>0.873520882436237</v>
+        <v>0.850766448508573</v>
       </c>
       <c r="G113" t="n">
         <v>0.0000000622104446457506</v>
@@ -3461,10 +3461,10 @@
         <v>0.687761631472487</v>
       </c>
       <c r="E114" t="n">
-        <v>0.882197334622362</v>
+        <v>0.6576603077867</v>
       </c>
       <c r="F114" t="n">
-        <v>1.03114127683168</v>
+        <v>0.938523294672451</v>
       </c>
       <c r="G114" t="n">
         <v>0.168022476499484</v>
@@ -3513,10 +3513,10 @@
         <v>0.978641715485304</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0000517897471280041</v>
+        <v>0.00000243299854206623</v>
       </c>
       <c r="F116" t="n">
-        <v>0.935008455092071</v>
+        <v>0.926829788749099</v>
       </c>
       <c r="G116" t="n">
         <v>0.378657201491386</v>
@@ -3539,10 +3539,10 @@
         <v>0.928561042608076</v>
       </c>
       <c r="E117" t="n">
-        <v>0.615533110640765</v>
+        <v>0.105984852651832</v>
       </c>
       <c r="F117" t="n">
-        <v>1.08556265018801</v>
+        <v>1.28220937131802</v>
       </c>
       <c r="G117" t="n">
         <v>0.313335014232152</v>
@@ -3565,10 +3565,10 @@
         <v>0.971909391640081</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0000001281927133531</v>
+        <v>0.00000000101891343749094</v>
       </c>
       <c r="F118" t="n">
-        <v>0.890398368003892</v>
+        <v>0.877456820701968</v>
       </c>
       <c r="G118" t="n">
         <v>0.000000671414737731842</v>
@@ -3591,10 +3591,10 @@
         <v>0.936077571216988</v>
       </c>
       <c r="E119" t="n">
-        <v>0.00315584258968539</v>
+        <v>0.0759260640137963</v>
       </c>
       <c r="F119" t="n">
-        <v>0.965619574261813</v>
+        <v>0.981220714318699</v>
       </c>
       <c r="G119" t="n">
         <v>0.954866559491656</v>
@@ -3617,10 +3617,10 @@
         <v>1.28314933871477</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0113018420611838</v>
+        <v>0.0111231155816218</v>
       </c>
       <c r="F120" t="n">
-        <v>1.41360994164798</v>
+        <v>1.41532689885286</v>
       </c>
       <c r="G120" t="n">
         <v>0.0119399162768811</v>
@@ -3643,10 +3643,10 @@
         <v>0.877751523647434</v>
       </c>
       <c r="E121" t="n">
-        <v>0.61782337054993</v>
+        <v>0.0089578371387808</v>
       </c>
       <c r="F121" t="n">
-        <v>1.2237323861333</v>
+        <v>0.895202160881271</v>
       </c>
       <c r="G121" t="n">
         <v>0.180640357426257</v>
@@ -3669,10 +3669,10 @@
         <v>0.709600221726007</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0340590970515598</v>
+        <v>0.0351696928203149</v>
       </c>
       <c r="F122" t="n">
-        <v>0.921929723966613</v>
+        <v>0.923063865870468</v>
       </c>
       <c r="G122" t="n">
         <v>0.403323934766295</v>
@@ -3695,10 +3695,10 @@
         <v>0.89168970317656</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0597598757655194</v>
+        <v>0.0729524068873135</v>
       </c>
       <c r="F123" t="n">
-        <v>1.15315215987769</v>
+        <v>1.14227622401792</v>
       </c>
       <c r="G123" t="n">
         <v>0.0037652167918329</v>
@@ -3747,10 +3747,10 @@
         <v>0.873850887348513</v>
       </c>
       <c r="E125" t="n">
-        <v>0.314284458107718</v>
+        <v>0.241953818640886</v>
       </c>
       <c r="F125" t="n">
-        <v>1.78126096305435</v>
+        <v>2.27220394765836</v>
       </c>
       <c r="G125" t="n">
         <v>0.221821401144156</v>
@@ -3773,10 +3773,10 @@
         <v>0.899819431582964</v>
       </c>
       <c r="E126" t="n">
-        <v>0.424320217596866</v>
+        <v>0.516742120710709</v>
       </c>
       <c r="F126" t="n">
-        <v>0.896040141183005</v>
+        <v>0.893795054884395</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -3799,10 +3799,10 @@
         <v>1.17234558595698</v>
       </c>
       <c r="E127" t="n">
-        <v>0.028669252482064</v>
+        <v>0.428400007135958</v>
       </c>
       <c r="F127" t="n">
-        <v>1.26801240938661</v>
+        <v>0.789375673495777</v>
       </c>
       <c r="G127" t="n">
         <v>0.256354688008296</v>
@@ -3851,10 +3851,10 @@
         <v>0.503577330213916</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0.192696479542733</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>0.726648780357015</v>
       </c>
       <c r="G129" t="n">
         <v>0.070485251664558</v>
@@ -3877,10 +3877,10 @@
         <v>1.14755078989109</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>0.133589314002428</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>0.746676255602539</v>
       </c>
       <c r="G130" t="n">
         <v>0.550605335365979</v>
@@ -3903,10 +3903,10 @@
         <v>1.36613375070655</v>
       </c>
       <c r="E131" t="n">
-        <v>0.000000000272623425000902</v>
+        <v>0.0000000000228999229438658</v>
       </c>
       <c r="F131" t="n">
-        <v>0.936515553867985</v>
+        <v>0.94426154294502</v>
       </c>
       <c r="G131" t="n">
         <v>0.0070318936179958</v>
@@ -3929,10 +3929,10 @@
         <v>1.04490319725491</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0000000000000000000000000000000000584733517166427</v>
+        <v>0.00000000000000000000000000000000000000783282500029203</v>
       </c>
       <c r="F132" t="n">
-        <v>1.05492397145664</v>
+        <v>1.06042572272789</v>
       </c>
       <c r="G132" t="n">
         <v>0.00000211639263707676</v>
@@ -3955,10 +3955,10 @@
         <v>1.06225473688036</v>
       </c>
       <c r="E133" t="n">
-        <v>0.415780655313911</v>
+        <v>0.196206218914928</v>
       </c>
       <c r="F133" t="n">
-        <v>0.984545594024136</v>
+        <v>0.977370031523485</v>
       </c>
       <c r="G133" t="n">
         <v>0.000180595504312276</v>
@@ -3981,10 +3981,10 @@
         <v>1.31432779830832</v>
       </c>
       <c r="E134" t="n">
-        <v>0.826198245720097</v>
+        <v>0.458697117764018</v>
       </c>
       <c r="F134" t="n">
-        <v>1.05686157504996</v>
+        <v>0.921008943961305</v>
       </c>
       <c r="G134" t="n">
         <v>0.506032045887422</v>
@@ -4007,10 +4007,10 @@
         <v>0.922039874483112</v>
       </c>
       <c r="E135" t="n">
-        <v>0.267610040169271</v>
+        <v>0.271028336606174</v>
       </c>
       <c r="F135" t="n">
-        <v>1.03391334240572</v>
+        <v>1.03132893911206</v>
       </c>
       <c r="G135" t="n">
         <v>0.902688598255976</v>
@@ -4033,10 +4033,10 @@
         <v>1.10510772689366</v>
       </c>
       <c r="E136" t="n">
-        <v>0.677350810867761</v>
+        <v>0.501475679633619</v>
       </c>
       <c r="F136" t="n">
-        <v>0.980846189711966</v>
+        <v>1.06013117164625</v>
       </c>
       <c r="G136" t="n">
         <v>0.79167745948263</v>
@@ -4085,10 +4085,10 @@
         <v>1.01322041918159</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>0.284397187804919</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>0.964044652335811</v>
       </c>
       <c r="G138" t="n">
         <v>0.237541398294868</v>
@@ -4111,10 +4111,10 @@
         <v>1.32821250580021</v>
       </c>
       <c r="E139" t="n">
-        <v>0.00985454910115613</v>
-      </c>
-      <c r="F139" t="n">
-        <v>2.81131419842087</v>
+        <v>0.481798715203425</v>
+      </c>
+      <c r="F139" t="s">
+        <v>61</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -4137,10 +4137,10 @@
         <v>1.53513949923437</v>
       </c>
       <c r="E140" t="n">
-        <v>0.333795063238493</v>
+        <v>0.496993893099875</v>
       </c>
       <c r="F140" t="n">
-        <v>0.979929821260514</v>
+        <v>0.986267005880436</v>
       </c>
       <c r="G140" t="n">
         <v>0.91621124484895</v>
@@ -4163,10 +4163,10 @@
         <v>1.03642845271285</v>
       </c>
       <c r="E141" t="n">
-        <v>0.815431563661823</v>
+        <v>0.252223727011758</v>
       </c>
       <c r="F141" t="n">
-        <v>0.889082184040746</v>
+        <v>0.917955562223715</v>
       </c>
       <c r="G141" t="n">
         <v>0.557120392749568</v>
@@ -4192,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>0.999575801468406</v>
       </c>
       <c r="G142" t="n">
         <v>0.851756284362089</v>
@@ -4215,10 +4215,10 @@
         <v>0.696030435917855</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0.624572393983684</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1.29343455585973</v>
       </c>
       <c r="G143" t="n">
         <v>0.163321347236551</v>
@@ -4241,10 +4241,10 @@
         <v>0.857120865119147</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0.16828213625366</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>2.46472533494415</v>
       </c>
       <c r="G144" t="n">
         <v>0.669758643480639</v>
@@ -4293,10 +4293,10 @@
         <v>1.12965264931117</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0.222003564419104</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>0.754035229418145</v>
       </c>
       <c r="G146" t="n">
         <v>0.580940607450012</v>
@@ -4345,10 +4345,10 @@
         <v>1.12587039002571</v>
       </c>
       <c r="E148" t="n">
-        <v>0.826587890170033</v>
+        <v>0.500700580912197</v>
       </c>
       <c r="F148" t="n">
-        <v>0.989260718186603</v>
+        <v>0.969462100374981</v>
       </c>
       <c r="G148" t="n">
         <v>0.4110319622763</v>
@@ -4371,10 +4371,10 @@
         <v>1.77530817908772</v>
       </c>
       <c r="E149" t="n">
-        <v>0.859877934725723</v>
+        <v>0.758046807899699</v>
       </c>
       <c r="F149" t="n">
-        <v>0.954288868821939</v>
+        <v>0.885561347164535</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -4397,10 +4397,10 @@
         <v>1.29122383692378</v>
       </c>
       <c r="E150" t="n">
-        <v>0.933139039473653</v>
+        <v>0.918988438952803</v>
       </c>
       <c r="F150" t="n">
-        <v>1.00915406909753</v>
+        <v>0.991572631552238</v>
       </c>
       <c r="G150" t="n">
         <v>0.098543214192561</v>
@@ -4423,10 +4423,10 @@
         <v>1.02154529962145</v>
       </c>
       <c r="E151" t="n">
-        <v>0.419025707978741</v>
+        <v>0.0903944957104802</v>
       </c>
       <c r="F151" t="n">
-        <v>0.978352112642983</v>
+        <v>1.04861879480038</v>
       </c>
       <c r="G151" t="n">
         <v>0.533169005062485</v>
@@ -4449,10 +4449,10 @@
         <v>1.21977598633392</v>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.663488217244431</v>
       </c>
       <c r="F152" t="n">
-        <v>1.06429190801152</v>
+        <v>1.08239590460302</v>
       </c>
       <c r="G152" t="n">
         <v>0.590526058014761</v>
@@ -4475,10 +4475,10 @@
         <v>1.01185104729344</v>
       </c>
       <c r="E153" t="n">
-        <v>0.860859556951613</v>
+        <v>0.0000230377286022431</v>
       </c>
       <c r="F153" t="n">
-        <v>1.03338975896423</v>
+        <v>0.938699233945871</v>
       </c>
       <c r="G153" t="n">
         <v>0.000813003004722223</v>
@@ -4501,10 +4501,10 @@
         <v>1.67464603194852</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0.38573985095026</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>0.582391440984184</v>
       </c>
       <c r="G154" t="n">
         <v>0.666409415396488</v>
@@ -4527,10 +4527,10 @@
         <v>0.962587042953296</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0.464980238821243</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>0.647933399140001</v>
       </c>
       <c r="G155" t="n">
         <v>0.454247231845299</v>
@@ -4605,10 +4605,10 @@
         <v>1.53746260187427</v>
       </c>
       <c r="E158" t="n">
-        <v>0.725072604457096</v>
+        <v>0.725516568321993</v>
       </c>
       <c r="F158" t="n">
-        <v>1.05295980013405</v>
+        <v>1.05301424646866</v>
       </c>
       <c r="G158" t="n">
         <v>0.124369604652105</v>
@@ -4631,10 +4631,10 @@
         <v>1.41114683522482</v>
       </c>
       <c r="E159" t="n">
-        <v>0.575012303985568</v>
+        <v>0.46200629047423</v>
       </c>
       <c r="F159" t="n">
-        <v>0.966781279654963</v>
+        <v>1.28573114855439</v>
       </c>
       <c r="G159" t="n">
         <v>0.632923061131837</v>
@@ -4683,10 +4683,10 @@
         <v>1.57530483416367</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0.701024753786172</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>1.11176191803991</v>
       </c>
       <c r="G161" t="n">
         <v>0.634792057449592</v>
@@ -4709,10 +4709,10 @@
         <v>1.12333259430165</v>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>0.658452405360271</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>0.755202924380174</v>
       </c>
       <c r="G162" t="n">
         <v>1</v>
@@ -4735,10 +4735,10 @@
         <v>1.55840496591141</v>
       </c>
       <c r="E163" t="n">
-        <v>0.000000219179871365367</v>
+        <v>0.00000000508111083790334</v>
       </c>
       <c r="F163" t="n">
-        <v>0.941365324656681</v>
+        <v>0.885695443020003</v>
       </c>
       <c r="G163" t="n">
         <v>0.197792283373964</v>
@@ -4761,10 +4761,10 @@
         <v>1.36399857391673</v>
       </c>
       <c r="E164" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000294506948568486</v>
+        <v>0.000000000000000138226224179774</v>
       </c>
       <c r="F164" t="n">
-        <v>0.918858128270922</v>
+        <v>0.965708221102061</v>
       </c>
       <c r="G164" t="n">
         <v>0.0753488426800764</v>
@@ -4787,10 +4787,10 @@
         <v>0.985055138401827</v>
       </c>
       <c r="E165" t="n">
-        <v>0.00000000000449595770081565</v>
+        <v>0.375321930685459</v>
       </c>
       <c r="F165" t="n">
-        <v>0.993451800209277</v>
+        <v>1.0010609348648</v>
       </c>
       <c r="G165" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000347970051868693</v>
@@ -4813,10 +4813,10 @@
         <v>1.74869097399227</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0157261487654545</v>
+        <v>0.108847566636971</v>
       </c>
       <c r="F166" t="n">
-        <v>1.29371849952102</v>
+        <v>1.1397678175145</v>
       </c>
       <c r="G166" t="n">
         <v>0.294109779337385</v>
@@ -4839,10 +4839,10 @@
         <v>1.12734324815481</v>
       </c>
       <c r="E167" t="n">
-        <v>0.453061428831015</v>
+        <v>0.366361217648141</v>
       </c>
       <c r="F167" t="n">
-        <v>0.91396522734239</v>
+        <v>0.933867700500877</v>
       </c>
       <c r="G167" t="n">
         <v>0.167641943411059</v>
@@ -4865,10 +4865,10 @@
         <v>1.22133764693728</v>
       </c>
       <c r="E168" t="n">
-        <v>0.822322468875071</v>
+        <v>0.374339339446067</v>
       </c>
       <c r="F168" t="n">
-        <v>1.00837763110321</v>
+        <v>1.0287873937944</v>
       </c>
       <c r="G168" t="n">
         <v>0.183300631853821</v>
@@ -4891,10 +4891,10 @@
         <v>1.14010931723533</v>
       </c>
       <c r="E169" t="n">
-        <v>0.393177467908408</v>
+        <v>0.319465607832266</v>
       </c>
       <c r="F169" t="n">
-        <v>0.943597023172647</v>
+        <v>0.942775612202395</v>
       </c>
       <c r="G169" t="n">
         <v>0.810871365626475</v>
@@ -4917,10 +4917,10 @@
         <v>0.986641315830587</v>
       </c>
       <c r="E170" t="n">
-        <v>0.448238651283559</v>
+        <v>0.00000000000000000000000000148223519873328</v>
       </c>
       <c r="F170" t="n">
-        <v>0.96757559094883</v>
+        <v>0.982436753339311</v>
       </c>
       <c r="G170" t="n">
         <v>0.966681278035713</v>
@@ -4943,10 +4943,10 @@
         <v>0.935892823462824</v>
       </c>
       <c r="E171" t="n">
-        <v>0.133099255191926</v>
+        <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>0.762158278015372</v>
+        <v>0.938580131012705</v>
       </c>
       <c r="G171" t="n">
         <v>0.49808463789099</v>
@@ -4969,10 +4969,10 @@
         <v>1.52001915568712</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0652311961346288</v>
+        <v>0.0445894361227125</v>
       </c>
       <c r="F172" t="n">
-        <v>0.924549715571901</v>
+        <v>0.923689981412908</v>
       </c>
       <c r="G172" t="n">
         <v>0.0152017598820963</v>
@@ -4995,10 +4995,10 @@
         <v>1.01148691941847</v>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>0.320927547024135</v>
       </c>
       <c r="F173" t="n">
-        <v>0.994907458502715</v>
+        <v>0.929285955823546</v>
       </c>
       <c r="G173" t="n">
         <v>0.539167385819632</v>
@@ -5021,10 +5021,10 @@
         <v>1.29839237524495</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>0.72491308171309</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>1.09985238120606</v>
       </c>
       <c r="G174" t="n">
         <v>0.423992084310007</v>
@@ -5047,10 +5047,10 @@
         <v>1.00242605355382</v>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>0.0891035869216433</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>6.53157162037894</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
@@ -5099,10 +5099,10 @@
         <v>1.40791452727019</v>
       </c>
       <c r="E177" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000583804365192473</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000185402445307203</v>
       </c>
       <c r="F177" t="n">
-        <v>0.889193010630206</v>
+        <v>0.889826575407192</v>
       </c>
       <c r="G177" t="n">
         <v>1.14547684727592e-315</v>
@@ -5128,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="F178" t="n">
-        <v>0</v>
+        <v>0.872977362357739</v>
       </c>
       <c r="G178" t="n">
         <v>0.646247423462613</v>
@@ -5151,10 +5151,10 @@
         <v>1.48897796402107</v>
       </c>
       <c r="E179" t="n">
-        <v>0.0729678428347064</v>
+        <v>0.105086398570413</v>
       </c>
       <c r="F179" t="n">
-        <v>1.02834158675648</v>
+        <v>1.02517318765896</v>
       </c>
       <c r="G179" t="n">
         <v>0.000000000259657571400124</v>
@@ -5177,10 +5177,10 @@
         <v>1.11364519962223</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0231449767177875</v>
+        <v>0.0000851599654759314</v>
       </c>
       <c r="F180" t="n">
-        <v>0.915173056772622</v>
+        <v>0.907433453916493</v>
       </c>
       <c r="G180" t="n">
         <v>0.74618518265692</v>
@@ -5203,10 +5203,10 @@
         <v>1.34755424767431</v>
       </c>
       <c r="E181" t="n">
-        <v>0.29802973530333</v>
+        <v>0.804370148978286</v>
       </c>
       <c r="F181" t="n">
-        <v>1.10055485922515</v>
+        <v>1.02179298043891</v>
       </c>
       <c r="G181" t="n">
         <v>0.0236783473373133</v>
@@ -5229,10 +5229,10 @@
         <v>1.65640954400691</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0202571185264488</v>
+        <v>0.0234368842133548</v>
       </c>
       <c r="F182" t="n">
-        <v>0.963893359191733</v>
+        <v>0.966689426290694</v>
       </c>
       <c r="G182" t="n">
         <v>0.166882153469264</v>
@@ -5255,10 +5255,10 @@
         <v>1.09838312986574</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0462989442563976</v>
+        <v>0.241365840823729</v>
       </c>
       <c r="F183" t="n">
-        <v>0.952606385896103</v>
+        <v>0.972686516331959</v>
       </c>
       <c r="G183" t="n">
         <v>0.455905122945962</v>
@@ -5281,10 +5281,10 @@
         <v>1.19035328638554</v>
       </c>
       <c r="E184" t="n">
-        <v>0.117913865321542</v>
+        <v>0.883217337162499</v>
       </c>
       <c r="F184" t="n">
-        <v>1.12500375946256</v>
+        <v>1.01806071386332</v>
       </c>
       <c r="G184" t="n">
         <v>0.220702432161086</v>
@@ -5307,10 +5307,10 @@
         <v>0.960473117662271</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0375870471577235</v>
+        <v>0.00000000609358944868311</v>
       </c>
       <c r="F185" t="n">
-        <v>0.955402758241958</v>
+        <v>0.9398401399693</v>
       </c>
       <c r="G185" t="n">
         <v>0.059114784013428</v>
@@ -5333,10 +5333,10 @@
         <v>0.971472571276218</v>
       </c>
       <c r="E186" t="n">
-        <v>0.102910123780776</v>
+        <v>0.082850705263664</v>
       </c>
       <c r="F186" t="n">
-        <v>0.886691516366866</v>
+        <v>0.880761060778605</v>
       </c>
       <c r="G186" t="n">
         <v>0.633036349101774</v>
@@ -5359,10 +5359,10 @@
         <v>0.796401169450435</v>
       </c>
       <c r="E187" t="n">
-        <v>0.228488502529235</v>
+        <v>0.0545956932055147</v>
       </c>
       <c r="F187" t="n">
-        <v>1.17026256693685</v>
+        <v>1.23672726297816</v>
       </c>
       <c r="G187" t="n">
         <v>0.157379996412574</v>
@@ -5385,10 +5385,10 @@
         <v>1.36662064344695</v>
       </c>
       <c r="E188" t="n">
-        <v>0.514594834148359</v>
+        <v>0.594802535289918</v>
       </c>
       <c r="F188" t="n">
-        <v>0.939858599001752</v>
+        <v>0.950559864003127</v>
       </c>
       <c r="G188" t="n">
         <v>0.000000042552817297745</v>
@@ -5437,10 +5437,10 @@
         <v>0.850998712727679</v>
       </c>
       <c r="E190" t="n">
-        <v>0.21276525426537</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>0.819113531390855</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
@@ -5463,10 +5463,10 @@
         <v>1.15406150399828</v>
       </c>
       <c r="E191" t="n">
-        <v>0.275521173250635</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>0.497687893279132</v>
+        <v>0.999029714204262</v>
       </c>
       <c r="G191" t="n">
         <v>0.796982875593063</v>
@@ -5489,10 +5489,10 @@
         <v>1.6626470754984</v>
       </c>
       <c r="E192" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000232582373769572</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000047160151739538</v>
       </c>
       <c r="F192" t="n">
-        <v>1.38413513964151</v>
+        <v>1.37850022837045</v>
       </c>
       <c r="G192" t="n">
         <v>0.00000192866849594636</v>
@@ -5515,10 +5515,10 @@
         <v>0.490670450848858</v>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>0.321052628950426</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>1.55859390082145</v>
       </c>
       <c r="G193" t="n">
         <v>0.427647120583711</v>
@@ -5541,10 +5541,10 @@
         <v>1.08269112649103</v>
       </c>
       <c r="E194" t="n">
-        <v>0.722733408279804</v>
+        <v>0.0000981664292817131</v>
       </c>
       <c r="F194" t="n">
-        <v>0.865975284873892</v>
+        <v>0.667029406093679</v>
       </c>
       <c r="G194" t="n">
         <v>0.0269693732978472</v>
@@ -5567,10 +5567,10 @@
         <v>1.61075277972148</v>
       </c>
       <c r="E195" t="n">
-        <v>0.000000000000000000000000000000000000000000000539313134183853</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000585283843158276</v>
       </c>
       <c r="F195" t="n">
-        <v>0.957946206360936</v>
+        <v>0.949392956256505</v>
       </c>
       <c r="G195" t="n">
         <v>0.000000000856810180708457</v>
@@ -5593,10 +5593,10 @@
         <v>1.29854304750257</v>
       </c>
       <c r="E196" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000735725021467973</v>
+        <v>0.0000000000000000000000223104313365766</v>
       </c>
       <c r="F196" t="n">
-        <v>0.86680944284956</v>
+        <v>0.867372058084835</v>
       </c>
       <c r="G196" t="n">
         <v>0.337454301799071</v>
@@ -5619,10 +5619,10 @@
         <v>1.26408457041245</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0389006074517984</v>
+        <v>0.222645421723146</v>
       </c>
       <c r="F197" t="n">
-        <v>1.01166255181868</v>
+        <v>1.00902180102296</v>
       </c>
       <c r="G197" t="n">
         <v>0.601255804525353</v>
@@ -5645,10 +5645,10 @@
         <v>1.63888513986462</v>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0.0666025728073281</v>
       </c>
       <c r="F198" t="n">
-        <v>0.968393004612357</v>
+        <v>6.17305448934277</v>
       </c>
       <c r="G198" t="n">
         <v>1</v>
@@ -5671,10 +5671,10 @@
         <v>0.962033501895974</v>
       </c>
       <c r="E199" t="n">
-        <v>0.29004294397135</v>
+        <v>0.607009245125132</v>
       </c>
       <c r="F199" t="n">
-        <v>0.792207267956161</v>
+        <v>0.918737106576106</v>
       </c>
       <c r="G199" t="n">
         <v>0.0963817287497052</v>
@@ -5697,10 +5697,10 @@
         <v>1.19904830725974</v>
       </c>
       <c r="E200" t="n">
-        <v>0.118755014864589</v>
+        <v>0.347436216745676</v>
       </c>
       <c r="F200" t="n">
-        <v>0.968346648312504</v>
+        <v>0.980853958427517</v>
       </c>
       <c r="G200" t="n">
         <v>0.89336398280022</v>
@@ -5723,10 +5723,10 @@
         <v>1.2030917706462</v>
       </c>
       <c r="E201" t="n">
-        <v>0.971446666922853</v>
+        <v>0.701875666084045</v>
       </c>
       <c r="F201" t="n">
-        <v>1.00399635224846</v>
+        <v>1.02815242283768</v>
       </c>
       <c r="G201" t="n">
         <v>0.470980963627931</v>
@@ -5749,10 +5749,10 @@
         <v>0.981492203822418</v>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>0.337852076566944</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>0.981074367495427</v>
       </c>
       <c r="G202" t="n">
         <v>0.367126163682166</v>
@@ -5775,10 +5775,10 @@
         <v>1.52608356118871</v>
       </c>
       <c r="E203" t="n">
-        <v>0.129644792994261</v>
+        <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>0.19097611825628</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
         <v>1</v>
@@ -5801,10 +5801,10 @@
         <v>1.36638142938344</v>
       </c>
       <c r="E204" t="n">
-        <v>0.738217347263676</v>
+        <v>0.694123697475289</v>
       </c>
       <c r="F204" t="n">
-        <v>1.01113215323279</v>
+        <v>1.01095391941899</v>
       </c>
       <c r="G204" t="n">
         <v>0.224478594365304</v>
@@ -5827,10 +5827,10 @@
         <v>0.968585974063987</v>
       </c>
       <c r="E205" t="n">
-        <v>0.474472149234392</v>
+        <v>0.71579164401642</v>
       </c>
       <c r="F205" t="n">
-        <v>0.724953478606778</v>
+        <v>0.932873491090169</v>
       </c>
       <c r="G205" t="n">
         <v>0.588237190070066</v>
@@ -5905,10 +5905,10 @@
         <v>1.57640704274645</v>
       </c>
       <c r="E208" t="n">
-        <v>0.0494479711543606</v>
+        <v>0.116827630160902</v>
       </c>
       <c r="F208" t="n">
-        <v>0.86515796723164</v>
+        <v>0.863725382641613</v>
       </c>
       <c r="G208" t="n">
         <v>0.805150451872181</v>
@@ -5931,10 +5931,10 @@
         <v>1.44836529559282</v>
       </c>
       <c r="E209" t="n">
-        <v>0.0000721768512939456</v>
+        <v>0.00000983324171547125</v>
       </c>
       <c r="F209" t="n">
-        <v>0.895053040642512</v>
+        <v>0.890464738563308</v>
       </c>
       <c r="G209" t="n">
         <v>0.000000000000000000000000000000181174753891318</v>
@@ -5960,7 +5960,7 @@
         <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>0.997775667212235</v>
       </c>
       <c r="G210" t="n">
         <v>1</v>
@@ -5983,10 +5983,10 @@
         <v>1.3466019813671</v>
       </c>
       <c r="E211" t="n">
-        <v>1</v>
+        <v>0.384564909476218</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>0.873038203401221</v>
       </c>
       <c r="G211" t="n">
         <v>0.398174853593825</v>
@@ -6009,10 +6009,10 @@
         <v>1.11323102380851</v>
       </c>
       <c r="E212" t="n">
-        <v>0.118559112823179</v>
+        <v>0.00613371319005169</v>
       </c>
       <c r="F212" t="n">
-        <v>0.919458777872575</v>
+        <v>0.903905278931687</v>
       </c>
       <c r="G212" t="n">
         <v>0.011139142908082</v>
@@ -6061,10 +6061,10 @@
         <v>1.43610381731399</v>
       </c>
       <c r="E214" t="n">
-        <v>0.000798241208339965</v>
+        <v>0.00806450446682452</v>
       </c>
       <c r="F214" t="n">
-        <v>0.788581401594353</v>
+        <v>0.80324069084816</v>
       </c>
       <c r="G214" t="n">
         <v>0.300374597420724</v>
@@ -6087,10 +6087,10 @@
         <v>1.07650340691491</v>
       </c>
       <c r="E215" t="n">
-        <v>0.237875558925155</v>
+        <v>0.186016658861717</v>
       </c>
       <c r="F215" t="n">
-        <v>0.946660512676362</v>
+        <v>0.95198761500372</v>
       </c>
       <c r="G215" t="n">
         <v>0.233307175666107</v>
@@ -6139,10 +6139,10 @@
         <v>1.35014230932809</v>
       </c>
       <c r="E217" t="n">
-        <v>0.40463631361805</v>
+        <v>0.185511803703405</v>
       </c>
       <c r="F217" t="n">
-        <v>1.30450884829047</v>
+        <v>1.08105429018674</v>
       </c>
       <c r="G217" t="n">
         <v>0.263624470106063</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>0.377198294566573</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>0.850194839140966</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
         <v>1</v>
@@ -6217,10 +6217,10 @@
         <v>1.53058284481493</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>0.550750386762784</v>
       </c>
       <c r="F220" t="n">
-        <v>0</v>
+        <v>0.82142272067669</v>
       </c>
       <c r="G220" t="n">
         <v>0.0598026733858417</v>
@@ -6269,10 +6269,10 @@
         <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>0.278818199830593</v>
+        <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>1.57323598385896</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
         <v>1</v>
@@ -6321,10 +6321,10 @@
         <v>2.20809398733723</v>
       </c>
       <c r="E224" t="n">
-        <v>1</v>
+        <v>0.859198877715593</v>
       </c>
       <c r="F224" t="n">
-        <v>0</v>
+        <v>1.03599401790046</v>
       </c>
       <c r="G224" t="n">
         <v>0.395740131214795</v>
@@ -6373,10 +6373,10 @@
         <v>2.29370112587672</v>
       </c>
       <c r="E226" t="n">
-        <v>0.503773403146866</v>
+        <v>1</v>
       </c>
       <c r="F226" t="n">
-        <v>0.531941202549483</v>
+        <v>1.14954340518464</v>
       </c>
       <c r="G226" t="n">
         <v>1</v>
@@ -6399,10 +6399,10 @@
         <v>1.50822768483256</v>
       </c>
       <c r="E227" t="n">
-        <v>0.0000000000000000000000000000215937608057625</v>
+        <v>0.000000000000000000000000000000000000000000000140172123957639</v>
       </c>
       <c r="F227" t="n">
-        <v>0.945101419568716</v>
+        <v>0.942796100917431</v>
       </c>
       <c r="G227" t="n">
         <v>0.00038992414551128</v>
@@ -6425,10 +6425,10 @@
         <v>1.40647950287503</v>
       </c>
       <c r="E228" t="n">
-        <v>0.00000000000000878596766539496</v>
+        <v>0.00000000000000308258205821624</v>
       </c>
       <c r="F228" t="n">
-        <v>0.894435421557751</v>
+        <v>0.887796893799757</v>
       </c>
       <c r="G228" t="n">
         <v>0.0891082999946377</v>
@@ -6451,10 +6451,10 @@
         <v>0.950393919111396</v>
       </c>
       <c r="E229" t="n">
-        <v>0.577183262953643</v>
+        <v>0.175014736775741</v>
       </c>
       <c r="F229" t="n">
-        <v>0.992745089463324</v>
+        <v>0.980238426094589</v>
       </c>
       <c r="G229" t="n">
         <v>0.0627419239936878</v>
@@ -6477,10 +6477,10 @@
         <v>1.66286098435018</v>
       </c>
       <c r="E230" t="n">
-        <v>0.255893570145855</v>
+        <v>0.574732207216154</v>
       </c>
       <c r="F230" t="n">
-        <v>1.04494118362125</v>
+        <v>1.02059322343884</v>
       </c>
       <c r="G230" t="n">
         <v>0.12855975882429</v>
@@ -6503,10 +6503,10 @@
         <v>0.623211888036993</v>
       </c>
       <c r="E231" t="n">
-        <v>0.844164922630947</v>
+        <v>0.767983993200008</v>
       </c>
       <c r="F231" t="n">
-        <v>0.981824012314054</v>
+        <v>0.978071555436565</v>
       </c>
       <c r="G231" t="n">
         <v>0.837112295186713</v>
@@ -6529,10 +6529,10 @@
         <v>0.993573654251139</v>
       </c>
       <c r="E232" t="n">
-        <v>0.67981335280701</v>
+        <v>0.908009718412637</v>
       </c>
       <c r="F232" t="n">
-        <v>0.990846300266555</v>
+        <v>0.99683530963762</v>
       </c>
       <c r="G232" t="n">
         <v>0.00000000106169103860549</v>
@@ -6555,10 +6555,10 @@
         <v>1.03498948991921</v>
       </c>
       <c r="E233" t="n">
-        <v>0.779101713000532</v>
+        <v>0.95566136091335</v>
       </c>
       <c r="F233" t="n">
-        <v>1.03528263707317</v>
+        <v>1.00790490495868</v>
       </c>
       <c r="G233" t="n">
         <v>0.677288478833821</v>
@@ -6581,10 +6581,10 @@
         <v>0.952642642938294</v>
       </c>
       <c r="E234" t="n">
-        <v>1</v>
+        <v>0.271824353099744</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>1.03577920482869</v>
       </c>
       <c r="G234" t="n">
         <v>0.666270977351411</v>
@@ -6607,10 +6607,10 @@
         <v>0.736457940630713</v>
       </c>
       <c r="E235" t="n">
-        <v>1</v>
-      </c>
-      <c r="F235" t="n">
-        <v>1.06679344248549</v>
+        <v>0.0266667754995429</v>
+      </c>
+      <c r="F235" t="s">
+        <v>61</v>
       </c>
       <c r="G235" t="n">
         <v>0.562904717853839</v>
@@ -6633,10 +6633,10 @@
         <v>1.01647873398323</v>
       </c>
       <c r="E236" t="n">
-        <v>0.389572950471147</v>
+        <v>0.0458138232349267</v>
       </c>
       <c r="F236" t="n">
-        <v>0.941753042179602</v>
+        <v>0.894596576676133</v>
       </c>
       <c r="G236" t="n">
         <v>0.899889562085381</v>
@@ -6659,10 +6659,10 @@
         <v>1.16855164645216</v>
       </c>
       <c r="E237" t="n">
-        <v>1</v>
+        <v>0.746653115207198</v>
       </c>
       <c r="F237" t="n">
-        <v>0</v>
+        <v>0.918828418414405</v>
       </c>
       <c r="G237" t="n">
         <v>0.575022305757971</v>
@@ -6763,10 +6763,10 @@
         <v>1.59521015162554</v>
       </c>
       <c r="E241" t="n">
-        <v>0.332021413075423</v>
+        <v>0.423704757483113</v>
       </c>
       <c r="F241" t="n">
-        <v>0.836717655954068</v>
+        <v>0.859375389187562</v>
       </c>
       <c r="G241" t="n">
         <v>0.556814915297992</v>
@@ -6841,10 +6841,10 @@
         <v>1.03219634892733</v>
       </c>
       <c r="E244" t="n">
-        <v>0.436319293635815</v>
+        <v>0.502021828127099</v>
       </c>
       <c r="F244" t="n">
-        <v>0.944673161241125</v>
+        <v>0.952838424855906</v>
       </c>
       <c r="G244" t="n">
         <v>0.0426093236257051</v>
@@ -6867,10 +6867,10 @@
         <v>1.45620809649646</v>
       </c>
       <c r="E245" t="n">
-        <v>0.823846706106535</v>
+        <v>0.904519411372985</v>
       </c>
       <c r="F245" t="n">
-        <v>0.957951902612593</v>
+        <v>1.05192007436788</v>
       </c>
       <c r="G245" t="n">
         <v>0.0742951396579403</v>
@@ -6893,10 +6893,10 @@
         <v>1.19877846437627</v>
       </c>
       <c r="E246" t="n">
-        <v>0.749240529755275</v>
+        <v>0.711422550079018</v>
       </c>
       <c r="F246" t="n">
-        <v>0.974242191112884</v>
+        <v>1.03612377584213</v>
       </c>
       <c r="G246" t="n">
         <v>0.552100044317595</v>
@@ -6919,10 +6919,10 @@
         <v>0.975191680460083</v>
       </c>
       <c r="E247" t="n">
-        <v>0.948275287277863</v>
+        <v>0.818688783882259</v>
       </c>
       <c r="F247" t="n">
-        <v>1.00234585303828</v>
+        <v>0.993523183526422</v>
       </c>
       <c r="G247" t="n">
         <v>0.100972359817672</v>
@@ -6971,10 +6971,10 @@
         <v>1.09543121656143</v>
       </c>
       <c r="E249" t="n">
-        <v>0.121155332093949</v>
+        <v>0.955292847322765</v>
       </c>
       <c r="F249" t="n">
-        <v>0.911180077089175</v>
+        <v>0.995875860973766</v>
       </c>
       <c r="G249" t="n">
         <v>0.259889963929279</v>
@@ -7023,10 +7023,10 @@
         <v>0.789571338015085</v>
       </c>
       <c r="E251" t="n">
-        <v>0.21721501559796</v>
+        <v>0.15179357936065</v>
       </c>
       <c r="F251" t="n">
-        <v>1.1007966501997</v>
+        <v>1.11876288909236</v>
       </c>
       <c r="G251" t="n">
         <v>0.0495913298201147</v>
@@ -7049,10 +7049,10 @@
         <v>0.980207715122111</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0127287857968509</v>
+        <v>0.0122491251568153</v>
       </c>
       <c r="F252" t="n">
-        <v>0.845322263872388</v>
+        <v>0.849020102005275</v>
       </c>
       <c r="G252" t="n">
         <v>0.000000000000000000977859103087648</v>
@@ -7179,10 +7179,10 @@
         <v>1.16630839741902</v>
       </c>
       <c r="E257" t="n">
-        <v>1</v>
+        <v>0.267115126750036</v>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>1.57835461605628</v>
       </c>
       <c r="G257" t="n">
         <v>0.76613684533315</v>
@@ -7231,10 +7231,10 @@
         <v>1.61099460360167</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0000000254044247948326</v>
+        <v>0.0526981723012413</v>
       </c>
       <c r="F259" t="n">
-        <v>0.905980970442084</v>
+        <v>0.956579804127974</v>
       </c>
       <c r="G259" t="n">
         <v>0.390721785330591</v>
@@ -7257,10 +7257,10 @@
         <v>1.20148278649717</v>
       </c>
       <c r="E260" t="n">
-        <v>0.0000000000000136693007399048</v>
+        <v>0.0000000000000000178765757963397</v>
       </c>
       <c r="F260" t="n">
-        <v>0.856022572391945</v>
+        <v>0.867489893475276</v>
       </c>
       <c r="G260" t="n">
         <v>0.000883151471636461</v>
@@ -7283,10 +7283,10 @@
         <v>1.00662842550611</v>
       </c>
       <c r="E261" t="n">
-        <v>0.000104114098183935</v>
+        <v>0.0696024812924608</v>
       </c>
       <c r="F261" t="n">
-        <v>0.967109911639305</v>
+        <v>0.959109368397228</v>
       </c>
       <c r="G261" t="n">
         <v>0.469618539453828</v>
@@ -7309,10 +7309,10 @@
         <v>1.00555264962526</v>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>0.913631960804795</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>0.964641186900636</v>
       </c>
       <c r="G262" t="n">
         <v>0.876833200103313</v>
@@ -7335,10 +7335,10 @@
         <v>0.757049015097241</v>
       </c>
       <c r="E263" t="n">
-        <v>0.316628102904242</v>
+        <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>0.732768703482119</v>
+        <v>1.01463615631451</v>
       </c>
       <c r="G263" t="n">
         <v>0.519987288585741</v>
@@ -7361,10 +7361,10 @@
         <v>0.897258970375158</v>
       </c>
       <c r="E264" t="n">
-        <v>0.421995735068773</v>
+        <v>0.467810466391411</v>
       </c>
       <c r="F264" t="n">
-        <v>1.00472564859743</v>
+        <v>1.00427568157273</v>
       </c>
       <c r="G264" t="n">
         <v>0.186054540249575</v>
@@ -7390,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>1</v>
+        <v>0.983960775290614</v>
       </c>
       <c r="G265" t="n">
         <v>0.0510173562990518</v>
@@ -7413,10 +7413,10 @@
         <v>1.02049392304817</v>
       </c>
       <c r="E266" t="n">
-        <v>1</v>
+        <v>0.27008558519496</v>
       </c>
       <c r="F266" t="n">
-        <v>1.00255605965338</v>
+        <v>0.987808955876634</v>
       </c>
       <c r="G266" t="n">
         <v>0.447019236259607</v>
@@ -7439,7 +7439,7 @@
         <v>0.677876020343282</v>
       </c>
       <c r="E267" t="n">
-        <v>0.500086251509401</v>
+        <v>1</v>
       </c>
       <c r="F267" t="n">
         <v>0</v>
@@ -7465,10 +7465,10 @@
         <v>1.38760977992158</v>
       </c>
       <c r="E268" t="n">
-        <v>0.773804920509488</v>
+        <v>0.917037258800055</v>
       </c>
       <c r="F268" t="n">
-        <v>0.96275869694997</v>
+        <v>1.01349795161542</v>
       </c>
       <c r="G268" t="n">
         <v>0.656501190414109</v>
@@ -7673,10 +7673,10 @@
         <v>1.03181646866544</v>
       </c>
       <c r="E276" t="n">
-        <v>0.236057050876257</v>
+        <v>0.370860851945719</v>
       </c>
       <c r="F276" t="n">
-        <v>0.902806889447588</v>
+        <v>0.930222478420409</v>
       </c>
       <c r="G276" t="n">
         <v>0.248101449532303</v>
@@ -7725,10 +7725,10 @@
         <v>1.54299426535873</v>
       </c>
       <c r="E278" t="n">
-        <v>0.863872819187571</v>
+        <v>0.608989566215577</v>
       </c>
       <c r="F278" t="n">
-        <v>0.901611937325648</v>
+        <v>0.825090261184467</v>
       </c>
       <c r="G278" t="n">
         <v>1</v>
@@ -7751,10 +7751,10 @@
         <v>0.834153589176787</v>
       </c>
       <c r="E279" t="n">
-        <v>0.441957351580527</v>
+        <v>0.0906521315772006</v>
       </c>
       <c r="F279" t="n">
-        <v>1.2019906828766</v>
+        <v>1.43958320326848</v>
       </c>
       <c r="G279" t="n">
         <v>0.874726874697164</v>
@@ -7803,10 +7803,10 @@
         <v>1.05466499404108</v>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>0.905411531188766</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>0.989890421397924</v>
       </c>
       <c r="G281" t="n">
         <v>0.223025103329521</v>
@@ -7829,10 +7829,10 @@
         <v>0.784142943824882</v>
       </c>
       <c r="E282" t="n">
-        <v>0.0399914909024082</v>
+        <v>0.0318884316309367</v>
       </c>
       <c r="F282" t="n">
-        <v>0.836856017897917</v>
+        <v>0.830882475839423</v>
       </c>
       <c r="G282" t="n">
         <v>0.208209593179862</v>
@@ -7855,10 +7855,10 @@
         <v>0.9973873294881</v>
       </c>
       <c r="E283" t="n">
-        <v>0.0827659053233949</v>
+        <v>0.210397803471027</v>
       </c>
       <c r="F283" t="n">
-        <v>1.29126652206436</v>
+        <v>1.22347877979003</v>
       </c>
       <c r="G283" t="n">
         <v>0.0285886429808315</v>
@@ -8011,10 +8011,10 @@
         <v>0.72175292039034</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>0.108564826951098</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>0.787695182824379</v>
       </c>
       <c r="G289" t="n">
         <v>0.279935901654276</v>
@@ -8037,10 +8037,10 @@
         <v>0.49737614469518</v>
       </c>
       <c r="E290" t="n">
-        <v>1</v>
+        <v>0.412166372344306</v>
       </c>
       <c r="F290" t="n">
-        <v>0</v>
+        <v>0.544611874973763</v>
       </c>
       <c r="G290" t="n">
         <v>0.687150650851689</v>
@@ -8063,10 +8063,10 @@
         <v>1.67282404646201</v>
       </c>
       <c r="E291" t="n">
-        <v>0.000921366127063594</v>
+        <v>0.592866347574758</v>
       </c>
       <c r="F291" t="n">
-        <v>0.917252933642525</v>
+        <v>1.03287021468123</v>
       </c>
       <c r="G291" t="n">
         <v>1</v>
@@ -8089,10 +8089,10 @@
         <v>1.28774691738046</v>
       </c>
       <c r="E292" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000161898217583247</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000703261267052221</v>
       </c>
       <c r="F292" t="n">
-        <v>0.856725900798483</v>
+        <v>0.861948961933529</v>
       </c>
       <c r="G292" t="n">
         <v>0.0000761092437245982</v>
@@ -8115,10 +8115,10 @@
         <v>0.963023355106649</v>
       </c>
       <c r="E293" t="n">
-        <v>0.307065360836038</v>
+        <v>0.0963044362370012</v>
       </c>
       <c r="F293" t="n">
-        <v>0.986746158639559</v>
+        <v>0.976818305150602</v>
       </c>
       <c r="G293" t="n">
         <v>0.00000744525131241432</v>
@@ -8141,10 +8141,10 @@
         <v>1.27333976848793</v>
       </c>
       <c r="E294" t="n">
-        <v>0.690115507615003</v>
+        <v>0.736584796773789</v>
       </c>
       <c r="F294" t="n">
-        <v>0.994979252339997</v>
+        <v>1.00375222049906</v>
       </c>
       <c r="G294" t="n">
         <v>0.309613507925197</v>
@@ -8167,10 +8167,10 @@
         <v>0.945337623809541</v>
       </c>
       <c r="E295" t="n">
-        <v>1</v>
+        <v>0.058631175563529</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>2.63860928240639</v>
       </c>
       <c r="G295" t="n">
         <v>1</v>
@@ -8193,10 +8193,10 @@
         <v>0.91988652598666</v>
       </c>
       <c r="E296" t="n">
-        <v>0.167874174685225</v>
+        <v>0.387382879120981</v>
       </c>
       <c r="F296" t="n">
-        <v>1.01341414239189</v>
+        <v>1.00957058757885</v>
       </c>
       <c r="G296" t="n">
         <v>0.000524244401837554</v>
@@ -8219,10 +8219,10 @@
         <v>1.14176163056546</v>
       </c>
       <c r="E297" t="n">
-        <v>0.712763485922792</v>
+        <v>0.494143262487133</v>
       </c>
       <c r="F297" t="n">
-        <v>1.05382856035141</v>
+        <v>1.07485216334607</v>
       </c>
       <c r="G297" t="n">
         <v>0.119688246908243</v>
@@ -8245,10 +8245,10 @@
         <v>1.01668198112674</v>
       </c>
       <c r="E298" t="n">
-        <v>1</v>
+        <v>0.890882220109052</v>
       </c>
       <c r="F298" t="n">
-        <v>0.999709503180628</v>
+        <v>1.00408447841114</v>
       </c>
       <c r="G298" t="n">
         <v>1</v>
@@ -8271,10 +8271,10 @@
         <v>0.576684737913113</v>
       </c>
       <c r="E299" t="n">
-        <v>0.333264737385609</v>
+        <v>0.109598065810935</v>
       </c>
       <c r="F299" t="n">
-        <v>0.816581097206224</v>
+        <v>0.721836789392824</v>
       </c>
       <c r="G299" t="n">
         <v>0.735526922212206</v>
@@ -8297,10 +8297,10 @@
         <v>1.26243960027053</v>
       </c>
       <c r="E300" t="n">
-        <v>0.133655581815413</v>
+        <v>0.94324518909246</v>
       </c>
       <c r="F300" t="n">
-        <v>1.07540254501382</v>
+        <v>0.995535650358411</v>
       </c>
       <c r="G300" t="n">
         <v>0.04560128682217</v>
@@ -8349,10 +8349,10 @@
         <v>1.82763121079483</v>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>0.906290429706361</v>
       </c>
       <c r="F302" t="n">
-        <v>0</v>
+        <v>1.04146678926767</v>
       </c>
       <c r="G302" t="n">
         <v>1</v>
@@ -8479,10 +8479,10 @@
         <v>1.76658011160242</v>
       </c>
       <c r="E307" t="n">
-        <v>1</v>
+        <v>0.124390789368096</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>0.558119007925651</v>
       </c>
       <c r="G307" t="n">
         <v>0.553533675227696</v>
@@ -8505,10 +8505,10 @@
         <v>1.05747076420155</v>
       </c>
       <c r="E308" t="n">
-        <v>0.0570817556651875</v>
+        <v>0.844901719980387</v>
       </c>
       <c r="F308" t="n">
-        <v>0.754109473941729</v>
+        <v>0.967206134501682</v>
       </c>
       <c r="G308" t="n">
         <v>0.128273751336887</v>
@@ -8531,10 +8531,10 @@
         <v>1.26886094084612</v>
       </c>
       <c r="E309" t="n">
-        <v>0.557910513157528</v>
+        <v>0.653928416559885</v>
       </c>
       <c r="F309" t="n">
-        <v>1.04084497571407</v>
+        <v>1.05761901734254</v>
       </c>
       <c r="G309" t="n">
         <v>0.422677001266946</v>
@@ -8557,10 +8557,10 @@
         <v>2.08666039054065</v>
       </c>
       <c r="E310" t="n">
-        <v>0.933990986714612</v>
+        <v>0.890381831412422</v>
       </c>
       <c r="F310" t="n">
-        <v>1.02442142697263</v>
+        <v>0.958647939258124</v>
       </c>
       <c r="G310" t="n">
         <v>0.197739045724421</v>
@@ -8583,10 +8583,10 @@
         <v>0.884161635547872</v>
       </c>
       <c r="E311" t="n">
-        <v>0.0162080432636543</v>
+        <v>0.00373679047729983</v>
       </c>
       <c r="F311" t="n">
-        <v>1.05055108388731</v>
+        <v>1.05902954305189</v>
       </c>
       <c r="G311" t="n">
         <v>0.00240769296334689</v>
@@ -8635,10 +8635,10 @@
         <v>0.934423121699871</v>
       </c>
       <c r="E313" t="n">
-        <v>1</v>
+        <v>0.724076251354254</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>1.03238195857541</v>
       </c>
       <c r="G313" t="n">
         <v>0.847886290138342</v>
@@ -8661,10 +8661,10 @@
         <v>0.800968412120852</v>
       </c>
       <c r="E314" t="n">
-        <v>0.89461684840194</v>
+        <v>1</v>
       </c>
       <c r="F314" t="n">
-        <v>1.02576620258866</v>
+        <v>0.994893616098203</v>
       </c>
       <c r="G314" t="n">
         <v>0.118401425406806</v>
@@ -8687,10 +8687,10 @@
         <v>0.634538509398408</v>
       </c>
       <c r="E315" t="n">
-        <v>0.308109054073072</v>
+        <v>1</v>
       </c>
       <c r="F315" t="n">
-        <v>1.96812832199367</v>
+        <v>0</v>
       </c>
       <c r="G315" t="n">
         <v>1</v>
@@ -8713,10 +8713,10 @@
         <v>1.1731436118615</v>
       </c>
       <c r="E316" t="n">
-        <v>0.23985360955124</v>
+        <v>0.685402985298669</v>
       </c>
       <c r="F316" t="n">
-        <v>0.866771634551908</v>
+        <v>0.955707426277829</v>
       </c>
       <c r="G316" t="n">
         <v>0.124104256728375</v>
@@ -8895,10 +8895,10 @@
         <v>1.86591968967953</v>
       </c>
       <c r="E323" t="n">
-        <v>0.000816512499930141</v>
+        <v>0.665631810956273</v>
       </c>
       <c r="F323" t="n">
-        <v>0.929910238071065</v>
+        <v>1.02814769697333</v>
       </c>
       <c r="G323" t="n">
         <v>0.53479338982692</v>
@@ -8921,10 +8921,10 @@
         <v>1.36083999286207</v>
       </c>
       <c r="E324" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000238892880114622</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000212615213641503</v>
       </c>
       <c r="F324" t="n">
-        <v>0.86687677586886</v>
+        <v>0.861275828046451</v>
       </c>
       <c r="G324" t="n">
         <v>0.00466924398404013</v>
@@ -8947,10 +8947,10 @@
         <v>1.01122184203777</v>
       </c>
       <c r="E325" t="n">
-        <v>0.205734494291134</v>
+        <v>0.534419041894123</v>
       </c>
       <c r="F325" t="n">
-        <v>0.994296612184484</v>
+        <v>1.00383585989534</v>
       </c>
       <c r="G325" t="n">
         <v>0.000145716017897379</v>
@@ -8973,10 +8973,10 @@
         <v>1.70874761015935</v>
       </c>
       <c r="E326" t="n">
-        <v>0.00887202568961815</v>
+        <v>0.0115454195500925</v>
       </c>
       <c r="F326" t="n">
-        <v>1.0075187610064</v>
+        <v>1.00722791850634</v>
       </c>
       <c r="G326" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000120740716393288</v>
@@ -8999,10 +8999,10 @@
         <v>0.916828465280007</v>
       </c>
       <c r="E327" t="n">
-        <v>0.727430769452905</v>
+        <v>0.872624826308791</v>
       </c>
       <c r="F327" t="n">
-        <v>1.0165633076801</v>
+        <v>0.994154336944343</v>
       </c>
       <c r="G327" t="n">
         <v>0.957630772242263</v>
@@ -9025,10 +9025,10 @@
         <v>1.06325772560119</v>
       </c>
       <c r="E328" t="n">
-        <v>0.0587356346865673</v>
+        <v>0.00740839197353263</v>
       </c>
       <c r="F328" t="n">
-        <v>0.961413458966569</v>
+        <v>0.944603044912964</v>
       </c>
       <c r="G328" t="n">
         <v>0.00165748358389121</v>
@@ -9051,10 +9051,10 @@
         <v>1.17987156897632</v>
       </c>
       <c r="E329" t="n">
-        <v>0.242028868546841</v>
+        <v>0.451377166911325</v>
       </c>
       <c r="F329" t="n">
-        <v>1.07173696071755</v>
+        <v>1.04605369181703</v>
       </c>
       <c r="G329" t="n">
         <v>0.778636233917641</v>
@@ -9077,10 +9077,10 @@
         <v>0.99325211863153</v>
       </c>
       <c r="E330" t="n">
-        <v>0.0520772932484878</v>
+        <v>0.196786251296532</v>
       </c>
       <c r="F330" t="n">
-        <v>0.910870303064252</v>
+        <v>0.99143090083709</v>
       </c>
       <c r="G330" t="n">
         <v>0.562237671142366</v>
@@ -9103,10 +9103,10 @@
         <v>0.78635519977395</v>
       </c>
       <c r="E331" t="n">
-        <v>0.167510888604687</v>
+        <v>1</v>
       </c>
       <c r="F331" t="n">
-        <v>1.30918446154797</v>
+        <v>0.959277746521078</v>
       </c>
       <c r="G331" t="n">
         <v>0.219904838732637</v>
@@ -9129,10 +9129,10 @@
         <v>1.29407577855814</v>
       </c>
       <c r="E332" t="n">
-        <v>0.876247353233758</v>
+        <v>0.262363956039188</v>
       </c>
       <c r="F332" t="n">
-        <v>1.00322347542085</v>
+        <v>0.979380242235262</v>
       </c>
       <c r="G332" t="n">
         <v>0.00365155167883011</v>
@@ -9155,10 +9155,10 @@
         <v>1.05457811677751</v>
       </c>
       <c r="E333" t="n">
-        <v>0.451526406697387</v>
+        <v>0.283090815074088</v>
       </c>
       <c r="F333" t="n">
-        <v>0.702407006440578</v>
+        <v>0.730423718082129</v>
       </c>
       <c r="G333" t="n">
         <v>0.699876743975261</v>
@@ -9181,10 +9181,10 @@
         <v>1.52957143559119</v>
       </c>
       <c r="E334" t="n">
-        <v>1</v>
+        <v>0.244793730834104</v>
       </c>
       <c r="F334" t="n">
-        <v>0</v>
+        <v>0.662216559813312</v>
       </c>
       <c r="G334" t="n">
         <v>0.568194130511406</v>
@@ -9207,10 +9207,10 @@
         <v>5.47056878786433</v>
       </c>
       <c r="E335" t="n">
-        <v>1</v>
+        <v>0.501010101010101</v>
       </c>
       <c r="F335" t="n">
-        <v>0.872279498270126</v>
+        <v>0</v>
       </c>
       <c r="G335" t="n">
         <v>1</v>
@@ -9259,10 +9259,10 @@
         <v>1.84387364735675</v>
       </c>
       <c r="E337" t="n">
-        <v>0.0764507928657412</v>
+        <v>0.0509803815722647</v>
       </c>
       <c r="F337" t="n">
-        <v>0.842427027351737</v>
+        <v>0.836948906141552</v>
       </c>
       <c r="G337" t="n">
         <v>0.000877583412193162</v>
@@ -9285,10 +9285,10 @@
         <v>1.09240761943307</v>
       </c>
       <c r="E338" t="n">
-        <v>0.722460537136873</v>
+        <v>0.542449266664582</v>
       </c>
       <c r="F338" t="n">
-        <v>0.927848355948479</v>
+        <v>0.885720921199767</v>
       </c>
       <c r="G338" t="n">
         <v>0.289871886110232</v>
@@ -9337,10 +9337,10 @@
         <v>1.06854101032424</v>
       </c>
       <c r="E340" t="n">
-        <v>0.00257855831035319</v>
+        <v>0.00129382017650671</v>
       </c>
       <c r="F340" t="n">
-        <v>0.894227511494957</v>
+        <v>0.893920499116194</v>
       </c>
       <c r="G340" t="n">
         <v>0.890050330677183</v>
@@ -9363,10 +9363,10 @@
         <v>0</v>
       </c>
       <c r="E341" t="n">
-        <v>0.103588378498975</v>
+        <v>1</v>
       </c>
       <c r="F341" t="n">
-        <v>0.678929815197517</v>
+        <v>0</v>
       </c>
       <c r="G341" t="n">
         <v>1</v>
@@ -9389,10 +9389,10 @@
         <v>1.21241974139565</v>
       </c>
       <c r="E342" t="n">
-        <v>0.0667984957159152</v>
+        <v>0.0375839273693438</v>
       </c>
       <c r="F342" t="n">
-        <v>1.22301363146793</v>
+        <v>1.23933204052022</v>
       </c>
       <c r="G342" t="n">
         <v>0.684317915424789</v>
@@ -9415,10 +9415,10 @@
         <v>0.95553104460125</v>
       </c>
       <c r="E343" t="n">
-        <v>0.00237354474381379</v>
+        <v>0.814118902851045</v>
       </c>
       <c r="F343" t="n">
-        <v>0.932888703998237</v>
+        <v>1.00570384924681</v>
       </c>
       <c r="G343" t="n">
         <v>0.883177641268012</v>
@@ -9467,10 +9467,10 @@
         <v>1.05966422697439</v>
       </c>
       <c r="E345" t="n">
-        <v>0.0708790301351725</v>
+        <v>0.965675384889354</v>
       </c>
       <c r="F345" t="n">
-        <v>1.26240452809362</v>
+        <v>1.0016204725271</v>
       </c>
       <c r="G345" t="n">
         <v>0.0256661247268251</v>
@@ -9493,10 +9493,10 @@
         <v>0.846833486611843</v>
       </c>
       <c r="E346" t="n">
-        <v>0.289532158862791</v>
+        <v>0.160384798788182</v>
       </c>
       <c r="F346" t="n">
-        <v>0.944856519227667</v>
+        <v>0.933709822396835</v>
       </c>
       <c r="G346" t="n">
         <v>0.706717846811696</v>
@@ -9519,10 +9519,10 @@
         <v>0.934063069210126</v>
       </c>
       <c r="E347" t="n">
-        <v>0.0319791442845163</v>
+        <v>0.053055001813928</v>
       </c>
       <c r="F347" t="n">
-        <v>1.18905277998366</v>
+        <v>1.18154484164473</v>
       </c>
       <c r="G347" t="n">
         <v>0.00481102435634317</v>
@@ -9545,10 +9545,10 @@
         <v>1.26427706029988</v>
       </c>
       <c r="E348" t="n">
-        <v>0.575210971392424</v>
+        <v>0.750249933549552</v>
       </c>
       <c r="F348" t="n">
-        <v>0.97020455673346</v>
+        <v>0.983732055546533</v>
       </c>
       <c r="G348" t="n">
         <v>0.00000293023725477135</v>
@@ -9600,7 +9600,7 @@
         <v>1</v>
       </c>
       <c r="F350" t="n">
-        <v>0.891472099976845</v>
+        <v>0</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
@@ -9623,10 +9623,10 @@
         <v>1.57555632660705</v>
       </c>
       <c r="E351" t="n">
-        <v>1</v>
+        <v>0.169780676982255</v>
       </c>
       <c r="F351" t="n">
-        <v>1.13801896043104</v>
+        <v>1.95424754173475</v>
       </c>
       <c r="G351" t="n">
         <v>0.447177124405402</v>
@@ -9649,10 +9649,10 @@
         <v>1.20333922592233</v>
       </c>
       <c r="E352" t="n">
-        <v>1</v>
+        <v>0.394907732179942</v>
       </c>
       <c r="F352" t="n">
-        <v>0</v>
+        <v>0.570882928557625</v>
       </c>
       <c r="G352" t="n">
         <v>0.668484500574053</v>
@@ -9675,10 +9675,10 @@
         <v>0.996609239709618</v>
       </c>
       <c r="E353" t="n">
-        <v>0.555493269513561</v>
+        <v>0.195513810249832</v>
       </c>
       <c r="F353" t="n">
-        <v>0.82123414347622</v>
+        <v>0.847692687326139</v>
       </c>
       <c r="G353" t="n">
         <v>0.0263980509716672</v>
@@ -9701,10 +9701,10 @@
         <v>1.00939082099237</v>
       </c>
       <c r="E354" t="n">
-        <v>0.505107252298264</v>
-      </c>
-      <c r="F354" t="s">
-        <v>61</v>
+        <v>0.620502856413228</v>
+      </c>
+      <c r="F354" t="n">
+        <v>1.33874893381467</v>
       </c>
       <c r="G354" t="n">
         <v>1</v>
@@ -9727,10 +9727,10 @@
         <v>1.62889427156991</v>
       </c>
       <c r="E355" t="n">
-        <v>0.000000000000000296612166511416</v>
+        <v>0.0000000103140148477399</v>
       </c>
       <c r="F355" t="n">
-        <v>0.931499380992996</v>
+        <v>0.946950017253012</v>
       </c>
       <c r="G355" t="n">
         <v>0.79588420840518</v>
@@ -9753,10 +9753,10 @@
         <v>1.49796968622818</v>
       </c>
       <c r="E356" t="n">
-        <v>0.00000000000000000000000000000332827878494898</v>
+        <v>0.000000000000000000106681084674328</v>
       </c>
       <c r="F356" t="n">
-        <v>0.849889177915296</v>
+        <v>0.850460357665355</v>
       </c>
       <c r="G356" t="n">
         <v>0.0249595216958491</v>
@@ -9779,10 +9779,10 @@
         <v>1.36989678076865</v>
       </c>
       <c r="E357" t="n">
-        <v>0.00000887726447973413</v>
+        <v>0.000718569414349439</v>
       </c>
       <c r="F357" t="n">
-        <v>1.07033363418279</v>
+        <v>1.05589488822083</v>
       </c>
       <c r="G357" t="n">
         <v>0.65112657501893</v>
@@ -9805,10 +9805,10 @@
         <v>1.23853474849567</v>
       </c>
       <c r="E358" t="n">
-        <v>1</v>
+        <v>0.935412374430043</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>0.97416860669119</v>
       </c>
       <c r="G358" t="n">
         <v>0.421737139364807</v>
@@ -9831,10 +9831,10 @@
         <v>1.18250134644537</v>
       </c>
       <c r="E359" t="n">
-        <v>0.241530421445548</v>
+        <v>0.109201289054906</v>
       </c>
       <c r="F359" t="n">
-        <v>0.786142306333665</v>
+        <v>0.789424833557862</v>
       </c>
       <c r="G359" t="n">
         <v>0.730005050468954</v>
@@ -9857,10 +9857,10 @@
         <v>1.21559652631298</v>
       </c>
       <c r="E360" t="n">
-        <v>0.024824248277967</v>
+        <v>0.349380564603002</v>
       </c>
       <c r="F360" t="n">
-        <v>0.896538562064155</v>
+        <v>0.957919006486778</v>
       </c>
       <c r="G360" t="n">
         <v>0.352185997974121</v>
@@ -9883,10 +9883,10 @@
         <v>1.29477580162815</v>
       </c>
       <c r="E361" t="n">
-        <v>0.539385704910575</v>
+        <v>0.763239253975357</v>
       </c>
       <c r="F361" t="n">
-        <v>0.866560339608675</v>
+        <v>0.937914581325531</v>
       </c>
       <c r="G361" t="n">
         <v>0.363534433962583</v>
@@ -9909,10 +9909,10 @@
         <v>0.988042199082714</v>
       </c>
       <c r="E362" t="n">
-        <v>1</v>
+        <v>0.0539408863436033</v>
       </c>
       <c r="F362" t="n">
-        <v>0</v>
+        <v>0.851145140072313</v>
       </c>
       <c r="G362" t="n">
         <v>0.0878236750379424</v>
@@ -9935,10 +9935,10 @@
         <v>1.05078047416884</v>
       </c>
       <c r="E363" t="n">
-        <v>1</v>
+        <v>0.5350720743923</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>0.817517129741284</v>
       </c>
       <c r="G363" t="n">
         <v>0.105704170843636</v>
@@ -9961,10 +9961,10 @@
         <v>1.32329536818715</v>
       </c>
       <c r="E364" t="n">
-        <v>0.901692649706519</v>
+        <v>0.930416840678662</v>
       </c>
       <c r="F364" t="n">
-        <v>0.995139905606652</v>
+        <v>0.996886098023866</v>
       </c>
       <c r="G364" t="n">
         <v>0.0636706140981164</v>
@@ -9987,10 +9987,10 @@
         <v>1.54327116353122</v>
       </c>
       <c r="E365" t="n">
-        <v>1</v>
+        <v>0.0869764481461386</v>
       </c>
       <c r="F365" t="n">
-        <v>1.32753443448184</v>
+        <v>0.75977061700935</v>
       </c>
       <c r="G365" t="n">
         <v>0.128519226727301</v>
@@ -10013,10 +10013,10 @@
         <v>3.12491437151953</v>
       </c>
       <c r="E366" t="n">
-        <v>1</v>
+        <v>0.336397189310423</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>1.41673824440643</v>
       </c>
       <c r="G366" t="n">
         <v>0.0879194896169188</v>
@@ -10039,10 +10039,10 @@
         <v>1.37787066663673</v>
       </c>
       <c r="E367" t="n">
-        <v>0.609943714821764</v>
+        <v>0.475967900363346</v>
       </c>
       <c r="F367" t="n">
-        <v>0.360222066516793</v>
+        <v>0.511977456736578</v>
       </c>
       <c r="G367" t="n">
         <v>1</v>
@@ -10065,10 +10065,10 @@
         <v>1.67966791404474</v>
       </c>
       <c r="E368" t="n">
-        <v>0.115944610543623</v>
+        <v>0.0581235386810652</v>
       </c>
       <c r="F368" t="n">
-        <v>0.855178058123991</v>
+        <v>0.838459504047736</v>
       </c>
       <c r="G368" t="n">
         <v>0.870381519864012</v>
@@ -10117,10 +10117,10 @@
         <v>1.10001642008205</v>
       </c>
       <c r="E370" t="n">
-        <v>1</v>
+        <v>0.123068752011634</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>0.790837693250545</v>
       </c>
       <c r="G370" t="n">
         <v>0.356870249006618</v>
@@ -10143,10 +10143,10 @@
         <v>0.942823386461426</v>
       </c>
       <c r="E371" t="n">
-        <v>0.608401326456237</v>
+        <v>0.799787744111939</v>
       </c>
       <c r="F371" t="n">
-        <v>0.681449031412838</v>
+        <v>0.778810391212602</v>
       </c>
       <c r="G371" t="n">
         <v>0.263914508583907</v>
@@ -10169,10 +10169,10 @@
         <v>1.14172963173548</v>
       </c>
       <c r="E372" t="n">
-        <v>0.0865560349770775</v>
+        <v>0.0804738393267085</v>
       </c>
       <c r="F372" t="n">
-        <v>0.847890391043396</v>
+        <v>0.855700283079216</v>
       </c>
       <c r="G372" t="n">
         <v>0.550348450288627</v>
@@ -10195,10 +10195,10 @@
         <v>1.29524070313663</v>
       </c>
       <c r="E373" t="n">
-        <v>0.63814363000128</v>
+        <v>0.862985240730722</v>
       </c>
       <c r="F373" t="n">
-        <v>0.93345950496037</v>
+        <v>0.974744231542053</v>
       </c>
       <c r="G373" t="n">
         <v>0.57544556139597</v>
@@ -10221,10 +10221,10 @@
         <v>1.55233390233085</v>
       </c>
       <c r="E374" t="n">
-        <v>0.749709668825683</v>
+        <v>0.368940228616554</v>
       </c>
       <c r="F374" t="n">
-        <v>0.917602964566281</v>
+        <v>1.18617416264517</v>
       </c>
       <c r="G374" t="n">
         <v>0.541842970828221</v>
@@ -10247,10 +10247,10 @@
         <v>1.13233133923901</v>
       </c>
       <c r="E375" t="n">
-        <v>0.880178544032319</v>
+        <v>0.875647524758589</v>
       </c>
       <c r="F375" t="n">
-        <v>0.982915610675029</v>
+        <v>1.02834370481438</v>
       </c>
       <c r="G375" t="n">
         <v>0.801780611656737</v>
@@ -10273,10 +10273,10 @@
         <v>1.13583038108966</v>
       </c>
       <c r="E376" t="n">
-        <v>1</v>
+        <v>0.669966850708769</v>
       </c>
       <c r="F376" t="n">
-        <v>0</v>
+        <v>1.22634583546171</v>
       </c>
       <c r="G376" t="n">
         <v>0.742254347710667</v>
@@ -10299,10 +10299,10 @@
         <v>0.993999493086678</v>
       </c>
       <c r="E377" t="n">
-        <v>0.437661702220807</v>
+        <v>0.228393176631485</v>
       </c>
       <c r="F377" t="n">
-        <v>1.60903940193275</v>
+        <v>1.24783332940322</v>
       </c>
       <c r="G377" t="n">
         <v>0.613979297766296</v>
@@ -10325,10 +10325,10 @@
         <v>1.40218116369355</v>
       </c>
       <c r="E378" t="n">
-        <v>1</v>
+        <v>0.649176049305505</v>
       </c>
       <c r="F378" t="n">
-        <v>0</v>
+        <v>1.13434995605315</v>
       </c>
       <c r="G378" t="n">
         <v>0.852086899667862</v>
@@ -10507,10 +10507,10 @@
         <v>1.50527822898516</v>
       </c>
       <c r="E385" t="n">
-        <v>1</v>
+        <v>0.374682632988906</v>
       </c>
       <c r="F385" t="n">
-        <v>0</v>
+        <v>1.29108083063665</v>
       </c>
       <c r="G385" t="n">
         <v>0.126587764954041</v>
@@ -10533,10 +10533,10 @@
         <v>2.08122045507834</v>
       </c>
       <c r="E386" t="n">
-        <v>1</v>
+        <v>0.567936232963499</v>
       </c>
       <c r="F386" t="n">
-        <v>0</v>
+        <v>0.785726655631257</v>
       </c>
       <c r="G386" t="n">
         <v>0.481915466151503</v>
@@ -10559,10 +10559,10 @@
         <v>1.5345443372037</v>
       </c>
       <c r="E387" t="n">
-        <v>0.00000136079214061959</v>
+        <v>0.000000000142880066506549</v>
       </c>
       <c r="F387" t="n">
-        <v>0.963192220162554</v>
+        <v>0.952779648062274</v>
       </c>
       <c r="G387" t="n">
         <v>0.324309798779124</v>
@@ -10585,10 +10585,10 @@
         <v>1.31545476796321</v>
       </c>
       <c r="E388" t="n">
-        <v>0.0807269071901967</v>
+        <v>0.103880940119618</v>
       </c>
       <c r="F388" t="n">
-        <v>0.893793117176684</v>
+        <v>0.896279348147477</v>
       </c>
       <c r="G388" t="n">
         <v>0.624269080941318</v>
@@ -10611,10 +10611,10 @@
         <v>1.1574168387166</v>
       </c>
       <c r="E389" t="n">
-        <v>0.801600959434612</v>
+        <v>1</v>
       </c>
       <c r="F389" t="n">
-        <v>0.805169230103222</v>
+        <v>0</v>
       </c>
       <c r="G389" t="n">
         <v>1</v>
@@ -10637,10 +10637,10 @@
         <v>1.34996991304494</v>
       </c>
       <c r="E390" t="n">
-        <v>0.38591931811081</v>
+        <v>0.388564856098556</v>
       </c>
       <c r="F390" t="n">
-        <v>1.39215891564082</v>
+        <v>1.39092325493424</v>
       </c>
       <c r="G390" t="n">
         <v>0.00651373601669491</v>
@@ -10689,10 +10689,10 @@
         <v>1.13160022352922</v>
       </c>
       <c r="E392" t="n">
-        <v>0.714099461584533</v>
+        <v>0.586938407552979</v>
       </c>
       <c r="F392" t="n">
-        <v>0.824518301376556</v>
+        <v>0.804038142867083</v>
       </c>
       <c r="G392" t="n">
         <v>0.706890061751947</v>
@@ -10793,10 +10793,10 @@
         <v>1.17210900919211</v>
       </c>
       <c r="E396" t="n">
-        <v>0.663780108205796</v>
+        <v>0.639733044289268</v>
       </c>
       <c r="F396" t="n">
-        <v>0.932217563707427</v>
+        <v>0.921971513389845</v>
       </c>
       <c r="G396" t="n">
         <v>1</v>
@@ -11004,7 +11004,7 @@
         <v>1</v>
       </c>
       <c r="F404" t="n">
-        <v>1.11103041071887</v>
+        <v>0.996524604329095</v>
       </c>
       <c r="G404" t="n">
         <v>0.106375233989594</v>
@@ -11027,10 +11027,10 @@
         <v>1.4759503884443</v>
       </c>
       <c r="E405" t="n">
-        <v>1</v>
+        <v>0.829510620278907</v>
       </c>
       <c r="F405" t="n">
-        <v>0</v>
+        <v>0.84737154803784</v>
       </c>
       <c r="G405" t="n">
         <v>0.116954866569842</v>
@@ -11053,10 +11053,10 @@
         <v>1.10565594959885</v>
       </c>
       <c r="E406" t="n">
-        <v>0.227257193835028</v>
+        <v>0.230818806958966</v>
       </c>
       <c r="F406" t="n">
-        <v>1.92038422090239</v>
+        <v>1.88082818916806</v>
       </c>
       <c r="G406" t="n">
         <v>0.685782955545174</v>
@@ -11079,10 +11079,10 @@
         <v>1.00032825200742</v>
       </c>
       <c r="E407" t="n">
-        <v>1</v>
+        <v>0.185631158333141</v>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>1.34788226649321</v>
       </c>
       <c r="G407" t="n">
         <v>0.742540079749891</v>
@@ -11105,10 +11105,10 @@
         <v>0.927497498819377</v>
       </c>
       <c r="E408" t="n">
-        <v>0.624940248183875</v>
+        <v>0.36592721626555</v>
       </c>
       <c r="F408" t="n">
-        <v>2.72890014321583</v>
+        <v>3.11303797984344</v>
       </c>
       <c r="G408" t="n">
         <v>1</v>
@@ -11391,10 +11391,10 @@
         <v>2.10773962029744</v>
       </c>
       <c r="E419" t="n">
-        <v>0.643079827619142</v>
+        <v>0.493810123673396</v>
       </c>
       <c r="F419" t="n">
-        <v>0.939709097693421</v>
+        <v>0.915518264759569</v>
       </c>
       <c r="G419" t="n">
         <v>0.625843708757695</v>
@@ -11417,10 +11417,10 @@
         <v>1.23736986988578</v>
       </c>
       <c r="E420" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000715316397050983</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000748024558100736</v>
       </c>
       <c r="F420" t="n">
-        <v>0.8675068192972</v>
+        <v>0.868324398111189</v>
       </c>
       <c r="G420" t="n">
         <v>0.00000451880453505586</v>
@@ -11443,10 +11443,10 @@
         <v>0.999069574312554</v>
       </c>
       <c r="E421" t="n">
-        <v>0.000163368754569613</v>
+        <v>0.0149643376576053</v>
       </c>
       <c r="F421" t="n">
-        <v>0.981196618378801</v>
+        <v>0.980896697436473</v>
       </c>
       <c r="G421" t="n">
         <v>0.000000244005914837256</v>
@@ -11469,10 +11469,10 @@
         <v>1.71181885844299</v>
       </c>
       <c r="E422" t="n">
-        <v>0.498793756017371</v>
+        <v>0.298383875116128</v>
       </c>
       <c r="F422" t="n">
-        <v>1.00603541292701</v>
+        <v>1.00925545753866</v>
       </c>
       <c r="G422" t="n">
         <v>0.000000000000162135111776401</v>
@@ -11495,10 +11495,10 @@
         <v>1.00470512028753</v>
       </c>
       <c r="E423" t="n">
-        <v>0.093709040612803</v>
+        <v>0.200502103080799</v>
       </c>
       <c r="F423" t="n">
-        <v>0.853378484221677</v>
+        <v>0.907159376359724</v>
       </c>
       <c r="G423" t="n">
         <v>0.822690877515119</v>
@@ -11521,10 +11521,10 @@
         <v>0.998282593563556</v>
       </c>
       <c r="E424" t="n">
-        <v>0.339561659699301</v>
+        <v>0.814461506563713</v>
       </c>
       <c r="F424" t="n">
-        <v>1.02436827402394</v>
+        <v>1.00741342836006</v>
       </c>
       <c r="G424" t="n">
         <v>0.772101035861394</v>
@@ -11547,10 +11547,10 @@
         <v>1.14130436149776</v>
       </c>
       <c r="E425" t="n">
-        <v>0.978790402084705</v>
+        <v>1</v>
       </c>
       <c r="F425" t="n">
-        <v>0.997459759130098</v>
+        <v>1.00115926747562</v>
       </c>
       <c r="G425" t="n">
         <v>0.314070195979684</v>
@@ -11573,10 +11573,10 @@
         <v>0.987290138032199</v>
       </c>
       <c r="E426" t="n">
-        <v>0.115444405058614</v>
+        <v>0.0250271134194396</v>
       </c>
       <c r="F426" t="n">
-        <v>0.833538919119713</v>
+        <v>0.977115661691551</v>
       </c>
       <c r="G426" t="n">
         <v>0.0712522813817185</v>
@@ -11599,10 +11599,10 @@
         <v>0.890220377309417</v>
       </c>
       <c r="E427" t="n">
-        <v>0.745936655634385</v>
+        <v>1</v>
       </c>
       <c r="F427" t="n">
-        <v>0.914190706637492</v>
+        <v>0</v>
       </c>
       <c r="G427" t="n">
         <v>1</v>
@@ -11625,10 +11625,10 @@
         <v>1.37432390892086</v>
       </c>
       <c r="E428" t="n">
-        <v>0.0781872634710388</v>
+        <v>0.185954267792539</v>
       </c>
       <c r="F428" t="n">
-        <v>0.946651257289442</v>
+        <v>0.962624269396521</v>
       </c>
       <c r="G428" t="n">
         <v>0.440674149580737</v>
@@ -11651,10 +11651,10 @@
         <v>1.04052929152744</v>
       </c>
       <c r="E429" t="n">
-        <v>0.11844462838438</v>
+        <v>0.0867965732329374</v>
       </c>
       <c r="F429" t="n">
-        <v>1.29948739689161</v>
+        <v>1.25777400317592</v>
       </c>
       <c r="G429" t="n">
         <v>0.300926316765357</v>
@@ -11703,10 +11703,10 @@
         <v>0.839767003228518</v>
       </c>
       <c r="E431" t="n">
-        <v>0.261687473243514</v>
+        <v>0.0548323557027719</v>
       </c>
       <c r="F431" t="n">
-        <v>2.01755425956117</v>
+        <v>3.94806473093007</v>
       </c>
       <c r="G431" t="n">
         <v>0.681457425380408</v>
@@ -11755,10 +11755,10 @@
         <v>1.34342676372287</v>
       </c>
       <c r="E433" t="n">
-        <v>0.000330132556237201</v>
+        <v>0.000176349866645502</v>
       </c>
       <c r="F433" t="n">
-        <v>0.869393616614484</v>
+        <v>0.865012691853146</v>
       </c>
       <c r="G433" t="n">
         <v>0.0000000000000000000906797648840441</v>
@@ -11781,10 +11781,10 @@
         <v>0.59938081460389</v>
       </c>
       <c r="E434" t="n">
-        <v>0.576796880608542</v>
+        <v>0.542188285227596</v>
       </c>
       <c r="F434" t="n">
-        <v>1.03198378059215</v>
+        <v>1.03458369689546</v>
       </c>
       <c r="G434" t="n">
         <v>0.43717652595951</v>
@@ -11807,10 +11807,10 @@
         <v>1.37313213527542</v>
       </c>
       <c r="E435" t="n">
-        <v>0.388261536697438</v>
+        <v>0.599915058421174</v>
       </c>
       <c r="F435" t="n">
-        <v>1.12956619886165</v>
+        <v>1.05705214073562</v>
       </c>
       <c r="G435" t="n">
         <v>0.604267944542718</v>
@@ -11833,10 +11833,10 @@
         <v>1.02156391591497</v>
       </c>
       <c r="E436" t="n">
-        <v>0.0000254506979499607</v>
+        <v>0.00000240220218992157</v>
       </c>
       <c r="F436" t="n">
-        <v>0.883170201107012</v>
+        <v>0.88248361313885</v>
       </c>
       <c r="G436" t="n">
         <v>0.0589730629921644</v>
@@ -11859,10 +11859,10 @@
         <v>0.752231268815914</v>
       </c>
       <c r="E437" t="n">
-        <v>0.800676264033029</v>
+        <v>1</v>
       </c>
       <c r="F437" t="n">
-        <v>1.04970654757691</v>
+        <v>0</v>
       </c>
       <c r="G437" t="n">
         <v>1</v>
@@ -11885,10 +11885,10 @@
         <v>1.32621660700826</v>
       </c>
       <c r="E438" t="n">
-        <v>0.815829204851839</v>
+        <v>0.465163343853695</v>
       </c>
       <c r="F438" t="n">
-        <v>1.00871584032046</v>
+        <v>1.0265314396444</v>
       </c>
       <c r="G438" t="n">
         <v>0.429019868929493</v>
@@ -11911,10 +11911,10 @@
         <v>0.983216830207536</v>
       </c>
       <c r="E439" t="n">
-        <v>0.345816986972854</v>
+        <v>0.571710245533134</v>
       </c>
       <c r="F439" t="n">
-        <v>0.9785516279092</v>
+        <v>1.01135652620933</v>
       </c>
       <c r="G439" t="n">
         <v>0.951311220388265</v>
@@ -11937,10 +11937,10 @@
         <v>1.02204403198269</v>
       </c>
       <c r="E440" t="n">
-        <v>0.835775736933473</v>
+        <v>0.944425386578109</v>
       </c>
       <c r="F440" t="n">
-        <v>1.03260379912365</v>
+        <v>0.981393922620285</v>
       </c>
       <c r="G440" t="n">
         <v>0.13208457716707</v>
@@ -11963,10 +11963,10 @@
         <v>1.14247802147385</v>
       </c>
       <c r="E441" t="n">
-        <v>0.566017844661603</v>
+        <v>0.0374357840429126</v>
       </c>
       <c r="F441" t="n">
-        <v>1.21660355536238</v>
+        <v>0.909493917964269</v>
       </c>
       <c r="G441" t="n">
         <v>0.972786701532384</v>
@@ -11989,10 +11989,10 @@
         <v>0.88352356211533</v>
       </c>
       <c r="E442" t="n">
-        <v>0.0135774500392615</v>
+        <v>0.035926026515276</v>
       </c>
       <c r="F442" t="n">
-        <v>0.812916076103866</v>
+        <v>0.838863214747686</v>
       </c>
       <c r="G442" t="n">
         <v>0.488368542405357</v>
@@ -12015,10 +12015,10 @@
         <v>0.905384234705677</v>
       </c>
       <c r="E443" t="n">
-        <v>0.100868221515719</v>
+        <v>0.126504899228155</v>
       </c>
       <c r="F443" t="n">
-        <v>1.05365432392942</v>
+        <v>1.04957479645912</v>
       </c>
       <c r="G443" t="n">
         <v>0.000000272626124932854</v>
@@ -12041,10 +12041,10 @@
         <v>1.16914469027077</v>
       </c>
       <c r="E444" t="n">
-        <v>0.399330024467772</v>
+        <v>0.244650790077725</v>
       </c>
       <c r="F444" t="n">
-        <v>0.942915588533092</v>
+        <v>0.928969665082346</v>
       </c>
       <c r="G444" t="n">
         <v>0.0000863722631747315</v>
@@ -12070,7 +12070,7 @@
         <v>1</v>
       </c>
       <c r="F445" t="n">
-        <v>0</v>
+        <v>1.10892204560755</v>
       </c>
       <c r="G445" t="n">
         <v>1</v>
@@ -12093,10 +12093,10 @@
         <v>1.25889802840794</v>
       </c>
       <c r="E446" t="n">
-        <v>0.343595502316472</v>
+        <v>0.137692292198633</v>
       </c>
       <c r="F446" t="n">
-        <v>1.3327706821449</v>
+        <v>1.47158727199777</v>
       </c>
       <c r="G446" t="n">
         <v>0.698789511759049</v>
@@ -12119,10 +12119,10 @@
         <v>1.76865341170872</v>
       </c>
       <c r="E447" t="n">
-        <v>0.0000593605261505241</v>
+        <v>0.437507278476078</v>
       </c>
       <c r="F447" t="n">
-        <v>1.55407231349375</v>
+        <v>2.13830622441037</v>
       </c>
       <c r="G447" t="n">
         <v>1</v>
@@ -12145,10 +12145,10 @@
         <v>1.64502888519725</v>
       </c>
       <c r="E448" t="n">
-        <v>0.526762842399213</v>
+        <v>1</v>
       </c>
       <c r="F448" t="n">
-        <v>1.18530605027</v>
+        <v>1.01427416756368</v>
       </c>
       <c r="G448" t="n">
         <v>0.864723013269529</v>
@@ -12197,10 +12197,10 @@
         <v>2.08042364994279</v>
       </c>
       <c r="E450" t="n">
-        <v>1</v>
+        <v>0.226939011668557</v>
       </c>
       <c r="F450" t="n">
-        <v>0</v>
+        <v>1.20377948067361</v>
       </c>
       <c r="G450" t="n">
         <v>0.153396183803328</v>
@@ -12223,10 +12223,10 @@
         <v>1.56011713227504</v>
       </c>
       <c r="E451" t="n">
-        <v>0.00000219716500191775</v>
+        <v>0.0000000104637117544194</v>
       </c>
       <c r="F451" t="n">
-        <v>0.950076235340248</v>
+        <v>0.944758429811207</v>
       </c>
       <c r="G451" t="n">
         <v>0.883891898395136</v>
@@ -12249,10 +12249,10 @@
         <v>1.18124374849837</v>
       </c>
       <c r="E452" t="n">
-        <v>0.00000000000000000000307245493645308</v>
+        <v>0.0000000000000000000128106809600926</v>
       </c>
       <c r="F452" t="n">
-        <v>0.896344489892105</v>
+        <v>0.888140496737824</v>
       </c>
       <c r="G452" t="n">
         <v>0.00379334338738056</v>
@@ -12275,10 +12275,10 @@
         <v>1.49342438788558</v>
       </c>
       <c r="E453" t="n">
-        <v>0.0054803965483806</v>
+        <v>0.0663980591571332</v>
       </c>
       <c r="F453" t="n">
-        <v>1.10232501898089</v>
+        <v>1.11826934731729</v>
       </c>
       <c r="G453" t="n">
         <v>0.121299549609954</v>
@@ -12301,10 +12301,10 @@
         <v>1.20883967461191</v>
       </c>
       <c r="E454" t="n">
-        <v>0.932333544241301</v>
+        <v>0.914099257675168</v>
       </c>
       <c r="F454" t="n">
-        <v>1.02861971157727</v>
+        <v>0.967927414562458</v>
       </c>
       <c r="G454" t="n">
         <v>0.0859079647282537</v>
@@ -12327,10 +12327,10 @@
         <v>1.05437307826668</v>
       </c>
       <c r="E455" t="n">
-        <v>0.678297691570337</v>
+        <v>0.37796178471737</v>
       </c>
       <c r="F455" t="n">
-        <v>1.04297104225724</v>
+        <v>1.08116729354225</v>
       </c>
       <c r="G455" t="n">
         <v>0.244633586629992</v>
@@ -12353,10 +12353,10 @@
         <v>1.16206278102733</v>
       </c>
       <c r="E456" t="n">
-        <v>0.719014598660344</v>
+        <v>0.328211583176198</v>
       </c>
       <c r="F456" t="n">
-        <v>0.983490119140428</v>
+        <v>1.04014182758725</v>
       </c>
       <c r="G456" t="n">
         <v>0.198621651003461</v>
@@ -12379,10 +12379,10 @@
         <v>1.20536491441762</v>
       </c>
       <c r="E457" t="n">
-        <v>0.0133059951384902</v>
+        <v>0.0139529995788182</v>
       </c>
       <c r="F457" t="n">
-        <v>0.963061342564304</v>
+        <v>0.963941334000286</v>
       </c>
       <c r="G457" t="n">
         <v>0.168782107455952</v>
@@ -12405,10 +12405,10 @@
         <v>0.423994534428666</v>
       </c>
       <c r="E458" t="n">
-        <v>1</v>
+        <v>0.299369408264863</v>
       </c>
       <c r="F458" t="n">
-        <v>0</v>
+        <v>0.677714117946814</v>
       </c>
       <c r="G458" t="n">
         <v>0.344827315154874</v>
@@ -12431,10 +12431,10 @@
         <v>1.00051916849083</v>
       </c>
       <c r="E459" t="n">
-        <v>0.270462246821308</v>
+        <v>0.290478173583472</v>
       </c>
       <c r="F459" t="n">
-        <v>0.821021640455662</v>
+        <v>0.831868055704404</v>
       </c>
       <c r="G459" t="n">
         <v>0.720255408576266</v>
@@ -12457,10 +12457,10 @@
         <v>1.36941166787107</v>
       </c>
       <c r="E460" t="n">
-        <v>0.81649886081416</v>
+        <v>0.781220595552237</v>
       </c>
       <c r="F460" t="n">
-        <v>1.00381426997008</v>
+        <v>0.995567556853061</v>
       </c>
       <c r="G460" t="n">
         <v>0.69195815980266</v>
@@ -12486,7 +12486,7 @@
         <v>1</v>
       </c>
       <c r="F461" t="n">
-        <v>0</v>
+        <v>0.787061555317256</v>
       </c>
       <c r="G461" t="n">
         <v>0.612006861063465</v>
@@ -12561,10 +12561,10 @@
         <v>3.53382040029055</v>
       </c>
       <c r="E464" t="n">
-        <v>1</v>
+        <v>0.462945141277936</v>
       </c>
       <c r="F464" t="n">
-        <v>0</v>
+        <v>1.773044807363</v>
       </c>
       <c r="G464" t="n">
         <v>0.489429175475687</v>
@@ -12613,10 +12613,10 @@
         <v>0</v>
       </c>
       <c r="E466" t="n">
-        <v>0.620184951050308</v>
+        <v>1</v>
       </c>
       <c r="F466" t="n">
-        <v>1.40015202151656</v>
+        <v>0</v>
       </c>
       <c r="G466" t="n">
         <v>1</v>
@@ -12665,10 +12665,10 @@
         <v>1.06364632209303</v>
       </c>
       <c r="E468" t="n">
-        <v>0.0835048959101331</v>
+        <v>0.115336276733466</v>
       </c>
       <c r="F468" t="n">
-        <v>0.93219234221851</v>
+        <v>0.943058347165505</v>
       </c>
       <c r="G468" t="n">
         <v>1</v>
@@ -12717,10 +12717,10 @@
         <v>1.28978698228238</v>
       </c>
       <c r="E470" t="n">
-        <v>0.150233895028613</v>
+        <v>0.28370787295988</v>
       </c>
       <c r="F470" t="n">
-        <v>1.13568653744173</v>
+        <v>1.0942756238444</v>
       </c>
       <c r="G470" t="n">
         <v>0.063390485404428</v>
@@ -12743,10 +12743,10 @@
         <v>1.0182801205347</v>
       </c>
       <c r="E471" t="n">
-        <v>0.728303492702014</v>
+        <v>0.439578541369711</v>
       </c>
       <c r="F471" t="n">
-        <v>0.988532387475283</v>
+        <v>0.960878672552371</v>
       </c>
       <c r="G471" t="n">
         <v>0.776819712427546</v>
@@ -12795,10 +12795,10 @@
         <v>1.00447225448077</v>
       </c>
       <c r="E473" t="n">
-        <v>1</v>
+        <v>0.554244221332322</v>
       </c>
       <c r="F473" t="n">
-        <v>0</v>
+        <v>1.02934220266762</v>
       </c>
       <c r="G473" t="n">
         <v>0.315302137247773</v>
@@ -12873,10 +12873,10 @@
         <v>1.3068828687957</v>
       </c>
       <c r="E476" t="n">
-        <v>0.301461475420851</v>
+        <v>0.252793539035254</v>
       </c>
       <c r="F476" t="n">
-        <v>0.816109551571951</v>
+        <v>0.798398338523091</v>
       </c>
       <c r="G476" t="n">
         <v>0.543159686662187</v>
@@ -12899,7 +12899,7 @@
         <v>0.57561245093786</v>
       </c>
       <c r="E477" t="n">
-        <v>0.450704225352113</v>
+        <v>0.452380952380952</v>
       </c>
       <c r="F477" t="n">
         <v>0</v>
@@ -12954,7 +12954,7 @@
         <v>1</v>
       </c>
       <c r="F479" t="n">
-        <v>0</v>
+        <v>0.940119180705926</v>
       </c>
       <c r="G479" t="n">
         <v>0.33976833976834</v>
@@ -13029,10 +13029,10 @@
         <v>0.792729074368496</v>
       </c>
       <c r="E482" t="n">
-        <v>1</v>
+        <v>0.566860078901668</v>
       </c>
       <c r="F482" t="n">
-        <v>0</v>
+        <v>0.634821123769532</v>
       </c>
       <c r="G482" t="n">
         <v>1</v>
@@ -13055,10 +13055,10 @@
         <v>1.54793282034689</v>
       </c>
       <c r="E483" t="n">
-        <v>0.66783838433984</v>
+        <v>0.297317678839188</v>
       </c>
       <c r="F483" t="n">
-        <v>0.989478196761637</v>
+        <v>0.98066384238196</v>
       </c>
       <c r="G483" t="n">
         <v>0.585367751819768</v>
@@ -13081,10 +13081,10 @@
         <v>1.33554742527343</v>
       </c>
       <c r="E484" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000197142468527752</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000010883230879056</v>
       </c>
       <c r="F484" t="n">
-        <v>0.889242411086798</v>
+        <v>0.877069370943763</v>
       </c>
       <c r="G484" t="n">
         <v>0.361869134759748</v>
@@ -13107,10 +13107,10 @@
         <v>1.00187683391127</v>
       </c>
       <c r="E485" t="n">
-        <v>0.0467226345079185</v>
+        <v>0.00127465613736825</v>
       </c>
       <c r="F485" t="n">
-        <v>1.00871133648633</v>
+        <v>1.01599619620175</v>
       </c>
       <c r="G485" t="n">
         <v>0.000000151479732220425</v>
@@ -13133,10 +13133,10 @@
         <v>1.10057789846467</v>
       </c>
       <c r="E486" t="n">
-        <v>0.237921705127382</v>
+        <v>0.9443792541419</v>
       </c>
       <c r="F486" t="n">
-        <v>0.739978126126359</v>
+        <v>0.98766444109297</v>
       </c>
       <c r="G486" t="n">
         <v>0.000836834117593883</v>
@@ -13159,10 +13159,10 @@
         <v>0.934174428224487</v>
       </c>
       <c r="E487" t="n">
-        <v>0.0947450533270168</v>
+        <v>0.510270497513059</v>
       </c>
       <c r="F487" t="n">
-        <v>1.31151382941055</v>
+        <v>1.06699079411263</v>
       </c>
       <c r="G487" t="n">
         <v>0.435431291740398</v>
@@ -13185,10 +13185,10 @@
         <v>1.04675670916245</v>
       </c>
       <c r="E488" t="n">
-        <v>0.631267390607195</v>
+        <v>0.214557128752801</v>
       </c>
       <c r="F488" t="n">
-        <v>1.01798157240195</v>
+        <v>1.03758636732524</v>
       </c>
       <c r="G488" t="n">
         <v>0.526462449448912</v>
@@ -13211,10 +13211,10 @@
         <v>1.14178509292645</v>
       </c>
       <c r="E489" t="n">
-        <v>0.653137295701989</v>
+        <v>0.533301034188092</v>
       </c>
       <c r="F489" t="n">
-        <v>0.989184589077109</v>
+        <v>0.985445992951605</v>
       </c>
       <c r="G489" t="n">
         <v>0.80662395306208</v>
@@ -13237,10 +13237,10 @@
         <v>0.998403886050254</v>
       </c>
       <c r="E490" t="n">
-        <v>1</v>
+        <v>0.122835403886337</v>
       </c>
       <c r="F490" t="n">
-        <v>0</v>
+        <v>0.986538338047268</v>
       </c>
       <c r="G490" t="n">
         <v>0.00285248103724472</v>
@@ -13263,10 +13263,10 @@
         <v>0.858943944103521</v>
       </c>
       <c r="E491" t="n">
-        <v>0.127837209910985</v>
+        <v>1</v>
       </c>
       <c r="F491" t="n">
-        <v>0.184938426905426</v>
+        <v>0.921051615219348</v>
       </c>
       <c r="G491" t="n">
         <v>0.727183790045878</v>
@@ -13289,10 +13289,10 @@
         <v>1.27002244620992</v>
       </c>
       <c r="E492" t="n">
-        <v>0.2518031455833</v>
+        <v>0.600710396174566</v>
       </c>
       <c r="F492" t="n">
-        <v>1.03501104548894</v>
+        <v>1.01485056651325</v>
       </c>
       <c r="G492" t="n">
         <v>0.981875488732466</v>
@@ -13315,10 +13315,10 @@
         <v>1.03857844588412</v>
       </c>
       <c r="E493" t="n">
-        <v>0.0703384086875147</v>
+        <v>0.218692968563835</v>
       </c>
       <c r="F493" t="n">
-        <v>6.55953514511514</v>
+        <v>0.914941058022784</v>
       </c>
       <c r="G493" t="n">
         <v>0.7341247317433</v>
@@ -13341,10 +13341,10 @@
         <v>0.96807485678605</v>
       </c>
       <c r="E494" t="n">
-        <v>0.578396922756476</v>
+        <v>0.63027167430897</v>
       </c>
       <c r="F494" t="n">
-        <v>0.983625363497901</v>
+        <v>0.985846339107328</v>
       </c>
       <c r="G494" t="n">
         <v>0.826848183527242</v>
@@ -13367,10 +13367,10 @@
         <v>1.20915934993572</v>
       </c>
       <c r="E495" t="n">
-        <v>0.819645481585379</v>
+        <v>0.27686460564849</v>
       </c>
       <c r="F495" t="n">
-        <v>1.13426168707287</v>
+        <v>1.09416870113688</v>
       </c>
       <c r="G495" t="n">
         <v>0.193305128705847</v>
@@ -13393,10 +13393,10 @@
         <v>1.22618231314146</v>
       </c>
       <c r="E496" t="n">
-        <v>1</v>
+        <v>0.357473420194112</v>
       </c>
       <c r="F496" t="n">
-        <v>0</v>
+        <v>0.674561260430231</v>
       </c>
       <c r="G496" t="n">
         <v>0.139321365317244</v>
@@ -13419,10 +13419,10 @@
         <v>1.256541729932</v>
       </c>
       <c r="E497" t="n">
-        <v>0.744496084786157</v>
+        <v>1</v>
       </c>
       <c r="F497" t="n">
-        <v>0.922804668614196</v>
+        <v>0.996445584352551</v>
       </c>
       <c r="G497" t="n">
         <v>0.000000336297564963159</v>
@@ -13445,10 +13445,10 @@
         <v>0.997700711717493</v>
       </c>
       <c r="E498" t="n">
-        <v>1</v>
+        <v>0.537065022923831</v>
       </c>
       <c r="F498" t="n">
-        <v>0</v>
+        <v>0.70742748732696</v>
       </c>
       <c r="G498" t="n">
         <v>0.526419072992032</v>
@@ -13471,10 +13471,10 @@
         <v>0.977684122468388</v>
       </c>
       <c r="E499" t="n">
-        <v>0.425847578071802</v>
+        <v>0.5948514364138</v>
       </c>
       <c r="F499" t="n">
-        <v>1.70880273063672</v>
+        <v>1.53919675401713</v>
       </c>
       <c r="G499" t="n">
         <v>0.699926639666426</v>
@@ -13497,10 +13497,10 @@
         <v>1.03861622657765</v>
       </c>
       <c r="E500" t="n">
-        <v>0.16670959263239</v>
+        <v>0.222553849579068</v>
       </c>
       <c r="F500" t="n">
-        <v>0.911549008244915</v>
+        <v>0.946138397825829</v>
       </c>
       <c r="G500" t="n">
         <v>0.530573528738811</v>
@@ -13523,10 +13523,10 @@
         <v>0.918943871117671</v>
       </c>
       <c r="E501" t="n">
-        <v>0.129433138929828</v>
+        <v>0.865977031730803</v>
       </c>
       <c r="F501" t="n">
-        <v>2.01926031261598</v>
+        <v>1.03999073289294</v>
       </c>
       <c r="G501" t="n">
         <v>0.899759693463871</v>
@@ -13549,10 +13549,10 @@
         <v>1.02168728378323</v>
       </c>
       <c r="E502" t="n">
-        <v>0.00175172462530347</v>
+        <v>0.110135747799385</v>
       </c>
       <c r="F502" t="n">
-        <v>1.67474912409858</v>
+        <v>1.22205200244158</v>
       </c>
       <c r="G502" t="n">
         <v>0.513017666563477</v>
@@ -13575,10 +13575,10 @@
         <v>0.922088787187905</v>
       </c>
       <c r="E503" t="n">
-        <v>0.0968175971681735</v>
+        <v>0.0846345384888044</v>
       </c>
       <c r="F503" t="n">
-        <v>1.06576185721435</v>
+        <v>1.0804541131557</v>
       </c>
       <c r="G503" t="n">
         <v>0.0577615846671801</v>
@@ -13601,10 +13601,10 @@
         <v>1.2498423825537</v>
       </c>
       <c r="E504" t="n">
-        <v>1</v>
+        <v>0.201951189107045</v>
       </c>
       <c r="F504" t="n">
-        <v>0</v>
+        <v>1.70628280962805</v>
       </c>
       <c r="G504" t="n">
         <v>0.0956559150114426</v>
@@ -13627,10 +13627,10 @@
         <v>1.1167629409902</v>
       </c>
       <c r="E505" t="n">
-        <v>1</v>
+        <v>0.298131497463106</v>
       </c>
       <c r="F505" t="n">
-        <v>0</v>
+        <v>0.958767085512351</v>
       </c>
       <c r="G505" t="n">
         <v>0.0158481735565824</v>
@@ -13653,10 +13653,10 @@
         <v>1.04260702265434</v>
       </c>
       <c r="E506" t="n">
-        <v>1</v>
+        <v>0.544044924367516</v>
       </c>
       <c r="F506" t="n">
-        <v>0</v>
+        <v>1.25706546508026</v>
       </c>
       <c r="G506" t="n">
         <v>0.635260725016801</v>
@@ -13679,10 +13679,10 @@
         <v>0.970497147662294</v>
       </c>
       <c r="E507" t="n">
-        <v>0.0818045112781955</v>
+        <v>0.733835100182475</v>
       </c>
       <c r="F507" t="n">
-        <v>0</v>
+        <v>1.45435311333775</v>
       </c>
       <c r="G507" t="n">
         <v>0.612392331203112</v>
@@ -13708,7 +13708,7 @@
         <v>1</v>
       </c>
       <c r="F508" t="n">
-        <v>0</v>
+        <v>0.98544179101363</v>
       </c>
       <c r="G508" t="n">
         <v>0.190425641138435</v>
@@ -13757,10 +13757,10 @@
         <v>1.53877198673944</v>
       </c>
       <c r="E510" t="n">
-        <v>1</v>
+        <v>0.637388117687366</v>
       </c>
       <c r="F510" t="n">
-        <v>0</v>
+        <v>0.929956134582922</v>
       </c>
       <c r="G510" t="n">
         <v>0.422438893562651</v>
@@ -13783,10 +13783,10 @@
         <v>1.17072886636904</v>
       </c>
       <c r="E511" t="n">
-        <v>1</v>
+        <v>0.233201786288498</v>
       </c>
       <c r="F511" t="n">
-        <v>0</v>
+        <v>0.68933627861326</v>
       </c>
       <c r="G511" t="n">
         <v>0.367533267169522</v>
@@ -13835,10 +13835,10 @@
         <v>0.754033754951005</v>
       </c>
       <c r="E513" t="n">
-        <v>0.00311071934469938</v>
+        <v>0.410259212403772</v>
       </c>
       <c r="F513" t="n">
-        <v>0.844633936427574</v>
+        <v>0.89543436326354</v>
       </c>
       <c r="G513" t="n">
         <v>0.25053913381007</v>
@@ -13864,7 +13864,7 @@
         <v>1</v>
       </c>
       <c r="F514" t="n">
-        <v>0</v>
+        <v>0.952068495042753</v>
       </c>
       <c r="G514" t="n">
         <v>1</v>
@@ -13887,10 +13887,10 @@
         <v>1.64011906601211</v>
       </c>
       <c r="E515" t="n">
-        <v>0.00113250961264735</v>
+        <v>0.00015709930174071</v>
       </c>
       <c r="F515" t="n">
-        <v>0.970093316079171</v>
+        <v>0.959913451893564</v>
       </c>
       <c r="G515" t="n">
         <v>0.0730618571465863</v>
@@ -13913,10 +13913,10 @@
         <v>1.27299071413904</v>
       </c>
       <c r="E516" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000145424051379481</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000261403104283094</v>
       </c>
       <c r="F516" t="n">
-        <v>0.901063450392538</v>
+        <v>0.888029654972034</v>
       </c>
       <c r="G516" t="n">
         <v>0.00367183220984154</v>
@@ -13939,10 +13939,10 @@
         <v>0.970181181271851</v>
       </c>
       <c r="E517" t="n">
-        <v>0.00000000000000174983296543546</v>
+        <v>0.000000911757940771174</v>
       </c>
       <c r="F517" t="n">
-        <v>0.985410650966616</v>
+        <v>0.988228616638467</v>
       </c>
       <c r="G517" t="n">
         <v>0.0000000000000000000000000000000000211006125901996</v>
@@ -13965,10 +13965,10 @@
         <v>1.59942473261429</v>
       </c>
       <c r="E518" t="n">
-        <v>1</v>
+        <v>0.956767038783269</v>
       </c>
       <c r="F518" t="n">
-        <v>1.00117900966062</v>
+        <v>0.996892089103133</v>
       </c>
       <c r="G518" t="n">
         <v>0.287650363893244</v>
@@ -13991,10 +13991,10 @@
         <v>0.899281256002042</v>
       </c>
       <c r="E519" t="n">
-        <v>0.0617785746617943</v>
+        <v>0.0616138823461198</v>
       </c>
       <c r="F519" t="n">
-        <v>0.849176042192911</v>
+        <v>0.870437989058427</v>
       </c>
       <c r="G519" t="n">
         <v>0.95795082287916</v>
@@ -14017,10 +14017,10 @@
         <v>1.03648512996405</v>
       </c>
       <c r="E520" t="n">
-        <v>0.940736738314138</v>
+        <v>0.884916072810158</v>
       </c>
       <c r="F520" t="n">
-        <v>1.00088702022338</v>
+        <v>1.00174106705426</v>
       </c>
       <c r="G520" t="n">
         <v>0.0881069175794858</v>
@@ -14043,10 +14043,10 @@
         <v>1.13017162024541</v>
       </c>
       <c r="E521" t="n">
-        <v>0.423222005750651</v>
+        <v>0.437573995500564</v>
       </c>
       <c r="F521" t="n">
-        <v>1.01289331924696</v>
+        <v>1.0123984178662</v>
       </c>
       <c r="G521" t="n">
         <v>0.0000722878125294148</v>
@@ -14069,10 +14069,10 @@
         <v>0.986408421751069</v>
       </c>
       <c r="E522" t="n">
-        <v>0.979133114168559</v>
+        <v>0.000000383592198480913</v>
       </c>
       <c r="F522" t="n">
-        <v>1.0005690366989</v>
+        <v>0.985259263669642</v>
       </c>
       <c r="G522" t="n">
         <v>0.0045601195783258</v>
@@ -14095,10 +14095,10 @@
         <v>0.914056784221351</v>
       </c>
       <c r="E523" t="n">
-        <v>0.477936195029252</v>
+        <v>0.90428772012343</v>
       </c>
       <c r="F523" t="n">
-        <v>0.831470877519878</v>
+        <v>0.954066979657426</v>
       </c>
       <c r="G523" t="n">
         <v>0.125068990427681</v>
@@ -14121,10 +14121,10 @@
         <v>1.30213335173968</v>
       </c>
       <c r="E524" t="n">
-        <v>0.352186314233337</v>
+        <v>0.901839275453688</v>
       </c>
       <c r="F524" t="n">
-        <v>0.981520442110668</v>
+        <v>1.00243481327544</v>
       </c>
       <c r="G524" t="n">
         <v>0.0871537017236969</v>
@@ -14147,10 +14147,10 @@
         <v>0.937055177659672</v>
       </c>
       <c r="E525" t="n">
-        <v>0.201478249721491</v>
+        <v>0.24056746348646</v>
       </c>
       <c r="F525" t="n">
-        <v>1.54712016027721</v>
+        <v>0.848463577128293</v>
       </c>
       <c r="G525" t="n">
         <v>0.54923086620454</v>
@@ -14173,10 +14173,10 @@
         <v>1.47589354854033</v>
       </c>
       <c r="E526" t="n">
-        <v>1</v>
+        <v>0.854937511774755</v>
       </c>
       <c r="F526" t="n">
-        <v>0</v>
+        <v>0.965088668285835</v>
       </c>
       <c r="G526" t="n">
         <v>1</v>
@@ -14199,10 +14199,10 @@
         <v>1.18467770716348</v>
       </c>
       <c r="E527" t="n">
-        <v>0.0522795308829216</v>
+        <v>0.0429080186632096</v>
       </c>
       <c r="F527" t="n">
-        <v>1.1841020517106</v>
+        <v>1.18703126799096</v>
       </c>
       <c r="G527" t="n">
         <v>0.546982671519951</v>
@@ -14303,10 +14303,10 @@
         <v>0.811554246028716</v>
       </c>
       <c r="E531" t="n">
-        <v>0.588470134920712</v>
+        <v>0.512348601048173</v>
       </c>
       <c r="F531" t="n">
-        <v>0.646993804795304</v>
+        <v>0.764013875190806</v>
       </c>
       <c r="G531" t="n">
         <v>0.50080903538201</v>
@@ -14329,10 +14329,10 @@
         <v>1.06744812291123</v>
       </c>
       <c r="E532" t="n">
-        <v>0.000562162190433421</v>
+        <v>0.00288130270332964</v>
       </c>
       <c r="F532" t="n">
-        <v>0.904673131731054</v>
+        <v>0.92993437151728</v>
       </c>
       <c r="G532" t="n">
         <v>0.0765704211614811</v>
@@ -14355,10 +14355,10 @@
         <v>1.12726668297157</v>
       </c>
       <c r="E533" t="n">
-        <v>0.279332018716921</v>
+        <v>0.869001039527669</v>
       </c>
       <c r="F533" t="n">
-        <v>0.870460147204182</v>
+        <v>0.980748456073751</v>
       </c>
       <c r="G533" t="n">
         <v>0.659197851593569</v>
@@ -14381,10 +14381,10 @@
         <v>0.990836380492635</v>
       </c>
       <c r="E534" t="n">
-        <v>0.632848084157489</v>
+        <v>1</v>
       </c>
       <c r="F534" t="n">
-        <v>0.917726917778493</v>
+        <v>1.00439392217211</v>
       </c>
       <c r="G534" t="n">
         <v>0.444326754215236</v>
@@ -14407,10 +14407,10 @@
         <v>0.97407272216497</v>
       </c>
       <c r="E535" t="n">
-        <v>0.848039022722267</v>
+        <v>0.967716869930803</v>
       </c>
       <c r="F535" t="n">
-        <v>1.00359269215199</v>
+        <v>0.999223195666734</v>
       </c>
       <c r="G535" t="n">
         <v>0.00105540791735466</v>
@@ -14433,10 +14433,10 @@
         <v>1.29961910917271</v>
       </c>
       <c r="E536" t="n">
-        <v>1</v>
+        <v>0.283679900402981</v>
       </c>
       <c r="F536" t="n">
-        <v>1.01708234052698</v>
+        <v>0.52119035074915</v>
       </c>
       <c r="G536" t="n">
         <v>0.59661732036515</v>
@@ -14459,10 +14459,10 @@
         <v>1.01674285092738</v>
       </c>
       <c r="E537" t="n">
-        <v>0.0507840758364256</v>
+        <v>0.00000411156305649394</v>
       </c>
       <c r="F537" t="n">
-        <v>1.12304676620181</v>
+        <v>0.94984482801227</v>
       </c>
       <c r="G537" t="n">
         <v>0.296614944442673</v>
@@ -14485,10 +14485,10 @@
         <v>0.731595295349173</v>
       </c>
       <c r="E538" t="n">
-        <v>0.295793671620832</v>
+        <v>0.158913202650195</v>
       </c>
       <c r="F538" t="n">
-        <v>0.943446876703656</v>
+        <v>0.925984096420246</v>
       </c>
       <c r="G538" t="n">
         <v>0.678912604785618</v>
@@ -14511,10 +14511,10 @@
         <v>0.908573360811514</v>
       </c>
       <c r="E539" t="n">
-        <v>0.791238534894555</v>
+        <v>0.568806018905984</v>
       </c>
       <c r="F539" t="n">
-        <v>1.02699893912439</v>
+        <v>1.05152997018938</v>
       </c>
       <c r="G539" t="n">
         <v>0.239114357436037</v>
@@ -14566,7 +14566,7 @@
         <v>1</v>
       </c>
       <c r="F541" t="n">
-        <v>1.16269445227067</v>
+        <v>0</v>
       </c>
       <c r="G541" t="n">
         <v>1</v>
@@ -14615,10 +14615,10 @@
         <v>1.2971786328596</v>
       </c>
       <c r="E543" t="n">
-        <v>1</v>
+        <v>0.593750831250282</v>
       </c>
       <c r="F543" t="n">
-        <v>0</v>
+        <v>1.13529922158581</v>
       </c>
       <c r="G543" t="n">
         <v>0.516306473433543</v>
@@ -14641,10 +14641,10 @@
         <v>0.794338324160656</v>
       </c>
       <c r="E544" t="n">
-        <v>0.472629438728859</v>
+        <v>0.43014802142058</v>
       </c>
       <c r="F544" t="n">
-        <v>1.11918519081713</v>
+        <v>1.12605353381823</v>
       </c>
       <c r="G544" t="n">
         <v>0.759698128737149</v>
@@ -14667,10 +14667,10 @@
         <v>2.8224120616495</v>
       </c>
       <c r="E545" t="n">
-        <v>0.530813321983847</v>
+        <v>0.692607423187037</v>
       </c>
       <c r="F545" t="n">
-        <v>1.6088485330933</v>
+        <v>1.93594349453513</v>
       </c>
       <c r="G545" t="n">
         <v>0.491978609625669</v>
@@ -14693,10 +14693,10 @@
         <v>1.11218929834349</v>
       </c>
       <c r="E546" t="n">
-        <v>0.0118044077624771</v>
+        <v>0.0932037720050378</v>
       </c>
       <c r="F546" t="n">
-        <v>1.4878247010543</v>
+        <v>1.21854954890978</v>
       </c>
       <c r="G546" t="n">
         <v>0.00167757709396522</v>
@@ -14719,10 +14719,10 @@
         <v>1.61310599390221</v>
       </c>
       <c r="E547" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000724405737466698</v>
+        <v>0.00231491636499218</v>
       </c>
       <c r="F547" t="n">
-        <v>0.916283184591501</v>
+        <v>0.96935081081073</v>
       </c>
       <c r="G547" t="n">
         <v>0.00486061146733067</v>
@@ -14745,10 +14745,10 @@
         <v>1.19194975644635</v>
       </c>
       <c r="E548" t="n">
-        <v>0.0000000000137270660704125</v>
+        <v>0.00000000729215141879772</v>
       </c>
       <c r="F548" t="n">
-        <v>0.916636401113646</v>
+        <v>0.922795842952849</v>
       </c>
       <c r="G548" t="n">
         <v>0.0155911476951612</v>
@@ -14771,10 +14771,10 @@
         <v>1.05459398140833</v>
       </c>
       <c r="E549" t="n">
-        <v>0.0740630020272998</v>
+        <v>0.556050270264706</v>
       </c>
       <c r="F549" t="n">
-        <v>0.984792717558826</v>
+        <v>0.992927008656908</v>
       </c>
       <c r="G549" t="n">
         <v>0.547486536991956</v>
@@ -14797,10 +14797,10 @@
         <v>1.72510633879906</v>
       </c>
       <c r="E550" t="n">
-        <v>0.297794982478684</v>
+        <v>0.848507146028361</v>
       </c>
       <c r="F550" t="n">
-        <v>1.13404482609918</v>
+        <v>0.97845456292457</v>
       </c>
       <c r="G550" t="n">
         <v>0.0352518622665374</v>
@@ -14823,10 +14823,10 @@
         <v>0.745754866897717</v>
       </c>
       <c r="E551" t="n">
-        <v>0.185539092156289</v>
+        <v>0.38825650905466</v>
       </c>
       <c r="F551" t="n">
-        <v>0.94419842965871</v>
+        <v>0.965560603094429</v>
       </c>
       <c r="G551" t="n">
         <v>0.0587299717919658</v>
@@ -14849,10 +14849,10 @@
         <v>1.03535415882477</v>
       </c>
       <c r="E552" t="n">
-        <v>0.457903442247923</v>
+        <v>0.223665370391067</v>
       </c>
       <c r="F552" t="n">
-        <v>0.973395483743337</v>
+        <v>0.950470121565474</v>
       </c>
       <c r="G552" t="n">
         <v>0.110568326271956</v>
@@ -14901,10 +14901,10 @@
         <v>0.931310446206927</v>
       </c>
       <c r="E554" t="n">
-        <v>0.245608788573093</v>
+        <v>0.200512268851865</v>
       </c>
       <c r="F554" t="n">
-        <v>1.06641120250724</v>
+        <v>0.97802388580512</v>
       </c>
       <c r="G554" t="n">
         <v>0.27204411516312</v>
@@ -14927,10 +14927,10 @@
         <v>0.980328845125112</v>
       </c>
       <c r="E555" t="n">
-        <v>0.689722396346315</v>
+        <v>0.748215089179362</v>
       </c>
       <c r="F555" t="n">
-        <v>0.910225401440779</v>
+        <v>1.08538609773559</v>
       </c>
       <c r="G555" t="n">
         <v>0.497731369535444</v>
@@ -14953,10 +14953,10 @@
         <v>1.34692994337113</v>
       </c>
       <c r="E556" t="n">
-        <v>0.206219786356027</v>
+        <v>0.311366350529229</v>
       </c>
       <c r="F556" t="n">
-        <v>1.04064708800552</v>
+        <v>1.03241341328358</v>
       </c>
       <c r="G556" t="n">
         <v>0.664108750153318</v>
@@ -14979,10 +14979,10 @@
         <v>0.912195837878965</v>
       </c>
       <c r="E557" t="n">
-        <v>0.109485700804602</v>
+        <v>0.529600348975233</v>
       </c>
       <c r="F557" t="n">
-        <v>1.70176177017613</v>
+        <v>1.15462005534815</v>
       </c>
       <c r="G557" t="n">
         <v>0.566472487444774</v>
@@ -15005,10 +15005,10 @@
         <v>1.68866385828731</v>
       </c>
       <c r="E558" t="n">
-        <v>1</v>
+        <v>0.134256210004206</v>
       </c>
       <c r="F558" t="n">
-        <v>0</v>
+        <v>1.52895199755844</v>
       </c>
       <c r="G558" t="n">
         <v>0.357307037091309</v>
@@ -15057,10 +15057,10 @@
         <v>1.32107660648817</v>
       </c>
       <c r="E560" t="n">
-        <v>0.0000378010488935427</v>
+        <v>0.000175594043614815</v>
       </c>
       <c r="F560" t="n">
-        <v>0.976613079650848</v>
+        <v>0.978904455778557</v>
       </c>
       <c r="G560" t="n">
         <v>0.0000000000000000000000000000000454599056996078</v>
@@ -15161,10 +15161,10 @@
         <v>1.11891281938764</v>
       </c>
       <c r="E564" t="n">
-        <v>0.000000000000000000502633891203517</v>
+        <v>0.0000000000000000291535301305253</v>
       </c>
       <c r="F564" t="n">
-        <v>0.792614599464861</v>
+        <v>0.80521695510019</v>
       </c>
       <c r="G564" t="n">
         <v>0.000000000580159639098878</v>
@@ -15187,10 +15187,10 @@
         <v>1.34150251940085</v>
       </c>
       <c r="E565" t="n">
-        <v>0.657163950936331</v>
+        <v>0.867154866828672</v>
       </c>
       <c r="F565" t="n">
-        <v>0.896126458690358</v>
+        <v>0.980153021770925</v>
       </c>
       <c r="G565" t="n">
         <v>0.782991000853499</v>
@@ -15213,10 +15213,10 @@
         <v>1.19737832959249</v>
       </c>
       <c r="E566" t="n">
-        <v>0.245272911674504</v>
+        <v>0.457982936876393</v>
       </c>
       <c r="F566" t="n">
-        <v>0.930319023438389</v>
+        <v>0.958631041062072</v>
       </c>
       <c r="G566" t="n">
         <v>0.00600625378760315</v>
@@ -15239,10 +15239,10 @@
         <v>0.976075118690312</v>
       </c>
       <c r="E567" t="n">
-        <v>0.0792218536211644</v>
+        <v>0.00321891145827149</v>
       </c>
       <c r="F567" t="n">
-        <v>0.939658375216784</v>
+        <v>0.904604201198503</v>
       </c>
       <c r="G567" t="n">
         <v>0.587724989799216</v>
@@ -15265,10 +15265,10 @@
         <v>1.06369478742427</v>
       </c>
       <c r="E568" t="n">
-        <v>0.260612066542524</v>
+        <v>0.260352647415607</v>
       </c>
       <c r="F568" t="n">
-        <v>0.874035157423814</v>
+        <v>0.87468383421214</v>
       </c>
       <c r="G568" t="n">
         <v>0.0980188650501897</v>
@@ -15291,10 +15291,10 @@
         <v>1.03779025092406</v>
       </c>
       <c r="E569" t="n">
-        <v>0.236625984476885</v>
+        <v>0.00928281913024159</v>
       </c>
       <c r="F569" t="n">
-        <v>1.09246644842183</v>
+        <v>1.13662726438871</v>
       </c>
       <c r="G569" t="n">
         <v>0.520535884818464</v>
@@ -15317,10 +15317,10 @@
         <v>0.874712440229736</v>
       </c>
       <c r="E570" t="n">
-        <v>0.976302869522768</v>
+        <v>0.953818314786533</v>
       </c>
       <c r="F570" t="n">
-        <v>0.997020992540001</v>
+        <v>0.996429462282822</v>
       </c>
       <c r="G570" t="n">
         <v>0.836662988922672</v>
@@ -15343,10 +15343,10 @@
         <v>0.630532414342399</v>
       </c>
       <c r="E571" t="n">
-        <v>0.00000290356953755593</v>
+        <v>0.00000331213681110608</v>
       </c>
       <c r="F571" t="n">
-        <v>1.16821891787551</v>
+        <v>1.17988900214036</v>
       </c>
       <c r="G571" t="n">
         <v>0.00000000000000000000000000000000250074585367791</v>
@@ -15369,10 +15369,10 @@
         <v>1.25083883141939</v>
       </c>
       <c r="E572" t="n">
-        <v>1</v>
+        <v>0.929930071599384</v>
       </c>
       <c r="F572" t="n">
-        <v>1.00109496841771</v>
+        <v>0.988877345243555</v>
       </c>
       <c r="G572" t="n">
         <v>0.000340584211472317</v>
@@ -15395,10 +15395,10 @@
         <v>0.930218966819824</v>
       </c>
       <c r="E573" t="n">
-        <v>0.46559118847277</v>
+        <v>0.350081381022109</v>
       </c>
       <c r="F573" t="n">
-        <v>0.829762601130022</v>
+        <v>0.750421567858586</v>
       </c>
       <c r="G573" t="n">
         <v>0.666735393196744</v>
@@ -15421,10 +15421,10 @@
         <v>1.5981529380694</v>
       </c>
       <c r="E574" t="n">
-        <v>0.235449830491758</v>
+        <v>0.926224140983808</v>
       </c>
       <c r="F574" t="n">
-        <v>1.09978140309417</v>
+        <v>0.99110843808993</v>
       </c>
       <c r="G574" t="n">
         <v>0.689649849335735</v>
@@ -15447,10 +15447,10 @@
         <v>2.10187935959429</v>
       </c>
       <c r="E575" t="n">
-        <v>0.00465156259957712</v>
+        <v>1</v>
       </c>
       <c r="F575" t="n">
-        <v>1.35627026863178</v>
+        <v>0</v>
       </c>
       <c r="G575" t="n">
         <v>1</v>
@@ -15499,10 +15499,10 @@
         <v>0.271184369793588</v>
       </c>
       <c r="E577" t="n">
-        <v>0.654587150409877</v>
+        <v>1</v>
       </c>
       <c r="F577" t="n">
-        <v>1.1138330954873</v>
+        <v>0.994428081203014</v>
       </c>
       <c r="G577" t="n">
         <v>0.741793870771955</v>
@@ -15525,10 +15525,10 @@
         <v>0.636480986493447</v>
       </c>
       <c r="E578" t="n">
-        <v>0.506211180124224</v>
+        <v>0.621129071965864</v>
       </c>
       <c r="F578" t="n">
-        <v>0</v>
+        <v>0.347818521280876</v>
       </c>
       <c r="G578" t="n">
         <v>0.585491723466407</v>
@@ -15551,10 +15551,10 @@
         <v>1.53498270052112</v>
       </c>
       <c r="E579" t="n">
-        <v>0.000000000766058214074198</v>
+        <v>0.0208741625964289</v>
       </c>
       <c r="F579" t="n">
-        <v>0.911587715705606</v>
+        <v>0.96178976846504</v>
       </c>
       <c r="G579" t="n">
         <v>0.795066026159611</v>
@@ -15577,10 +15577,10 @@
         <v>0.80560951059227</v>
       </c>
       <c r="E580" t="n">
-        <v>0.00000000000000798659683463918</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000285014416719467</v>
       </c>
       <c r="F580" t="n">
-        <v>0.894746150381456</v>
+        <v>0.876746168563857</v>
       </c>
       <c r="G580" t="n">
         <v>0.0000000000000000000000000000000110320368775508</v>
@@ -15603,10 +15603,10 @@
         <v>0.968661064487986</v>
       </c>
       <c r="E581" t="n">
-        <v>0.0449143287503613</v>
+        <v>0.00684433402651196</v>
       </c>
       <c r="F581" t="n">
-        <v>1.00499335786354</v>
+        <v>1.00770897166355</v>
       </c>
       <c r="G581" t="n">
         <v>0.0000000000000281836035998903</v>
@@ -15629,10 +15629,10 @@
         <v>1.53246188453731</v>
       </c>
       <c r="E582" t="n">
-        <v>1</v>
+        <v>0.653534813994563</v>
       </c>
       <c r="F582" t="n">
-        <v>0</v>
+        <v>0.861078952459</v>
       </c>
       <c r="G582" t="n">
         <v>0.449132953879548</v>
@@ -15655,10 +15655,10 @@
         <v>1.07123045823987</v>
       </c>
       <c r="E583" t="n">
-        <v>0.791067208661289</v>
+        <v>1</v>
       </c>
       <c r="F583" t="n">
-        <v>1.04285402649149</v>
+        <v>1.00036577643138</v>
       </c>
       <c r="G583" t="n">
         <v>0.50791603205865</v>
@@ -15681,10 +15681,10 @@
         <v>1.12450281389036</v>
       </c>
       <c r="E584" t="n">
-        <v>0.443939805654395</v>
+        <v>0.0212529388986402</v>
       </c>
       <c r="F584" t="n">
-        <v>1.02733198817295</v>
+        <v>1.09300718200521</v>
       </c>
       <c r="G584" t="n">
         <v>0.828947399018799</v>
@@ -15707,10 +15707,10 @@
         <v>1.13744762013565</v>
       </c>
       <c r="E585" t="n">
-        <v>0.713157679992947</v>
+        <v>0.70113972812332</v>
       </c>
       <c r="F585" t="n">
-        <v>0.981548888749729</v>
+        <v>1.017341924655</v>
       </c>
       <c r="G585" t="n">
         <v>0.0508131969093587</v>
@@ -15733,10 +15733,10 @@
         <v>0.957852407662211</v>
       </c>
       <c r="E586" t="n">
-        <v>0.805088301993656</v>
+        <v>0.00364867751161782</v>
       </c>
       <c r="F586" t="n">
-        <v>0.994207247709976</v>
+        <v>0.98549503954261</v>
       </c>
       <c r="G586" t="n">
         <v>0.0125744332816132</v>
@@ -15785,10 +15785,10 @@
         <v>1.32486452280382</v>
       </c>
       <c r="E588" t="n">
-        <v>0.3726129217927</v>
+        <v>0.676498082533876</v>
       </c>
       <c r="F588" t="n">
-        <v>1.0635154537497</v>
+        <v>1.02376339090663</v>
       </c>
       <c r="G588" t="n">
         <v>0.418285874372172</v>
@@ -15811,10 +15811,10 @@
         <v>1.39347766911249</v>
       </c>
       <c r="E589" t="n">
-        <v>1</v>
+        <v>0.00140300626683317</v>
       </c>
       <c r="F589" t="n">
-        <v>0</v>
+        <v>0.650759205655105</v>
       </c>
       <c r="G589" t="n">
         <v>0.501700740869248</v>
@@ -15889,10 +15889,10 @@
         <v>1.488187454374</v>
       </c>
       <c r="E592" t="n">
-        <v>1</v>
+        <v>0.00667503982791399</v>
       </c>
       <c r="F592" t="n">
-        <v>0</v>
+        <v>0.498190157147701</v>
       </c>
       <c r="G592" t="n">
         <v>0.405219733144624</v>
@@ -15915,10 +15915,10 @@
         <v>1.2630941941124</v>
       </c>
       <c r="E593" t="n">
-        <v>0.157339381544812</v>
+        <v>0.00416884214346426</v>
       </c>
       <c r="F593" t="n">
-        <v>0.950375891944823</v>
+        <v>0.913911555567012</v>
       </c>
       <c r="G593" t="n">
         <v>0.000000000000000000000265768188828062</v>
@@ -15941,10 +15941,10 @@
         <v>0.325074310880308</v>
       </c>
       <c r="E594" t="n">
-        <v>1</v>
+        <v>0.706817175211976</v>
       </c>
       <c r="F594" t="n">
-        <v>0</v>
+        <v>0.679946458493766</v>
       </c>
       <c r="G594" t="n">
         <v>0.627177850612386</v>
@@ -15993,10 +15993,10 @@
         <v>0.973376824687895</v>
       </c>
       <c r="E596" t="n">
-        <v>0.954574240269905</v>
+        <v>0.518264920649321</v>
       </c>
       <c r="F596" t="n">
-        <v>1.01282779812677</v>
+        <v>0.94662185608309</v>
       </c>
       <c r="G596" t="n">
         <v>0.900889816091228</v>
@@ -16045,10 +16045,10 @@
         <v>0.929217523024408</v>
       </c>
       <c r="E598" t="n">
-        <v>0.0784596566133361</v>
+        <v>0.0399388808144302</v>
       </c>
       <c r="F598" t="n">
-        <v>2.08935752661584</v>
+        <v>1.97870363215501</v>
       </c>
       <c r="G598" t="n">
         <v>0.18084472119621</v>
@@ -16071,10 +16071,10 @@
         <v>1.24964495214034</v>
       </c>
       <c r="E599" t="n">
-        <v>0.165945841621359</v>
+        <v>0.132957508194478</v>
       </c>
       <c r="F599" t="n">
-        <v>1.1204327302635</v>
+        <v>1.15325574831617</v>
       </c>
       <c r="G599" t="n">
         <v>0.938906861495187</v>
@@ -16123,10 +16123,10 @@
         <v>1.03702633016224</v>
       </c>
       <c r="E601" t="n">
-        <v>0.000000000324493718510988</v>
+        <v>0.961060613157922</v>
       </c>
       <c r="F601" t="n">
-        <v>0.973109155276009</v>
+        <v>1.00279717740763</v>
       </c>
       <c r="G601" t="n">
         <v>0.831596752918026</v>
@@ -16279,10 +16279,10 @@
         <v>0.897120856454649</v>
       </c>
       <c r="E607" t="n">
-        <v>1</v>
+        <v>0.661343924069023</v>
       </c>
       <c r="F607" t="n">
-        <v>0</v>
+        <v>0.869148335264423</v>
       </c>
       <c r="G607" t="n">
         <v>0.525658022848185</v>
@@ -16305,10 +16305,10 @@
         <v>1.52318703444567</v>
       </c>
       <c r="E608" t="n">
-        <v>1</v>
+        <v>0.898441420540627</v>
       </c>
       <c r="F608" t="n">
-        <v>0</v>
+        <v>0.956749372256365</v>
       </c>
       <c r="G608" t="n">
         <v>0.134895310073015</v>
@@ -16331,10 +16331,10 @@
         <v>0.669713968169676</v>
       </c>
       <c r="E609" t="n">
-        <v>0.073123455088461</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000230488141695672</v>
       </c>
       <c r="F609" t="n">
-        <v>1.07997221571166</v>
+        <v>1.14493303358965</v>
       </c>
       <c r="G609" t="n">
         <v>0.0734142837948725</v>
@@ -16383,10 +16383,10 @@
         <v>1.47215245121394</v>
       </c>
       <c r="E611" t="n">
-        <v>0.0000000000000000000116912756163838</v>
+        <v>0.000000000000595416271329971</v>
       </c>
       <c r="F611" t="n">
-        <v>0.921725630121216</v>
+        <v>0.945516565982321</v>
       </c>
       <c r="G611" t="n">
         <v>0.033166113352931</v>
@@ -16409,10 +16409,10 @@
         <v>1.16950383317857</v>
       </c>
       <c r="E612" t="n">
-        <v>0.008440271416077</v>
+        <v>0.0127971614711915</v>
       </c>
       <c r="F612" t="n">
-        <v>0.886715743270454</v>
+        <v>0.874618319371854</v>
       </c>
       <c r="G612" t="n">
         <v>0.0373139143647234</v>
@@ -16435,10 +16435,10 @@
         <v>1.2589318167964</v>
       </c>
       <c r="E613" t="n">
-        <v>0.161735329128833</v>
+        <v>0.508921355438288</v>
       </c>
       <c r="F613" t="n">
-        <v>1.18551079921374</v>
+        <v>0.825736754517928</v>
       </c>
       <c r="G613" t="n">
         <v>1</v>
@@ -16461,10 +16461,10 @@
         <v>1.23509571172076</v>
       </c>
       <c r="E614" t="n">
-        <v>0.345130745394954</v>
+        <v>0.159924328538658</v>
       </c>
       <c r="F614" t="n">
-        <v>0.846875528298853</v>
+        <v>0.79302718277339</v>
       </c>
       <c r="G614" t="n">
         <v>0.314884690781402</v>
@@ -16487,10 +16487,10 @@
         <v>1.04707658948756</v>
       </c>
       <c r="E615" t="n">
-        <v>0.0825418025031519</v>
+        <v>0.114456500523583</v>
       </c>
       <c r="F615" t="n">
-        <v>2.2345315748006</v>
+        <v>1.49396926877605</v>
       </c>
       <c r="G615" t="n">
         <v>0.538032441807369</v>
@@ -16513,10 +16513,10 @@
         <v>0.919224975012635</v>
       </c>
       <c r="E616" t="n">
-        <v>1</v>
+        <v>0.317942385640233</v>
       </c>
       <c r="F616" t="n">
-        <v>1.01106968618516</v>
+        <v>0.739546196044304</v>
       </c>
       <c r="G616" t="n">
         <v>1</v>
@@ -16591,10 +16591,10 @@
         <v>0.945455131767039</v>
       </c>
       <c r="E619" t="n">
-        <v>0.276406159049098</v>
+        <v>0.232238835753011</v>
       </c>
       <c r="F619" t="n">
-        <v>1.68682671549104</v>
+        <v>1.63451971861475</v>
       </c>
       <c r="G619" t="n">
         <v>0.326217521671233</v>
@@ -16825,10 +16825,10 @@
         <v>1.05834726981161</v>
       </c>
       <c r="E628" t="n">
-        <v>0.460151581293896</v>
+        <v>0.961133528144944</v>
       </c>
       <c r="F628" t="n">
-        <v>0.91557255690422</v>
+        <v>0.992187784194759</v>
       </c>
       <c r="G628" t="n">
         <v>0.307622735680645</v>
@@ -16880,7 +16880,7 @@
         <v>1</v>
       </c>
       <c r="F630" t="n">
-        <v>0</v>
+        <v>0.960023105984833</v>
       </c>
       <c r="G630" t="n">
         <v>0.273819952454299</v>
@@ -16903,10 +16903,10 @@
         <v>1.00101422742822</v>
       </c>
       <c r="E631" t="n">
-        <v>0.169925431398435</v>
+        <v>0.00453022338039509</v>
       </c>
       <c r="F631" t="n">
-        <v>1.21134096488934</v>
+        <v>1.55399200089783</v>
       </c>
       <c r="G631" t="n">
         <v>0.139663764318582</v>
@@ -16955,10 +16955,10 @@
         <v>1.06188623028008</v>
       </c>
       <c r="E633" t="n">
-        <v>1</v>
+        <v>0.426726950192574</v>
       </c>
       <c r="F633" t="n">
-        <v>0</v>
+        <v>0.785539166914619</v>
       </c>
       <c r="G633" t="n">
         <v>0.438911868397312</v>
@@ -17111,10 +17111,10 @@
         <v>0.928220637672543</v>
       </c>
       <c r="E639" t="n">
-        <v>0.220025307179764</v>
+        <v>1</v>
       </c>
       <c r="F639" t="n">
-        <v>0.218304424476441</v>
+        <v>0</v>
       </c>
       <c r="G639" t="n">
         <v>1</v>
@@ -17215,10 +17215,10 @@
         <v>1.58476287579968</v>
       </c>
       <c r="E643" t="n">
-        <v>0.741341804523935</v>
+        <v>0.6266052568146</v>
       </c>
       <c r="F643" t="n">
-        <v>1.01408010656404</v>
+        <v>1.01900995241101</v>
       </c>
       <c r="G643" t="n">
         <v>0.512806393981879</v>
@@ -17241,10 +17241,10 @@
         <v>1.06086970876343</v>
       </c>
       <c r="E644" t="n">
-        <v>0.00000696459834528908</v>
+        <v>0.000000000000000000000000000000000976867992797482</v>
       </c>
       <c r="F644" t="n">
-        <v>0.9324015670059</v>
+        <v>0.894329046571604</v>
       </c>
       <c r="G644" t="n">
         <v>0.0000000125672291176348</v>
@@ -17267,10 +17267,10 @@
         <v>0.95023312250097</v>
       </c>
       <c r="E645" t="n">
-        <v>0.000000000000000000000000351316506871852</v>
+        <v>0.0000000000000651349682340067</v>
       </c>
       <c r="F645" t="n">
-        <v>0.973203535357877</v>
+        <v>0.974400298610932</v>
       </c>
       <c r="G645" t="n">
         <v>0.00000000000000000661104279511249</v>
@@ -17293,10 +17293,10 @@
         <v>1.06879676711889</v>
       </c>
       <c r="E646" t="n">
-        <v>1</v>
+        <v>0.687328265262014</v>
       </c>
       <c r="F646" t="n">
-        <v>0</v>
+        <v>1.07216669300441</v>
       </c>
       <c r="G646" t="n">
         <v>0.478953678830115</v>
@@ -17319,10 +17319,10 @@
         <v>0.953801763834972</v>
       </c>
       <c r="E647" t="n">
-        <v>0.630679431567102</v>
+        <v>0.315621353876653</v>
       </c>
       <c r="F647" t="n">
-        <v>1.04836474486351</v>
+        <v>0.916951630708245</v>
       </c>
       <c r="G647" t="n">
         <v>0.423421477747389</v>
@@ -17345,10 +17345,10 @@
         <v>1.04596378584047</v>
       </c>
       <c r="E648" t="n">
-        <v>0.394850747962837</v>
+        <v>0.26470058987298</v>
       </c>
       <c r="F648" t="n">
-        <v>1.03813877556815</v>
+        <v>1.05875811179078</v>
       </c>
       <c r="G648" t="n">
         <v>0.807915338580105</v>
@@ -17371,10 +17371,10 @@
         <v>1.15690538706027</v>
       </c>
       <c r="E649" t="n">
-        <v>0.756590412307206</v>
+        <v>0.624606190130956</v>
       </c>
       <c r="F649" t="n">
-        <v>1.01716300786155</v>
+        <v>1.02657994557795</v>
       </c>
       <c r="G649" t="n">
         <v>0.762313623348236</v>
@@ -17397,10 +17397,10 @@
         <v>0.958855128992472</v>
       </c>
       <c r="E650" t="n">
-        <v>0.725450153839105</v>
+        <v>0.0000000000000000000535950942591291</v>
       </c>
       <c r="F650" t="n">
-        <v>0.986515260799063</v>
+        <v>0.966712196594575</v>
       </c>
       <c r="G650" t="n">
         <v>0.17592642073886</v>
@@ -17423,10 +17423,10 @@
         <v>0.715995776873932</v>
       </c>
       <c r="E651" t="n">
-        <v>0.549835978326289</v>
+        <v>1</v>
       </c>
       <c r="F651" t="n">
-        <v>0.609130363292696</v>
+        <v>0.972343621328186</v>
       </c>
       <c r="G651" t="n">
         <v>1</v>
@@ -17449,10 +17449,10 @@
         <v>1.25705093242329</v>
       </c>
       <c r="E652" t="n">
-        <v>0.790464552315093</v>
+        <v>0.504267901309404</v>
       </c>
       <c r="F652" t="n">
-        <v>0.991642719077672</v>
+        <v>0.978494443478669</v>
       </c>
       <c r="G652" t="n">
         <v>0.776243606089543</v>
@@ -17475,10 +17475,10 @@
         <v>0.879163088916306</v>
       </c>
       <c r="E653" t="n">
-        <v>0.626936390200427</v>
+        <v>0.683877704914621</v>
       </c>
       <c r="F653" t="n">
-        <v>0.893018282008936</v>
+        <v>0.929021571769757</v>
       </c>
       <c r="G653" t="n">
         <v>0.00784430248870212</v>
@@ -17605,10 +17605,10 @@
         <v>0.521035917043722</v>
       </c>
       <c r="E658" t="n">
-        <v>0.636188893891782</v>
+        <v>0.881086063518976</v>
       </c>
       <c r="F658" t="n">
-        <v>0.724342621339328</v>
+        <v>0.943125436044994</v>
       </c>
       <c r="G658" t="n">
         <v>0.838754293893274</v>
@@ -17657,10 +17657,10 @@
         <v>0.975649055848883</v>
       </c>
       <c r="E660" t="n">
-        <v>0.325094520608292</v>
+        <v>0.336065816423443</v>
       </c>
       <c r="F660" t="n">
-        <v>0.930281803677307</v>
+        <v>0.948319196189364</v>
       </c>
       <c r="G660" t="n">
         <v>0.533843329902386</v>
@@ -17683,10 +17683,10 @@
         <v>1.52329785862305</v>
       </c>
       <c r="E661" t="n">
-        <v>1</v>
+        <v>0.792870853695953</v>
       </c>
       <c r="F661" t="n">
-        <v>0</v>
+        <v>1.09694861652144</v>
       </c>
       <c r="G661" t="n">
         <v>0.664738612499607</v>
@@ -17709,10 +17709,10 @@
         <v>1.05749345796874</v>
       </c>
       <c r="E662" t="n">
-        <v>0.733841634739534</v>
+        <v>0.427664062653339</v>
       </c>
       <c r="F662" t="n">
-        <v>0.973212071119626</v>
+        <v>0.938067071337443</v>
       </c>
       <c r="G662" t="n">
         <v>0.00161564131198908</v>
@@ -17735,10 +17735,10 @@
         <v>0.979062288278972</v>
       </c>
       <c r="E663" t="n">
-        <v>0.0279150586518981</v>
+        <v>0.664164223938972</v>
       </c>
       <c r="F663" t="n">
-        <v>0.926157887313889</v>
+        <v>0.985546464955933</v>
       </c>
       <c r="G663" t="n">
         <v>0.91862446124274</v>
@@ -17787,10 +17787,10 @@
         <v>0.992271526565627</v>
       </c>
       <c r="E665" t="n">
-        <v>0.000000633878531597611</v>
+        <v>0.000443695771752749</v>
       </c>
       <c r="F665" t="n">
-        <v>0.857942490541002</v>
+        <v>0.938379196870465</v>
       </c>
       <c r="G665" t="n">
         <v>0.305511554865759</v>
@@ -17813,10 +17813,10 @@
         <v>0.768552480636915</v>
       </c>
       <c r="E666" t="n">
-        <v>0.309108784536105</v>
+        <v>0.63689935350268</v>
       </c>
       <c r="F666" t="n">
-        <v>0.916084538920959</v>
+        <v>0.960777942322076</v>
       </c>
       <c r="G666" t="n">
         <v>0.740216026583131</v>
@@ -17842,7 +17842,7 @@
         <v>1</v>
       </c>
       <c r="F667" t="n">
-        <v>1.12925950270472</v>
+        <v>0</v>
       </c>
       <c r="G667" t="n">
         <v>1</v>
@@ -17865,10 +17865,10 @@
         <v>1.06281310731039</v>
       </c>
       <c r="E668" t="n">
-        <v>0.382297087134463</v>
+        <v>0.124080200374287</v>
       </c>
       <c r="F668" t="n">
-        <v>0.921397908651831</v>
+        <v>0.868601794367033</v>
       </c>
       <c r="G668" t="n">
         <v>0.037788031396591</v>
@@ -17943,10 +17943,10 @@
         <v>0.920887121914506</v>
       </c>
       <c r="E671" t="n">
-        <v>1</v>
+        <v>0.138049799100782</v>
       </c>
       <c r="F671" t="n">
-        <v>0</v>
+        <v>0.814228350562761</v>
       </c>
       <c r="G671" t="n">
         <v>1</v>
@@ -17969,10 +17969,10 @@
         <v>0.933946826602949</v>
       </c>
       <c r="E672" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000029468672599617</v>
+        <v>0.0000000000000000000000000000000000000000000000000000272107685631006</v>
       </c>
       <c r="F672" t="n">
-        <v>1.27450409666367</v>
+        <v>1.23429163131142</v>
       </c>
       <c r="G672" t="n">
         <v>0.0000000128200057444796</v>
@@ -17995,10 +17995,10 @@
         <v>0.628127132384884</v>
       </c>
       <c r="E673" t="n">
-        <v>0.874817571859601</v>
+        <v>0.566482688703622</v>
       </c>
       <c r="F673" t="n">
-        <v>0.926246412978971</v>
+        <v>0.841982217274669</v>
       </c>
       <c r="G673" t="n">
         <v>0.0448167398067829</v>
@@ -18021,10 +18021,10 @@
         <v>1.01590716437725</v>
       </c>
       <c r="E674" t="n">
-        <v>1</v>
+        <v>0.156167852973573</v>
       </c>
       <c r="F674" t="n">
-        <v>0</v>
+        <v>0.463254968472737</v>
       </c>
       <c r="G674" t="n">
         <v>0.11981366762597</v>
@@ -18047,10 +18047,10 @@
         <v>1.02944813630769</v>
       </c>
       <c r="E675" t="n">
-        <v>0.00000000000000000369786769735766</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000800798504252984</v>
       </c>
       <c r="F675" t="n">
-        <v>1.03473231726391</v>
+        <v>1.10955669129329</v>
       </c>
       <c r="G675" t="n">
         <v>0.161994866779467</v>
